--- a/docs/src/reference/data-dictionaries/T_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/T_Dict.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD173"/>
+  <dimension ref="A1:AD178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -7817,12 +7817,12 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr"/>
@@ -7881,12 +7881,12 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr"/>
@@ -7924,7 +7924,11 @@
       <c r="P96" t="inlineStr"/>
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr"/>
-      <c r="S96" t="inlineStr"/>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T96" t="inlineStr"/>
       <c r="U96" t="inlineStr"/>
       <c r="V96" t="inlineStr">
@@ -7945,12 +7949,12 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr"/>
@@ -8009,12 +8013,12 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr"/>
@@ -8073,12 +8077,12 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr"/>
@@ -8137,12 +8141,12 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr"/>
@@ -8201,12 +8205,12 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr"/>
@@ -8265,12 +8269,12 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr"/>
@@ -8329,12 +8333,12 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr"/>
@@ -8397,12 +8401,12 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr"/>
@@ -8440,7 +8444,11 @@
       <c r="P104" t="inlineStr"/>
       <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr"/>
-      <c r="S104" t="inlineStr"/>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T104" t="inlineStr">
         <is>
           <t>x</t>
@@ -8465,12 +8473,12 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr"/>
@@ -8499,16 +8507,16 @@
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr"/>
       <c r="Q105" t="inlineStr"/>
       <c r="R105" t="inlineStr"/>
-      <c r="S105" t="inlineStr"/>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T105" t="inlineStr">
         <is>
           <t>x</t>
@@ -8517,12 +8525,12 @@
       <c r="U105" t="inlineStr"/>
       <c r="V105" t="inlineStr">
         <is>
-          <t>BupTmWk</t>
+          <t>BupTmDr2</t>
         </is>
       </c>
       <c r="W105" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Buprenorphine Provider</t>
+          <t>Driving time to nearest buprenorphine provider (with impedance)</t>
         </is>
       </c>
       <c r="X105" t="inlineStr"/>
@@ -8533,12 +8541,12 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr"/>
@@ -8577,16 +8585,20 @@
       <c r="Q106" t="inlineStr"/>
       <c r="R106" t="inlineStr"/>
       <c r="S106" t="inlineStr"/>
-      <c r="T106" t="inlineStr"/>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U106" t="inlineStr"/>
       <c r="V106" t="inlineStr">
         <is>
-          <t>MetCntBk30</t>
+          <t>BupTmWk</t>
         </is>
       </c>
       <c r="W106" t="inlineStr">
         <is>
-          <t>Count of methadone providers (30-min bike)</t>
+          <t>Walking Time (min) to nearest Buprenorphine Provider</t>
         </is>
       </c>
       <c r="X106" t="inlineStr"/>
@@ -8597,12 +8609,12 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr"/>
@@ -8645,12 +8657,12 @@
       <c r="U107" t="inlineStr"/>
       <c r="V107" t="inlineStr">
         <is>
-          <t>MetCntBk60</t>
+          <t>MetCntBk30</t>
         </is>
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>Count of Methadone Providers (60-min bike)</t>
+          <t>Count of methadone providers (30-min bike)</t>
         </is>
       </c>
       <c r="X107" t="inlineStr"/>
@@ -8661,12 +8673,12 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr"/>
@@ -8709,12 +8721,12 @@
       <c r="U108" t="inlineStr"/>
       <c r="V108" t="inlineStr">
         <is>
-          <t>MetCntDr30</t>
+          <t>MetCntBk60</t>
         </is>
       </c>
       <c r="W108" t="inlineStr">
         <is>
-          <t>Count of Methadone Providers (30-min drive)</t>
+          <t>Count of Methadone Providers (60-min bike)</t>
         </is>
       </c>
       <c r="X108" t="inlineStr"/>
@@ -8725,12 +8737,12 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr"/>
@@ -8768,17 +8780,21 @@
       <c r="P109" t="inlineStr"/>
       <c r="Q109" t="inlineStr"/>
       <c r="R109" t="inlineStr"/>
-      <c r="S109" t="inlineStr"/>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T109" t="inlineStr"/>
       <c r="U109" t="inlineStr"/>
       <c r="V109" t="inlineStr">
         <is>
-          <t>MetCntWk30</t>
+          <t>MetCntDr30</t>
         </is>
       </c>
       <c r="W109" t="inlineStr">
         <is>
-          <t>Count of Methadone Providers (60-min walk)</t>
+          <t>Count of Methadone Providers (30-min drive)</t>
         </is>
       </c>
       <c r="X109" t="inlineStr"/>
@@ -8789,12 +8805,12 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr"/>
@@ -8837,12 +8853,12 @@
       <c r="U110" t="inlineStr"/>
       <c r="V110" t="inlineStr">
         <is>
-          <t>MetCntWk60</t>
+          <t>MetCntWk30</t>
         </is>
       </c>
       <c r="W110" t="inlineStr">
         <is>
-          <t>Count of Methadone Providers (30-min walk)</t>
+          <t>Count of Methadone Providers (60-min walk)</t>
         </is>
       </c>
       <c r="X110" t="inlineStr"/>
@@ -8853,12 +8869,12 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr"/>
@@ -8901,12 +8917,12 @@
       <c r="U111" t="inlineStr"/>
       <c r="V111" t="inlineStr">
         <is>
-          <t>MetMinDis</t>
+          <t>MetCntWk60</t>
         </is>
       </c>
       <c r="W111" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Methadone Provider</t>
+          <t>Count of Methadone Providers (30-min walk)</t>
         </is>
       </c>
       <c r="X111" t="inlineStr"/>
@@ -8917,12 +8933,12 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr"/>
@@ -8940,26 +8956,10 @@
           <t>Spatial Access to MOUDs</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
@@ -8981,12 +8981,12 @@
       <c r="U112" t="inlineStr"/>
       <c r="V112" t="inlineStr">
         <is>
-          <t>MetRm30</t>
+          <t>MetMinDis</t>
         </is>
       </c>
       <c r="W112" t="inlineStr">
         <is>
-          <t>Methadone access 30 minutes (RAAM)</t>
+          <t>Distance (mi) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X112" t="inlineStr"/>
@@ -8997,12 +8997,12 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr"/>
@@ -9061,12 +9061,12 @@
       <c r="U113" t="inlineStr"/>
       <c r="V113" t="inlineStr">
         <is>
-          <t>MetRm60</t>
+          <t>MetRm30</t>
         </is>
       </c>
       <c r="W113" t="inlineStr">
         <is>
-          <t>Methadone access 60 minutes (RAAM)</t>
+          <t>Methadone access 30 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X113" t="inlineStr"/>
@@ -9077,12 +9077,12 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr"/>
@@ -9141,12 +9141,12 @@
       <c r="U114" t="inlineStr"/>
       <c r="V114" t="inlineStr">
         <is>
-          <t>MetRm90</t>
+          <t>MetRm60</t>
         </is>
       </c>
       <c r="W114" t="inlineStr">
         <is>
-          <t>Methadone access 90 minutes (RAAM)</t>
+          <t>Methadone access 60 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X114" t="inlineStr"/>
@@ -9157,12 +9157,12 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr"/>
@@ -9180,10 +9180,26 @@
           <t>Spatial Access to MOUDs</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr"/>
-      <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr"/>
@@ -9201,20 +9217,16 @@
       <c r="Q115" t="inlineStr"/>
       <c r="R115" t="inlineStr"/>
       <c r="S115" t="inlineStr"/>
-      <c r="T115" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T115" t="inlineStr"/>
       <c r="U115" t="inlineStr"/>
       <c r="V115" t="inlineStr">
         <is>
-          <t>MetTmBk</t>
+          <t>MetRm90</t>
         </is>
       </c>
       <c r="W115" t="inlineStr">
         <is>
-          <t>Biking Time (min) to nearest Methadone Provider</t>
+          <t>Methadone access 90 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X115" t="inlineStr"/>
@@ -9225,12 +9237,12 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr"/>
@@ -9277,12 +9289,12 @@
       <c r="U116" t="inlineStr"/>
       <c r="V116" t="inlineStr">
         <is>
-          <t>MetTmDr</t>
+          <t>MetTmBk</t>
         </is>
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Methadone Provider</t>
+          <t>Biking Time (min) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X116" t="inlineStr"/>
@@ -9293,12 +9305,12 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr"/>
@@ -9336,7 +9348,11 @@
       <c r="P117" t="inlineStr"/>
       <c r="Q117" t="inlineStr"/>
       <c r="R117" t="inlineStr"/>
-      <c r="S117" t="inlineStr"/>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T117" t="inlineStr">
         <is>
           <t>x</t>
@@ -9345,12 +9361,12 @@
       <c r="U117" t="inlineStr"/>
       <c r="V117" t="inlineStr">
         <is>
-          <t>MetTmWk</t>
+          <t>MetTmDr</t>
         </is>
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Methadone Provider</t>
+          <t>Driving Time (min) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X117" t="inlineStr"/>
@@ -9361,12 +9377,12 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr"/>
@@ -9395,26 +9411,30 @@
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="inlineStr"/>
       <c r="Q118" t="inlineStr"/>
       <c r="R118" t="inlineStr"/>
-      <c r="S118" t="inlineStr"/>
-      <c r="T118" t="inlineStr"/>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U118" t="inlineStr"/>
       <c r="V118" t="inlineStr">
         <is>
-          <t>MoudMinDis</t>
+          <t>MetTmDr2</t>
         </is>
       </c>
       <c r="W118" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest MOUD (any)</t>
+          <t>Driving time to nearest methadone provider (with impedance)</t>
         </is>
       </c>
       <c r="X118" t="inlineStr"/>
@@ -9425,12 +9445,12 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr"/>
@@ -9469,16 +9489,20 @@
       <c r="Q119" t="inlineStr"/>
       <c r="R119" t="inlineStr"/>
       <c r="S119" t="inlineStr"/>
-      <c r="T119" t="inlineStr"/>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U119" t="inlineStr"/>
       <c r="V119" t="inlineStr">
         <is>
-          <t>NaltCntBk30</t>
+          <t>MetTmWk</t>
         </is>
       </c>
       <c r="W119" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (30-min bike)</t>
+          <t>Walking Time (min) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X119" t="inlineStr"/>
@@ -9489,12 +9513,12 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr"/>
@@ -9537,12 +9561,12 @@
       <c r="U120" t="inlineStr"/>
       <c r="V120" t="inlineStr">
         <is>
-          <t>NaltCntBk60</t>
+          <t>MoudMinDis</t>
         </is>
       </c>
       <c r="W120" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (60-min bike)</t>
+          <t>Distance (mi) to nearest MOUD (any)</t>
         </is>
       </c>
       <c r="X120" t="inlineStr"/>
@@ -9553,12 +9577,12 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr"/>
@@ -9587,26 +9611,30 @@
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr"/>
       <c r="P121" t="inlineStr"/>
       <c r="Q121" t="inlineStr"/>
       <c r="R121" t="inlineStr"/>
-      <c r="S121" t="inlineStr"/>
-      <c r="T121" t="inlineStr"/>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U121" t="inlineStr"/>
       <c r="V121" t="inlineStr">
         <is>
-          <t>NaltCntDr30</t>
+          <t>MoudTyp</t>
         </is>
       </c>
       <c r="W121" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (30-min drive)</t>
+          <t xml:space="preserve">MOUD Types Within 30-Min Drive  (impedance, adjusted) </t>
         </is>
       </c>
       <c r="X121" t="inlineStr"/>
@@ -9617,12 +9645,12 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr"/>
@@ -9665,12 +9693,12 @@
       <c r="U122" t="inlineStr"/>
       <c r="V122" t="inlineStr">
         <is>
-          <t>NaltCntWk30</t>
+          <t>NaltCntBk30</t>
         </is>
       </c>
       <c r="W122" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (30-min walk)</t>
+          <t>Count of Naltrexone Providers (30-min bike)</t>
         </is>
       </c>
       <c r="X122" t="inlineStr"/>
@@ -9681,12 +9709,12 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr"/>
@@ -9729,12 +9757,12 @@
       <c r="U123" t="inlineStr"/>
       <c r="V123" t="inlineStr">
         <is>
-          <t>NaltCntWk60</t>
+          <t>NaltCntBk60</t>
         </is>
       </c>
       <c r="W123" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (60-min walk)</t>
+          <t>Count of Naltrexone Providers (60-min bike)</t>
         </is>
       </c>
       <c r="X123" t="inlineStr"/>
@@ -9745,12 +9773,12 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr"/>
@@ -9788,17 +9816,21 @@
       <c r="P124" t="inlineStr"/>
       <c r="Q124" t="inlineStr"/>
       <c r="R124" t="inlineStr"/>
-      <c r="S124" t="inlineStr"/>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T124" t="inlineStr"/>
       <c r="U124" t="inlineStr"/>
       <c r="V124" t="inlineStr">
         <is>
-          <t>NaltMinDis</t>
+          <t>NaltCntDr30</t>
         </is>
       </c>
       <c r="W124" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Naltrexone Provider</t>
+          <t>Count of Naltrexone Providers (30-min drive)</t>
         </is>
       </c>
       <c r="X124" t="inlineStr"/>
@@ -9809,12 +9841,12 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr"/>
@@ -9857,12 +9889,12 @@
       <c r="U125" t="inlineStr"/>
       <c r="V125" t="inlineStr">
         <is>
-          <t>NaltRm30</t>
+          <t>NaltCntWk30</t>
         </is>
       </c>
       <c r="W125" t="inlineStr">
         <is>
-          <t>Naltrexone access 30 minutes (RAAM)</t>
+          <t>Count of Naltrexone Providers (30-min walk)</t>
         </is>
       </c>
       <c r="X125" t="inlineStr"/>
@@ -9873,12 +9905,12 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr"/>
@@ -9921,12 +9953,12 @@
       <c r="U126" t="inlineStr"/>
       <c r="V126" t="inlineStr">
         <is>
-          <t>NaltRm60</t>
+          <t>NaltCntWk60</t>
         </is>
       </c>
       <c r="W126" t="inlineStr">
         <is>
-          <t>Naltrexone access 60 minutes (RAAM)</t>
+          <t>Count of Naltrexone Providers (60-min walk)</t>
         </is>
       </c>
       <c r="X126" t="inlineStr"/>
@@ -9937,12 +9969,12 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr"/>
@@ -9985,12 +10017,12 @@
       <c r="U127" t="inlineStr"/>
       <c r="V127" t="inlineStr">
         <is>
-          <t>NaltRm90</t>
+          <t>NaltMinDis</t>
         </is>
       </c>
       <c r="W127" t="inlineStr">
         <is>
-          <t>Naltrexone access 90 minutes (RAAM)</t>
+          <t>Distance (mi) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X127" t="inlineStr"/>
@@ -10001,12 +10033,12 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr"/>
@@ -10045,20 +10077,16 @@
       <c r="Q128" t="inlineStr"/>
       <c r="R128" t="inlineStr"/>
       <c r="S128" t="inlineStr"/>
-      <c r="T128" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T128" t="inlineStr"/>
       <c r="U128" t="inlineStr"/>
       <c r="V128" t="inlineStr">
         <is>
-          <t>NaltTmBk</t>
+          <t>NaltRm30</t>
         </is>
       </c>
       <c r="W128" t="inlineStr">
         <is>
-          <t>Biking Time (min) to nearest Naltrexone Provider</t>
+          <t>Naltrexone access 30 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X128" t="inlineStr"/>
@@ -10069,12 +10097,12 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr"/>
@@ -10113,20 +10141,16 @@
       <c r="Q129" t="inlineStr"/>
       <c r="R129" t="inlineStr"/>
       <c r="S129" t="inlineStr"/>
-      <c r="T129" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T129" t="inlineStr"/>
       <c r="U129" t="inlineStr"/>
       <c r="V129" t="inlineStr">
         <is>
-          <t>NaltTmDr</t>
+          <t>NaltRm60</t>
         </is>
       </c>
       <c r="W129" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Naltrexone Provider</t>
+          <t>Naltrexone access 60 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X129" t="inlineStr"/>
@@ -10137,12 +10161,12 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr"/>
@@ -10181,20 +10205,16 @@
       <c r="Q130" t="inlineStr"/>
       <c r="R130" t="inlineStr"/>
       <c r="S130" t="inlineStr"/>
-      <c r="T130" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T130" t="inlineStr"/>
       <c r="U130" t="inlineStr"/>
       <c r="V130" t="inlineStr">
         <is>
-          <t>NaltTmWk</t>
+          <t>NaltRm90</t>
         </is>
       </c>
       <c r="W130" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Naltrexone Provider</t>
+          <t>Naltrexone access 90 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X130" t="inlineStr"/>
@@ -10205,12 +10225,12 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr"/>
@@ -10239,26 +10259,30 @@
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
-      <c r="O131" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr"/>
       <c r="P131" t="inlineStr"/>
       <c r="Q131" t="inlineStr"/>
       <c r="R131" t="inlineStr"/>
       <c r="S131" t="inlineStr"/>
-      <c r="T131" t="inlineStr"/>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U131" t="inlineStr"/>
       <c r="V131" t="inlineStr">
         <is>
-          <t>OtpCntDr</t>
+          <t>NaltTmBk</t>
         </is>
       </c>
       <c r="W131" t="inlineStr">
         <is>
-          <t>Count of Opioid Treatment Programs (OTP) (30-min drive)</t>
+          <t>Biking Time (min) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X131" t="inlineStr"/>
@@ -10269,12 +10293,12 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr"/>
@@ -10303,26 +10327,34 @@
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
-      <c r="O132" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr"/>
       <c r="P132" t="inlineStr"/>
       <c r="Q132" t="inlineStr"/>
       <c r="R132" t="inlineStr"/>
-      <c r="S132" t="inlineStr"/>
-      <c r="T132" t="inlineStr"/>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U132" t="inlineStr"/>
       <c r="V132" t="inlineStr">
         <is>
-          <t>OtpMinDis</t>
+          <t>NaltTmDr</t>
         </is>
       </c>
       <c r="W132" t="inlineStr">
         <is>
-          <t>Distance to nearest OTP</t>
+          <t>Driving Time (min) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X132" t="inlineStr"/>
@@ -10333,12 +10365,12 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr"/>
@@ -10368,29 +10400,25 @@
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr"/>
       <c r="N133" t="inlineStr"/>
-      <c r="O133" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="O133" t="inlineStr"/>
       <c r="P133" t="inlineStr"/>
       <c r="Q133" t="inlineStr"/>
       <c r="R133" t="inlineStr"/>
-      <c r="S133" t="inlineStr"/>
-      <c r="T133" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr"/>
       <c r="U133" t="inlineStr"/>
       <c r="V133" t="inlineStr">
         <is>
-          <t>OtpTmDr</t>
+          <t>NaltTmDr2</t>
         </is>
       </c>
       <c r="W133" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP)</t>
+          <t>Driving time to nearest naltrexone provider (with impedance)</t>
         </is>
       </c>
       <c r="X133" t="inlineStr"/>
@@ -10401,12 +10429,12 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr"/>
@@ -10421,7 +10449,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
@@ -10445,32 +10473,36 @@
       <c r="Q134" t="inlineStr"/>
       <c r="R134" t="inlineStr"/>
       <c r="S134" t="inlineStr"/>
-      <c r="T134" t="inlineStr"/>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U134" t="inlineStr"/>
       <c r="V134" t="inlineStr">
         <is>
-          <t>MhCntDr</t>
+          <t>NaltTmWk</t>
         </is>
       </c>
       <c r="W134" t="inlineStr">
         <is>
-          <t>Count of Mental Health Providers (30-min drive)</t>
+          <t>Walking Time (min) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X134" t="inlineStr"/>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr"/>
@@ -10485,7 +10517,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -10499,42 +10531,46 @@
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr"/>
       <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr"/>
       <c r="Q135" t="inlineStr"/>
       <c r="R135" t="inlineStr"/>
-      <c r="S135" t="inlineStr"/>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T135" t="inlineStr"/>
       <c r="U135" t="inlineStr"/>
       <c r="V135" t="inlineStr">
         <is>
-          <t>MhMinDis</t>
+          <t>OtpCntDr</t>
         </is>
       </c>
       <c r="W135" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Mental Health Provider</t>
+          <t>Count of Opioid Treatment Programs (OTP) (30-min drive)</t>
         </is>
       </c>
       <c r="X135" t="inlineStr"/>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr"/>
@@ -10549,7 +10585,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -10563,46 +10599,42 @@
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr"/>
       <c r="Q136" t="inlineStr"/>
       <c r="R136" t="inlineStr"/>
       <c r="S136" t="inlineStr"/>
-      <c r="T136" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T136" t="inlineStr"/>
       <c r="U136" t="inlineStr"/>
       <c r="V136" t="inlineStr">
         <is>
-          <t>MhTmDr</t>
+          <t>OtpMinDis</t>
         </is>
       </c>
       <c r="W136" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Mental Health Provider</t>
+          <t>Distance to nearest OTP</t>
         </is>
       </c>
       <c r="X136" t="inlineStr"/>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr"/>
@@ -10617,7 +10649,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -10630,43 +10662,51 @@
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M137" t="inlineStr"/>
       <c r="N137" t="inlineStr"/>
-      <c r="O137" t="inlineStr"/>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr"/>
       <c r="Q137" t="inlineStr"/>
       <c r="R137" t="inlineStr"/>
-      <c r="S137" t="inlineStr"/>
-      <c r="T137" t="inlineStr"/>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U137" t="inlineStr"/>
       <c r="V137" t="inlineStr">
         <is>
-          <t>RxCntDr</t>
+          <t>OtpTmDr</t>
         </is>
       </c>
       <c r="W137" t="inlineStr">
         <is>
-          <t>Count of Pharmacies (30-min drive)</t>
+          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP)</t>
         </is>
       </c>
       <c r="X137" t="inlineStr"/>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>InfoGroup 2019</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr"/>
@@ -10681,7 +10721,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -10694,43 +10734,43 @@
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr"/>
       <c r="P138" t="inlineStr"/>
       <c r="Q138" t="inlineStr"/>
       <c r="R138" t="inlineStr"/>
-      <c r="S138" t="inlineStr"/>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T138" t="inlineStr"/>
       <c r="U138" t="inlineStr"/>
       <c r="V138" t="inlineStr">
         <is>
-          <t>RxMinDis</t>
+          <t>OtpTmDr2</t>
         </is>
       </c>
       <c r="W138" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Pharmacy</t>
+          <t>Driving time to nearest OTP (impedance-adjusted)</t>
         </is>
       </c>
       <c r="X138" t="inlineStr"/>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>InfoGroup 2019</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr"/>
@@ -10745,7 +10785,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -10758,47 +10798,43 @@
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O139" t="inlineStr"/>
       <c r="P139" t="inlineStr"/>
       <c r="Q139" t="inlineStr"/>
       <c r="R139" t="inlineStr"/>
       <c r="S139" t="inlineStr"/>
-      <c r="T139" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T139" t="inlineStr"/>
       <c r="U139" t="inlineStr"/>
       <c r="V139" t="inlineStr">
         <is>
-          <t>RxTmDr</t>
+          <t>MhCntDr</t>
         </is>
       </c>
       <c r="W139" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Pharmacy</t>
+          <t>Count of Mental Health Providers (30-min drive)</t>
         </is>
       </c>
       <c r="X139" t="inlineStr"/>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>InfoGroup 2019</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr"/>
@@ -10813,7 +10849,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -10841,18 +10877,18 @@
       <c r="U140" t="inlineStr"/>
       <c r="V140" t="inlineStr">
         <is>
-          <t>SutCntDr</t>
+          <t>MhMinDis</t>
         </is>
       </c>
       <c r="W140" t="inlineStr">
         <is>
-          <t>Count of Substance Use Treatment (SUT) facility (30-min drive)</t>
+          <t>Distance (mi) to nearest Mental Health Provider</t>
         </is>
       </c>
       <c r="X140" t="inlineStr"/>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z140" t="inlineStr">
@@ -10877,7 +10913,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -10901,22 +10937,26 @@
       <c r="Q141" t="inlineStr"/>
       <c r="R141" t="inlineStr"/>
       <c r="S141" t="inlineStr"/>
-      <c r="T141" t="inlineStr"/>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U141" t="inlineStr"/>
       <c r="V141" t="inlineStr">
         <is>
-          <t>SutMinDis</t>
+          <t>MhTmDr</t>
         </is>
       </c>
       <c r="W141" t="inlineStr">
         <is>
-          <t>Distance (mi) to Substance Use Treatment (SUT) facility</t>
+          <t>Driving Time (min) to nearest Mental Health Provider</t>
         </is>
       </c>
       <c r="X141" t="inlineStr"/>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z141" t="inlineStr">
@@ -10941,7 +10981,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -10954,47 +10994,43 @@
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr"/>
       <c r="O142" t="inlineStr"/>
       <c r="P142" t="inlineStr"/>
       <c r="Q142" t="inlineStr"/>
       <c r="R142" t="inlineStr"/>
       <c r="S142" t="inlineStr"/>
-      <c r="T142" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T142" t="inlineStr"/>
       <c r="U142" t="inlineStr"/>
       <c r="V142" t="inlineStr">
         <is>
-          <t>SutTmDr</t>
+          <t>RxCntDr</t>
         </is>
       </c>
       <c r="W142" t="inlineStr">
         <is>
-          <t>Driving time (min) to Substance Use Treatment (SUT) facility</t>
+          <t>Count of Pharmacies (30-min drive)</t>
         </is>
       </c>
       <c r="X142" t="inlineStr"/>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>InfoGroup 2019</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>InfoGroup, 2019</t>
         </is>
       </c>
       <c r="AB142" t="inlineStr"/>
@@ -11009,7 +11045,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -11022,47 +11058,43 @@
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr"/>
-      <c r="N143" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr"/>
       <c r="O143" t="inlineStr"/>
       <c r="P143" t="inlineStr"/>
       <c r="Q143" t="inlineStr"/>
       <c r="R143" t="inlineStr"/>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S143" t="inlineStr"/>
       <c r="T143" t="inlineStr"/>
       <c r="U143" t="inlineStr"/>
       <c r="V143" t="inlineStr">
         <is>
-          <t>FqhcCntDr</t>
+          <t>RxMinDis</t>
         </is>
       </c>
       <c r="W143" t="inlineStr">
         <is>
-          <t>Count of Federally Qualified Health Centers (FQHCs) within 30-min drive</t>
+          <t>Distance (mi) to nearest Pharmacy</t>
         </is>
       </c>
       <c r="X143" t="inlineStr"/>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019</t>
         </is>
       </c>
       <c r="AB143" t="inlineStr"/>
@@ -11077,7 +11109,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -11090,43 +11122,47 @@
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr"/>
-      <c r="N144" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr"/>
       <c r="P144" t="inlineStr"/>
       <c r="Q144" t="inlineStr"/>
       <c r="R144" t="inlineStr"/>
       <c r="S144" t="inlineStr"/>
-      <c r="T144" t="inlineStr"/>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U144" t="inlineStr"/>
       <c r="V144" t="inlineStr">
         <is>
-          <t>FqhcMinDis</t>
+          <t>RxTmDr</t>
         </is>
       </c>
       <c r="W144" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Federally Qualified Health Centers (FQHC)</t>
+          <t>Driving Time (min) to nearest Pharmacy</t>
         </is>
       </c>
       <c r="X144" t="inlineStr"/>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr"/>
@@ -11141,7 +11177,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -11164,41 +11200,33 @@
       <c r="P145" t="inlineStr"/>
       <c r="Q145" t="inlineStr"/>
       <c r="R145" t="inlineStr"/>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="T145" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S145" t="inlineStr"/>
+      <c r="T145" t="inlineStr"/>
       <c r="U145" t="inlineStr"/>
       <c r="V145" t="inlineStr">
         <is>
-          <t>FqhcTmDr</t>
+          <t>SutCntDr</t>
         </is>
       </c>
       <c r="W145" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC)</t>
+          <t>Count of Substance Use Treatment (SUT) facility (30-min drive)</t>
         </is>
       </c>
       <c r="X145" t="inlineStr"/>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr"/>
@@ -11213,7 +11241,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -11227,46 +11255,42 @@
       <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr"/>
       <c r="M146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O146" t="inlineStr"/>
       <c r="P146" t="inlineStr"/>
       <c r="Q146" t="inlineStr"/>
       <c r="R146" t="inlineStr"/>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="T146" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S146" t="inlineStr"/>
+      <c r="T146" t="inlineStr"/>
       <c r="U146" t="inlineStr"/>
       <c r="V146" t="inlineStr">
         <is>
-          <t>FqhcTmDr2</t>
+          <t>SutMinDis</t>
         </is>
       </c>
       <c r="W146" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC), with Impedance factor</t>
+          <t>Distance (mi) to Substance Use Treatment (SUT) facility</t>
         </is>
       </c>
       <c r="X146" t="inlineStr"/>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr"/>
@@ -11281,17 +11305,13 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr"/>
@@ -11299,38 +11319,46 @@
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O147" t="inlineStr"/>
       <c r="P147" t="inlineStr"/>
       <c r="Q147" t="inlineStr"/>
       <c r="R147" t="inlineStr"/>
       <c r="S147" t="inlineStr"/>
-      <c r="T147" t="inlineStr"/>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U147" t="inlineStr"/>
       <c r="V147" t="inlineStr">
         <is>
-          <t>Ruca1</t>
+          <t>SutTmDr</t>
         </is>
       </c>
       <c r="W147" t="inlineStr">
         <is>
-          <t>Primary RUCA Code</t>
+          <t>Driving time (min) to Substance Use Treatment (SUT) facility</t>
         </is>
       </c>
       <c r="X147" t="inlineStr"/>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB147" t="inlineStr"/>
@@ -11345,17 +11373,13 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr"/>
@@ -11363,38 +11387,46 @@
       <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr"/>
       <c r="M148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O148" t="inlineStr"/>
       <c r="P148" t="inlineStr"/>
       <c r="Q148" t="inlineStr"/>
       <c r="R148" t="inlineStr"/>
-      <c r="S148" t="inlineStr"/>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T148" t="inlineStr"/>
       <c r="U148" t="inlineStr"/>
       <c r="V148" t="inlineStr">
         <is>
-          <t>Ruca2</t>
+          <t>FqhcCntDr</t>
         </is>
       </c>
       <c r="W148" t="inlineStr">
         <is>
-          <t>Secondary RUCA Code</t>
+          <t>Count of Federally Qualified Health Centers (FQHCs) within 30-min drive</t>
         </is>
       </c>
       <c r="X148" t="inlineStr"/>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr"/>
@@ -11409,17 +11441,13 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr"/>
@@ -11427,42 +11455,42 @@
       <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr"/>
       <c r="M149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O149" t="inlineStr"/>
       <c r="P149" t="inlineStr"/>
       <c r="Q149" t="inlineStr"/>
       <c r="R149" t="inlineStr"/>
       <c r="S149" t="inlineStr"/>
-      <c r="T149" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T149" t="inlineStr"/>
       <c r="U149" t="inlineStr"/>
       <c r="V149" t="inlineStr">
         <is>
-          <t>Rurality</t>
+          <t>FqhcMinDis</t>
         </is>
       </c>
       <c r="W149" t="inlineStr">
         <is>
-          <t>Urban-Suburban-Rural</t>
+          <t>Distance (mi) to nearest Federally Qualified Health Centers (FQHC)</t>
         </is>
       </c>
       <c r="X149" t="inlineStr"/>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr"/>
@@ -11472,12 +11500,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -11489,44 +11517,52 @@
       <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L150" t="inlineStr"/>
       <c r="M150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O150" t="inlineStr"/>
       <c r="P150" t="inlineStr"/>
       <c r="Q150" t="inlineStr"/>
       <c r="R150" t="inlineStr"/>
-      <c r="S150" t="inlineStr"/>
-      <c r="T150" t="inlineStr"/>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U150" t="inlineStr"/>
       <c r="V150" t="inlineStr">
         <is>
-          <t>EssnWrkE</t>
+          <t>FqhcTmDr</t>
         </is>
       </c>
       <c r="W150" t="inlineStr">
         <is>
-          <t>Count of Essential Workers</t>
+          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC)</t>
         </is>
       </c>
       <c r="X150" t="inlineStr"/>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr"/>
@@ -11536,12 +11572,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -11553,52 +11589,48 @@
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L151" t="inlineStr"/>
       <c r="M151" t="inlineStr"/>
-      <c r="N151" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N151" t="inlineStr"/>
       <c r="O151" t="inlineStr"/>
       <c r="P151" t="inlineStr"/>
-      <c r="Q151" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q151" t="inlineStr"/>
       <c r="R151" t="inlineStr"/>
-      <c r="S151" t="inlineStr"/>
-      <c r="T151" t="inlineStr"/>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U151" t="inlineStr"/>
       <c r="V151" t="inlineStr">
         <is>
-          <t>EssnWrkP</t>
+          <t>FqhcTmDr2</t>
         </is>
       </c>
       <c r="W151" t="inlineStr">
         <is>
-          <t>Essential Workers %</t>
+          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC), with Impedance factor</t>
         </is>
       </c>
       <c r="X151" t="inlineStr"/>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB151" t="inlineStr"/>
@@ -11608,69 +11640,61 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr"/>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L152" t="inlineStr"/>
       <c r="M152" t="inlineStr"/>
-      <c r="N152" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N152" t="inlineStr"/>
       <c r="O152" t="inlineStr"/>
       <c r="P152" t="inlineStr"/>
-      <c r="Q152" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q152" t="inlineStr"/>
       <c r="R152" t="inlineStr"/>
       <c r="S152" t="inlineStr"/>
       <c r="T152" t="inlineStr"/>
       <c r="U152" t="inlineStr"/>
       <c r="V152" t="inlineStr">
         <is>
-          <t>HghRskP</t>
+          <t>Ruca1</t>
         </is>
       </c>
       <c r="W152" t="inlineStr">
         <is>
-          <t>Employed % - High Risk of Injury</t>
+          <t>Primary RUCA Code</t>
         </is>
       </c>
       <c r="X152" t="inlineStr"/>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB152" t="inlineStr"/>
@@ -11680,69 +11704,61 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr"/>
-      <c r="F153" t="inlineStr"/>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L153" t="inlineStr"/>
       <c r="M153" t="inlineStr"/>
-      <c r="N153" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N153" t="inlineStr"/>
       <c r="O153" t="inlineStr"/>
       <c r="P153" t="inlineStr"/>
-      <c r="Q153" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q153" t="inlineStr"/>
       <c r="R153" t="inlineStr"/>
       <c r="S153" t="inlineStr"/>
       <c r="T153" t="inlineStr"/>
       <c r="U153" t="inlineStr"/>
       <c r="V153" t="inlineStr">
         <is>
-          <t>HltCrP</t>
+          <t>Ruca2</t>
         </is>
       </c>
       <c r="W153" t="inlineStr">
         <is>
-          <t>Employed % - Health Care</t>
+          <t>Secondary RUCA Code</t>
         </is>
       </c>
       <c r="X153" t="inlineStr"/>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB153" t="inlineStr"/>
@@ -11752,69 +11768,65 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr"/>
-      <c r="F154" t="inlineStr"/>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L154" t="inlineStr"/>
       <c r="M154" t="inlineStr"/>
-      <c r="N154" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N154" t="inlineStr"/>
       <c r="O154" t="inlineStr"/>
       <c r="P154" t="inlineStr"/>
-      <c r="Q154" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q154" t="inlineStr"/>
       <c r="R154" t="inlineStr"/>
       <c r="S154" t="inlineStr"/>
-      <c r="T154" t="inlineStr"/>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U154" t="inlineStr"/>
       <c r="V154" t="inlineStr">
         <is>
-          <t>RetailP</t>
+          <t>Rurality</t>
         </is>
       </c>
       <c r="W154" t="inlineStr">
         <is>
-          <t>Employed % - Retail</t>
+          <t>Urban-Suburban-Rural</t>
         </is>
       </c>
       <c r="X154" t="inlineStr"/>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB154" t="inlineStr"/>
@@ -11847,30 +11859,22 @@
         </is>
       </c>
       <c r="M155" t="inlineStr"/>
-      <c r="N155" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N155" t="inlineStr"/>
       <c r="O155" t="inlineStr"/>
       <c r="P155" t="inlineStr"/>
-      <c r="Q155" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q155" t="inlineStr"/>
       <c r="R155" t="inlineStr"/>
       <c r="S155" t="inlineStr"/>
       <c r="T155" t="inlineStr"/>
       <c r="U155" t="inlineStr"/>
       <c r="V155" t="inlineStr">
         <is>
-          <t>TotWrkE</t>
+          <t>EssnWrkE</t>
         </is>
       </c>
       <c r="W155" t="inlineStr">
         <is>
-          <t>Count of Working Population</t>
+          <t>Count of Essential Workers</t>
         </is>
       </c>
       <c r="X155" t="inlineStr"/>
@@ -11901,7 +11905,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -11919,38 +11923,46 @@
         </is>
       </c>
       <c r="M156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O156" t="inlineStr"/>
       <c r="P156" t="inlineStr"/>
-      <c r="Q156" t="inlineStr"/>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R156" t="inlineStr"/>
       <c r="S156" t="inlineStr"/>
       <c r="T156" t="inlineStr"/>
       <c r="U156" t="inlineStr"/>
       <c r="V156" t="inlineStr">
         <is>
-          <t>ForDqP</t>
+          <t>EssnWrkP</t>
         </is>
       </c>
       <c r="W156" t="inlineStr">
         <is>
-          <t>Foreclosure &amp; Delinquency %</t>
+          <t>Essential Workers %</t>
         </is>
       </c>
       <c r="X156" t="inlineStr"/>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB156" t="inlineStr"/>
@@ -11965,7 +11977,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -11983,38 +11995,46 @@
         </is>
       </c>
       <c r="M157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O157" t="inlineStr"/>
       <c r="P157" t="inlineStr"/>
-      <c r="Q157" t="inlineStr"/>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R157" t="inlineStr"/>
       <c r="S157" t="inlineStr"/>
       <c r="T157" t="inlineStr"/>
       <c r="U157" t="inlineStr"/>
       <c r="V157" t="inlineStr">
         <is>
-          <t>ForDqTot</t>
+          <t>HghRskP</t>
         </is>
       </c>
       <c r="W157" t="inlineStr">
         <is>
-          <t>Foreclosure &amp; Delinquency Count</t>
+          <t>Employed % - High Risk of Injury</t>
         </is>
       </c>
       <c r="X157" t="inlineStr"/>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB157" t="inlineStr"/>
@@ -12029,17 +12049,13 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr"/>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr"/>
@@ -12069,28 +12085,28 @@
       <c r="U158" t="inlineStr"/>
       <c r="V158" t="inlineStr">
         <is>
-          <t>GiniCoeff</t>
+          <t>HltCrP</t>
         </is>
       </c>
       <c r="W158" t="inlineStr">
         <is>
-          <t>Income Inequality (Gini Coefficient)</t>
+          <t>Employed % - Health Care</t>
         </is>
       </c>
       <c r="X158" t="inlineStr"/>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB158" t="inlineStr"/>
@@ -12105,7 +12121,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Internet Access</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
@@ -12117,44 +12133,52 @@
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N159" t="inlineStr"/>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O159" t="inlineStr"/>
       <c r="P159" t="inlineStr"/>
-      <c r="Q159" t="inlineStr"/>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R159" t="inlineStr"/>
       <c r="S159" t="inlineStr"/>
       <c r="T159" t="inlineStr"/>
       <c r="U159" t="inlineStr"/>
       <c r="V159" t="inlineStr">
         <is>
-          <t>NoIntP</t>
+          <t>RetailP</t>
         </is>
       </c>
       <c r="W159" t="inlineStr">
         <is>
-          <t>Households without Internet Access %</t>
+          <t>Employed % - Retail</t>
         </is>
       </c>
       <c r="X159" t="inlineStr"/>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Internet_Access.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>ACS 2019</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>American Community Survey 2015-2019 5-Year Estimate</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB159" t="inlineStr"/>
@@ -12169,17 +12193,13 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F160" t="inlineStr"/>
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr"/>
@@ -12209,28 +12229,28 @@
       <c r="U160" t="inlineStr"/>
       <c r="V160" t="inlineStr">
         <is>
-          <t>MedInc</t>
+          <t>TotWrkE</t>
         </is>
       </c>
       <c r="W160" t="inlineStr">
         <is>
-          <t>Median Income</t>
+          <t>Count of Working Population</t>
         </is>
       </c>
       <c r="X160" t="inlineStr"/>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB160" t="inlineStr"/>
@@ -12245,17 +12265,13 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
+          <t>Great Recession Foreclosure Rate</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr"/>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr"/>
@@ -12267,46 +12283,38 @@
         </is>
       </c>
       <c r="M161" t="inlineStr"/>
-      <c r="N161" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N161" t="inlineStr"/>
       <c r="O161" t="inlineStr"/>
       <c r="P161" t="inlineStr"/>
-      <c r="Q161" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q161" t="inlineStr"/>
       <c r="R161" t="inlineStr"/>
       <c r="S161" t="inlineStr"/>
       <c r="T161" t="inlineStr"/>
       <c r="U161" t="inlineStr"/>
       <c r="V161" t="inlineStr">
         <is>
-          <t>PciE</t>
+          <t>ForDqP</t>
         </is>
       </c>
       <c r="W161" t="inlineStr">
         <is>
-          <t>Per Capita Income</t>
+          <t>Foreclosure &amp; Delinquency %</t>
         </is>
       </c>
       <c r="X161" t="inlineStr"/>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
         </is>
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>HUD 2018; ACS 2012, 2018</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB161" t="inlineStr"/>
@@ -12321,29 +12329,13 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>Great Recession Foreclosure Rate</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr"/>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr"/>
@@ -12355,50 +12347,38 @@
         </is>
       </c>
       <c r="M162" t="inlineStr"/>
-      <c r="N162" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N162" t="inlineStr"/>
       <c r="O162" t="inlineStr"/>
       <c r="P162" t="inlineStr"/>
-      <c r="Q162" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q162" t="inlineStr"/>
       <c r="R162" t="inlineStr"/>
       <c r="S162" t="inlineStr"/>
       <c r="T162" t="inlineStr"/>
-      <c r="U162" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="U162" t="inlineStr"/>
       <c r="V162" t="inlineStr">
         <is>
-          <t>PovP</t>
+          <t>ForDqTot</t>
         </is>
       </c>
       <c r="W162" t="inlineStr">
         <is>
-          <t>Poverty %</t>
+          <t>Foreclosure &amp; Delinquency Count</t>
         </is>
       </c>
       <c r="X162" t="inlineStr"/>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
         </is>
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>HUD 2018; ACS 2012, 2018</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB162" t="inlineStr"/>
@@ -12413,24 +12393,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>Great Recession Foreclosure Rate</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr"/>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
           <t>x</t>
@@ -12462,35 +12430,31 @@
       <c r="R163" t="inlineStr"/>
       <c r="S163" t="inlineStr"/>
       <c r="T163" t="inlineStr"/>
-      <c r="U163" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="U163" t="inlineStr"/>
       <c r="V163" t="inlineStr">
         <is>
-          <t>UnempP</t>
+          <t>GiniCoeff</t>
         </is>
       </c>
       <c r="W163" t="inlineStr">
         <is>
-          <t>Unemployment %</t>
+          <t>Income Inequality (Gini Coefficient)</t>
         </is>
       </c>
       <c r="X163" t="inlineStr"/>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
         </is>
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>HUD 2018; ACS 2012, 2018</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB163" t="inlineStr"/>
@@ -12500,12 +12464,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>SDOH Indices &amp; Typology</t>
+          <t>Internet Access</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
@@ -12513,52 +12477,48 @@
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr"/>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr"/>
-      <c r="M164" t="inlineStr"/>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N164" t="inlineStr"/>
       <c r="O164" t="inlineStr"/>
       <c r="P164" t="inlineStr"/>
       <c r="Q164" t="inlineStr"/>
       <c r="R164" t="inlineStr"/>
       <c r="S164" t="inlineStr"/>
-      <c r="T164" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T164" t="inlineStr"/>
       <c r="U164" t="inlineStr"/>
       <c r="V164" t="inlineStr">
         <is>
-          <t>LimMobInd</t>
+          <t>NoIntP</t>
         </is>
       </c>
       <c r="W164" t="inlineStr">
         <is>
-          <t>Limited Moblility Index</t>
+          <t>Households without Internet Access %</t>
         </is>
       </c>
       <c r="X164" t="inlineStr"/>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Internet_Access.md</t>
         </is>
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>ACS 2019</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>American Community Survey 2015-2019 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB164" t="inlineStr"/>
@@ -12568,65 +12528,73 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>SDOH Indices &amp; Typology</t>
+          <t>Poverty, Income, Gini Coefficient</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr"/>
-      <c r="F165" t="inlineStr"/>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G165" t="inlineStr"/>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O165" t="inlineStr"/>
       <c r="P165" t="inlineStr"/>
-      <c r="Q165" t="inlineStr"/>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R165" t="inlineStr"/>
       <c r="S165" t="inlineStr"/>
-      <c r="T165" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T165" t="inlineStr"/>
       <c r="U165" t="inlineStr"/>
       <c r="V165" t="inlineStr">
         <is>
-          <t>MicaInd</t>
+          <t>MedInc</t>
         </is>
       </c>
       <c r="W165" t="inlineStr">
         <is>
-          <t>Mixed Immigrant Cohesion and Accesibility (MICA) Index</t>
+          <t>Median Income</t>
         </is>
       </c>
       <c r="X165" t="inlineStr"/>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB165" t="inlineStr"/>
@@ -12636,61 +12604,73 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>SDOH Indices &amp; Typology</t>
+          <t>Poverty, Income, Gini Coefficient</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr"/>
-      <c r="F166" t="inlineStr"/>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G166" t="inlineStr"/>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr"/>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M166" t="inlineStr"/>
-      <c r="N166" t="inlineStr"/>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O166" t="inlineStr"/>
       <c r="P166" t="inlineStr"/>
-      <c r="Q166" t="inlineStr"/>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R166" t="inlineStr"/>
       <c r="S166" t="inlineStr"/>
       <c r="T166" t="inlineStr"/>
       <c r="U166" t="inlineStr"/>
       <c r="V166" t="inlineStr">
         <is>
-          <t>NeighbTyp</t>
+          <t>PciE</t>
         </is>
       </c>
       <c r="W166" t="inlineStr">
         <is>
-          <t>Neighborhood Type</t>
+          <t>Per Capita Income</t>
         </is>
       </c>
       <c r="X166" t="inlineStr"/>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB166" t="inlineStr"/>
@@ -12700,65 +12680,89 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>SDOH Indices &amp; Typology</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr"/>
-      <c r="D167" t="inlineStr"/>
-      <c r="E167" t="inlineStr"/>
-      <c r="F167" t="inlineStr"/>
+          <t>Poverty, Income, Gini Coefficient</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G167" t="inlineStr"/>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr"/>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O167" t="inlineStr"/>
       <c r="P167" t="inlineStr"/>
-      <c r="Q167" t="inlineStr"/>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R167" t="inlineStr"/>
       <c r="S167" t="inlineStr"/>
-      <c r="T167" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="U167" t="inlineStr"/>
+      <c r="T167" t="inlineStr"/>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="V167" t="inlineStr">
         <is>
-          <t>SocEcAdvIn</t>
+          <t>PovP</t>
         </is>
       </c>
       <c r="W167" t="inlineStr">
         <is>
-          <t>Socioeconomic Advantage Index</t>
+          <t>Poverty %</t>
         </is>
       </c>
       <c r="X167" t="inlineStr"/>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB167" t="inlineStr"/>
@@ -12768,65 +12772,89 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>SDOH Indices &amp; Typology</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr"/>
-      <c r="D168" t="inlineStr"/>
-      <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
+          <t>Poverty, Income, Gini Coefficient</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G168" t="inlineStr"/>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M168" t="inlineStr"/>
-      <c r="N168" t="inlineStr"/>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O168" t="inlineStr"/>
       <c r="P168" t="inlineStr"/>
-      <c r="Q168" t="inlineStr"/>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R168" t="inlineStr"/>
       <c r="S168" t="inlineStr"/>
-      <c r="T168" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="U168" t="inlineStr"/>
+      <c r="T168" t="inlineStr"/>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="V168" t="inlineStr">
         <is>
-          <t>UrbCoreInd</t>
+          <t>UnempP</t>
         </is>
       </c>
       <c r="W168" t="inlineStr">
         <is>
-          <t>Urban Core Opportunity Index</t>
+          <t>Unemployment %</t>
         </is>
       </c>
       <c r="X168" t="inlineStr"/>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB168" t="inlineStr"/>
@@ -12841,7 +12869,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>SDOH Indices &amp; Typology</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
@@ -12849,56 +12877,52 @@
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr"/>
       <c r="G169" t="inlineStr"/>
-      <c r="H169" t="inlineStr"/>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L169" t="inlineStr"/>
       <c r="M169" t="inlineStr"/>
-      <c r="N169" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N169" t="inlineStr"/>
       <c r="O169" t="inlineStr"/>
-      <c r="P169" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P169" t="inlineStr"/>
       <c r="Q169" t="inlineStr"/>
       <c r="R169" t="inlineStr"/>
       <c r="S169" t="inlineStr"/>
-      <c r="T169" t="inlineStr"/>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U169" t="inlineStr"/>
       <c r="V169" t="inlineStr">
         <is>
-          <t>SviSmryRnk</t>
+          <t>LimMobInd</t>
         </is>
       </c>
       <c r="W169" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) Summary Ranking</t>
+          <t>Limited Moblility Index</t>
         </is>
       </c>
       <c r="X169" t="inlineStr"/>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
         </is>
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AB169" t="inlineStr"/>
@@ -12913,7 +12937,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>SDOH Indices &amp; Typology</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
@@ -12921,27 +12945,19 @@
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr"/>
       <c r="G170" t="inlineStr"/>
-      <c r="H170" t="inlineStr"/>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L170" t="inlineStr"/>
       <c r="M170" t="inlineStr"/>
-      <c r="N170" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N170" t="inlineStr"/>
       <c r="O170" t="inlineStr"/>
-      <c r="P170" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P170" t="inlineStr"/>
       <c r="Q170" t="inlineStr"/>
       <c r="R170" t="inlineStr"/>
       <c r="S170" t="inlineStr"/>
@@ -12953,28 +12969,28 @@
       <c r="U170" t="inlineStr"/>
       <c r="V170" t="inlineStr">
         <is>
-          <t>SviTh1</t>
+          <t>MicaInd</t>
         </is>
       </c>
       <c r="W170" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 1</t>
+          <t>Mixed Immigrant Cohesion and Accesibility (MICA) Index</t>
         </is>
       </c>
       <c r="X170" t="inlineStr"/>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
         </is>
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AB170" t="inlineStr"/>
@@ -12989,7 +13005,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>SDOH Indices &amp; Typology</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
@@ -12997,27 +13013,19 @@
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr"/>
       <c r="G171" t="inlineStr"/>
-      <c r="H171" t="inlineStr"/>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr"/>
-      <c r="L171" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L171" t="inlineStr"/>
       <c r="M171" t="inlineStr"/>
-      <c r="N171" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N171" t="inlineStr"/>
       <c r="O171" t="inlineStr"/>
-      <c r="P171" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P171" t="inlineStr"/>
       <c r="Q171" t="inlineStr"/>
       <c r="R171" t="inlineStr"/>
       <c r="S171" t="inlineStr"/>
@@ -13025,28 +13033,28 @@
       <c r="U171" t="inlineStr"/>
       <c r="V171" t="inlineStr">
         <is>
-          <t>SviTh2</t>
+          <t>NeighbTyp</t>
         </is>
       </c>
       <c r="W171" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 2</t>
+          <t>Neighborhood Type</t>
         </is>
       </c>
       <c r="X171" t="inlineStr"/>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
         </is>
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AB171" t="inlineStr"/>
@@ -13061,7 +13069,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>SDOH Indices &amp; Typology</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
@@ -13069,56 +13077,52 @@
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr"/>
       <c r="G172" t="inlineStr"/>
-      <c r="H172" t="inlineStr"/>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr"/>
-      <c r="L172" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L172" t="inlineStr"/>
       <c r="M172" t="inlineStr"/>
-      <c r="N172" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N172" t="inlineStr"/>
       <c r="O172" t="inlineStr"/>
-      <c r="P172" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P172" t="inlineStr"/>
       <c r="Q172" t="inlineStr"/>
       <c r="R172" t="inlineStr"/>
       <c r="S172" t="inlineStr"/>
-      <c r="T172" t="inlineStr"/>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U172" t="inlineStr"/>
       <c r="V172" t="inlineStr">
         <is>
-          <t>SviTh3</t>
+          <t>SocEcAdvIn</t>
         </is>
       </c>
       <c r="W172" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 3</t>
+          <t>Socioeconomic Advantage Index</t>
         </is>
       </c>
       <c r="X172" t="inlineStr"/>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
         </is>
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AB172" t="inlineStr"/>
@@ -13133,7 +13137,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>SDOH Indices &amp; Typology</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -13141,27 +13145,19 @@
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr"/>
       <c r="G173" t="inlineStr"/>
-      <c r="H173" t="inlineStr"/>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr"/>
-      <c r="L173" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L173" t="inlineStr"/>
       <c r="M173" t="inlineStr"/>
-      <c r="N173" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N173" t="inlineStr"/>
       <c r="O173" t="inlineStr"/>
-      <c r="P173" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P173" t="inlineStr"/>
       <c r="Q173" t="inlineStr"/>
       <c r="R173" t="inlineStr"/>
       <c r="S173" t="inlineStr"/>
@@ -13173,33 +13169,401 @@
       <c r="U173" t="inlineStr"/>
       <c r="V173" t="inlineStr">
         <is>
-          <t>SviTh4</t>
+          <t>UrbCoreInd</t>
         </is>
       </c>
       <c r="W173" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 4</t>
+          <t>Urban Core Opportunity Index</t>
         </is>
       </c>
       <c r="X173" t="inlineStr"/>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
         </is>
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AB173" t="inlineStr"/>
       <c r="AC173" t="inlineStr"/>
       <c r="AD173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr"/>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr"/>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr"/>
+      <c r="R174" t="inlineStr"/>
+      <c r="S174" t="inlineStr"/>
+      <c r="T174" t="inlineStr"/>
+      <c r="U174" t="inlineStr"/>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>SviSmryRnk</t>
+        </is>
+      </c>
+      <c r="W174" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) Summary Ranking</t>
+        </is>
+      </c>
+      <c r="X174" t="inlineStr"/>
+      <c r="Y174" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z174" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB174" t="inlineStr"/>
+      <c r="AC174" t="inlineStr"/>
+      <c r="AD174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr"/>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr"/>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr"/>
+      <c r="R175" t="inlineStr"/>
+      <c r="S175" t="inlineStr"/>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr"/>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>SviTh1</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 1</t>
+        </is>
+      </c>
+      <c r="X175" t="inlineStr"/>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB175" t="inlineStr"/>
+      <c r="AC175" t="inlineStr"/>
+      <c r="AD175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr"/>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr"/>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr"/>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr"/>
+      <c r="R176" t="inlineStr"/>
+      <c r="S176" t="inlineStr"/>
+      <c r="T176" t="inlineStr"/>
+      <c r="U176" t="inlineStr"/>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>SviTh2</t>
+        </is>
+      </c>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 2</t>
+        </is>
+      </c>
+      <c r="X176" t="inlineStr"/>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB176" t="inlineStr"/>
+      <c r="AC176" t="inlineStr"/>
+      <c r="AD176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr"/>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr"/>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr"/>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr"/>
+      <c r="R177" t="inlineStr"/>
+      <c r="S177" t="inlineStr"/>
+      <c r="T177" t="inlineStr"/>
+      <c r="U177" t="inlineStr"/>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>SviTh3</t>
+        </is>
+      </c>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 3</t>
+        </is>
+      </c>
+      <c r="X177" t="inlineStr"/>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB177" t="inlineStr"/>
+      <c r="AC177" t="inlineStr"/>
+      <c r="AD177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr"/>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr"/>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr"/>
+      <c r="R178" t="inlineStr"/>
+      <c r="S178" t="inlineStr"/>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr"/>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>SviTh4</t>
+        </is>
+      </c>
+      <c r="W178" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 4</t>
+        </is>
+      </c>
+      <c r="X178" t="inlineStr"/>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB178" t="inlineStr"/>
+      <c r="AC178" t="inlineStr"/>
+      <c r="AD178" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/src/reference/data-dictionaries/T_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/T_Dict.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD178"/>
+  <dimension ref="A1:AD180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -7621,12 +7621,12 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>CovidCareMap 2020</t>
+          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>CovidCareMap, 2020</t>
+          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr"/>
@@ -7685,12 +7685,12 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>CovidCareMap 2020</t>
+          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>CovidCareMap, 2020</t>
+          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr"/>
@@ -7753,12 +7753,12 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>CovidCareMap 2020</t>
+          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>CovidCareMap, 2020</t>
+          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr"/>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Spatial Access to MOUDs</t>
+          <t>Spatial Access to Hospitals</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -7787,42 +7787,42 @@
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr"/>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr"/>
-      <c r="S94" t="inlineStr"/>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T94" t="inlineStr"/>
       <c r="U94" t="inlineStr"/>
       <c r="V94" t="inlineStr">
         <is>
-          <t>BupCntBk30</t>
+          <t>HospTmDr2</t>
         </is>
       </c>
       <c r="W94" t="inlineStr">
         <is>
-          <t>Count of Buprenorphine Providers (30-min bike)</t>
+          <t>Driving time (min) to nearest Hospital with Impedance Factor</t>
         </is>
       </c>
       <c r="X94" t="inlineStr"/>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Hospitals.md</t>
         </is>
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
+          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
+          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr"/>
@@ -7865,12 +7865,12 @@
       <c r="U95" t="inlineStr"/>
       <c r="V95" t="inlineStr">
         <is>
-          <t>BupCntBk60</t>
+          <t>BupCntBk30</t>
         </is>
       </c>
       <c r="W95" t="inlineStr">
         <is>
-          <t>Count of Buprenorphine Providers (60-min bike)</t>
+          <t>Count of Buprenorphine Providers (30-min bike)</t>
         </is>
       </c>
       <c r="X95" t="inlineStr"/>
@@ -7924,21 +7924,17 @@
       <c r="P96" t="inlineStr"/>
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr"/>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S96" t="inlineStr"/>
       <c r="T96" t="inlineStr"/>
       <c r="U96" t="inlineStr"/>
       <c r="V96" t="inlineStr">
         <is>
-          <t>BupCntDr30</t>
+          <t>BupCntBk60</t>
         </is>
       </c>
       <c r="W96" t="inlineStr">
         <is>
-          <t>Count of Buprenorphine Providers (30-min drive)</t>
+          <t>Count of Buprenorphine Providers (60-min bike)</t>
         </is>
       </c>
       <c r="X96" t="inlineStr"/>
@@ -7992,17 +7988,21 @@
       <c r="P97" t="inlineStr"/>
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr"/>
-      <c r="S97" t="inlineStr"/>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T97" t="inlineStr"/>
       <c r="U97" t="inlineStr"/>
       <c r="V97" t="inlineStr">
         <is>
-          <t>BupCntWk30</t>
+          <t>BupCntDr30</t>
         </is>
       </c>
       <c r="W97" t="inlineStr">
         <is>
-          <t>Count of Buprenorphine Providers (30-min walk)</t>
+          <t>Count of Buprenorphine Providers (30-min drive)</t>
         </is>
       </c>
       <c r="X97" t="inlineStr"/>
@@ -8061,12 +8061,12 @@
       <c r="U98" t="inlineStr"/>
       <c r="V98" t="inlineStr">
         <is>
-          <t>BupCntWk60</t>
+          <t>BupCntWk30</t>
         </is>
       </c>
       <c r="W98" t="inlineStr">
         <is>
-          <t>Count of Buprenorphine Providers (60-min walk)</t>
+          <t>Count of Buprenorphine Providers (30-min walk)</t>
         </is>
       </c>
       <c r="X98" t="inlineStr"/>
@@ -8125,12 +8125,12 @@
       <c r="U99" t="inlineStr"/>
       <c r="V99" t="inlineStr">
         <is>
-          <t>BupMinDis</t>
+          <t>BupCntWk60</t>
         </is>
       </c>
       <c r="W99" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Buprenorphine Provider</t>
+          <t>Count of Buprenorphine Providers (60-min walk)</t>
         </is>
       </c>
       <c r="X99" t="inlineStr"/>
@@ -8189,12 +8189,12 @@
       <c r="U100" t="inlineStr"/>
       <c r="V100" t="inlineStr">
         <is>
-          <t>BupRm30</t>
+          <t>BupMinDis</t>
         </is>
       </c>
       <c r="W100" t="inlineStr">
         <is>
-          <t>Buprenorphine access 30 minutes (RAAM)</t>
+          <t>Distance (mi) to nearest Buprenorphine Provider</t>
         </is>
       </c>
       <c r="X100" t="inlineStr"/>
@@ -8253,12 +8253,12 @@
       <c r="U101" t="inlineStr"/>
       <c r="V101" t="inlineStr">
         <is>
-          <t>BupRm60</t>
+          <t>BupRm30</t>
         </is>
       </c>
       <c r="W101" t="inlineStr">
         <is>
-          <t>Buprenorphine access 60 minutes (RAAM)</t>
+          <t>Buprenorphine access 30 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X101" t="inlineStr"/>
@@ -8317,12 +8317,12 @@
       <c r="U102" t="inlineStr"/>
       <c r="V102" t="inlineStr">
         <is>
-          <t>BupRm90</t>
+          <t>BupRm60</t>
         </is>
       </c>
       <c r="W102" t="inlineStr">
         <is>
-          <t>Buprenorphine access 90 minutes (RAAM)</t>
+          <t>Buprenorphine access 60 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X102" t="inlineStr"/>
@@ -8377,20 +8377,16 @@
       <c r="Q103" t="inlineStr"/>
       <c r="R103" t="inlineStr"/>
       <c r="S103" t="inlineStr"/>
-      <c r="T103" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T103" t="inlineStr"/>
       <c r="U103" t="inlineStr"/>
       <c r="V103" t="inlineStr">
         <is>
-          <t>BupTmBk</t>
+          <t>BupRm90</t>
         </is>
       </c>
       <c r="W103" t="inlineStr">
         <is>
-          <t>Biking Time (min) to nearest Buprenorphine Provider</t>
+          <t>Buprenorphine access 90 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X103" t="inlineStr"/>
@@ -8444,11 +8440,7 @@
       <c r="P104" t="inlineStr"/>
       <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr"/>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S104" t="inlineStr"/>
       <c r="T104" t="inlineStr">
         <is>
           <t>x</t>
@@ -8457,12 +8449,12 @@
       <c r="U104" t="inlineStr"/>
       <c r="V104" t="inlineStr">
         <is>
-          <t>BupTmDr</t>
+          <t>BupTmBk</t>
         </is>
       </c>
       <c r="W104" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Buprenorphine Provider</t>
+          <t>Biking Time (min) to nearest Buprenorphine Provider</t>
         </is>
       </c>
       <c r="X104" t="inlineStr"/>
@@ -8507,7 +8499,11 @@
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr"/>
       <c r="Q105" t="inlineStr"/>
@@ -8525,12 +8521,12 @@
       <c r="U105" t="inlineStr"/>
       <c r="V105" t="inlineStr">
         <is>
-          <t>BupTmDr2</t>
+          <t>BupTmDr</t>
         </is>
       </c>
       <c r="W105" t="inlineStr">
         <is>
-          <t>Driving time to nearest buprenorphine provider (with impedance)</t>
+          <t>Driving Time (min) to nearest Buprenorphine Provider</t>
         </is>
       </c>
       <c r="X105" t="inlineStr"/>
@@ -8575,16 +8571,16 @@
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr"/>
       <c r="P106" t="inlineStr"/>
       <c r="Q106" t="inlineStr"/>
       <c r="R106" t="inlineStr"/>
-      <c r="S106" t="inlineStr"/>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T106" t="inlineStr">
         <is>
           <t>x</t>
@@ -8593,12 +8589,12 @@
       <c r="U106" t="inlineStr"/>
       <c r="V106" t="inlineStr">
         <is>
-          <t>BupTmWk</t>
+          <t>BupTmDr2</t>
         </is>
       </c>
       <c r="W106" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Buprenorphine Provider</t>
+          <t>Driving time to nearest buprenorphine provider (with impedance)</t>
         </is>
       </c>
       <c r="X106" t="inlineStr"/>
@@ -8653,16 +8649,20 @@
       <c r="Q107" t="inlineStr"/>
       <c r="R107" t="inlineStr"/>
       <c r="S107" t="inlineStr"/>
-      <c r="T107" t="inlineStr"/>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U107" t="inlineStr"/>
       <c r="V107" t="inlineStr">
         <is>
-          <t>MetCntBk30</t>
+          <t>BupTmWk</t>
         </is>
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>Count of methadone providers (30-min bike)</t>
+          <t>Walking Time (min) to nearest Buprenorphine Provider</t>
         </is>
       </c>
       <c r="X107" t="inlineStr"/>
@@ -8721,12 +8721,12 @@
       <c r="U108" t="inlineStr"/>
       <c r="V108" t="inlineStr">
         <is>
-          <t>MetCntBk60</t>
+          <t>MetCntBk30</t>
         </is>
       </c>
       <c r="W108" t="inlineStr">
         <is>
-          <t>Count of Methadone Providers (60-min bike)</t>
+          <t>Count of methadone providers (30-min bike)</t>
         </is>
       </c>
       <c r="X108" t="inlineStr"/>
@@ -8780,21 +8780,17 @@
       <c r="P109" t="inlineStr"/>
       <c r="Q109" t="inlineStr"/>
       <c r="R109" t="inlineStr"/>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S109" t="inlineStr"/>
       <c r="T109" t="inlineStr"/>
       <c r="U109" t="inlineStr"/>
       <c r="V109" t="inlineStr">
         <is>
-          <t>MetCntDr30</t>
+          <t>MetCntBk60</t>
         </is>
       </c>
       <c r="W109" t="inlineStr">
         <is>
-          <t>Count of Methadone Providers (30-min drive)</t>
+          <t>Count of Methadone Providers (60-min bike)</t>
         </is>
       </c>
       <c r="X109" t="inlineStr"/>
@@ -8848,17 +8844,21 @@
       <c r="P110" t="inlineStr"/>
       <c r="Q110" t="inlineStr"/>
       <c r="R110" t="inlineStr"/>
-      <c r="S110" t="inlineStr"/>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T110" t="inlineStr"/>
       <c r="U110" t="inlineStr"/>
       <c r="V110" t="inlineStr">
         <is>
-          <t>MetCntWk30</t>
+          <t>MetCntDr30</t>
         </is>
       </c>
       <c r="W110" t="inlineStr">
         <is>
-          <t>Count of Methadone Providers (60-min walk)</t>
+          <t>Count of Methadone Providers (30-min drive)</t>
         </is>
       </c>
       <c r="X110" t="inlineStr"/>
@@ -8917,12 +8917,12 @@
       <c r="U111" t="inlineStr"/>
       <c r="V111" t="inlineStr">
         <is>
-          <t>MetCntWk60</t>
+          <t>MetCntWk30</t>
         </is>
       </c>
       <c r="W111" t="inlineStr">
         <is>
-          <t>Count of Methadone Providers (30-min walk)</t>
+          <t>Count of Methadone Providers (60-min walk)</t>
         </is>
       </c>
       <c r="X111" t="inlineStr"/>
@@ -8981,12 +8981,12 @@
       <c r="U112" t="inlineStr"/>
       <c r="V112" t="inlineStr">
         <is>
-          <t>MetMinDis</t>
+          <t>MetCntWk60</t>
         </is>
       </c>
       <c r="W112" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Methadone Provider</t>
+          <t>Count of Methadone Providers (30-min walk)</t>
         </is>
       </c>
       <c r="X112" t="inlineStr"/>
@@ -9020,26 +9020,10 @@
           <t>Spatial Access to MOUDs</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr"/>
@@ -9061,12 +9045,12 @@
       <c r="U113" t="inlineStr"/>
       <c r="V113" t="inlineStr">
         <is>
-          <t>MetRm30</t>
+          <t>MetMinDis</t>
         </is>
       </c>
       <c r="W113" t="inlineStr">
         <is>
-          <t>Methadone access 30 minutes (RAAM)</t>
+          <t>Distance (mi) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X113" t="inlineStr"/>
@@ -9141,12 +9125,12 @@
       <c r="U114" t="inlineStr"/>
       <c r="V114" t="inlineStr">
         <is>
-          <t>MetRm60</t>
+          <t>MetRm30</t>
         </is>
       </c>
       <c r="W114" t="inlineStr">
         <is>
-          <t>Methadone access 60 minutes (RAAM)</t>
+          <t>Methadone access 30 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X114" t="inlineStr"/>
@@ -9221,12 +9205,12 @@
       <c r="U115" t="inlineStr"/>
       <c r="V115" t="inlineStr">
         <is>
-          <t>MetRm90</t>
+          <t>MetRm60</t>
         </is>
       </c>
       <c r="W115" t="inlineStr">
         <is>
-          <t>Methadone access 90 minutes (RAAM)</t>
+          <t>Methadone access 60 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X115" t="inlineStr"/>
@@ -9260,10 +9244,26 @@
           <t>Spatial Access to MOUDs</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr"/>
-      <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr"/>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr"/>
@@ -9281,20 +9281,16 @@
       <c r="Q116" t="inlineStr"/>
       <c r="R116" t="inlineStr"/>
       <c r="S116" t="inlineStr"/>
-      <c r="T116" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T116" t="inlineStr"/>
       <c r="U116" t="inlineStr"/>
       <c r="V116" t="inlineStr">
         <is>
-          <t>MetTmBk</t>
+          <t>MetRm90</t>
         </is>
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>Biking Time (min) to nearest Methadone Provider</t>
+          <t>Methadone access 90 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X116" t="inlineStr"/>
@@ -9348,11 +9344,7 @@
       <c r="P117" t="inlineStr"/>
       <c r="Q117" t="inlineStr"/>
       <c r="R117" t="inlineStr"/>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S117" t="inlineStr"/>
       <c r="T117" t="inlineStr">
         <is>
           <t>x</t>
@@ -9361,12 +9353,12 @@
       <c r="U117" t="inlineStr"/>
       <c r="V117" t="inlineStr">
         <is>
-          <t>MetTmDr</t>
+          <t>MetTmBk</t>
         </is>
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Methadone Provider</t>
+          <t>Biking Time (min) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X117" t="inlineStr"/>
@@ -9411,7 +9403,11 @@
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="inlineStr"/>
       <c r="Q118" t="inlineStr"/>
@@ -9429,12 +9425,12 @@
       <c r="U118" t="inlineStr"/>
       <c r="V118" t="inlineStr">
         <is>
-          <t>MetTmDr2</t>
+          <t>MetTmDr</t>
         </is>
       </c>
       <c r="W118" t="inlineStr">
         <is>
-          <t>Driving time to nearest methadone provider (with impedance)</t>
+          <t>Driving Time (min) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X118" t="inlineStr"/>
@@ -9479,16 +9475,16 @@
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr"/>
       <c r="P119" t="inlineStr"/>
       <c r="Q119" t="inlineStr"/>
       <c r="R119" t="inlineStr"/>
-      <c r="S119" t="inlineStr"/>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T119" t="inlineStr">
         <is>
           <t>x</t>
@@ -9497,12 +9493,12 @@
       <c r="U119" t="inlineStr"/>
       <c r="V119" t="inlineStr">
         <is>
-          <t>MetTmWk</t>
+          <t>MetTmDr2</t>
         </is>
       </c>
       <c r="W119" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Methadone Provider</t>
+          <t>Driving time to nearest methadone provider (with impedance)</t>
         </is>
       </c>
       <c r="X119" t="inlineStr"/>
@@ -9557,16 +9553,20 @@
       <c r="Q120" t="inlineStr"/>
       <c r="R120" t="inlineStr"/>
       <c r="S120" t="inlineStr"/>
-      <c r="T120" t="inlineStr"/>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U120" t="inlineStr"/>
       <c r="V120" t="inlineStr">
         <is>
-          <t>MoudMinDis</t>
+          <t>MetTmWk</t>
         </is>
       </c>
       <c r="W120" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest MOUD (any)</t>
+          <t>Walking Time (min) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X120" t="inlineStr"/>
@@ -9611,30 +9611,26 @@
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O121" t="inlineStr"/>
       <c r="P121" t="inlineStr"/>
       <c r="Q121" t="inlineStr"/>
       <c r="R121" t="inlineStr"/>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="T121" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S121" t="inlineStr"/>
+      <c r="T121" t="inlineStr"/>
       <c r="U121" t="inlineStr"/>
       <c r="V121" t="inlineStr">
         <is>
-          <t>MoudTyp</t>
+          <t>MoudMinDis</t>
         </is>
       </c>
       <c r="W121" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOUD Types Within 30-Min Drive  (impedance, adjusted) </t>
+          <t>Distance (mi) to nearest MOUD (any)</t>
         </is>
       </c>
       <c r="X121" t="inlineStr"/>
@@ -9679,26 +9675,30 @@
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr"/>
       <c r="P122" t="inlineStr"/>
       <c r="Q122" t="inlineStr"/>
       <c r="R122" t="inlineStr"/>
-      <c r="S122" t="inlineStr"/>
-      <c r="T122" t="inlineStr"/>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U122" t="inlineStr"/>
       <c r="V122" t="inlineStr">
         <is>
-          <t>NaltCntBk30</t>
+          <t>MoudTyp</t>
         </is>
       </c>
       <c r="W122" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (30-min bike)</t>
+          <t xml:space="preserve">MOUD Types Within 30-Min Drive  (impedance, adjusted) </t>
         </is>
       </c>
       <c r="X122" t="inlineStr"/>
@@ -9757,12 +9757,12 @@
       <c r="U123" t="inlineStr"/>
       <c r="V123" t="inlineStr">
         <is>
-          <t>NaltCntBk60</t>
+          <t>NaltCntBk30</t>
         </is>
       </c>
       <c r="W123" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (60-min bike)</t>
+          <t>Count of Naltrexone Providers (30-min bike)</t>
         </is>
       </c>
       <c r="X123" t="inlineStr"/>
@@ -9816,21 +9816,17 @@
       <c r="P124" t="inlineStr"/>
       <c r="Q124" t="inlineStr"/>
       <c r="R124" t="inlineStr"/>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S124" t="inlineStr"/>
       <c r="T124" t="inlineStr"/>
       <c r="U124" t="inlineStr"/>
       <c r="V124" t="inlineStr">
         <is>
-          <t>NaltCntDr30</t>
+          <t>NaltCntBk60</t>
         </is>
       </c>
       <c r="W124" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (30-min drive)</t>
+          <t>Count of Naltrexone Providers (60-min bike)</t>
         </is>
       </c>
       <c r="X124" t="inlineStr"/>
@@ -9884,17 +9880,21 @@
       <c r="P125" t="inlineStr"/>
       <c r="Q125" t="inlineStr"/>
       <c r="R125" t="inlineStr"/>
-      <c r="S125" t="inlineStr"/>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T125" t="inlineStr"/>
       <c r="U125" t="inlineStr"/>
       <c r="V125" t="inlineStr">
         <is>
-          <t>NaltCntWk30</t>
+          <t>NaltCntDr30</t>
         </is>
       </c>
       <c r="W125" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (30-min walk)</t>
+          <t>Count of Naltrexone Providers (30-min drive)</t>
         </is>
       </c>
       <c r="X125" t="inlineStr"/>
@@ -9953,12 +9953,12 @@
       <c r="U126" t="inlineStr"/>
       <c r="V126" t="inlineStr">
         <is>
-          <t>NaltCntWk60</t>
+          <t>NaltCntWk30</t>
         </is>
       </c>
       <c r="W126" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (60-min walk)</t>
+          <t>Count of Naltrexone Providers (30-min walk)</t>
         </is>
       </c>
       <c r="X126" t="inlineStr"/>
@@ -10017,12 +10017,12 @@
       <c r="U127" t="inlineStr"/>
       <c r="V127" t="inlineStr">
         <is>
-          <t>NaltMinDis</t>
+          <t>NaltCntWk60</t>
         </is>
       </c>
       <c r="W127" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Naltrexone Provider</t>
+          <t>Count of Naltrexone Providers (60-min walk)</t>
         </is>
       </c>
       <c r="X127" t="inlineStr"/>
@@ -10081,12 +10081,12 @@
       <c r="U128" t="inlineStr"/>
       <c r="V128" t="inlineStr">
         <is>
-          <t>NaltRm30</t>
+          <t>NaltMinDis</t>
         </is>
       </c>
       <c r="W128" t="inlineStr">
         <is>
-          <t>Naltrexone access 30 minutes (RAAM)</t>
+          <t>Distance (mi) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X128" t="inlineStr"/>
@@ -10145,12 +10145,12 @@
       <c r="U129" t="inlineStr"/>
       <c r="V129" t="inlineStr">
         <is>
-          <t>NaltRm60</t>
+          <t>NaltRm30</t>
         </is>
       </c>
       <c r="W129" t="inlineStr">
         <is>
-          <t>Naltrexone access 60 minutes (RAAM)</t>
+          <t>Naltrexone access 30 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X129" t="inlineStr"/>
@@ -10209,12 +10209,12 @@
       <c r="U130" t="inlineStr"/>
       <c r="V130" t="inlineStr">
         <is>
-          <t>NaltRm90</t>
+          <t>NaltRm60</t>
         </is>
       </c>
       <c r="W130" t="inlineStr">
         <is>
-          <t>Naltrexone access 90 minutes (RAAM)</t>
+          <t>Naltrexone access 60 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X130" t="inlineStr"/>
@@ -10269,20 +10269,16 @@
       <c r="Q131" t="inlineStr"/>
       <c r="R131" t="inlineStr"/>
       <c r="S131" t="inlineStr"/>
-      <c r="T131" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T131" t="inlineStr"/>
       <c r="U131" t="inlineStr"/>
       <c r="V131" t="inlineStr">
         <is>
-          <t>NaltTmBk</t>
+          <t>NaltRm90</t>
         </is>
       </c>
       <c r="W131" t="inlineStr">
         <is>
-          <t>Biking Time (min) to nearest Naltrexone Provider</t>
+          <t>Naltrexone access 90 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X131" t="inlineStr"/>
@@ -10336,11 +10332,7 @@
       <c r="P132" t="inlineStr"/>
       <c r="Q132" t="inlineStr"/>
       <c r="R132" t="inlineStr"/>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S132" t="inlineStr"/>
       <c r="T132" t="inlineStr">
         <is>
           <t>x</t>
@@ -10349,12 +10341,12 @@
       <c r="U132" t="inlineStr"/>
       <c r="V132" t="inlineStr">
         <is>
-          <t>NaltTmDr</t>
+          <t>NaltTmBk</t>
         </is>
       </c>
       <c r="W132" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Naltrexone Provider</t>
+          <t>Biking Time (min) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X132" t="inlineStr"/>
@@ -10399,7 +10391,11 @@
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O133" t="inlineStr"/>
       <c r="P133" t="inlineStr"/>
       <c r="Q133" t="inlineStr"/>
@@ -10409,16 +10405,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T133" t="inlineStr"/>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U133" t="inlineStr"/>
       <c r="V133" t="inlineStr">
         <is>
-          <t>NaltTmDr2</t>
+          <t>NaltTmDr</t>
         </is>
       </c>
       <c r="W133" t="inlineStr">
         <is>
-          <t>Driving time to nearest naltrexone provider (with impedance)</t>
+          <t>Driving Time (min) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X133" t="inlineStr"/>
@@ -10463,30 +10463,26 @@
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr"/>
       <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr"/>
       <c r="P134" t="inlineStr"/>
       <c r="Q134" t="inlineStr"/>
       <c r="R134" t="inlineStr"/>
-      <c r="S134" t="inlineStr"/>
-      <c r="T134" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr"/>
       <c r="U134" t="inlineStr"/>
       <c r="V134" t="inlineStr">
         <is>
-          <t>NaltTmWk</t>
+          <t>NaltTmDr2</t>
         </is>
       </c>
       <c r="W134" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Naltrexone Provider</t>
+          <t>Driving time to nearest naltrexone provider (with impedance)</t>
         </is>
       </c>
       <c r="X134" t="inlineStr"/>
@@ -10531,30 +10527,30 @@
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr"/>
       <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
-      <c r="O135" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr"/>
       <c r="P135" t="inlineStr"/>
       <c r="Q135" t="inlineStr"/>
       <c r="R135" t="inlineStr"/>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="T135" t="inlineStr"/>
+      <c r="S135" t="inlineStr"/>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U135" t="inlineStr"/>
       <c r="V135" t="inlineStr">
         <is>
-          <t>OtpCntDr</t>
+          <t>NaltTmWk</t>
         </is>
       </c>
       <c r="W135" t="inlineStr">
         <is>
-          <t>Count of Opioid Treatment Programs (OTP) (30-min drive)</t>
+          <t>Walking Time (min) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X135" t="inlineStr"/>
@@ -10608,17 +10604,21 @@
       <c r="P136" t="inlineStr"/>
       <c r="Q136" t="inlineStr"/>
       <c r="R136" t="inlineStr"/>
-      <c r="S136" t="inlineStr"/>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T136" t="inlineStr"/>
       <c r="U136" t="inlineStr"/>
       <c r="V136" t="inlineStr">
         <is>
-          <t>OtpMinDis</t>
+          <t>OtpCntDr</t>
         </is>
       </c>
       <c r="W136" t="inlineStr">
         <is>
-          <t>Distance to nearest OTP</t>
+          <t>Count of Opioid Treatment Programs (OTP) (30-min drive)</t>
         </is>
       </c>
       <c r="X136" t="inlineStr"/>
@@ -10672,25 +10672,17 @@
       <c r="P137" t="inlineStr"/>
       <c r="Q137" t="inlineStr"/>
       <c r="R137" t="inlineStr"/>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="T137" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S137" t="inlineStr"/>
+      <c r="T137" t="inlineStr"/>
       <c r="U137" t="inlineStr"/>
       <c r="V137" t="inlineStr">
         <is>
-          <t>OtpTmDr</t>
+          <t>OtpMinDis</t>
         </is>
       </c>
       <c r="W137" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP)</t>
+          <t>Distance to nearest OTP</t>
         </is>
       </c>
       <c r="X137" t="inlineStr"/>
@@ -10736,7 +10728,11 @@
       <c r="L138" t="inlineStr"/>
       <c r="M138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
-      <c r="O138" t="inlineStr"/>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr"/>
       <c r="Q138" t="inlineStr"/>
       <c r="R138" t="inlineStr"/>
@@ -10745,16 +10741,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T138" t="inlineStr"/>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U138" t="inlineStr"/>
       <c r="V138" t="inlineStr">
         <is>
-          <t>OtpTmDr2</t>
+          <t>OtpTmDr</t>
         </is>
       </c>
       <c r="W138" t="inlineStr">
         <is>
-          <t>Driving time to nearest OTP (impedance-adjusted)</t>
+          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP)</t>
         </is>
       </c>
       <c r="X138" t="inlineStr"/>
@@ -10785,7 +10785,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -10799,42 +10799,42 @@
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr"/>
       <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr"/>
       <c r="P139" t="inlineStr"/>
       <c r="Q139" t="inlineStr"/>
       <c r="R139" t="inlineStr"/>
-      <c r="S139" t="inlineStr"/>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T139" t="inlineStr"/>
       <c r="U139" t="inlineStr"/>
       <c r="V139" t="inlineStr">
         <is>
-          <t>MhCntDr</t>
+          <t>OtpTmDr2</t>
         </is>
       </c>
       <c r="W139" t="inlineStr">
         <is>
-          <t>Count of Mental Health Providers (30-min drive)</t>
+          <t>Driving time to nearest OTP (impedance-adjusted)</t>
         </is>
       </c>
       <c r="X139" t="inlineStr"/>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr"/>
@@ -10877,12 +10877,12 @@
       <c r="U140" t="inlineStr"/>
       <c r="V140" t="inlineStr">
         <is>
-          <t>MhMinDis</t>
+          <t>MhCntDr</t>
         </is>
       </c>
       <c r="W140" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Mental Health Provider</t>
+          <t>Count of Mental Health Providers (30-min drive)</t>
         </is>
       </c>
       <c r="X140" t="inlineStr"/>
@@ -10937,20 +10937,16 @@
       <c r="Q141" t="inlineStr"/>
       <c r="R141" t="inlineStr"/>
       <c r="S141" t="inlineStr"/>
-      <c r="T141" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T141" t="inlineStr"/>
       <c r="U141" t="inlineStr"/>
       <c r="V141" t="inlineStr">
         <is>
-          <t>MhTmDr</t>
+          <t>MhMinDis</t>
         </is>
       </c>
       <c r="W141" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Mental Health Provider</t>
+          <t>Distance (mi) to nearest Mental Health Provider</t>
         </is>
       </c>
       <c r="X141" t="inlineStr"/>
@@ -10981,7 +10977,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -10994,43 +10990,47 @@
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N142" t="inlineStr"/>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O142" t="inlineStr"/>
       <c r="P142" t="inlineStr"/>
       <c r="Q142" t="inlineStr"/>
       <c r="R142" t="inlineStr"/>
       <c r="S142" t="inlineStr"/>
-      <c r="T142" t="inlineStr"/>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U142" t="inlineStr"/>
       <c r="V142" t="inlineStr">
         <is>
-          <t>RxCntDr</t>
+          <t>MhTmDr</t>
         </is>
       </c>
       <c r="W142" t="inlineStr">
         <is>
-          <t>Count of Pharmacies (30-min drive)</t>
+          <t>Driving Time (min) to nearest Mental Health Provider</t>
         </is>
       </c>
       <c r="X142" t="inlineStr"/>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>InfoGroup 2019</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB142" t="inlineStr"/>
@@ -11068,17 +11068,21 @@
       <c r="P143" t="inlineStr"/>
       <c r="Q143" t="inlineStr"/>
       <c r="R143" t="inlineStr"/>
-      <c r="S143" t="inlineStr"/>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T143" t="inlineStr"/>
       <c r="U143" t="inlineStr"/>
       <c r="V143" t="inlineStr">
         <is>
-          <t>RxMinDis</t>
+          <t>RxCntDr</t>
         </is>
       </c>
       <c r="W143" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Pharmacy</t>
+          <t>Count of Pharmacies (30-min drive)</t>
         </is>
       </c>
       <c r="X143" t="inlineStr"/>
@@ -11089,12 +11093,12 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>InfoGroup 2019</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB143" t="inlineStr"/>
@@ -11133,20 +11137,16 @@
       <c r="Q144" t="inlineStr"/>
       <c r="R144" t="inlineStr"/>
       <c r="S144" t="inlineStr"/>
-      <c r="T144" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T144" t="inlineStr"/>
       <c r="U144" t="inlineStr"/>
       <c r="V144" t="inlineStr">
         <is>
-          <t>RxTmDr</t>
+          <t>RxMinDis</t>
         </is>
       </c>
       <c r="W144" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Pharmacy</t>
+          <t>Distance (mi) to nearest Pharmacy</t>
         </is>
       </c>
       <c r="X144" t="inlineStr"/>
@@ -11157,12 +11157,12 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>InfoGroup 2019</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr"/>
@@ -11177,7 +11177,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -11190,43 +11190,51 @@
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr"/>
-      <c r="N145" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr"/>
       <c r="O145" t="inlineStr"/>
       <c r="P145" t="inlineStr"/>
       <c r="Q145" t="inlineStr"/>
       <c r="R145" t="inlineStr"/>
-      <c r="S145" t="inlineStr"/>
-      <c r="T145" t="inlineStr"/>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U145" t="inlineStr"/>
       <c r="V145" t="inlineStr">
         <is>
-          <t>SutCntDr</t>
+          <t>RxTmDr</t>
         </is>
       </c>
       <c r="W145" t="inlineStr">
         <is>
-          <t>Count of Substance Use Treatment (SUT) facility (30-min drive)</t>
+          <t>Driving Time (min) to nearest Pharmacy</t>
         </is>
       </c>
       <c r="X145" t="inlineStr"/>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr"/>
@@ -11241,7 +11249,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -11255,42 +11263,42 @@
       <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr"/>
       <c r="M146" t="inlineStr"/>
-      <c r="N146" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N146" t="inlineStr"/>
       <c r="O146" t="inlineStr"/>
       <c r="P146" t="inlineStr"/>
       <c r="Q146" t="inlineStr"/>
       <c r="R146" t="inlineStr"/>
-      <c r="S146" t="inlineStr"/>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T146" t="inlineStr"/>
       <c r="U146" t="inlineStr"/>
       <c r="V146" t="inlineStr">
         <is>
-          <t>SutMinDis</t>
+          <t>RxTmDr2</t>
         </is>
       </c>
       <c r="W146" t="inlineStr">
         <is>
-          <t>Distance (mi) to Substance Use Treatment (SUT) facility</t>
+          <t>Driving Time (min) to nearest Pharmacy with Impedance Factor</t>
         </is>
       </c>
       <c r="X146" t="inlineStr"/>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr"/>
@@ -11329,20 +11337,16 @@
       <c r="Q147" t="inlineStr"/>
       <c r="R147" t="inlineStr"/>
       <c r="S147" t="inlineStr"/>
-      <c r="T147" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T147" t="inlineStr"/>
       <c r="U147" t="inlineStr"/>
       <c r="V147" t="inlineStr">
         <is>
-          <t>SutTmDr</t>
+          <t>SutCntDr</t>
         </is>
       </c>
       <c r="W147" t="inlineStr">
         <is>
-          <t>Driving time (min) to Substance Use Treatment (SUT) facility</t>
+          <t>Count of Substance Use Treatment (SUT) facility (30-min drive)</t>
         </is>
       </c>
       <c r="X147" t="inlineStr"/>
@@ -11373,7 +11377,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
@@ -11396,37 +11400,33 @@
       <c r="P148" t="inlineStr"/>
       <c r="Q148" t="inlineStr"/>
       <c r="R148" t="inlineStr"/>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S148" t="inlineStr"/>
       <c r="T148" t="inlineStr"/>
       <c r="U148" t="inlineStr"/>
       <c r="V148" t="inlineStr">
         <is>
-          <t>FqhcCntDr</t>
+          <t>SutMinDis</t>
         </is>
       </c>
       <c r="W148" t="inlineStr">
         <is>
-          <t>Count of Federally Qualified Health Centers (FQHCs) within 30-min drive</t>
+          <t>Distance (mi) to Substance Use Treatment (SUT) facility</t>
         </is>
       </c>
       <c r="X148" t="inlineStr"/>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr"/>
@@ -11441,7 +11441,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -11465,32 +11465,36 @@
       <c r="Q149" t="inlineStr"/>
       <c r="R149" t="inlineStr"/>
       <c r="S149" t="inlineStr"/>
-      <c r="T149" t="inlineStr"/>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U149" t="inlineStr"/>
       <c r="V149" t="inlineStr">
         <is>
-          <t>FqhcMinDis</t>
+          <t>SutTmDr</t>
         </is>
       </c>
       <c r="W149" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Federally Qualified Health Centers (FQHC)</t>
+          <t>Driving time (min) to Substance Use Treatment (SUT) facility</t>
         </is>
       </c>
       <c r="X149" t="inlineStr"/>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr"/>
@@ -11533,20 +11537,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T150" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T150" t="inlineStr"/>
       <c r="U150" t="inlineStr"/>
       <c r="V150" t="inlineStr">
         <is>
-          <t>FqhcTmDr</t>
+          <t>FqhcCntDr</t>
         </is>
       </c>
       <c r="W150" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC)</t>
+          <t>Count of Federally Qualified Health Centers (FQHCs) within 30-min drive</t>
         </is>
       </c>
       <c r="X150" t="inlineStr"/>
@@ -11591,30 +11591,26 @@
       <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr"/>
       <c r="M151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O151" t="inlineStr"/>
       <c r="P151" t="inlineStr"/>
       <c r="Q151" t="inlineStr"/>
       <c r="R151" t="inlineStr"/>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="T151" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S151" t="inlineStr"/>
+      <c r="T151" t="inlineStr"/>
       <c r="U151" t="inlineStr"/>
       <c r="V151" t="inlineStr">
         <is>
-          <t>FqhcTmDr2</t>
+          <t>FqhcMinDis</t>
         </is>
       </c>
       <c r="W151" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC), with Impedance factor</t>
+          <t>Distance (mi) to nearest Federally Qualified Health Centers (FQHC)</t>
         </is>
       </c>
       <c r="X151" t="inlineStr"/>
@@ -11645,17 +11641,13 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr"/>
@@ -11663,38 +11655,50 @@
       <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr"/>
       <c r="M152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O152" t="inlineStr"/>
       <c r="P152" t="inlineStr"/>
       <c r="Q152" t="inlineStr"/>
       <c r="R152" t="inlineStr"/>
-      <c r="S152" t="inlineStr"/>
-      <c r="T152" t="inlineStr"/>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U152" t="inlineStr"/>
       <c r="V152" t="inlineStr">
         <is>
-          <t>Ruca1</t>
+          <t>FqhcTmDr</t>
         </is>
       </c>
       <c r="W152" t="inlineStr">
         <is>
-          <t>Primary RUCA Code</t>
+          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC)</t>
         </is>
       </c>
       <c r="X152" t="inlineStr"/>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB152" t="inlineStr"/>
@@ -11709,17 +11713,13 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr"/>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr"/>
@@ -11732,33 +11732,41 @@
       <c r="P153" t="inlineStr"/>
       <c r="Q153" t="inlineStr"/>
       <c r="R153" t="inlineStr"/>
-      <c r="S153" t="inlineStr"/>
-      <c r="T153" t="inlineStr"/>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U153" t="inlineStr"/>
       <c r="V153" t="inlineStr">
         <is>
-          <t>Ruca2</t>
+          <t>FqhcTmDr2</t>
         </is>
       </c>
       <c r="W153" t="inlineStr">
         <is>
-          <t>Secondary RUCA Code</t>
+          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC), with Impedance factor</t>
         </is>
       </c>
       <c r="X153" t="inlineStr"/>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB153" t="inlineStr"/>
@@ -11797,20 +11805,16 @@
       <c r="Q154" t="inlineStr"/>
       <c r="R154" t="inlineStr"/>
       <c r="S154" t="inlineStr"/>
-      <c r="T154" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T154" t="inlineStr"/>
       <c r="U154" t="inlineStr"/>
       <c r="V154" t="inlineStr">
         <is>
-          <t>Rurality</t>
+          <t>Ruca1</t>
         </is>
       </c>
       <c r="W154" t="inlineStr">
         <is>
-          <t>Urban-Suburban-Rural</t>
+          <t>Primary RUCA Code</t>
         </is>
       </c>
       <c r="X154" t="inlineStr"/>
@@ -11836,28 +11840,28 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr"/>
-      <c r="F155" t="inlineStr"/>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L155" t="inlineStr"/>
       <c r="M155" t="inlineStr"/>
       <c r="N155" t="inlineStr"/>
       <c r="O155" t="inlineStr"/>
@@ -11869,28 +11873,28 @@
       <c r="U155" t="inlineStr"/>
       <c r="V155" t="inlineStr">
         <is>
-          <t>EssnWrkE</t>
+          <t>Ruca2</t>
         </is>
       </c>
       <c r="W155" t="inlineStr">
         <is>
-          <t>Count of Essential Workers</t>
+          <t>Secondary RUCA Code</t>
         </is>
       </c>
       <c r="X155" t="inlineStr"/>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB155" t="inlineStr"/>
@@ -11900,69 +11904,65 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr"/>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L156" t="inlineStr"/>
       <c r="M156" t="inlineStr"/>
-      <c r="N156" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N156" t="inlineStr"/>
       <c r="O156" t="inlineStr"/>
       <c r="P156" t="inlineStr"/>
-      <c r="Q156" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q156" t="inlineStr"/>
       <c r="R156" t="inlineStr"/>
       <c r="S156" t="inlineStr"/>
-      <c r="T156" t="inlineStr"/>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U156" t="inlineStr"/>
       <c r="V156" t="inlineStr">
         <is>
-          <t>EssnWrkP</t>
+          <t>Rurality</t>
         </is>
       </c>
       <c r="W156" t="inlineStr">
         <is>
-          <t>Essential Workers %</t>
+          <t>Urban-Suburban-Rural</t>
         </is>
       </c>
       <c r="X156" t="inlineStr"/>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB156" t="inlineStr"/>
@@ -11995,30 +11995,22 @@
         </is>
       </c>
       <c r="M157" t="inlineStr"/>
-      <c r="N157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N157" t="inlineStr"/>
       <c r="O157" t="inlineStr"/>
       <c r="P157" t="inlineStr"/>
-      <c r="Q157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q157" t="inlineStr"/>
       <c r="R157" t="inlineStr"/>
       <c r="S157" t="inlineStr"/>
       <c r="T157" t="inlineStr"/>
       <c r="U157" t="inlineStr"/>
       <c r="V157" t="inlineStr">
         <is>
-          <t>HghRskP</t>
+          <t>EssnWrkE</t>
         </is>
       </c>
       <c r="W157" t="inlineStr">
         <is>
-          <t>Employed % - High Risk of Injury</t>
+          <t>Count of Essential Workers</t>
         </is>
       </c>
       <c r="X157" t="inlineStr"/>
@@ -12085,12 +12077,12 @@
       <c r="U158" t="inlineStr"/>
       <c r="V158" t="inlineStr">
         <is>
-          <t>HltCrP</t>
+          <t>EssnWrkP</t>
         </is>
       </c>
       <c r="W158" t="inlineStr">
         <is>
-          <t>Employed % - Health Care</t>
+          <t>Essential Workers %</t>
         </is>
       </c>
       <c r="X158" t="inlineStr"/>
@@ -12157,12 +12149,12 @@
       <c r="U159" t="inlineStr"/>
       <c r="V159" t="inlineStr">
         <is>
-          <t>RetailP</t>
+          <t>HghRskP</t>
         </is>
       </c>
       <c r="W159" t="inlineStr">
         <is>
-          <t>Employed % - Retail</t>
+          <t>Employed % - High Risk of Injury</t>
         </is>
       </c>
       <c r="X159" t="inlineStr"/>
@@ -12229,12 +12221,12 @@
       <c r="U160" t="inlineStr"/>
       <c r="V160" t="inlineStr">
         <is>
-          <t>TotWrkE</t>
+          <t>HltCrP</t>
         </is>
       </c>
       <c r="W160" t="inlineStr">
         <is>
-          <t>Count of Working Population</t>
+          <t>Employed % - Health Care</t>
         </is>
       </c>
       <c r="X160" t="inlineStr"/>
@@ -12265,7 +12257,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
@@ -12283,38 +12275,46 @@
         </is>
       </c>
       <c r="M161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O161" t="inlineStr"/>
       <c r="P161" t="inlineStr"/>
-      <c r="Q161" t="inlineStr"/>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R161" t="inlineStr"/>
       <c r="S161" t="inlineStr"/>
       <c r="T161" t="inlineStr"/>
       <c r="U161" t="inlineStr"/>
       <c r="V161" t="inlineStr">
         <is>
-          <t>ForDqP</t>
+          <t>RetailP</t>
         </is>
       </c>
       <c r="W161" t="inlineStr">
         <is>
-          <t>Foreclosure &amp; Delinquency %</t>
+          <t>Employed % - Retail</t>
         </is>
       </c>
       <c r="X161" t="inlineStr"/>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB161" t="inlineStr"/>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
@@ -12347,38 +12347,46 @@
         </is>
       </c>
       <c r="M162" t="inlineStr"/>
-      <c r="N162" t="inlineStr"/>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O162" t="inlineStr"/>
       <c r="P162" t="inlineStr"/>
-      <c r="Q162" t="inlineStr"/>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R162" t="inlineStr"/>
       <c r="S162" t="inlineStr"/>
       <c r="T162" t="inlineStr"/>
       <c r="U162" t="inlineStr"/>
       <c r="V162" t="inlineStr">
         <is>
-          <t>ForDqTot</t>
+          <t>TotWrkE</t>
         </is>
       </c>
       <c r="W162" t="inlineStr">
         <is>
-          <t>Foreclosure &amp; Delinquency Count</t>
+          <t>Count of Working Population</t>
         </is>
       </c>
       <c r="X162" t="inlineStr"/>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB162" t="inlineStr"/>
@@ -12399,11 +12407,7 @@
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr"/>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr"/>
@@ -12415,30 +12419,22 @@
         </is>
       </c>
       <c r="M163" t="inlineStr"/>
-      <c r="N163" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N163" t="inlineStr"/>
       <c r="O163" t="inlineStr"/>
       <c r="P163" t="inlineStr"/>
-      <c r="Q163" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q163" t="inlineStr"/>
       <c r="R163" t="inlineStr"/>
       <c r="S163" t="inlineStr"/>
       <c r="T163" t="inlineStr"/>
       <c r="U163" t="inlineStr"/>
       <c r="V163" t="inlineStr">
         <is>
-          <t>GiniCoeff</t>
+          <t>ForDqP</t>
         </is>
       </c>
       <c r="W163" t="inlineStr">
         <is>
-          <t>Income Inequality (Gini Coefficient)</t>
+          <t>Foreclosure &amp; Delinquency %</t>
         </is>
       </c>
       <c r="X163" t="inlineStr"/>
@@ -12469,7 +12465,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Internet Access</t>
+          <t>Great Recession Foreclosure Rate</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
@@ -12481,12 +12477,12 @@
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr"/>
-      <c r="L164" t="inlineStr"/>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr"/>
       <c r="N164" t="inlineStr"/>
       <c r="O164" t="inlineStr"/>
       <c r="P164" t="inlineStr"/>
@@ -12497,28 +12493,28 @@
       <c r="U164" t="inlineStr"/>
       <c r="V164" t="inlineStr">
         <is>
-          <t>NoIntP</t>
+          <t>ForDqTot</t>
         </is>
       </c>
       <c r="W164" t="inlineStr">
         <is>
-          <t>Households without Internet Access %</t>
+          <t>Foreclosure &amp; Delinquency Count</t>
         </is>
       </c>
       <c r="X164" t="inlineStr"/>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Internet_Access.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
         </is>
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>ACS 2019</t>
+          <t>HUD 2018; ACS 2012, 2018</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>American Community Survey 2015-2019 5-Year Estimate</t>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB164" t="inlineStr"/>
@@ -12533,7 +12529,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
+          <t>Great Recession Foreclosure Rate</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
@@ -12573,28 +12569,28 @@
       <c r="U165" t="inlineStr"/>
       <c r="V165" t="inlineStr">
         <is>
-          <t>MedInc</t>
+          <t>GiniCoeff</t>
         </is>
       </c>
       <c r="W165" t="inlineStr">
         <is>
-          <t>Median Income</t>
+          <t>Income Inequality (Gini Coefficient)</t>
         </is>
       </c>
       <c r="X165" t="inlineStr"/>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
         </is>
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>HUD 2018; ACS 2012, 2018</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB165" t="inlineStr"/>
@@ -12609,68 +12605,56 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
+          <t>Internet Access</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr"/>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F166" t="inlineStr"/>
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M166" t="inlineStr"/>
-      <c r="N166" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr"/>
       <c r="O166" t="inlineStr"/>
       <c r="P166" t="inlineStr"/>
-      <c r="Q166" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q166" t="inlineStr"/>
       <c r="R166" t="inlineStr"/>
       <c r="S166" t="inlineStr"/>
       <c r="T166" t="inlineStr"/>
       <c r="U166" t="inlineStr"/>
       <c r="V166" t="inlineStr">
         <is>
-          <t>PciE</t>
+          <t>NoIntP</t>
         </is>
       </c>
       <c r="W166" t="inlineStr">
         <is>
-          <t>Per Capita Income</t>
+          <t>Households without Internet Access %</t>
         </is>
       </c>
       <c r="X166" t="inlineStr"/>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Internet_Access.md</t>
         </is>
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>ACS 2019</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>American Community Survey 2015-2019 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB166" t="inlineStr"/>
@@ -12688,21 +12672,9 @@
           <t>Poverty, Income, Gini Coefficient</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="C167" t="inlineStr"/>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
           <t>x</t>
@@ -12734,19 +12706,15 @@
       <c r="R167" t="inlineStr"/>
       <c r="S167" t="inlineStr"/>
       <c r="T167" t="inlineStr"/>
-      <c r="U167" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="U167" t="inlineStr"/>
       <c r="V167" t="inlineStr">
         <is>
-          <t>PovP</t>
+          <t>MedInc</t>
         </is>
       </c>
       <c r="W167" t="inlineStr">
         <is>
-          <t>Poverty %</t>
+          <t>Median Income</t>
         </is>
       </c>
       <c r="X167" t="inlineStr"/>
@@ -12780,21 +12748,9 @@
           <t>Poverty, Income, Gini Coefficient</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="C168" t="inlineStr"/>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
           <t>x</t>
@@ -12826,19 +12782,15 @@
       <c r="R168" t="inlineStr"/>
       <c r="S168" t="inlineStr"/>
       <c r="T168" t="inlineStr"/>
-      <c r="U168" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="U168" t="inlineStr"/>
       <c r="V168" t="inlineStr">
         <is>
-          <t>UnempP</t>
+          <t>PciE</t>
         </is>
       </c>
       <c r="W168" t="inlineStr">
         <is>
-          <t>Unemployment %</t>
+          <t>Per Capita Income</t>
         </is>
       </c>
       <c r="X168" t="inlineStr"/>
@@ -12864,65 +12816,89 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>SDOH Indices &amp; Typology</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr"/>
-      <c r="D169" t="inlineStr"/>
-      <c r="E169" t="inlineStr"/>
-      <c r="F169" t="inlineStr"/>
+          <t>Poverty, Income, Gini Coefficient</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G169" t="inlineStr"/>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr"/>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O169" t="inlineStr"/>
       <c r="P169" t="inlineStr"/>
-      <c r="Q169" t="inlineStr"/>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R169" t="inlineStr"/>
       <c r="S169" t="inlineStr"/>
-      <c r="T169" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="U169" t="inlineStr"/>
+      <c r="T169" t="inlineStr"/>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="V169" t="inlineStr">
         <is>
-          <t>LimMobInd</t>
+          <t>PovP</t>
         </is>
       </c>
       <c r="W169" t="inlineStr">
         <is>
-          <t>Limited Moblility Index</t>
+          <t>Poverty %</t>
         </is>
       </c>
       <c r="X169" t="inlineStr"/>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB169" t="inlineStr"/>
@@ -12932,65 +12908,89 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>SDOH Indices &amp; Typology</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr"/>
-      <c r="D170" t="inlineStr"/>
-      <c r="E170" t="inlineStr"/>
-      <c r="F170" t="inlineStr"/>
+          <t>Poverty, Income, Gini Coefficient</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G170" t="inlineStr"/>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr"/>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M170" t="inlineStr"/>
-      <c r="N170" t="inlineStr"/>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O170" t="inlineStr"/>
       <c r="P170" t="inlineStr"/>
-      <c r="Q170" t="inlineStr"/>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R170" t="inlineStr"/>
       <c r="S170" t="inlineStr"/>
-      <c r="T170" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="U170" t="inlineStr"/>
+      <c r="T170" t="inlineStr"/>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="V170" t="inlineStr">
         <is>
-          <t>MicaInd</t>
+          <t>UnempP</t>
         </is>
       </c>
       <c r="W170" t="inlineStr">
         <is>
-          <t>Mixed Immigrant Cohesion and Accesibility (MICA) Index</t>
+          <t>Unemployment %</t>
         </is>
       </c>
       <c r="X170" t="inlineStr"/>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB170" t="inlineStr"/>
@@ -13029,16 +13029,20 @@
       <c r="Q171" t="inlineStr"/>
       <c r="R171" t="inlineStr"/>
       <c r="S171" t="inlineStr"/>
-      <c r="T171" t="inlineStr"/>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U171" t="inlineStr"/>
       <c r="V171" t="inlineStr">
         <is>
-          <t>NeighbTyp</t>
+          <t>LimMobInd</t>
         </is>
       </c>
       <c r="W171" t="inlineStr">
         <is>
-          <t>Neighborhood Type</t>
+          <t>Limited Moblility Index</t>
         </is>
       </c>
       <c r="X171" t="inlineStr"/>
@@ -13101,12 +13105,12 @@
       <c r="U172" t="inlineStr"/>
       <c r="V172" t="inlineStr">
         <is>
-          <t>SocEcAdvIn</t>
+          <t>MicaInd</t>
         </is>
       </c>
       <c r="W172" t="inlineStr">
         <is>
-          <t>Socioeconomic Advantage Index</t>
+          <t>Mixed Immigrant Cohesion and Accesibility (MICA) Index</t>
         </is>
       </c>
       <c r="X172" t="inlineStr"/>
@@ -13161,20 +13165,16 @@
       <c r="Q173" t="inlineStr"/>
       <c r="R173" t="inlineStr"/>
       <c r="S173" t="inlineStr"/>
-      <c r="T173" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T173" t="inlineStr"/>
       <c r="U173" t="inlineStr"/>
       <c r="V173" t="inlineStr">
         <is>
-          <t>UrbCoreInd</t>
+          <t>NeighbTyp</t>
         </is>
       </c>
       <c r="W173" t="inlineStr">
         <is>
-          <t>Urban Core Opportunity Index</t>
+          <t>Neighborhood Type</t>
         </is>
       </c>
       <c r="X173" t="inlineStr"/>
@@ -13205,7 +13205,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>SDOH Indices &amp; Typology</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
@@ -13213,56 +13213,52 @@
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr"/>
       <c r="G174" t="inlineStr"/>
-      <c r="H174" t="inlineStr"/>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr"/>
-      <c r="L174" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L174" t="inlineStr"/>
       <c r="M174" t="inlineStr"/>
-      <c r="N174" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N174" t="inlineStr"/>
       <c r="O174" t="inlineStr"/>
-      <c r="P174" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P174" t="inlineStr"/>
       <c r="Q174" t="inlineStr"/>
       <c r="R174" t="inlineStr"/>
       <c r="S174" t="inlineStr"/>
-      <c r="T174" t="inlineStr"/>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U174" t="inlineStr"/>
       <c r="V174" t="inlineStr">
         <is>
-          <t>SviSmryRnk</t>
+          <t>SocEcAdvIn</t>
         </is>
       </c>
       <c r="W174" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) Summary Ranking</t>
+          <t>Socioeconomic Advantage Index</t>
         </is>
       </c>
       <c r="X174" t="inlineStr"/>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
         </is>
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AB174" t="inlineStr"/>
@@ -13277,7 +13273,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>SDOH Indices &amp; Typology</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
@@ -13285,27 +13281,19 @@
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr"/>
       <c r="G175" t="inlineStr"/>
-      <c r="H175" t="inlineStr"/>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L175" t="inlineStr"/>
       <c r="M175" t="inlineStr"/>
-      <c r="N175" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N175" t="inlineStr"/>
       <c r="O175" t="inlineStr"/>
-      <c r="P175" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P175" t="inlineStr"/>
       <c r="Q175" t="inlineStr"/>
       <c r="R175" t="inlineStr"/>
       <c r="S175" t="inlineStr"/>
@@ -13317,28 +13305,28 @@
       <c r="U175" t="inlineStr"/>
       <c r="V175" t="inlineStr">
         <is>
-          <t>SviTh1</t>
+          <t>UrbCoreInd</t>
         </is>
       </c>
       <c r="W175" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 1</t>
+          <t>Urban Core Opportunity Index</t>
         </is>
       </c>
       <c r="X175" t="inlineStr"/>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
         </is>
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AB175" t="inlineStr"/>
@@ -13389,12 +13377,12 @@
       <c r="U176" t="inlineStr"/>
       <c r="V176" t="inlineStr">
         <is>
-          <t>SviTh2</t>
+          <t>SviSmryRnk</t>
         </is>
       </c>
       <c r="W176" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 2</t>
+          <t>Social Vulnerability Index (SVI) Summary Ranking</t>
         </is>
       </c>
       <c r="X176" t="inlineStr"/>
@@ -13457,16 +13445,20 @@
       <c r="Q177" t="inlineStr"/>
       <c r="R177" t="inlineStr"/>
       <c r="S177" t="inlineStr"/>
-      <c r="T177" t="inlineStr"/>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U177" t="inlineStr"/>
       <c r="V177" t="inlineStr">
         <is>
-          <t>SviTh3</t>
+          <t>SviTh1</t>
         </is>
       </c>
       <c r="W177" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 3</t>
+          <t>Social Vulnerability Index (SVI) 1</t>
         </is>
       </c>
       <c r="X177" t="inlineStr"/>
@@ -13529,20 +13521,16 @@
       <c r="Q178" t="inlineStr"/>
       <c r="R178" t="inlineStr"/>
       <c r="S178" t="inlineStr"/>
-      <c r="T178" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T178" t="inlineStr"/>
       <c r="U178" t="inlineStr"/>
       <c r="V178" t="inlineStr">
         <is>
-          <t>SviTh4</t>
+          <t>SviTh2</t>
         </is>
       </c>
       <c r="W178" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 4</t>
+          <t>Social Vulnerability Index (SVI) 2</t>
         </is>
       </c>
       <c r="X178" t="inlineStr"/>
@@ -13564,6 +13552,154 @@
       <c r="AB178" t="inlineStr"/>
       <c r="AC178" t="inlineStr"/>
       <c r="AD178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr"/>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr"/>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr"/>
+      <c r="R179" t="inlineStr"/>
+      <c r="S179" t="inlineStr"/>
+      <c r="T179" t="inlineStr"/>
+      <c r="U179" t="inlineStr"/>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>SviTh3</t>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 3</t>
+        </is>
+      </c>
+      <c r="X179" t="inlineStr"/>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB179" t="inlineStr"/>
+      <c r="AC179" t="inlineStr"/>
+      <c r="AD179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr"/>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr"/>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr"/>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr"/>
+      <c r="R180" t="inlineStr"/>
+      <c r="S180" t="inlineStr"/>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr"/>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>SviTh4</t>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 4</t>
+        </is>
+      </c>
+      <c r="X180" t="inlineStr"/>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB180" t="inlineStr"/>
+      <c r="AC180" t="inlineStr"/>
+      <c r="AD180" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/src/reference/data-dictionaries/T_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/T_Dict.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD180"/>
+  <dimension ref="A1:AD194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Spatial Access to Hospitals</t>
+          <t>Spatial Access to HIV Testing</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -7591,42 +7591,42 @@
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr"/>
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr"/>
-      <c r="S91" t="inlineStr"/>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T91" t="inlineStr"/>
       <c r="U91" t="inlineStr"/>
       <c r="V91" t="inlineStr">
         <is>
-          <t>HospCntDr</t>
+          <t>HivTmDr2</t>
         </is>
       </c>
       <c r="W91" t="inlineStr">
         <is>
-          <t>Count of Hospitals (30-min drive)</t>
+          <t>Driving time (min) to nearest HIV Testing Facility, with impedance</t>
         </is>
       </c>
       <c r="X91" t="inlineStr"/>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Hospitals.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HIVTesting.md</t>
         </is>
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr"/>
@@ -7664,17 +7664,21 @@
       <c r="P92" t="inlineStr"/>
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr"/>
-      <c r="S92" t="inlineStr"/>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T92" t="inlineStr"/>
       <c r="U92" t="inlineStr"/>
       <c r="V92" t="inlineStr">
         <is>
-          <t>HospMinDis</t>
+          <t>HospCntDr</t>
         </is>
       </c>
       <c r="W92" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Hospital</t>
+          <t>Count of Hospitals (30-min drive)</t>
         </is>
       </c>
       <c r="X92" t="inlineStr"/>
@@ -7728,21 +7732,21 @@
       <c r="P93" t="inlineStr"/>
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr"/>
-      <c r="S93" t="inlineStr"/>
-      <c r="T93" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr"/>
       <c r="U93" t="inlineStr"/>
       <c r="V93" t="inlineStr">
         <is>
-          <t>HospTmDr</t>
+          <t>HospMinDis</t>
         </is>
       </c>
       <c r="W93" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest Hospital</t>
+          <t>Distance (mi) to nearest Hospital</t>
         </is>
       </c>
       <c r="X93" t="inlineStr"/>
@@ -7787,7 +7791,11 @@
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr"/>
       <c r="Q94" t="inlineStr"/>
@@ -7797,16 +7805,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T94" t="inlineStr"/>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U94" t="inlineStr"/>
       <c r="V94" t="inlineStr">
         <is>
-          <t>HospTmDr2</t>
+          <t>HospTmDr</t>
         </is>
       </c>
       <c r="W94" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest Hospital with Impedance Factor</t>
+          <t>Driving time (min) to nearest Hospital</t>
         </is>
       </c>
       <c r="X94" t="inlineStr"/>
@@ -7837,7 +7849,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Spatial Access to MOUDs</t>
+          <t>Spatial Access to Hospitals</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -7851,42 +7863,42 @@
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr"/>
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr"/>
-      <c r="S95" t="inlineStr"/>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T95" t="inlineStr"/>
       <c r="U95" t="inlineStr"/>
       <c r="V95" t="inlineStr">
         <is>
-          <t>BupCntBk30</t>
+          <t>HospTmDr2</t>
         </is>
       </c>
       <c r="W95" t="inlineStr">
         <is>
-          <t>Count of Buprenorphine Providers (30-min bike)</t>
+          <t>Driving time (min) to nearest Hospital with Impedance Factor</t>
         </is>
       </c>
       <c r="X95" t="inlineStr"/>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Hospitals.md</t>
         </is>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
+          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
+          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr"/>
@@ -7924,17 +7936,21 @@
       <c r="P96" t="inlineStr"/>
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr"/>
-      <c r="S96" t="inlineStr"/>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T96" t="inlineStr"/>
       <c r="U96" t="inlineStr"/>
       <c r="V96" t="inlineStr">
         <is>
-          <t>BupCntBk60</t>
+          <t>BupCntBk30</t>
         </is>
       </c>
       <c r="W96" t="inlineStr">
         <is>
-          <t>Count of Buprenorphine Providers (60-min bike)</t>
+          <t>Count of Buprenorphine Providers (30-min bike)</t>
         </is>
       </c>
       <c r="X96" t="inlineStr"/>
@@ -7997,12 +8013,12 @@
       <c r="U97" t="inlineStr"/>
       <c r="V97" t="inlineStr">
         <is>
-          <t>BupCntDr30</t>
+          <t>BupCntBk60</t>
         </is>
       </c>
       <c r="W97" t="inlineStr">
         <is>
-          <t>Count of Buprenorphine Providers (30-min drive)</t>
+          <t>Count of Buprenorphine Providers (60-min bike)</t>
         </is>
       </c>
       <c r="X97" t="inlineStr"/>
@@ -8056,17 +8072,21 @@
       <c r="P98" t="inlineStr"/>
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr"/>
-      <c r="S98" t="inlineStr"/>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T98" t="inlineStr"/>
       <c r="U98" t="inlineStr"/>
       <c r="V98" t="inlineStr">
         <is>
-          <t>BupCntWk30</t>
+          <t>BupCntDr30</t>
         </is>
       </c>
       <c r="W98" t="inlineStr">
         <is>
-          <t>Count of Buprenorphine Providers (30-min walk)</t>
+          <t>Count of Buprenorphine Providers (30-min drive)</t>
         </is>
       </c>
       <c r="X98" t="inlineStr"/>
@@ -8111,26 +8131,26 @@
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr"/>
       <c r="Q99" t="inlineStr"/>
       <c r="R99" t="inlineStr"/>
-      <c r="S99" t="inlineStr"/>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T99" t="inlineStr"/>
       <c r="U99" t="inlineStr"/>
       <c r="V99" t="inlineStr">
         <is>
-          <t>BupCntWk60</t>
+          <t>BupCntDr60</t>
         </is>
       </c>
       <c r="W99" t="inlineStr">
         <is>
-          <t>Count of Buprenorphine Providers (60-min walk)</t>
+          <t>Count of buprenorphine providers (drive)</t>
         </is>
       </c>
       <c r="X99" t="inlineStr"/>
@@ -8184,17 +8204,21 @@
       <c r="P100" t="inlineStr"/>
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr"/>
-      <c r="S100" t="inlineStr"/>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T100" t="inlineStr"/>
       <c r="U100" t="inlineStr"/>
       <c r="V100" t="inlineStr">
         <is>
-          <t>BupMinDis</t>
+          <t>BupCntWk30</t>
         </is>
       </c>
       <c r="W100" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Buprenorphine Provider</t>
+          <t>Count of Buprenorphine Providers (30-min walk)</t>
         </is>
       </c>
       <c r="X100" t="inlineStr"/>
@@ -8248,17 +8272,21 @@
       <c r="P101" t="inlineStr"/>
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr"/>
-      <c r="S101" t="inlineStr"/>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T101" t="inlineStr"/>
       <c r="U101" t="inlineStr"/>
       <c r="V101" t="inlineStr">
         <is>
-          <t>BupRm30</t>
+          <t>BupCntWk60</t>
         </is>
       </c>
       <c r="W101" t="inlineStr">
         <is>
-          <t>Buprenorphine access 30 minutes (RAAM)</t>
+          <t>Count of Buprenorphine Providers (60-min walk)</t>
         </is>
       </c>
       <c r="X101" t="inlineStr"/>
@@ -8312,17 +8340,21 @@
       <c r="P102" t="inlineStr"/>
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr"/>
-      <c r="S102" t="inlineStr"/>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T102" t="inlineStr"/>
       <c r="U102" t="inlineStr"/>
       <c r="V102" t="inlineStr">
         <is>
-          <t>BupRm60</t>
+          <t>BupMinDis</t>
         </is>
       </c>
       <c r="W102" t="inlineStr">
         <is>
-          <t>Buprenorphine access 60 minutes (RAAM)</t>
+          <t>Distance (mi) to nearest Buprenorphine Provider</t>
         </is>
       </c>
       <c r="X102" t="inlineStr"/>
@@ -8381,12 +8413,12 @@
       <c r="U103" t="inlineStr"/>
       <c r="V103" t="inlineStr">
         <is>
-          <t>BupRm90</t>
+          <t>BupRm30</t>
         </is>
       </c>
       <c r="W103" t="inlineStr">
         <is>
-          <t>Buprenorphine access 90 minutes (RAAM)</t>
+          <t>Buprenorphine access 30 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X103" t="inlineStr"/>
@@ -8441,20 +8473,16 @@
       <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr"/>
-      <c r="T104" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T104" t="inlineStr"/>
       <c r="U104" t="inlineStr"/>
       <c r="V104" t="inlineStr">
         <is>
-          <t>BupTmBk</t>
+          <t>BupRm60</t>
         </is>
       </c>
       <c r="W104" t="inlineStr">
         <is>
-          <t>Biking Time (min) to nearest Buprenorphine Provider</t>
+          <t>Buprenorphine access 60 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X104" t="inlineStr"/>
@@ -8508,25 +8536,17 @@
       <c r="P105" t="inlineStr"/>
       <c r="Q105" t="inlineStr"/>
       <c r="R105" t="inlineStr"/>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="T105" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S105" t="inlineStr"/>
+      <c r="T105" t="inlineStr"/>
       <c r="U105" t="inlineStr"/>
       <c r="V105" t="inlineStr">
         <is>
-          <t>BupTmDr</t>
+          <t>BupRm90</t>
         </is>
       </c>
       <c r="W105" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Buprenorphine Provider</t>
+          <t>Buprenorphine access 90 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X105" t="inlineStr"/>
@@ -8571,7 +8591,11 @@
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O106" t="inlineStr"/>
       <c r="P106" t="inlineStr"/>
       <c r="Q106" t="inlineStr"/>
@@ -8589,12 +8613,12 @@
       <c r="U106" t="inlineStr"/>
       <c r="V106" t="inlineStr">
         <is>
-          <t>BupTmDr2</t>
+          <t>BupTmBk</t>
         </is>
       </c>
       <c r="W106" t="inlineStr">
         <is>
-          <t>Driving time to nearest buprenorphine provider (with impedance)</t>
+          <t>Biking Time (min) to nearest Buprenorphine Provider</t>
         </is>
       </c>
       <c r="X106" t="inlineStr"/>
@@ -8648,7 +8672,11 @@
       <c r="P107" t="inlineStr"/>
       <c r="Q107" t="inlineStr"/>
       <c r="R107" t="inlineStr"/>
-      <c r="S107" t="inlineStr"/>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T107" t="inlineStr">
         <is>
           <t>x</t>
@@ -8657,12 +8685,12 @@
       <c r="U107" t="inlineStr"/>
       <c r="V107" t="inlineStr">
         <is>
-          <t>BupTmWk</t>
+          <t>BupTmDr</t>
         </is>
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Buprenorphine Provider</t>
+          <t>Driving Time (min) to nearest Buprenorphine Provider</t>
         </is>
       </c>
       <c r="X107" t="inlineStr"/>
@@ -8716,17 +8744,25 @@
       <c r="P108" t="inlineStr"/>
       <c r="Q108" t="inlineStr"/>
       <c r="R108" t="inlineStr"/>
-      <c r="S108" t="inlineStr"/>
-      <c r="T108" t="inlineStr"/>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U108" t="inlineStr"/>
       <c r="V108" t="inlineStr">
         <is>
-          <t>MetCntBk30</t>
+          <t>BupTmWk</t>
         </is>
       </c>
       <c r="W108" t="inlineStr">
         <is>
-          <t>Count of methadone providers (30-min bike)</t>
+          <t>Walking Time (min) to nearest Buprenorphine Provider</t>
         </is>
       </c>
       <c r="X108" t="inlineStr"/>
@@ -8780,17 +8816,21 @@
       <c r="P109" t="inlineStr"/>
       <c r="Q109" t="inlineStr"/>
       <c r="R109" t="inlineStr"/>
-      <c r="S109" t="inlineStr"/>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T109" t="inlineStr"/>
       <c r="U109" t="inlineStr"/>
       <c r="V109" t="inlineStr">
         <is>
-          <t>MetCntBk60</t>
+          <t>MetCntBk30</t>
         </is>
       </c>
       <c r="W109" t="inlineStr">
         <is>
-          <t>Count of Methadone Providers (60-min bike)</t>
+          <t>Count of methadone providers (30-min bike)</t>
         </is>
       </c>
       <c r="X109" t="inlineStr"/>
@@ -8853,12 +8893,12 @@
       <c r="U110" t="inlineStr"/>
       <c r="V110" t="inlineStr">
         <is>
-          <t>MetCntDr30</t>
+          <t>MetCntBk60</t>
         </is>
       </c>
       <c r="W110" t="inlineStr">
         <is>
-          <t>Count of Methadone Providers (30-min drive)</t>
+          <t>Count of Methadone Providers (60-min bike)</t>
         </is>
       </c>
       <c r="X110" t="inlineStr"/>
@@ -8912,17 +8952,21 @@
       <c r="P111" t="inlineStr"/>
       <c r="Q111" t="inlineStr"/>
       <c r="R111" t="inlineStr"/>
-      <c r="S111" t="inlineStr"/>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T111" t="inlineStr"/>
       <c r="U111" t="inlineStr"/>
       <c r="V111" t="inlineStr">
         <is>
-          <t>MetCntWk30</t>
+          <t>MetCntDr30</t>
         </is>
       </c>
       <c r="W111" t="inlineStr">
         <is>
-          <t>Count of Methadone Providers (60-min walk)</t>
+          <t>Count of Methadone Providers (30-min drive)</t>
         </is>
       </c>
       <c r="X111" t="inlineStr"/>
@@ -8967,26 +9011,26 @@
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr"/>
       <c r="P112" t="inlineStr"/>
       <c r="Q112" t="inlineStr"/>
       <c r="R112" t="inlineStr"/>
-      <c r="S112" t="inlineStr"/>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T112" t="inlineStr"/>
       <c r="U112" t="inlineStr"/>
       <c r="V112" t="inlineStr">
         <is>
-          <t>MetCntWk60</t>
+          <t>MetCntDr60</t>
         </is>
       </c>
       <c r="W112" t="inlineStr">
         <is>
-          <t>Count of Methadone Providers (30-min walk)</t>
+          <t>Count of methadone providers (drive)</t>
         </is>
       </c>
       <c r="X112" t="inlineStr"/>
@@ -9040,17 +9084,21 @@
       <c r="P113" t="inlineStr"/>
       <c r="Q113" t="inlineStr"/>
       <c r="R113" t="inlineStr"/>
-      <c r="S113" t="inlineStr"/>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T113" t="inlineStr"/>
       <c r="U113" t="inlineStr"/>
       <c r="V113" t="inlineStr">
         <is>
-          <t>MetMinDis</t>
+          <t>MetCntWk30</t>
         </is>
       </c>
       <c r="W113" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Methadone Provider</t>
+          <t>Count of Methadone Providers (60-min walk)</t>
         </is>
       </c>
       <c r="X113" t="inlineStr"/>
@@ -9084,26 +9132,10 @@
           <t>Spatial Access to MOUDs</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr"/>
@@ -9120,17 +9152,21 @@
       <c r="P114" t="inlineStr"/>
       <c r="Q114" t="inlineStr"/>
       <c r="R114" t="inlineStr"/>
-      <c r="S114" t="inlineStr"/>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T114" t="inlineStr"/>
       <c r="U114" t="inlineStr"/>
       <c r="V114" t="inlineStr">
         <is>
-          <t>MetRm30</t>
+          <t>MetCntWk60</t>
         </is>
       </c>
       <c r="W114" t="inlineStr">
         <is>
-          <t>Methadone access 30 minutes (RAAM)</t>
+          <t>Count of Methadone Providers (30-min walk)</t>
         </is>
       </c>
       <c r="X114" t="inlineStr"/>
@@ -9164,26 +9200,10 @@
           <t>Spatial Access to MOUDs</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr"/>
@@ -9200,17 +9220,21 @@
       <c r="P115" t="inlineStr"/>
       <c r="Q115" t="inlineStr"/>
       <c r="R115" t="inlineStr"/>
-      <c r="S115" t="inlineStr"/>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T115" t="inlineStr"/>
       <c r="U115" t="inlineStr"/>
       <c r="V115" t="inlineStr">
         <is>
-          <t>MetRm60</t>
+          <t>MetMinDis</t>
         </is>
       </c>
       <c r="W115" t="inlineStr">
         <is>
-          <t>Methadone access 60 minutes (RAAM)</t>
+          <t>Distance (mi) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X115" t="inlineStr"/>
@@ -9285,12 +9309,12 @@
       <c r="U116" t="inlineStr"/>
       <c r="V116" t="inlineStr">
         <is>
-          <t>MetRm90</t>
+          <t>MetRm30</t>
         </is>
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>Methadone access 90 minutes (RAAM)</t>
+          <t>Methadone access 30 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X116" t="inlineStr"/>
@@ -9324,10 +9348,26 @@
           <t>Spatial Access to MOUDs</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr"/>
-      <c r="D117" t="inlineStr"/>
-      <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr"/>
@@ -9345,20 +9385,16 @@
       <c r="Q117" t="inlineStr"/>
       <c r="R117" t="inlineStr"/>
       <c r="S117" t="inlineStr"/>
-      <c r="T117" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T117" t="inlineStr"/>
       <c r="U117" t="inlineStr"/>
       <c r="V117" t="inlineStr">
         <is>
-          <t>MetTmBk</t>
+          <t>MetRm60</t>
         </is>
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>Biking Time (min) to nearest Methadone Provider</t>
+          <t>Methadone access 60 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X117" t="inlineStr"/>
@@ -9392,10 +9428,26 @@
           <t>Spatial Access to MOUDs</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr"/>
-      <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr"/>
@@ -9412,25 +9464,17 @@
       <c r="P118" t="inlineStr"/>
       <c r="Q118" t="inlineStr"/>
       <c r="R118" t="inlineStr"/>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="T118" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S118" t="inlineStr"/>
+      <c r="T118" t="inlineStr"/>
       <c r="U118" t="inlineStr"/>
       <c r="V118" t="inlineStr">
         <is>
-          <t>MetTmDr</t>
+          <t>MetRm90</t>
         </is>
       </c>
       <c r="W118" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Methadone Provider</t>
+          <t>Methadone access 90 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X118" t="inlineStr"/>
@@ -9475,7 +9519,11 @@
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O119" t="inlineStr"/>
       <c r="P119" t="inlineStr"/>
       <c r="Q119" t="inlineStr"/>
@@ -9493,12 +9541,12 @@
       <c r="U119" t="inlineStr"/>
       <c r="V119" t="inlineStr">
         <is>
-          <t>MetTmDr2</t>
+          <t>MetTmBk</t>
         </is>
       </c>
       <c r="W119" t="inlineStr">
         <is>
-          <t>Driving time to nearest methadone provider (with impedance)</t>
+          <t>Biking Time (min) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X119" t="inlineStr"/>
@@ -9552,7 +9600,11 @@
       <c r="P120" t="inlineStr"/>
       <c r="Q120" t="inlineStr"/>
       <c r="R120" t="inlineStr"/>
-      <c r="S120" t="inlineStr"/>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T120" t="inlineStr">
         <is>
           <t>x</t>
@@ -9561,12 +9613,12 @@
       <c r="U120" t="inlineStr"/>
       <c r="V120" t="inlineStr">
         <is>
-          <t>MetTmWk</t>
+          <t>MetTmDr</t>
         </is>
       </c>
       <c r="W120" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Methadone Provider</t>
+          <t>Driving Time (min) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X120" t="inlineStr"/>
@@ -9620,17 +9672,25 @@
       <c r="P121" t="inlineStr"/>
       <c r="Q121" t="inlineStr"/>
       <c r="R121" t="inlineStr"/>
-      <c r="S121" t="inlineStr"/>
-      <c r="T121" t="inlineStr"/>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U121" t="inlineStr"/>
       <c r="V121" t="inlineStr">
         <is>
-          <t>MoudMinDis</t>
+          <t>MetTmWk</t>
         </is>
       </c>
       <c r="W121" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest MOUD (any)</t>
+          <t>Walking Time (min) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X121" t="inlineStr"/>
@@ -9675,7 +9735,11 @@
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O122" t="inlineStr"/>
       <c r="P122" t="inlineStr"/>
       <c r="Q122" t="inlineStr"/>
@@ -9685,20 +9749,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T122" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T122" t="inlineStr"/>
       <c r="U122" t="inlineStr"/>
       <c r="V122" t="inlineStr">
         <is>
-          <t>MoudTyp</t>
+          <t>MoudMinDis</t>
         </is>
       </c>
       <c r="W122" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOUD Types Within 30-Min Drive  (impedance, adjusted) </t>
+          <t>Distance (mi) to nearest MOUD (any)</t>
         </is>
       </c>
       <c r="X122" t="inlineStr"/>
@@ -9752,7 +9812,11 @@
       <c r="P123" t="inlineStr"/>
       <c r="Q123" t="inlineStr"/>
       <c r="R123" t="inlineStr"/>
-      <c r="S123" t="inlineStr"/>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T123" t="inlineStr"/>
       <c r="U123" t="inlineStr"/>
       <c r="V123" t="inlineStr">
@@ -9816,7 +9880,11 @@
       <c r="P124" t="inlineStr"/>
       <c r="Q124" t="inlineStr"/>
       <c r="R124" t="inlineStr"/>
-      <c r="S124" t="inlineStr"/>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T124" t="inlineStr"/>
       <c r="U124" t="inlineStr"/>
       <c r="V124" t="inlineStr">
@@ -9939,26 +10007,26 @@
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr"/>
       <c r="Q126" t="inlineStr"/>
       <c r="R126" t="inlineStr"/>
-      <c r="S126" t="inlineStr"/>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T126" t="inlineStr"/>
       <c r="U126" t="inlineStr"/>
       <c r="V126" t="inlineStr">
         <is>
-          <t>NaltCntWk30</t>
+          <t>NaltCntDr60</t>
         </is>
       </c>
       <c r="W126" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (30-min walk)</t>
+          <t>Count of naltrexone providers (drive)</t>
         </is>
       </c>
       <c r="X126" t="inlineStr"/>
@@ -10012,17 +10080,21 @@
       <c r="P127" t="inlineStr"/>
       <c r="Q127" t="inlineStr"/>
       <c r="R127" t="inlineStr"/>
-      <c r="S127" t="inlineStr"/>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T127" t="inlineStr"/>
       <c r="U127" t="inlineStr"/>
       <c r="V127" t="inlineStr">
         <is>
-          <t>NaltCntWk60</t>
+          <t>NaltCntWk30</t>
         </is>
       </c>
       <c r="W127" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (60-min walk)</t>
+          <t>Count of Naltrexone Providers (30-min walk)</t>
         </is>
       </c>
       <c r="X127" t="inlineStr"/>
@@ -10076,17 +10148,21 @@
       <c r="P128" t="inlineStr"/>
       <c r="Q128" t="inlineStr"/>
       <c r="R128" t="inlineStr"/>
-      <c r="S128" t="inlineStr"/>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T128" t="inlineStr"/>
       <c r="U128" t="inlineStr"/>
       <c r="V128" t="inlineStr">
         <is>
-          <t>NaltMinDis</t>
+          <t>NaltCntWk60</t>
         </is>
       </c>
       <c r="W128" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Naltrexone Provider</t>
+          <t>Count of Naltrexone Providers (60-min walk)</t>
         </is>
       </c>
       <c r="X128" t="inlineStr"/>
@@ -10140,17 +10216,21 @@
       <c r="P129" t="inlineStr"/>
       <c r="Q129" t="inlineStr"/>
       <c r="R129" t="inlineStr"/>
-      <c r="S129" t="inlineStr"/>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T129" t="inlineStr"/>
       <c r="U129" t="inlineStr"/>
       <c r="V129" t="inlineStr">
         <is>
-          <t>NaltRm30</t>
+          <t>NaltMinDis</t>
         </is>
       </c>
       <c r="W129" t="inlineStr">
         <is>
-          <t>Naltrexone access 30 minutes (RAAM)</t>
+          <t>Distance (mi) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X129" t="inlineStr"/>
@@ -10209,12 +10289,12 @@
       <c r="U130" t="inlineStr"/>
       <c r="V130" t="inlineStr">
         <is>
-          <t>NaltRm60</t>
+          <t>NaltRm30</t>
         </is>
       </c>
       <c r="W130" t="inlineStr">
         <is>
-          <t>Naltrexone access 60 minutes (RAAM)</t>
+          <t>Naltrexone access 30 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X130" t="inlineStr"/>
@@ -10273,12 +10353,12 @@
       <c r="U131" t="inlineStr"/>
       <c r="V131" t="inlineStr">
         <is>
-          <t>NaltRm90</t>
+          <t>NaltRm60</t>
         </is>
       </c>
       <c r="W131" t="inlineStr">
         <is>
-          <t>Naltrexone access 90 minutes (RAAM)</t>
+          <t>Naltrexone access 60 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X131" t="inlineStr"/>
@@ -10333,20 +10413,16 @@
       <c r="Q132" t="inlineStr"/>
       <c r="R132" t="inlineStr"/>
       <c r="S132" t="inlineStr"/>
-      <c r="T132" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T132" t="inlineStr"/>
       <c r="U132" t="inlineStr"/>
       <c r="V132" t="inlineStr">
         <is>
-          <t>NaltTmBk</t>
+          <t>NaltRm90</t>
         </is>
       </c>
       <c r="W132" t="inlineStr">
         <is>
-          <t>Biking Time (min) to nearest Naltrexone Provider</t>
+          <t>Naltrexone access 90 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X132" t="inlineStr"/>
@@ -10413,12 +10489,12 @@
       <c r="U133" t="inlineStr"/>
       <c r="V133" t="inlineStr">
         <is>
-          <t>NaltTmDr</t>
+          <t>NaltTmBk</t>
         </is>
       </c>
       <c r="W133" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Naltrexone Provider</t>
+          <t>Biking Time (min) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X133" t="inlineStr"/>
@@ -10463,7 +10539,11 @@
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr"/>
       <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O134" t="inlineStr"/>
       <c r="P134" t="inlineStr"/>
       <c r="Q134" t="inlineStr"/>
@@ -10473,16 +10553,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T134" t="inlineStr"/>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U134" t="inlineStr"/>
       <c r="V134" t="inlineStr">
         <is>
-          <t>NaltTmDr2</t>
+          <t>NaltTmDr</t>
         </is>
       </c>
       <c r="W134" t="inlineStr">
         <is>
-          <t>Driving time to nearest naltrexone provider (with impedance)</t>
+          <t>Driving Time (min) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X134" t="inlineStr"/>
@@ -10536,7 +10620,11 @@
       <c r="P135" t="inlineStr"/>
       <c r="Q135" t="inlineStr"/>
       <c r="R135" t="inlineStr"/>
-      <c r="S135" t="inlineStr"/>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T135" t="inlineStr">
         <is>
           <t>x</t>
@@ -10672,7 +10760,11 @@
       <c r="P137" t="inlineStr"/>
       <c r="Q137" t="inlineStr"/>
       <c r="R137" t="inlineStr"/>
-      <c r="S137" t="inlineStr"/>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T137" t="inlineStr"/>
       <c r="U137" t="inlineStr"/>
       <c r="V137" t="inlineStr">
@@ -10813,12 +10905,12 @@
       <c r="U139" t="inlineStr"/>
       <c r="V139" t="inlineStr">
         <is>
-          <t>OtpTmDr2</t>
+          <t>TlBupCntBk30</t>
         </is>
       </c>
       <c r="W139" t="inlineStr">
         <is>
-          <t>Driving time to nearest OTP (impedance-adjusted)</t>
+          <t>Count of telehealth buprenorphine providers within 30-minute bike ride</t>
         </is>
       </c>
       <c r="X139" t="inlineStr"/>
@@ -10849,7 +10941,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -10863,42 +10955,42 @@
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr"/>
       <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr"/>
       <c r="P140" t="inlineStr"/>
       <c r="Q140" t="inlineStr"/>
       <c r="R140" t="inlineStr"/>
-      <c r="S140" t="inlineStr"/>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T140" t="inlineStr"/>
       <c r="U140" t="inlineStr"/>
       <c r="V140" t="inlineStr">
         <is>
-          <t>MhCntDr</t>
+          <t>TlBupCntDr30</t>
         </is>
       </c>
       <c r="W140" t="inlineStr">
         <is>
-          <t>Count of Mental Health Providers (30-min drive)</t>
+          <t>Count of telehealth buprenorphine providers within 30-minute drive</t>
         </is>
       </c>
       <c r="X140" t="inlineStr"/>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr"/>
@@ -10913,7 +11005,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -10927,42 +11019,42 @@
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N141" t="inlineStr"/>
       <c r="O141" t="inlineStr"/>
       <c r="P141" t="inlineStr"/>
       <c r="Q141" t="inlineStr"/>
       <c r="R141" t="inlineStr"/>
-      <c r="S141" t="inlineStr"/>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T141" t="inlineStr"/>
       <c r="U141" t="inlineStr"/>
       <c r="V141" t="inlineStr">
         <is>
-          <t>MhMinDis</t>
+          <t>TlBupCntDr60</t>
         </is>
       </c>
       <c r="W141" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Mental Health Provider</t>
+          <t>Count of telehealth buprenorphine providers within 60-minute drive</t>
         </is>
       </c>
       <c r="X141" t="inlineStr"/>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB141" t="inlineStr"/>
@@ -10977,7 +11069,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -10991,46 +11083,42 @@
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr"/>
       <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N142" t="inlineStr"/>
       <c r="O142" t="inlineStr"/>
       <c r="P142" t="inlineStr"/>
       <c r="Q142" t="inlineStr"/>
       <c r="R142" t="inlineStr"/>
-      <c r="S142" t="inlineStr"/>
-      <c r="T142" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr"/>
       <c r="U142" t="inlineStr"/>
       <c r="V142" t="inlineStr">
         <is>
-          <t>MhTmDr</t>
+          <t>TlBupCntWk30</t>
         </is>
       </c>
       <c r="W142" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Mental Health Provider</t>
+          <t>Count of telehealth buprenorphine providers within 30-minute walk</t>
         </is>
       </c>
       <c r="X142" t="inlineStr"/>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB142" t="inlineStr"/>
@@ -11045,7 +11133,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -11058,11 +11146,7 @@
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M143" t="inlineStr"/>
       <c r="N143" t="inlineStr"/>
       <c r="O143" t="inlineStr"/>
       <c r="P143" t="inlineStr"/>
@@ -11077,28 +11161,28 @@
       <c r="U143" t="inlineStr"/>
       <c r="V143" t="inlineStr">
         <is>
-          <t>RxCntDr</t>
+          <t>TlBupMinDis</t>
         </is>
       </c>
       <c r="W143" t="inlineStr">
         <is>
-          <t>Count of Pharmacies (30-min drive)</t>
+          <t>Minimum distance to telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X143" t="inlineStr"/>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB143" t="inlineStr"/>
@@ -11113,7 +11197,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -11126,43 +11210,43 @@
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M144" t="inlineStr"/>
       <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr"/>
       <c r="P144" t="inlineStr"/>
       <c r="Q144" t="inlineStr"/>
       <c r="R144" t="inlineStr"/>
-      <c r="S144" t="inlineStr"/>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T144" t="inlineStr"/>
       <c r="U144" t="inlineStr"/>
       <c r="V144" t="inlineStr">
         <is>
-          <t>RxMinDis</t>
+          <t>TlBupTmBk</t>
         </is>
       </c>
       <c r="W144" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Pharmacy</t>
+          <t>Biking time to nearest telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X144" t="inlineStr"/>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr"/>
@@ -11177,7 +11261,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -11190,11 +11274,7 @@
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M145" t="inlineStr"/>
       <c r="N145" t="inlineStr"/>
       <c r="O145" t="inlineStr"/>
       <c r="P145" t="inlineStr"/>
@@ -11205,36 +11285,32 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T145" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T145" t="inlineStr"/>
       <c r="U145" t="inlineStr"/>
       <c r="V145" t="inlineStr">
         <is>
-          <t>RxTmDr</t>
+          <t>TlBupTmDr</t>
         </is>
       </c>
       <c r="W145" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Pharmacy</t>
+          <t>Driving time to nearest telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X145" t="inlineStr"/>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr"/>
@@ -11249,7 +11325,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -11277,28 +11353,28 @@
       <c r="U146" t="inlineStr"/>
       <c r="V146" t="inlineStr">
         <is>
-          <t>RxTmDr2</t>
+          <t>TlBupTmWk</t>
         </is>
       </c>
       <c r="W146" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Pharmacy with Impedance Factor</t>
+          <t>Walking time to nearest telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X146" t="inlineStr"/>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr"/>
@@ -11313,7 +11389,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -11336,23 +11412,27 @@
       <c r="P147" t="inlineStr"/>
       <c r="Q147" t="inlineStr"/>
       <c r="R147" t="inlineStr"/>
-      <c r="S147" t="inlineStr"/>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T147" t="inlineStr"/>
       <c r="U147" t="inlineStr"/>
       <c r="V147" t="inlineStr">
         <is>
-          <t>SutCntDr</t>
+          <t>MhCntDr</t>
         </is>
       </c>
       <c r="W147" t="inlineStr">
         <is>
-          <t>Count of Substance Use Treatment (SUT) facility (30-min drive)</t>
+          <t>Count of Mental Health Providers (30-min drive)</t>
         </is>
       </c>
       <c r="X147" t="inlineStr"/>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z147" t="inlineStr">
@@ -11377,7 +11457,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
@@ -11400,23 +11480,27 @@
       <c r="P148" t="inlineStr"/>
       <c r="Q148" t="inlineStr"/>
       <c r="R148" t="inlineStr"/>
-      <c r="S148" t="inlineStr"/>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T148" t="inlineStr"/>
       <c r="U148" t="inlineStr"/>
       <c r="V148" t="inlineStr">
         <is>
-          <t>SutMinDis</t>
+          <t>MhMinDis</t>
         </is>
       </c>
       <c r="W148" t="inlineStr">
         <is>
-          <t>Distance (mi) to Substance Use Treatment (SUT) facility</t>
+          <t>Distance (mi) to nearest Mental Health Provider</t>
         </is>
       </c>
       <c r="X148" t="inlineStr"/>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z148" t="inlineStr">
@@ -11441,7 +11525,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -11464,7 +11548,11 @@
       <c r="P149" t="inlineStr"/>
       <c r="Q149" t="inlineStr"/>
       <c r="R149" t="inlineStr"/>
-      <c r="S149" t="inlineStr"/>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T149" t="inlineStr">
         <is>
           <t>x</t>
@@ -11473,18 +11561,18 @@
       <c r="U149" t="inlineStr"/>
       <c r="V149" t="inlineStr">
         <is>
-          <t>SutTmDr</t>
+          <t>MhTmDr</t>
         </is>
       </c>
       <c r="W149" t="inlineStr">
         <is>
-          <t>Driving time (min) to Substance Use Treatment (SUT) facility</t>
+          <t>Driving Time (min) to nearest Mental Health Provider</t>
         </is>
       </c>
       <c r="X149" t="inlineStr"/>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z149" t="inlineStr">
@@ -11509,7 +11597,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -11522,12 +11610,12 @@
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr"/>
-      <c r="N150" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr"/>
       <c r="O150" t="inlineStr"/>
       <c r="P150" t="inlineStr"/>
       <c r="Q150" t="inlineStr"/>
@@ -11541,28 +11629,28 @@
       <c r="U150" t="inlineStr"/>
       <c r="V150" t="inlineStr">
         <is>
-          <t>FqhcCntDr</t>
+          <t>RxCntDr</t>
         </is>
       </c>
       <c r="W150" t="inlineStr">
         <is>
-          <t>Count of Federally Qualified Health Centers (FQHCs) within 30-min drive</t>
+          <t>Count of Pharmacies (30-min drive)</t>
         </is>
       </c>
       <c r="X150" t="inlineStr"/>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr"/>
@@ -11577,7 +11665,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -11590,12 +11678,12 @@
       <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr"/>
-      <c r="N151" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
       <c r="O151" t="inlineStr"/>
       <c r="P151" t="inlineStr"/>
       <c r="Q151" t="inlineStr"/>
@@ -11605,28 +11693,28 @@
       <c r="U151" t="inlineStr"/>
       <c r="V151" t="inlineStr">
         <is>
-          <t>FqhcMinDis</t>
+          <t>RxMinDis</t>
         </is>
       </c>
       <c r="W151" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Federally Qualified Health Centers (FQHC)</t>
+          <t>Distance (mi) to nearest Pharmacy</t>
         </is>
       </c>
       <c r="X151" t="inlineStr"/>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB151" t="inlineStr"/>
@@ -11641,7 +11729,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
@@ -11654,12 +11742,12 @@
       <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr"/>
-      <c r="N152" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr"/>
       <c r="O152" t="inlineStr"/>
       <c r="P152" t="inlineStr"/>
       <c r="Q152" t="inlineStr"/>
@@ -11677,28 +11765,28 @@
       <c r="U152" t="inlineStr"/>
       <c r="V152" t="inlineStr">
         <is>
-          <t>FqhcTmDr</t>
+          <t>RxTmDr</t>
         </is>
       </c>
       <c r="W152" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC)</t>
+          <t>Driving Time (min) to nearest Pharmacy</t>
         </is>
       </c>
       <c r="X152" t="inlineStr"/>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB152" t="inlineStr"/>
@@ -11713,7 +11801,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -11737,36 +11825,32 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T153" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T153" t="inlineStr"/>
       <c r="U153" t="inlineStr"/>
       <c r="V153" t="inlineStr">
         <is>
-          <t>FqhcTmDr2</t>
+          <t>RxTmDr2</t>
         </is>
       </c>
       <c r="W153" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC), with Impedance factor</t>
+          <t>Driving Time (min) to nearest Pharmacy with Impedance Factor</t>
         </is>
       </c>
       <c r="X153" t="inlineStr"/>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB153" t="inlineStr"/>
@@ -11781,17 +11865,13 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr"/>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr"/>
@@ -11799,38 +11879,46 @@
       <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr"/>
       <c r="M154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O154" t="inlineStr"/>
       <c r="P154" t="inlineStr"/>
       <c r="Q154" t="inlineStr"/>
       <c r="R154" t="inlineStr"/>
-      <c r="S154" t="inlineStr"/>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T154" t="inlineStr"/>
       <c r="U154" t="inlineStr"/>
       <c r="V154" t="inlineStr">
         <is>
-          <t>Ruca1</t>
+          <t>SutCntDr</t>
         </is>
       </c>
       <c r="W154" t="inlineStr">
         <is>
-          <t>Primary RUCA Code</t>
+          <t>Count of Substance Use Treatment (SUT) facility (30-min drive)</t>
         </is>
       </c>
       <c r="X154" t="inlineStr"/>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB154" t="inlineStr"/>
@@ -11845,17 +11933,13 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr"/>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr"/>
@@ -11863,38 +11947,46 @@
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr"/>
       <c r="M155" t="inlineStr"/>
-      <c r="N155" t="inlineStr"/>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O155" t="inlineStr"/>
       <c r="P155" t="inlineStr"/>
       <c r="Q155" t="inlineStr"/>
       <c r="R155" t="inlineStr"/>
-      <c r="S155" t="inlineStr"/>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T155" t="inlineStr"/>
       <c r="U155" t="inlineStr"/>
       <c r="V155" t="inlineStr">
         <is>
-          <t>Ruca2</t>
+          <t>SutMinDis</t>
         </is>
       </c>
       <c r="W155" t="inlineStr">
         <is>
-          <t>Secondary RUCA Code</t>
+          <t>Distance (mi) to Substance Use Treatment (SUT) facility</t>
         </is>
       </c>
       <c r="X155" t="inlineStr"/>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB155" t="inlineStr"/>
@@ -11909,17 +12001,13 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr"/>
@@ -11927,12 +12015,20 @@
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr"/>
       <c r="M156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O156" t="inlineStr"/>
       <c r="P156" t="inlineStr"/>
       <c r="Q156" t="inlineStr"/>
       <c r="R156" t="inlineStr"/>
-      <c r="S156" t="inlineStr"/>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T156" t="inlineStr">
         <is>
           <t>x</t>
@@ -11941,28 +12037,28 @@
       <c r="U156" t="inlineStr"/>
       <c r="V156" t="inlineStr">
         <is>
-          <t>Rurality</t>
+          <t>SutTmDr</t>
         </is>
       </c>
       <c r="W156" t="inlineStr">
         <is>
-          <t>Urban-Suburban-Rural</t>
+          <t>Driving time (min) to Substance Use Treatment (SUT) facility</t>
         </is>
       </c>
       <c r="X156" t="inlineStr"/>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB156" t="inlineStr"/>
@@ -11972,12 +12068,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -11989,44 +12085,48 @@
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L157" t="inlineStr"/>
       <c r="M157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O157" t="inlineStr"/>
       <c r="P157" t="inlineStr"/>
       <c r="Q157" t="inlineStr"/>
       <c r="R157" t="inlineStr"/>
-      <c r="S157" t="inlineStr"/>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T157" t="inlineStr"/>
       <c r="U157" t="inlineStr"/>
       <c r="V157" t="inlineStr">
         <is>
-          <t>EssnWrkE</t>
+          <t>FqhcCntDr</t>
         </is>
       </c>
       <c r="W157" t="inlineStr">
         <is>
-          <t>Count of Essential Workers</t>
+          <t>Count of Federally Qualified Health Centers (FQHCs) within 30-min drive</t>
         </is>
       </c>
       <c r="X157" t="inlineStr"/>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB157" t="inlineStr"/>
@@ -12036,12 +12136,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -12053,11 +12153,7 @@
       <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L158" t="inlineStr"/>
       <c r="M158" t="inlineStr"/>
       <c r="N158" t="inlineStr">
         <is>
@@ -12066,39 +12162,39 @@
       </c>
       <c r="O158" t="inlineStr"/>
       <c r="P158" t="inlineStr"/>
-      <c r="Q158" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q158" t="inlineStr"/>
       <c r="R158" t="inlineStr"/>
-      <c r="S158" t="inlineStr"/>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T158" t="inlineStr"/>
       <c r="U158" t="inlineStr"/>
       <c r="V158" t="inlineStr">
         <is>
-          <t>EssnWrkP</t>
+          <t>FqhcMinDis</t>
         </is>
       </c>
       <c r="W158" t="inlineStr">
         <is>
-          <t>Essential Workers %</t>
+          <t>Distance (mi) to nearest Federally Qualified Health Centers (FQHC)</t>
         </is>
       </c>
       <c r="X158" t="inlineStr"/>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB158" t="inlineStr"/>
@@ -12108,12 +12204,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
@@ -12125,11 +12221,7 @@
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L159" t="inlineStr"/>
       <c r="M159" t="inlineStr"/>
       <c r="N159" t="inlineStr">
         <is>
@@ -12138,39 +12230,43 @@
       </c>
       <c r="O159" t="inlineStr"/>
       <c r="P159" t="inlineStr"/>
-      <c r="Q159" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q159" t="inlineStr"/>
       <c r="R159" t="inlineStr"/>
-      <c r="S159" t="inlineStr"/>
-      <c r="T159" t="inlineStr"/>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U159" t="inlineStr"/>
       <c r="V159" t="inlineStr">
         <is>
-          <t>HghRskP</t>
+          <t>FqhcTmDr</t>
         </is>
       </c>
       <c r="W159" t="inlineStr">
         <is>
-          <t>Employed % - High Risk of Injury</t>
+          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC)</t>
         </is>
       </c>
       <c r="X159" t="inlineStr"/>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB159" t="inlineStr"/>
@@ -12180,12 +12276,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
@@ -12197,52 +12293,48 @@
       <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L160" t="inlineStr"/>
       <c r="M160" t="inlineStr"/>
-      <c r="N160" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N160" t="inlineStr"/>
       <c r="O160" t="inlineStr"/>
       <c r="P160" t="inlineStr"/>
-      <c r="Q160" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q160" t="inlineStr"/>
       <c r="R160" t="inlineStr"/>
-      <c r="S160" t="inlineStr"/>
-      <c r="T160" t="inlineStr"/>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U160" t="inlineStr"/>
       <c r="V160" t="inlineStr">
         <is>
-          <t>HltCrP</t>
+          <t>FqhcTmDr2</t>
         </is>
       </c>
       <c r="W160" t="inlineStr">
         <is>
-          <t>Employed % - Health Care</t>
+          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC), with Impedance factor</t>
         </is>
       </c>
       <c r="X160" t="inlineStr"/>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB160" t="inlineStr"/>
@@ -12252,12 +12344,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
@@ -12269,52 +12361,44 @@
       <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L161" t="inlineStr"/>
       <c r="M161" t="inlineStr"/>
-      <c r="N161" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N161" t="inlineStr"/>
       <c r="O161" t="inlineStr"/>
       <c r="P161" t="inlineStr"/>
-      <c r="Q161" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q161" t="inlineStr"/>
       <c r="R161" t="inlineStr"/>
-      <c r="S161" t="inlineStr"/>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T161" t="inlineStr"/>
       <c r="U161" t="inlineStr"/>
       <c r="V161" t="inlineStr">
         <is>
-          <t>RetailP</t>
+          <t>HcvCntDr</t>
         </is>
       </c>
       <c r="W161" t="inlineStr">
         <is>
-          <t>Employed % - Retail</t>
+          <t>Count of HCV Providers</t>
         </is>
       </c>
       <c r="X161" t="inlineStr"/>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB161" t="inlineStr"/>
@@ -12324,12 +12408,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
@@ -12341,52 +12425,44 @@
       <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr"/>
-      <c r="L162" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L162" t="inlineStr"/>
       <c r="M162" t="inlineStr"/>
-      <c r="N162" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N162" t="inlineStr"/>
       <c r="O162" t="inlineStr"/>
       <c r="P162" t="inlineStr"/>
-      <c r="Q162" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q162" t="inlineStr"/>
       <c r="R162" t="inlineStr"/>
-      <c r="S162" t="inlineStr"/>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T162" t="inlineStr"/>
       <c r="U162" t="inlineStr"/>
       <c r="V162" t="inlineStr">
         <is>
-          <t>TotWrkE</t>
+          <t>HcvMinDis</t>
         </is>
       </c>
       <c r="W162" t="inlineStr">
         <is>
-          <t>Count of Working Population</t>
+          <t>Distance to nearest HCV Provider</t>
         </is>
       </c>
       <c r="X162" t="inlineStr"/>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB162" t="inlineStr"/>
@@ -12396,12 +12472,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
@@ -12413,44 +12489,44 @@
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L163" t="inlineStr"/>
       <c r="M163" t="inlineStr"/>
       <c r="N163" t="inlineStr"/>
       <c r="O163" t="inlineStr"/>
       <c r="P163" t="inlineStr"/>
       <c r="Q163" t="inlineStr"/>
       <c r="R163" t="inlineStr"/>
-      <c r="S163" t="inlineStr"/>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T163" t="inlineStr"/>
       <c r="U163" t="inlineStr"/>
       <c r="V163" t="inlineStr">
         <is>
-          <t>ForDqP</t>
+          <t>HcvTmDr</t>
         </is>
       </c>
       <c r="W163" t="inlineStr">
         <is>
-          <t>Foreclosure &amp; Delinquency %</t>
+          <t>Driving time to nearest HCV Provider</t>
         </is>
       </c>
       <c r="X163" t="inlineStr"/>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB163" t="inlineStr"/>
@@ -12460,12 +12536,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
@@ -12477,44 +12553,44 @@
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr"/>
-      <c r="L164" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L164" t="inlineStr"/>
       <c r="M164" t="inlineStr"/>
       <c r="N164" t="inlineStr"/>
       <c r="O164" t="inlineStr"/>
       <c r="P164" t="inlineStr"/>
       <c r="Q164" t="inlineStr"/>
       <c r="R164" t="inlineStr"/>
-      <c r="S164" t="inlineStr"/>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T164" t="inlineStr"/>
       <c r="U164" t="inlineStr"/>
       <c r="V164" t="inlineStr">
         <is>
-          <t>ForDqTot</t>
+          <t>HcvTmDr2</t>
         </is>
       </c>
       <c r="W164" t="inlineStr">
         <is>
-          <t>Foreclosure &amp; Delinquency Count</t>
+          <t>Driving time (min) to nearest HIV Testing Facility with impedance</t>
         </is>
       </c>
       <c r="X164" t="inlineStr"/>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB164" t="inlineStr"/>
@@ -12524,73 +12600,61 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr"/>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F165" t="inlineStr"/>
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L165" t="inlineStr"/>
       <c r="M165" t="inlineStr"/>
-      <c r="N165" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N165" t="inlineStr"/>
       <c r="O165" t="inlineStr"/>
       <c r="P165" t="inlineStr"/>
-      <c r="Q165" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q165" t="inlineStr"/>
       <c r="R165" t="inlineStr"/>
-      <c r="S165" t="inlineStr"/>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T165" t="inlineStr"/>
       <c r="U165" t="inlineStr"/>
       <c r="V165" t="inlineStr">
         <is>
-          <t>GiniCoeff</t>
+          <t>HivCntDr</t>
         </is>
       </c>
       <c r="W165" t="inlineStr">
         <is>
-          <t>Income Inequality (Gini Coefficient)</t>
+          <t>Count of HIV Providers</t>
         </is>
       </c>
       <c r="X165" t="inlineStr"/>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB165" t="inlineStr"/>
@@ -12600,12 +12664,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Internet Access</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
@@ -12618,43 +12682,43 @@
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M166" t="inlineStr"/>
       <c r="N166" t="inlineStr"/>
       <c r="O166" t="inlineStr"/>
       <c r="P166" t="inlineStr"/>
       <c r="Q166" t="inlineStr"/>
       <c r="R166" t="inlineStr"/>
-      <c r="S166" t="inlineStr"/>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T166" t="inlineStr"/>
       <c r="U166" t="inlineStr"/>
       <c r="V166" t="inlineStr">
         <is>
-          <t>NoIntP</t>
+          <t>HivMinDis</t>
         </is>
       </c>
       <c r="W166" t="inlineStr">
         <is>
-          <t>Households without Internet Access %</t>
+          <t>Distance to nearest HIV Provider</t>
         </is>
       </c>
       <c r="X166" t="inlineStr"/>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Internet_Access.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>ACS 2019</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>American Community Survey 2015-2019 5-Year Estimate</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB166" t="inlineStr"/>
@@ -12664,73 +12728,61 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr"/>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F167" t="inlineStr"/>
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L167" t="inlineStr"/>
       <c r="M167" t="inlineStr"/>
-      <c r="N167" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N167" t="inlineStr"/>
       <c r="O167" t="inlineStr"/>
       <c r="P167" t="inlineStr"/>
-      <c r="Q167" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q167" t="inlineStr"/>
       <c r="R167" t="inlineStr"/>
-      <c r="S167" t="inlineStr"/>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T167" t="inlineStr"/>
       <c r="U167" t="inlineStr"/>
       <c r="V167" t="inlineStr">
         <is>
-          <t>MedInc</t>
+          <t>HivTmDr</t>
         </is>
       </c>
       <c r="W167" t="inlineStr">
         <is>
-          <t>Median Income</t>
+          <t>Driving time to nearest HIV Provider</t>
         </is>
       </c>
       <c r="X167" t="inlineStr"/>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB167" t="inlineStr"/>
@@ -12740,12 +12792,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
@@ -12761,52 +12813,40 @@
       <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L168" t="inlineStr"/>
       <c r="M168" t="inlineStr"/>
-      <c r="N168" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N168" t="inlineStr"/>
       <c r="O168" t="inlineStr"/>
       <c r="P168" t="inlineStr"/>
-      <c r="Q168" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q168" t="inlineStr"/>
       <c r="R168" t="inlineStr"/>
       <c r="S168" t="inlineStr"/>
       <c r="T168" t="inlineStr"/>
       <c r="U168" t="inlineStr"/>
       <c r="V168" t="inlineStr">
         <is>
-          <t>PciE</t>
+          <t>Ruca1</t>
         </is>
       </c>
       <c r="W168" t="inlineStr">
         <is>
-          <t>Per Capita Income</t>
+          <t>Primary RUCA Code</t>
         </is>
       </c>
       <c r="X168" t="inlineStr"/>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB168" t="inlineStr"/>
@@ -12816,29 +12856,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>Urban/Suburban/Rural Classification</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr"/>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
           <t>x</t>
@@ -12849,56 +12877,40 @@
       <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L169" t="inlineStr"/>
       <c r="M169" t="inlineStr"/>
-      <c r="N169" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N169" t="inlineStr"/>
       <c r="O169" t="inlineStr"/>
       <c r="P169" t="inlineStr"/>
-      <c r="Q169" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q169" t="inlineStr"/>
       <c r="R169" t="inlineStr"/>
       <c r="S169" t="inlineStr"/>
       <c r="T169" t="inlineStr"/>
-      <c r="U169" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="U169" t="inlineStr"/>
       <c r="V169" t="inlineStr">
         <is>
-          <t>PovP</t>
+          <t>Ruca2</t>
         </is>
       </c>
       <c r="W169" t="inlineStr">
         <is>
-          <t>Poverty %</t>
+          <t>Secondary RUCA Code</t>
         </is>
       </c>
       <c r="X169" t="inlineStr"/>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB169" t="inlineStr"/>
@@ -12908,29 +12920,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>Urban/Suburban/Rural Classification</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr"/>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
           <t>x</t>
@@ -12941,56 +12941,44 @@
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L170" t="inlineStr"/>
       <c r="M170" t="inlineStr"/>
-      <c r="N170" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N170" t="inlineStr"/>
       <c r="O170" t="inlineStr"/>
       <c r="P170" t="inlineStr"/>
-      <c r="Q170" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q170" t="inlineStr"/>
       <c r="R170" t="inlineStr"/>
       <c r="S170" t="inlineStr"/>
-      <c r="T170" t="inlineStr"/>
-      <c r="U170" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr"/>
       <c r="V170" t="inlineStr">
         <is>
-          <t>UnempP</t>
+          <t>Rurality</t>
         </is>
       </c>
       <c r="W170" t="inlineStr">
         <is>
-          <t>Unemployment %</t>
+          <t>Urban-Suburban-Rural</t>
         </is>
       </c>
       <c r="X170" t="inlineStr"/>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB170" t="inlineStr"/>
@@ -13000,12 +12988,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>SDOH Indices &amp; Typology</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
@@ -13013,15 +13001,15 @@
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr"/>
       <c r="G171" t="inlineStr"/>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr"/>
-      <c r="L171" t="inlineStr"/>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M171" t="inlineStr"/>
       <c r="N171" t="inlineStr"/>
       <c r="O171" t="inlineStr"/>
@@ -13029,36 +13017,32 @@
       <c r="Q171" t="inlineStr"/>
       <c r="R171" t="inlineStr"/>
       <c r="S171" t="inlineStr"/>
-      <c r="T171" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T171" t="inlineStr"/>
       <c r="U171" t="inlineStr"/>
       <c r="V171" t="inlineStr">
         <is>
-          <t>LimMobInd</t>
+          <t>EssnWrkE</t>
         </is>
       </c>
       <c r="W171" t="inlineStr">
         <is>
-          <t>Limited Moblility Index</t>
+          <t>Count of Essential Workers</t>
         </is>
       </c>
       <c r="X171" t="inlineStr"/>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB171" t="inlineStr"/>
@@ -13068,12 +13052,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>SDOH Indices &amp; Typology</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
@@ -13081,52 +13065,56 @@
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr"/>
       <c r="G172" t="inlineStr"/>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr"/>
-      <c r="L172" t="inlineStr"/>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O172" t="inlineStr"/>
       <c r="P172" t="inlineStr"/>
-      <c r="Q172" t="inlineStr"/>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R172" t="inlineStr"/>
       <c r="S172" t="inlineStr"/>
-      <c r="T172" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T172" t="inlineStr"/>
       <c r="U172" t="inlineStr"/>
       <c r="V172" t="inlineStr">
         <is>
-          <t>MicaInd</t>
+          <t>EssnWrkP</t>
         </is>
       </c>
       <c r="W172" t="inlineStr">
         <is>
-          <t>Mixed Immigrant Cohesion and Accesibility (MICA) Index</t>
+          <t>Essential Workers %</t>
         </is>
       </c>
       <c r="X172" t="inlineStr"/>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB172" t="inlineStr"/>
@@ -13136,12 +13124,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>SDOH Indices &amp; Typology</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -13149,48 +13137,56 @@
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr"/>
       <c r="G173" t="inlineStr"/>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr"/>
-      <c r="L173" t="inlineStr"/>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M173" t="inlineStr"/>
-      <c r="N173" t="inlineStr"/>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O173" t="inlineStr"/>
       <c r="P173" t="inlineStr"/>
-      <c r="Q173" t="inlineStr"/>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R173" t="inlineStr"/>
       <c r="S173" t="inlineStr"/>
       <c r="T173" t="inlineStr"/>
       <c r="U173" t="inlineStr"/>
       <c r="V173" t="inlineStr">
         <is>
-          <t>NeighbTyp</t>
+          <t>HghRskP</t>
         </is>
       </c>
       <c r="W173" t="inlineStr">
         <is>
-          <t>Neighborhood Type</t>
+          <t>Employed % - High Risk of Injury</t>
         </is>
       </c>
       <c r="X173" t="inlineStr"/>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB173" t="inlineStr"/>
@@ -13200,12 +13196,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>SDOH Indices &amp; Typology</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
@@ -13213,52 +13209,56 @@
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr"/>
       <c r="G174" t="inlineStr"/>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr"/>
-      <c r="L174" t="inlineStr"/>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M174" t="inlineStr"/>
-      <c r="N174" t="inlineStr"/>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O174" t="inlineStr"/>
       <c r="P174" t="inlineStr"/>
-      <c r="Q174" t="inlineStr"/>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R174" t="inlineStr"/>
       <c r="S174" t="inlineStr"/>
-      <c r="T174" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T174" t="inlineStr"/>
       <c r="U174" t="inlineStr"/>
       <c r="V174" t="inlineStr">
         <is>
-          <t>SocEcAdvIn</t>
+          <t>HltCrP</t>
         </is>
       </c>
       <c r="W174" t="inlineStr">
         <is>
-          <t>Socioeconomic Advantage Index</t>
+          <t>Employed % - Health Care</t>
         </is>
       </c>
       <c r="X174" t="inlineStr"/>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB174" t="inlineStr"/>
@@ -13268,12 +13268,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>SDOH Indices &amp; Typology</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
@@ -13281,52 +13281,56 @@
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr"/>
       <c r="G175" t="inlineStr"/>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr"/>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O175" t="inlineStr"/>
       <c r="P175" t="inlineStr"/>
-      <c r="Q175" t="inlineStr"/>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R175" t="inlineStr"/>
       <c r="S175" t="inlineStr"/>
-      <c r="T175" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T175" t="inlineStr"/>
       <c r="U175" t="inlineStr"/>
       <c r="V175" t="inlineStr">
         <is>
-          <t>UrbCoreInd</t>
+          <t>RetailP</t>
         </is>
       </c>
       <c r="W175" t="inlineStr">
         <is>
-          <t>Urban Core Opportunity Index</t>
+          <t>Employed % - Retail</t>
         </is>
       </c>
       <c r="X175" t="inlineStr"/>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB175" t="inlineStr"/>
@@ -13336,12 +13340,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
@@ -13365,40 +13369,40 @@
         </is>
       </c>
       <c r="O176" t="inlineStr"/>
-      <c r="P176" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q176" t="inlineStr"/>
+      <c r="P176" t="inlineStr"/>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R176" t="inlineStr"/>
       <c r="S176" t="inlineStr"/>
       <c r="T176" t="inlineStr"/>
       <c r="U176" t="inlineStr"/>
       <c r="V176" t="inlineStr">
         <is>
-          <t>SviSmryRnk</t>
+          <t>TotWrkE</t>
         </is>
       </c>
       <c r="W176" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) Summary Ranking</t>
+          <t>Count of Working Population</t>
         </is>
       </c>
       <c r="X176" t="inlineStr"/>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB176" t="inlineStr"/>
@@ -13408,12 +13412,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>Great Recession Foreclosure Rate</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
@@ -13431,50 +13435,38 @@
         </is>
       </c>
       <c r="M177" t="inlineStr"/>
-      <c r="N177" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N177" t="inlineStr"/>
       <c r="O177" t="inlineStr"/>
-      <c r="P177" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P177" t="inlineStr"/>
       <c r="Q177" t="inlineStr"/>
       <c r="R177" t="inlineStr"/>
       <c r="S177" t="inlineStr"/>
-      <c r="T177" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T177" t="inlineStr"/>
       <c r="U177" t="inlineStr"/>
       <c r="V177" t="inlineStr">
         <is>
-          <t>SviTh1</t>
+          <t>ForDqP</t>
         </is>
       </c>
       <c r="W177" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 1</t>
+          <t>Foreclosure &amp; Delinquency %</t>
         </is>
       </c>
       <c r="X177" t="inlineStr"/>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
         </is>
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>HUD 2018; ACS 2012, 2018</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB177" t="inlineStr"/>
@@ -13484,12 +13476,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>Great Recession Foreclosure Rate</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
@@ -13507,17 +13499,9 @@
         </is>
       </c>
       <c r="M178" t="inlineStr"/>
-      <c r="N178" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N178" t="inlineStr"/>
       <c r="O178" t="inlineStr"/>
-      <c r="P178" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P178" t="inlineStr"/>
       <c r="Q178" t="inlineStr"/>
       <c r="R178" t="inlineStr"/>
       <c r="S178" t="inlineStr"/>
@@ -13525,28 +13509,28 @@
       <c r="U178" t="inlineStr"/>
       <c r="V178" t="inlineStr">
         <is>
-          <t>SviTh2</t>
+          <t>ForDqTot</t>
         </is>
       </c>
       <c r="W178" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 2</t>
+          <t>Foreclosure &amp; Delinquency Count</t>
         </is>
       </c>
       <c r="X178" t="inlineStr"/>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
         </is>
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>HUD 2018; ACS 2012, 2018</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB178" t="inlineStr"/>
@@ -13556,18 +13540,22 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>Great Recession Foreclosure Rate</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr"/>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr"/>
@@ -13585,40 +13573,40 @@
         </is>
       </c>
       <c r="O179" t="inlineStr"/>
-      <c r="P179" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q179" t="inlineStr"/>
+      <c r="P179" t="inlineStr"/>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R179" t="inlineStr"/>
       <c r="S179" t="inlineStr"/>
       <c r="T179" t="inlineStr"/>
       <c r="U179" t="inlineStr"/>
       <c r="V179" t="inlineStr">
         <is>
-          <t>SviTh3</t>
+          <t>GiniCoeff</t>
         </is>
       </c>
       <c r="W179" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 3</t>
+          <t>Income Inequality (Gini Coefficient)</t>
         </is>
       </c>
       <c r="X179" t="inlineStr"/>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
         </is>
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>HUD 2018; ACS 2012, 2018</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB179" t="inlineStr"/>
@@ -13628,12 +13616,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>Internet Access</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
@@ -13645,61 +13633,1089 @@
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr"/>
-      <c r="L180" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M180" t="inlineStr"/>
-      <c r="N180" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr"/>
       <c r="O180" t="inlineStr"/>
-      <c r="P180" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P180" t="inlineStr"/>
       <c r="Q180" t="inlineStr"/>
       <c r="R180" t="inlineStr"/>
       <c r="S180" t="inlineStr"/>
-      <c r="T180" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T180" t="inlineStr"/>
       <c r="U180" t="inlineStr"/>
       <c r="V180" t="inlineStr">
         <is>
-          <t>SviTh4</t>
+          <t>NoIntP</t>
         </is>
       </c>
       <c r="W180" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 4</t>
+          <t>Households without Internet Access %</t>
         </is>
       </c>
       <c r="X180" t="inlineStr"/>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Internet_Access.md</t>
         </is>
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>ACS 2019</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>American Community Survey 2015-2019 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB180" t="inlineStr"/>
       <c r="AC180" t="inlineStr"/>
       <c r="AD180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Poverty, Income, Gini Coefficient</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr"/>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr"/>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr"/>
+      <c r="P181" t="inlineStr"/>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr"/>
+      <c r="S181" t="inlineStr"/>
+      <c r="T181" t="inlineStr"/>
+      <c r="U181" t="inlineStr"/>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>MedInc</t>
+        </is>
+      </c>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>Median Income</t>
+        </is>
+      </c>
+      <c r="X181" t="inlineStr"/>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+        </is>
+      </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+        </is>
+      </c>
+      <c r="AB181" t="inlineStr"/>
+      <c r="AC181" t="inlineStr"/>
+      <c r="AD181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Poverty, Income, Gini Coefficient</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr"/>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr"/>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr"/>
+      <c r="P182" t="inlineStr"/>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr"/>
+      <c r="S182" t="inlineStr"/>
+      <c r="T182" t="inlineStr"/>
+      <c r="U182" t="inlineStr"/>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>PciE</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>Per Capita Income</t>
+        </is>
+      </c>
+      <c r="X182" t="inlineStr"/>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+        </is>
+      </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+        </is>
+      </c>
+      <c r="AB182" t="inlineStr"/>
+      <c r="AC182" t="inlineStr"/>
+      <c r="AD182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Poverty, Income, Gini Coefficient</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr"/>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr"/>
+      <c r="P183" t="inlineStr"/>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr"/>
+      <c r="S183" t="inlineStr"/>
+      <c r="T183" t="inlineStr"/>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>PovP</t>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t>Poverty %</t>
+        </is>
+      </c>
+      <c r="X183" t="inlineStr"/>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+        </is>
+      </c>
+      <c r="Z183" t="inlineStr">
+        <is>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
+        </is>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+        </is>
+      </c>
+      <c r="AB183" t="inlineStr"/>
+      <c r="AC183" t="inlineStr"/>
+      <c r="AD183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Poverty, Income, Gini Coefficient</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr"/>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr"/>
+      <c r="P184" t="inlineStr"/>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr"/>
+      <c r="S184" t="inlineStr"/>
+      <c r="T184" t="inlineStr"/>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>UnempP</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>Unemployment %</t>
+        </is>
+      </c>
+      <c r="X184" t="inlineStr"/>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+        </is>
+      </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+        </is>
+      </c>
+      <c r="AB184" t="inlineStr"/>
+      <c r="AC184" t="inlineStr"/>
+      <c r="AD184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>SDOH Indices &amp; Typology</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr"/>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr"/>
+      <c r="N185" t="inlineStr"/>
+      <c r="O185" t="inlineStr"/>
+      <c r="P185" t="inlineStr"/>
+      <c r="Q185" t="inlineStr"/>
+      <c r="R185" t="inlineStr"/>
+      <c r="S185" t="inlineStr"/>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr"/>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>LimMobInd</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>Limited Moblility Index</t>
+        </is>
+      </c>
+      <c r="X185" t="inlineStr"/>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
+        </is>
+      </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>Kolak et al., 2020</t>
+        </is>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>Kolak et al., 2020</t>
+        </is>
+      </c>
+      <c r="AB185" t="inlineStr"/>
+      <c r="AC185" t="inlineStr"/>
+      <c r="AD185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>SDOH Indices &amp; Typology</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr"/>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="inlineStr"/>
+      <c r="N186" t="inlineStr"/>
+      <c r="O186" t="inlineStr"/>
+      <c r="P186" t="inlineStr"/>
+      <c r="Q186" t="inlineStr"/>
+      <c r="R186" t="inlineStr"/>
+      <c r="S186" t="inlineStr"/>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr"/>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>MicaInd</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>Mixed Immigrant Cohesion and Accesibility (MICA) Index</t>
+        </is>
+      </c>
+      <c r="X186" t="inlineStr"/>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
+        </is>
+      </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>Kolak et al., 2020</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>Kolak et al., 2020</t>
+        </is>
+      </c>
+      <c r="AB186" t="inlineStr"/>
+      <c r="AC186" t="inlineStr"/>
+      <c r="AD186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>SDOH Indices &amp; Typology</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr"/>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr"/>
+      <c r="N187" t="inlineStr"/>
+      <c r="O187" t="inlineStr"/>
+      <c r="P187" t="inlineStr"/>
+      <c r="Q187" t="inlineStr"/>
+      <c r="R187" t="inlineStr"/>
+      <c r="S187" t="inlineStr"/>
+      <c r="T187" t="inlineStr"/>
+      <c r="U187" t="inlineStr"/>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>NeighbTyp</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>Neighborhood Type</t>
+        </is>
+      </c>
+      <c r="X187" t="inlineStr"/>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
+        </is>
+      </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>Kolak et al., 2020</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>Kolak et al., 2020</t>
+        </is>
+      </c>
+      <c r="AB187" t="inlineStr"/>
+      <c r="AC187" t="inlineStr"/>
+      <c r="AD187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>SDOH Indices &amp; Typology</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr"/>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" t="inlineStr"/>
+      <c r="N188" t="inlineStr"/>
+      <c r="O188" t="inlineStr"/>
+      <c r="P188" t="inlineStr"/>
+      <c r="Q188" t="inlineStr"/>
+      <c r="R188" t="inlineStr"/>
+      <c r="S188" t="inlineStr"/>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr"/>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>SocEcAdvIn</t>
+        </is>
+      </c>
+      <c r="W188" t="inlineStr">
+        <is>
+          <t>Socioeconomic Advantage Index</t>
+        </is>
+      </c>
+      <c r="X188" t="inlineStr"/>
+      <c r="Y188" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
+        </is>
+      </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>Kolak et al., 2020</t>
+        </is>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>Kolak et al., 2020</t>
+        </is>
+      </c>
+      <c r="AB188" t="inlineStr"/>
+      <c r="AC188" t="inlineStr"/>
+      <c r="AD188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>SDOH Indices &amp; Typology</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr"/>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
+      <c r="O189" t="inlineStr"/>
+      <c r="P189" t="inlineStr"/>
+      <c r="Q189" t="inlineStr"/>
+      <c r="R189" t="inlineStr"/>
+      <c r="S189" t="inlineStr"/>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr"/>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>UrbCoreInd</t>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t>Urban Core Opportunity Index</t>
+        </is>
+      </c>
+      <c r="X189" t="inlineStr"/>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
+        </is>
+      </c>
+      <c r="Z189" t="inlineStr">
+        <is>
+          <t>Kolak et al., 2020</t>
+        </is>
+      </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>Kolak et al., 2020</t>
+        </is>
+      </c>
+      <c r="AB189" t="inlineStr"/>
+      <c r="AC189" t="inlineStr"/>
+      <c r="AD189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr"/>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr"/>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr"/>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr"/>
+      <c r="R190" t="inlineStr"/>
+      <c r="S190" t="inlineStr"/>
+      <c r="T190" t="inlineStr"/>
+      <c r="U190" t="inlineStr"/>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>SviSmryRnk</t>
+        </is>
+      </c>
+      <c r="W190" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) Summary Ranking</t>
+        </is>
+      </c>
+      <c r="X190" t="inlineStr"/>
+      <c r="Y190" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z190" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB190" t="inlineStr"/>
+      <c r="AC190" t="inlineStr"/>
+      <c r="AD190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr"/>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr"/>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr"/>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr"/>
+      <c r="R191" t="inlineStr"/>
+      <c r="S191" t="inlineStr"/>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr"/>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>SviTh1</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 1</t>
+        </is>
+      </c>
+      <c r="X191" t="inlineStr"/>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB191" t="inlineStr"/>
+      <c r="AC191" t="inlineStr"/>
+      <c r="AD191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr"/>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr"/>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr"/>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr"/>
+      <c r="R192" t="inlineStr"/>
+      <c r="S192" t="inlineStr"/>
+      <c r="T192" t="inlineStr"/>
+      <c r="U192" t="inlineStr"/>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>SviTh2</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 2</t>
+        </is>
+      </c>
+      <c r="X192" t="inlineStr"/>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z192" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB192" t="inlineStr"/>
+      <c r="AC192" t="inlineStr"/>
+      <c r="AD192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr"/>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr"/>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr"/>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q193" t="inlineStr"/>
+      <c r="R193" t="inlineStr"/>
+      <c r="S193" t="inlineStr"/>
+      <c r="T193" t="inlineStr"/>
+      <c r="U193" t="inlineStr"/>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>SviTh3</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 3</t>
+        </is>
+      </c>
+      <c r="X193" t="inlineStr"/>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB193" t="inlineStr"/>
+      <c r="AC193" t="inlineStr"/>
+      <c r="AD193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr"/>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr"/>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr"/>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr"/>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q194" t="inlineStr"/>
+      <c r="R194" t="inlineStr"/>
+      <c r="S194" t="inlineStr"/>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr"/>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>SviTh4</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 4</t>
+        </is>
+      </c>
+      <c r="X194" t="inlineStr"/>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB194" t="inlineStr"/>
+      <c r="AC194" t="inlineStr"/>
+      <c r="AD194" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/src/reference/data-dictionaries/T_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/T_Dict.xlsx
@@ -12574,7 +12574,7 @@
       </c>
       <c r="W164" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest HIV Testing Facility with impedance</t>
+          <t>Driving time (min) to nearest HCV Testing Facility with impedance</t>
         </is>
       </c>
       <c r="X164" t="inlineStr"/>

--- a/docs/src/reference/data-dictionaries/T_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/T_Dict.xlsx
@@ -7605,12 +7605,12 @@
       <c r="U91" t="inlineStr"/>
       <c r="V91" t="inlineStr">
         <is>
-          <t>HivTmDr2</t>
+          <t>HcvTmDr2</t>
         </is>
       </c>
       <c r="W91" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest HIV Testing Facility, with impedance</t>
+          <t>Driving time (min) to nearest HCV Testing Facility with impedance</t>
         </is>
       </c>
       <c r="X91" t="inlineStr"/>
@@ -7641,7 +7641,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Spatial Access to Hospitals</t>
+          <t>Spatial Access to HIV Testing</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -7655,11 +7655,7 @@
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr"/>
       <c r="Q92" t="inlineStr"/>
@@ -7673,28 +7669,28 @@
       <c r="U92" t="inlineStr"/>
       <c r="V92" t="inlineStr">
         <is>
-          <t>HospCntDr</t>
+          <t>HivCntDr</t>
         </is>
       </c>
       <c r="W92" t="inlineStr">
         <is>
-          <t>Count of Hospitals (30-min drive)</t>
+          <t>Count of HIV Providers</t>
         </is>
       </c>
       <c r="X92" t="inlineStr"/>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Hospitals.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HIVTesting.md</t>
         </is>
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr"/>
@@ -7709,7 +7705,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Spatial Access to Hospitals</t>
+          <t>Spatial Access to HIV Testing</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -7723,11 +7719,7 @@
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr"/>
       <c r="Q93" t="inlineStr"/>
@@ -7741,28 +7733,28 @@
       <c r="U93" t="inlineStr"/>
       <c r="V93" t="inlineStr">
         <is>
-          <t>HospMinDis</t>
+          <t>HivMinDis</t>
         </is>
       </c>
       <c r="W93" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Hospital</t>
+          <t>Distance to nearest HIV Provider</t>
         </is>
       </c>
       <c r="X93" t="inlineStr"/>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Hospitals.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HIVTesting.md</t>
         </is>
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr"/>
@@ -7777,7 +7769,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Spatial Access to Hospitals</t>
+          <t>Spatial Access to HIV Testing</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -7791,11 +7783,7 @@
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr"/>
       <c r="Q94" t="inlineStr"/>
@@ -7805,36 +7793,32 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T94" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T94" t="inlineStr"/>
       <c r="U94" t="inlineStr"/>
       <c r="V94" t="inlineStr">
         <is>
-          <t>HospTmDr</t>
+          <t>HivTmDr</t>
         </is>
       </c>
       <c r="W94" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest Hospital</t>
+          <t>Driving time to nearest HIV Provider</t>
         </is>
       </c>
       <c r="X94" t="inlineStr"/>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Hospitals.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HIVTesting.md</t>
         </is>
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr"/>
@@ -7849,7 +7833,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Spatial Access to Hospitals</t>
+          <t>Spatial Access to HIV Testing</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -7877,28 +7861,28 @@
       <c r="U95" t="inlineStr"/>
       <c r="V95" t="inlineStr">
         <is>
-          <t>HospTmDr2</t>
+          <t>HivTmDr2</t>
         </is>
       </c>
       <c r="W95" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest Hospital with Impedance Factor</t>
+          <t>Driving time (min) to nearest HIV Testing Facility, with impedance</t>
         </is>
       </c>
       <c r="X95" t="inlineStr"/>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Hospitals.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HIVTesting.md</t>
         </is>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr"/>
@@ -7913,7 +7897,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Spatial Access to MOUDs</t>
+          <t>Spatial Access to Hospitals</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -7945,28 +7929,28 @@
       <c r="U96" t="inlineStr"/>
       <c r="V96" t="inlineStr">
         <is>
-          <t>BupCntBk30</t>
+          <t>HospCntDr</t>
         </is>
       </c>
       <c r="W96" t="inlineStr">
         <is>
-          <t>Count of Buprenorphine Providers (30-min bike)</t>
+          <t>Count of Hospitals (30-min drive)</t>
         </is>
       </c>
       <c r="X96" t="inlineStr"/>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Hospitals.md</t>
         </is>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
+          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
+          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr"/>
@@ -7981,7 +7965,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Spatial Access to MOUDs</t>
+          <t>Spatial Access to Hospitals</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -8013,28 +7997,28 @@
       <c r="U97" t="inlineStr"/>
       <c r="V97" t="inlineStr">
         <is>
-          <t>BupCntBk60</t>
+          <t>HospMinDis</t>
         </is>
       </c>
       <c r="W97" t="inlineStr">
         <is>
-          <t>Count of Buprenorphine Providers (60-min bike)</t>
+          <t>Distance (mi) to nearest Hospital</t>
         </is>
       </c>
       <c r="X97" t="inlineStr"/>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Hospitals.md</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
+          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
+          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr"/>
@@ -8049,7 +8033,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Spatial Access to MOUDs</t>
+          <t>Spatial Access to Hospitals</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -8077,32 +8061,36 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T98" t="inlineStr"/>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U98" t="inlineStr"/>
       <c r="V98" t="inlineStr">
         <is>
-          <t>BupCntDr30</t>
+          <t>HospTmDr</t>
         </is>
       </c>
       <c r="W98" t="inlineStr">
         <is>
-          <t>Count of Buprenorphine Providers (30-min drive)</t>
+          <t>Driving time (min) to nearest Hospital</t>
         </is>
       </c>
       <c r="X98" t="inlineStr"/>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Hospitals.md</t>
         </is>
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
+          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
+          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr"/>
@@ -8117,7 +8105,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Spatial Access to MOUDs</t>
+          <t>Spatial Access to Hospitals</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -8145,28 +8133,28 @@
       <c r="U99" t="inlineStr"/>
       <c r="V99" t="inlineStr">
         <is>
-          <t>BupCntDr60</t>
+          <t>HospTmDr2</t>
         </is>
       </c>
       <c r="W99" t="inlineStr">
         <is>
-          <t>Count of buprenorphine providers (drive)</t>
+          <t>Driving time (min) to nearest Hospital with Impedance Factor</t>
         </is>
       </c>
       <c r="X99" t="inlineStr"/>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Hospitals.md</t>
         </is>
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
+          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
+          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr"/>
@@ -8213,12 +8201,12 @@
       <c r="U100" t="inlineStr"/>
       <c r="V100" t="inlineStr">
         <is>
-          <t>BupCntWk30</t>
+          <t>BupCntBk30</t>
         </is>
       </c>
       <c r="W100" t="inlineStr">
         <is>
-          <t>Count of Buprenorphine Providers (30-min walk)</t>
+          <t>Count of Buprenorphine Providers (30-min bike)</t>
         </is>
       </c>
       <c r="X100" t="inlineStr"/>
@@ -8281,12 +8269,12 @@
       <c r="U101" t="inlineStr"/>
       <c r="V101" t="inlineStr">
         <is>
-          <t>BupCntWk60</t>
+          <t>BupCntBk60</t>
         </is>
       </c>
       <c r="W101" t="inlineStr">
         <is>
-          <t>Count of Buprenorphine Providers (60-min walk)</t>
+          <t>Count of Buprenorphine Providers (60-min bike)</t>
         </is>
       </c>
       <c r="X101" t="inlineStr"/>
@@ -8349,12 +8337,12 @@
       <c r="U102" t="inlineStr"/>
       <c r="V102" t="inlineStr">
         <is>
-          <t>BupMinDis</t>
+          <t>BupCntDr30</t>
         </is>
       </c>
       <c r="W102" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Buprenorphine Provider</t>
+          <t>Count of Buprenorphine Providers (30-min drive)</t>
         </is>
       </c>
       <c r="X102" t="inlineStr"/>
@@ -8399,26 +8387,26 @@
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr"/>
       <c r="Q103" t="inlineStr"/>
       <c r="R103" t="inlineStr"/>
-      <c r="S103" t="inlineStr"/>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T103" t="inlineStr"/>
       <c r="U103" t="inlineStr"/>
       <c r="V103" t="inlineStr">
         <is>
-          <t>BupRm30</t>
+          <t>BupCntDr60</t>
         </is>
       </c>
       <c r="W103" t="inlineStr">
         <is>
-          <t>Buprenorphine access 30 minutes (RAAM)</t>
+          <t>Count of buprenorphine providers (drive)</t>
         </is>
       </c>
       <c r="X103" t="inlineStr"/>
@@ -8472,17 +8460,21 @@
       <c r="P104" t="inlineStr"/>
       <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr"/>
-      <c r="S104" t="inlineStr"/>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T104" t="inlineStr"/>
       <c r="U104" t="inlineStr"/>
       <c r="V104" t="inlineStr">
         <is>
-          <t>BupRm60</t>
+          <t>BupCntWk30</t>
         </is>
       </c>
       <c r="W104" t="inlineStr">
         <is>
-          <t>Buprenorphine access 60 minutes (RAAM)</t>
+          <t>Count of Buprenorphine Providers (30-min walk)</t>
         </is>
       </c>
       <c r="X104" t="inlineStr"/>
@@ -8536,17 +8528,21 @@
       <c r="P105" t="inlineStr"/>
       <c r="Q105" t="inlineStr"/>
       <c r="R105" t="inlineStr"/>
-      <c r="S105" t="inlineStr"/>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T105" t="inlineStr"/>
       <c r="U105" t="inlineStr"/>
       <c r="V105" t="inlineStr">
         <is>
-          <t>BupRm90</t>
+          <t>BupCntWk60</t>
         </is>
       </c>
       <c r="W105" t="inlineStr">
         <is>
-          <t>Buprenorphine access 90 minutes (RAAM)</t>
+          <t>Count of Buprenorphine Providers (60-min walk)</t>
         </is>
       </c>
       <c r="X105" t="inlineStr"/>
@@ -8605,20 +8601,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T106" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T106" t="inlineStr"/>
       <c r="U106" t="inlineStr"/>
       <c r="V106" t="inlineStr">
         <is>
-          <t>BupTmBk</t>
+          <t>BupMinDis</t>
         </is>
       </c>
       <c r="W106" t="inlineStr">
         <is>
-          <t>Biking Time (min) to nearest Buprenorphine Provider</t>
+          <t>Distance (mi) to nearest Buprenorphine Provider</t>
         </is>
       </c>
       <c r="X106" t="inlineStr"/>
@@ -8672,25 +8664,17 @@
       <c r="P107" t="inlineStr"/>
       <c r="Q107" t="inlineStr"/>
       <c r="R107" t="inlineStr"/>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="T107" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S107" t="inlineStr"/>
+      <c r="T107" t="inlineStr"/>
       <c r="U107" t="inlineStr"/>
       <c r="V107" t="inlineStr">
         <is>
-          <t>BupTmDr</t>
+          <t>BupRm30</t>
         </is>
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Buprenorphine Provider</t>
+          <t>Buprenorphine access 30 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X107" t="inlineStr"/>
@@ -8744,25 +8728,17 @@
       <c r="P108" t="inlineStr"/>
       <c r="Q108" t="inlineStr"/>
       <c r="R108" t="inlineStr"/>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="T108" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S108" t="inlineStr"/>
+      <c r="T108" t="inlineStr"/>
       <c r="U108" t="inlineStr"/>
       <c r="V108" t="inlineStr">
         <is>
-          <t>BupTmWk</t>
+          <t>BupRm60</t>
         </is>
       </c>
       <c r="W108" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Buprenorphine Provider</t>
+          <t>Buprenorphine access 60 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X108" t="inlineStr"/>
@@ -8816,21 +8792,17 @@
       <c r="P109" t="inlineStr"/>
       <c r="Q109" t="inlineStr"/>
       <c r="R109" t="inlineStr"/>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S109" t="inlineStr"/>
       <c r="T109" t="inlineStr"/>
       <c r="U109" t="inlineStr"/>
       <c r="V109" t="inlineStr">
         <is>
-          <t>MetCntBk30</t>
+          <t>BupRm90</t>
         </is>
       </c>
       <c r="W109" t="inlineStr">
         <is>
-          <t>Count of methadone providers (30-min bike)</t>
+          <t>Buprenorphine access 90 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X109" t="inlineStr"/>
@@ -8889,16 +8861,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T110" t="inlineStr"/>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U110" t="inlineStr"/>
       <c r="V110" t="inlineStr">
         <is>
-          <t>MetCntBk60</t>
+          <t>BupTmBk</t>
         </is>
       </c>
       <c r="W110" t="inlineStr">
         <is>
-          <t>Count of Methadone Providers (60-min bike)</t>
+          <t>Biking Time (min) to nearest Buprenorphine Provider</t>
         </is>
       </c>
       <c r="X110" t="inlineStr"/>
@@ -8957,16 +8933,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T111" t="inlineStr"/>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U111" t="inlineStr"/>
       <c r="V111" t="inlineStr">
         <is>
-          <t>MetCntDr30</t>
+          <t>BupTmDr</t>
         </is>
       </c>
       <c r="W111" t="inlineStr">
         <is>
-          <t>Count of Methadone Providers (30-min drive)</t>
+          <t>Driving Time (min) to nearest Buprenorphine Provider</t>
         </is>
       </c>
       <c r="X111" t="inlineStr"/>
@@ -9011,7 +8991,11 @@
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O112" t="inlineStr"/>
       <c r="P112" t="inlineStr"/>
       <c r="Q112" t="inlineStr"/>
@@ -9021,16 +9005,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T112" t="inlineStr"/>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U112" t="inlineStr"/>
       <c r="V112" t="inlineStr">
         <is>
-          <t>MetCntDr60</t>
+          <t>BupTmWk</t>
         </is>
       </c>
       <c r="W112" t="inlineStr">
         <is>
-          <t>Count of methadone providers (drive)</t>
+          <t>Walking Time (min) to nearest Buprenorphine Provider</t>
         </is>
       </c>
       <c r="X112" t="inlineStr"/>
@@ -9093,12 +9081,12 @@
       <c r="U113" t="inlineStr"/>
       <c r="V113" t="inlineStr">
         <is>
-          <t>MetCntWk30</t>
+          <t>MetCntBk30</t>
         </is>
       </c>
       <c r="W113" t="inlineStr">
         <is>
-          <t>Count of Methadone Providers (60-min walk)</t>
+          <t>Count of methadone providers (30-min bike)</t>
         </is>
       </c>
       <c r="X113" t="inlineStr"/>
@@ -9161,12 +9149,12 @@
       <c r="U114" t="inlineStr"/>
       <c r="V114" t="inlineStr">
         <is>
-          <t>MetCntWk60</t>
+          <t>MetCntBk60</t>
         </is>
       </c>
       <c r="W114" t="inlineStr">
         <is>
-          <t>Count of Methadone Providers (30-min walk)</t>
+          <t>Count of Methadone Providers (60-min bike)</t>
         </is>
       </c>
       <c r="X114" t="inlineStr"/>
@@ -9229,12 +9217,12 @@
       <c r="U115" t="inlineStr"/>
       <c r="V115" t="inlineStr">
         <is>
-          <t>MetMinDis</t>
+          <t>MetCntDr30</t>
         </is>
       </c>
       <c r="W115" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Methadone Provider</t>
+          <t>Count of Methadone Providers (30-min drive)</t>
         </is>
       </c>
       <c r="X115" t="inlineStr"/>
@@ -9268,26 +9256,10 @@
           <t>Spatial Access to MOUDs</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr"/>
@@ -9295,26 +9267,26 @@
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr"/>
       <c r="P116" t="inlineStr"/>
       <c r="Q116" t="inlineStr"/>
       <c r="R116" t="inlineStr"/>
-      <c r="S116" t="inlineStr"/>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T116" t="inlineStr"/>
       <c r="U116" t="inlineStr"/>
       <c r="V116" t="inlineStr">
         <is>
-          <t>MetRm30</t>
+          <t>MetCntDr60</t>
         </is>
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>Methadone access 30 minutes (RAAM)</t>
+          <t>Count of methadone providers (drive)</t>
         </is>
       </c>
       <c r="X116" t="inlineStr"/>
@@ -9348,26 +9320,10 @@
           <t>Spatial Access to MOUDs</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr"/>
@@ -9384,17 +9340,21 @@
       <c r="P117" t="inlineStr"/>
       <c r="Q117" t="inlineStr"/>
       <c r="R117" t="inlineStr"/>
-      <c r="S117" t="inlineStr"/>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T117" t="inlineStr"/>
       <c r="U117" t="inlineStr"/>
       <c r="V117" t="inlineStr">
         <is>
-          <t>MetRm60</t>
+          <t>MetCntWk30</t>
         </is>
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>Methadone access 60 minutes (RAAM)</t>
+          <t>Count of Methadone Providers (60-min walk)</t>
         </is>
       </c>
       <c r="X117" t="inlineStr"/>
@@ -9428,26 +9388,10 @@
           <t>Spatial Access to MOUDs</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr"/>
@@ -9464,17 +9408,21 @@
       <c r="P118" t="inlineStr"/>
       <c r="Q118" t="inlineStr"/>
       <c r="R118" t="inlineStr"/>
-      <c r="S118" t="inlineStr"/>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T118" t="inlineStr"/>
       <c r="U118" t="inlineStr"/>
       <c r="V118" t="inlineStr">
         <is>
-          <t>MetRm90</t>
+          <t>MetCntWk60</t>
         </is>
       </c>
       <c r="W118" t="inlineStr">
         <is>
-          <t>Methadone access 90 minutes (RAAM)</t>
+          <t>Count of Methadone Providers (30-min walk)</t>
         </is>
       </c>
       <c r="X118" t="inlineStr"/>
@@ -9533,20 +9481,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T119" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T119" t="inlineStr"/>
       <c r="U119" t="inlineStr"/>
       <c r="V119" t="inlineStr">
         <is>
-          <t>MetTmBk</t>
+          <t>MetMinDis</t>
         </is>
       </c>
       <c r="W119" t="inlineStr">
         <is>
-          <t>Biking Time (min) to nearest Methadone Provider</t>
+          <t>Distance (mi) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X119" t="inlineStr"/>
@@ -9580,10 +9524,26 @@
           <t>Spatial Access to MOUDs</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr"/>
-      <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr"/>
@@ -9600,25 +9560,17 @@
       <c r="P120" t="inlineStr"/>
       <c r="Q120" t="inlineStr"/>
       <c r="R120" t="inlineStr"/>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="T120" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S120" t="inlineStr"/>
+      <c r="T120" t="inlineStr"/>
       <c r="U120" t="inlineStr"/>
       <c r="V120" t="inlineStr">
         <is>
-          <t>MetTmDr</t>
+          <t>MetRm30</t>
         </is>
       </c>
       <c r="W120" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Methadone Provider</t>
+          <t>Methadone access 30 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X120" t="inlineStr"/>
@@ -9652,10 +9604,26 @@
           <t>Spatial Access to MOUDs</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr"/>
-      <c r="D121" t="inlineStr"/>
-      <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr"/>
@@ -9672,25 +9640,17 @@
       <c r="P121" t="inlineStr"/>
       <c r="Q121" t="inlineStr"/>
       <c r="R121" t="inlineStr"/>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="T121" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S121" t="inlineStr"/>
+      <c r="T121" t="inlineStr"/>
       <c r="U121" t="inlineStr"/>
       <c r="V121" t="inlineStr">
         <is>
-          <t>MetTmWk</t>
+          <t>MetRm60</t>
         </is>
       </c>
       <c r="W121" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Methadone Provider</t>
+          <t>Methadone access 60 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X121" t="inlineStr"/>
@@ -9724,10 +9684,26 @@
           <t>Spatial Access to MOUDs</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr"/>
-      <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr"/>
@@ -9744,21 +9720,17 @@
       <c r="P122" t="inlineStr"/>
       <c r="Q122" t="inlineStr"/>
       <c r="R122" t="inlineStr"/>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S122" t="inlineStr"/>
       <c r="T122" t="inlineStr"/>
       <c r="U122" t="inlineStr"/>
       <c r="V122" t="inlineStr">
         <is>
-          <t>MoudMinDis</t>
+          <t>MetRm90</t>
         </is>
       </c>
       <c r="W122" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest MOUD (any)</t>
+          <t>Methadone access 90 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X122" t="inlineStr"/>
@@ -9817,16 +9789,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T123" t="inlineStr"/>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U123" t="inlineStr"/>
       <c r="V123" t="inlineStr">
         <is>
-          <t>NaltCntBk30</t>
+          <t>MetTmBk</t>
         </is>
       </c>
       <c r="W123" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (30-min bike)</t>
+          <t>Biking Time (min) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X123" t="inlineStr"/>
@@ -9885,16 +9861,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T124" t="inlineStr"/>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U124" t="inlineStr"/>
       <c r="V124" t="inlineStr">
         <is>
-          <t>NaltCntBk60</t>
+          <t>MetTmDr</t>
         </is>
       </c>
       <c r="W124" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (60-min bike)</t>
+          <t>Driving Time (min) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X124" t="inlineStr"/>
@@ -9953,16 +9933,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T125" t="inlineStr"/>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U125" t="inlineStr"/>
       <c r="V125" t="inlineStr">
         <is>
-          <t>NaltCntDr30</t>
+          <t>MetTmWk</t>
         </is>
       </c>
       <c r="W125" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (30-min drive)</t>
+          <t>Walking Time (min) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X125" t="inlineStr"/>
@@ -10007,7 +9991,11 @@
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr"/>
       <c r="Q126" t="inlineStr"/>
@@ -10021,12 +10009,12 @@
       <c r="U126" t="inlineStr"/>
       <c r="V126" t="inlineStr">
         <is>
-          <t>NaltCntDr60</t>
+          <t>MoudMinDis</t>
         </is>
       </c>
       <c r="W126" t="inlineStr">
         <is>
-          <t>Count of naltrexone providers (drive)</t>
+          <t>Distance (mi) to nearest MOUD (any)</t>
         </is>
       </c>
       <c r="X126" t="inlineStr"/>
@@ -10089,12 +10077,12 @@
       <c r="U127" t="inlineStr"/>
       <c r="V127" t="inlineStr">
         <is>
-          <t>NaltCntWk30</t>
+          <t>NaltCntBk30</t>
         </is>
       </c>
       <c r="W127" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (30-min walk)</t>
+          <t>Count of Naltrexone Providers (30-min bike)</t>
         </is>
       </c>
       <c r="X127" t="inlineStr"/>
@@ -10157,12 +10145,12 @@
       <c r="U128" t="inlineStr"/>
       <c r="V128" t="inlineStr">
         <is>
-          <t>NaltCntWk60</t>
+          <t>NaltCntBk60</t>
         </is>
       </c>
       <c r="W128" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (60-min walk)</t>
+          <t>Count of Naltrexone Providers (60-min bike)</t>
         </is>
       </c>
       <c r="X128" t="inlineStr"/>
@@ -10225,12 +10213,12 @@
       <c r="U129" t="inlineStr"/>
       <c r="V129" t="inlineStr">
         <is>
-          <t>NaltMinDis</t>
+          <t>NaltCntDr30</t>
         </is>
       </c>
       <c r="W129" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Naltrexone Provider</t>
+          <t>Count of Naltrexone Providers (30-min drive)</t>
         </is>
       </c>
       <c r="X129" t="inlineStr"/>
@@ -10275,26 +10263,26 @@
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr"/>
       <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N130" t="inlineStr"/>
       <c r="O130" t="inlineStr"/>
       <c r="P130" t="inlineStr"/>
       <c r="Q130" t="inlineStr"/>
       <c r="R130" t="inlineStr"/>
-      <c r="S130" t="inlineStr"/>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T130" t="inlineStr"/>
       <c r="U130" t="inlineStr"/>
       <c r="V130" t="inlineStr">
         <is>
-          <t>NaltRm30</t>
+          <t>NaltCntDr60</t>
         </is>
       </c>
       <c r="W130" t="inlineStr">
         <is>
-          <t>Naltrexone access 30 minutes (RAAM)</t>
+          <t>Count of naltrexone providers (drive)</t>
         </is>
       </c>
       <c r="X130" t="inlineStr"/>
@@ -10348,17 +10336,21 @@
       <c r="P131" t="inlineStr"/>
       <c r="Q131" t="inlineStr"/>
       <c r="R131" t="inlineStr"/>
-      <c r="S131" t="inlineStr"/>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T131" t="inlineStr"/>
       <c r="U131" t="inlineStr"/>
       <c r="V131" t="inlineStr">
         <is>
-          <t>NaltRm60</t>
+          <t>NaltCntWk30</t>
         </is>
       </c>
       <c r="W131" t="inlineStr">
         <is>
-          <t>Naltrexone access 60 minutes (RAAM)</t>
+          <t>Count of Naltrexone Providers (30-min walk)</t>
         </is>
       </c>
       <c r="X131" t="inlineStr"/>
@@ -10412,17 +10404,21 @@
       <c r="P132" t="inlineStr"/>
       <c r="Q132" t="inlineStr"/>
       <c r="R132" t="inlineStr"/>
-      <c r="S132" t="inlineStr"/>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T132" t="inlineStr"/>
       <c r="U132" t="inlineStr"/>
       <c r="V132" t="inlineStr">
         <is>
-          <t>NaltRm90</t>
+          <t>NaltCntWk60</t>
         </is>
       </c>
       <c r="W132" t="inlineStr">
         <is>
-          <t>Naltrexone access 90 minutes (RAAM)</t>
+          <t>Count of Naltrexone Providers (60-min walk)</t>
         </is>
       </c>
       <c r="X132" t="inlineStr"/>
@@ -10481,20 +10477,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T133" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T133" t="inlineStr"/>
       <c r="U133" t="inlineStr"/>
       <c r="V133" t="inlineStr">
         <is>
-          <t>NaltTmBk</t>
+          <t>NaltMinDis</t>
         </is>
       </c>
       <c r="W133" t="inlineStr">
         <is>
-          <t>Biking Time (min) to nearest Naltrexone Provider</t>
+          <t>Distance (mi) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X133" t="inlineStr"/>
@@ -10548,25 +10540,17 @@
       <c r="P134" t="inlineStr"/>
       <c r="Q134" t="inlineStr"/>
       <c r="R134" t="inlineStr"/>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="T134" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S134" t="inlineStr"/>
+      <c r="T134" t="inlineStr"/>
       <c r="U134" t="inlineStr"/>
       <c r="V134" t="inlineStr">
         <is>
-          <t>NaltTmDr</t>
+          <t>NaltRm30</t>
         </is>
       </c>
       <c r="W134" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Naltrexone Provider</t>
+          <t>Naltrexone access 30 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X134" t="inlineStr"/>
@@ -10620,25 +10604,17 @@
       <c r="P135" t="inlineStr"/>
       <c r="Q135" t="inlineStr"/>
       <c r="R135" t="inlineStr"/>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="T135" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S135" t="inlineStr"/>
+      <c r="T135" t="inlineStr"/>
       <c r="U135" t="inlineStr"/>
       <c r="V135" t="inlineStr">
         <is>
-          <t>NaltTmWk</t>
+          <t>NaltRm60</t>
         </is>
       </c>
       <c r="W135" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Naltrexone Provider</t>
+          <t>Naltrexone access 60 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X135" t="inlineStr"/>
@@ -10683,30 +10659,26 @@
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
-      <c r="O136" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr"/>
       <c r="P136" t="inlineStr"/>
       <c r="Q136" t="inlineStr"/>
       <c r="R136" t="inlineStr"/>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S136" t="inlineStr"/>
       <c r="T136" t="inlineStr"/>
       <c r="U136" t="inlineStr"/>
       <c r="V136" t="inlineStr">
         <is>
-          <t>OtpCntDr</t>
+          <t>NaltRm90</t>
         </is>
       </c>
       <c r="W136" t="inlineStr">
         <is>
-          <t>Count of Opioid Treatment Programs (OTP) (30-min drive)</t>
+          <t>Naltrexone access 90 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X136" t="inlineStr"/>
@@ -10751,12 +10723,12 @@
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
-      <c r="O137" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr"/>
       <c r="P137" t="inlineStr"/>
       <c r="Q137" t="inlineStr"/>
       <c r="R137" t="inlineStr"/>
@@ -10765,16 +10737,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T137" t="inlineStr"/>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U137" t="inlineStr"/>
       <c r="V137" t="inlineStr">
         <is>
-          <t>OtpMinDis</t>
+          <t>NaltTmBk</t>
         </is>
       </c>
       <c r="W137" t="inlineStr">
         <is>
-          <t>Distance to nearest OTP</t>
+          <t>Biking Time (min) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X137" t="inlineStr"/>
@@ -10819,12 +10795,12 @@
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr"/>
       <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
-      <c r="O138" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr"/>
       <c r="P138" t="inlineStr"/>
       <c r="Q138" t="inlineStr"/>
       <c r="R138" t="inlineStr"/>
@@ -10841,12 +10817,12 @@
       <c r="U138" t="inlineStr"/>
       <c r="V138" t="inlineStr">
         <is>
-          <t>OtpTmDr</t>
+          <t>NaltTmDr</t>
         </is>
       </c>
       <c r="W138" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP)</t>
+          <t>Driving Time (min) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X138" t="inlineStr"/>
@@ -10891,7 +10867,11 @@
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr"/>
       <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O139" t="inlineStr"/>
       <c r="P139" t="inlineStr"/>
       <c r="Q139" t="inlineStr"/>
@@ -10901,16 +10881,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T139" t="inlineStr"/>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U139" t="inlineStr"/>
       <c r="V139" t="inlineStr">
         <is>
-          <t>TlBupCntBk30</t>
+          <t>NaltTmWk</t>
         </is>
       </c>
       <c r="W139" t="inlineStr">
         <is>
-          <t>Count of telehealth buprenorphine providers within 30-minute bike ride</t>
+          <t>Walking Time (min) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X139" t="inlineStr"/>
@@ -10956,7 +10940,11 @@
       <c r="L140" t="inlineStr"/>
       <c r="M140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
-      <c r="O140" t="inlineStr"/>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr"/>
       <c r="Q140" t="inlineStr"/>
       <c r="R140" t="inlineStr"/>
@@ -10969,12 +10957,12 @@
       <c r="U140" t="inlineStr"/>
       <c r="V140" t="inlineStr">
         <is>
-          <t>TlBupCntDr30</t>
+          <t>OtpCntDr</t>
         </is>
       </c>
       <c r="W140" t="inlineStr">
         <is>
-          <t>Count of telehealth buprenorphine providers within 30-minute drive</t>
+          <t>Count of Opioid Treatment Programs (OTP) (30-min drive)</t>
         </is>
       </c>
       <c r="X140" t="inlineStr"/>
@@ -11020,7 +11008,11 @@
       <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
-      <c r="O141" t="inlineStr"/>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr"/>
       <c r="Q141" t="inlineStr"/>
       <c r="R141" t="inlineStr"/>
@@ -11033,12 +11025,12 @@
       <c r="U141" t="inlineStr"/>
       <c r="V141" t="inlineStr">
         <is>
-          <t>TlBupCntDr60</t>
+          <t>OtpMinDis</t>
         </is>
       </c>
       <c r="W141" t="inlineStr">
         <is>
-          <t>Count of telehealth buprenorphine providers within 60-minute drive</t>
+          <t>Distance to nearest OTP</t>
         </is>
       </c>
       <c r="X141" t="inlineStr"/>
@@ -11084,7 +11076,11 @@
       <c r="L142" t="inlineStr"/>
       <c r="M142" t="inlineStr"/>
       <c r="N142" t="inlineStr"/>
-      <c r="O142" t="inlineStr"/>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr"/>
       <c r="Q142" t="inlineStr"/>
       <c r="R142" t="inlineStr"/>
@@ -11093,16 +11089,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T142" t="inlineStr"/>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U142" t="inlineStr"/>
       <c r="V142" t="inlineStr">
         <is>
-          <t>TlBupCntWk30</t>
+          <t>OtpTmDr</t>
         </is>
       </c>
       <c r="W142" t="inlineStr">
         <is>
-          <t>Count of telehealth buprenorphine providers within 30-minute walk</t>
+          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP)</t>
         </is>
       </c>
       <c r="X142" t="inlineStr"/>
@@ -11161,12 +11161,12 @@
       <c r="U143" t="inlineStr"/>
       <c r="V143" t="inlineStr">
         <is>
-          <t>TlBupMinDis</t>
+          <t>TlBupCntBk30</t>
         </is>
       </c>
       <c r="W143" t="inlineStr">
         <is>
-          <t>Minimum distance to telehealth buprenorphine provider</t>
+          <t>Count of telehealth buprenorphine providers within 30-minute bike ride</t>
         </is>
       </c>
       <c r="X143" t="inlineStr"/>
@@ -11225,12 +11225,12 @@
       <c r="U144" t="inlineStr"/>
       <c r="V144" t="inlineStr">
         <is>
-          <t>TlBupTmBk</t>
+          <t>TlBupCntDr30</t>
         </is>
       </c>
       <c r="W144" t="inlineStr">
         <is>
-          <t>Biking time to nearest telehealth buprenorphine provider</t>
+          <t>Count of telehealth buprenorphine providers within 30-minute drive</t>
         </is>
       </c>
       <c r="X144" t="inlineStr"/>
@@ -11289,12 +11289,12 @@
       <c r="U145" t="inlineStr"/>
       <c r="V145" t="inlineStr">
         <is>
-          <t>TlBupTmDr</t>
+          <t>TlBupCntDr60</t>
         </is>
       </c>
       <c r="W145" t="inlineStr">
         <is>
-          <t>Driving time to nearest telehealth buprenorphine provider</t>
+          <t>Count of telehealth buprenorphine providers within 60-minute drive</t>
         </is>
       </c>
       <c r="X145" t="inlineStr"/>
@@ -11353,12 +11353,12 @@
       <c r="U146" t="inlineStr"/>
       <c r="V146" t="inlineStr">
         <is>
-          <t>TlBupTmWk</t>
+          <t>TlBupCntWk30</t>
         </is>
       </c>
       <c r="W146" t="inlineStr">
         <is>
-          <t>Walking time to nearest telehealth buprenorphine provider</t>
+          <t>Count of telehealth buprenorphine providers within 30-minute walk</t>
         </is>
       </c>
       <c r="X146" t="inlineStr"/>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -11403,11 +11403,7 @@
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr"/>
-      <c r="N147" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N147" t="inlineStr"/>
       <c r="O147" t="inlineStr"/>
       <c r="P147" t="inlineStr"/>
       <c r="Q147" t="inlineStr"/>
@@ -11421,28 +11417,28 @@
       <c r="U147" t="inlineStr"/>
       <c r="V147" t="inlineStr">
         <is>
-          <t>MhCntDr</t>
+          <t>TlBupMinDis</t>
         </is>
       </c>
       <c r="W147" t="inlineStr">
         <is>
-          <t>Count of Mental Health Providers (30-min drive)</t>
+          <t>Minimum distance to telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X147" t="inlineStr"/>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB147" t="inlineStr"/>
@@ -11457,7 +11453,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
@@ -11471,11 +11467,7 @@
       <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr"/>
       <c r="M148" t="inlineStr"/>
-      <c r="N148" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N148" t="inlineStr"/>
       <c r="O148" t="inlineStr"/>
       <c r="P148" t="inlineStr"/>
       <c r="Q148" t="inlineStr"/>
@@ -11489,28 +11481,28 @@
       <c r="U148" t="inlineStr"/>
       <c r="V148" t="inlineStr">
         <is>
-          <t>MhMinDis</t>
+          <t>TlBupTmBk</t>
         </is>
       </c>
       <c r="W148" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Mental Health Provider</t>
+          <t>Biking time to nearest telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X148" t="inlineStr"/>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr"/>
@@ -11525,7 +11517,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -11539,11 +11531,7 @@
       <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr"/>
       <c r="M149" t="inlineStr"/>
-      <c r="N149" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr"/>
       <c r="P149" t="inlineStr"/>
       <c r="Q149" t="inlineStr"/>
@@ -11553,36 +11541,32 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T149" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T149" t="inlineStr"/>
       <c r="U149" t="inlineStr"/>
       <c r="V149" t="inlineStr">
         <is>
-          <t>MhTmDr</t>
+          <t>TlBupTmDr</t>
         </is>
       </c>
       <c r="W149" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Mental Health Provider</t>
+          <t>Driving time to nearest telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X149" t="inlineStr"/>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr"/>
@@ -11597,7 +11581,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -11610,11 +11594,7 @@
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M150" t="inlineStr"/>
       <c r="N150" t="inlineStr"/>
       <c r="O150" t="inlineStr"/>
       <c r="P150" t="inlineStr"/>
@@ -11629,28 +11609,28 @@
       <c r="U150" t="inlineStr"/>
       <c r="V150" t="inlineStr">
         <is>
-          <t>RxCntDr</t>
+          <t>TlBupTmWk</t>
         </is>
       </c>
       <c r="W150" t="inlineStr">
         <is>
-          <t>Count of Pharmacies (30-min drive)</t>
+          <t>Walking time to nearest telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X150" t="inlineStr"/>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr"/>
@@ -11665,7 +11645,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -11678,43 +11658,47 @@
       <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N151" t="inlineStr"/>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O151" t="inlineStr"/>
       <c r="P151" t="inlineStr"/>
       <c r="Q151" t="inlineStr"/>
       <c r="R151" t="inlineStr"/>
-      <c r="S151" t="inlineStr"/>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T151" t="inlineStr"/>
       <c r="U151" t="inlineStr"/>
       <c r="V151" t="inlineStr">
         <is>
-          <t>RxMinDis</t>
+          <t>MhCntDr</t>
         </is>
       </c>
       <c r="W151" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Pharmacy</t>
+          <t>Count of Mental Health Providers (30-min drive)</t>
         </is>
       </c>
       <c r="X151" t="inlineStr"/>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB151" t="inlineStr"/>
@@ -11729,7 +11713,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
@@ -11742,12 +11726,12 @@
       <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N152" t="inlineStr"/>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O152" t="inlineStr"/>
       <c r="P152" t="inlineStr"/>
       <c r="Q152" t="inlineStr"/>
@@ -11757,36 +11741,32 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T152" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T152" t="inlineStr"/>
       <c r="U152" t="inlineStr"/>
       <c r="V152" t="inlineStr">
         <is>
-          <t>RxTmDr</t>
+          <t>MhMinDis</t>
         </is>
       </c>
       <c r="W152" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Pharmacy</t>
+          <t>Distance (mi) to nearest Mental Health Provider</t>
         </is>
       </c>
       <c r="X152" t="inlineStr"/>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB152" t="inlineStr"/>
@@ -11801,7 +11781,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -11815,7 +11795,11 @@
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr"/>
       <c r="M153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O153" t="inlineStr"/>
       <c r="P153" t="inlineStr"/>
       <c r="Q153" t="inlineStr"/>
@@ -11825,32 +11809,36 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T153" t="inlineStr"/>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U153" t="inlineStr"/>
       <c r="V153" t="inlineStr">
         <is>
-          <t>RxTmDr2</t>
+          <t>MhTmDr</t>
         </is>
       </c>
       <c r="W153" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Pharmacy with Impedance Factor</t>
+          <t>Driving Time (min) to nearest Mental Health Provider</t>
         </is>
       </c>
       <c r="X153" t="inlineStr"/>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB153" t="inlineStr"/>
@@ -11865,7 +11853,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
@@ -11878,12 +11866,12 @@
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr"/>
-      <c r="M154" t="inlineStr"/>
-      <c r="N154" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr"/>
       <c r="O154" t="inlineStr"/>
       <c r="P154" t="inlineStr"/>
       <c r="Q154" t="inlineStr"/>
@@ -11897,28 +11885,28 @@
       <c r="U154" t="inlineStr"/>
       <c r="V154" t="inlineStr">
         <is>
-          <t>SutCntDr</t>
+          <t>RxCntDr</t>
         </is>
       </c>
       <c r="W154" t="inlineStr">
         <is>
-          <t>Count of Substance Use Treatment (SUT) facility (30-min drive)</t>
+          <t>Count of Pharmacies (30-min drive)</t>
         </is>
       </c>
       <c r="X154" t="inlineStr"/>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB154" t="inlineStr"/>
@@ -11933,7 +11921,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
@@ -11946,47 +11934,43 @@
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr"/>
-      <c r="N155" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr"/>
       <c r="O155" t="inlineStr"/>
       <c r="P155" t="inlineStr"/>
       <c r="Q155" t="inlineStr"/>
       <c r="R155" t="inlineStr"/>
-      <c r="S155" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S155" t="inlineStr"/>
       <c r="T155" t="inlineStr"/>
       <c r="U155" t="inlineStr"/>
       <c r="V155" t="inlineStr">
         <is>
-          <t>SutMinDis</t>
+          <t>RxMinDis</t>
         </is>
       </c>
       <c r="W155" t="inlineStr">
         <is>
-          <t>Distance (mi) to Substance Use Treatment (SUT) facility</t>
+          <t>Distance (mi) to nearest Pharmacy</t>
         </is>
       </c>
       <c r="X155" t="inlineStr"/>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB155" t="inlineStr"/>
@@ -12001,7 +11985,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -12014,12 +11998,12 @@
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr"/>
-      <c r="N156" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr"/>
       <c r="O156" t="inlineStr"/>
       <c r="P156" t="inlineStr"/>
       <c r="Q156" t="inlineStr"/>
@@ -12037,28 +12021,28 @@
       <c r="U156" t="inlineStr"/>
       <c r="V156" t="inlineStr">
         <is>
-          <t>SutTmDr</t>
+          <t>RxTmDr</t>
         </is>
       </c>
       <c r="W156" t="inlineStr">
         <is>
-          <t>Driving time (min) to Substance Use Treatment (SUT) facility</t>
+          <t>Driving Time (min) to nearest Pharmacy</t>
         </is>
       </c>
       <c r="X156" t="inlineStr"/>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB156" t="inlineStr"/>
@@ -12073,7 +12057,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -12087,11 +12071,7 @@
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr"/>
       <c r="M157" t="inlineStr"/>
-      <c r="N157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N157" t="inlineStr"/>
       <c r="O157" t="inlineStr"/>
       <c r="P157" t="inlineStr"/>
       <c r="Q157" t="inlineStr"/>
@@ -12105,28 +12085,28 @@
       <c r="U157" t="inlineStr"/>
       <c r="V157" t="inlineStr">
         <is>
-          <t>FqhcCntDr</t>
+          <t>RxTmDr2</t>
         </is>
       </c>
       <c r="W157" t="inlineStr">
         <is>
-          <t>Count of Federally Qualified Health Centers (FQHCs) within 30-min drive</t>
+          <t>Driving Time (min) to nearest Pharmacy with Impedance Factor</t>
         </is>
       </c>
       <c r="X157" t="inlineStr"/>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB157" t="inlineStr"/>
@@ -12141,7 +12121,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -12173,28 +12153,28 @@
       <c r="U158" t="inlineStr"/>
       <c r="V158" t="inlineStr">
         <is>
-          <t>FqhcMinDis</t>
+          <t>SutCntDr</t>
         </is>
       </c>
       <c r="W158" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Federally Qualified Health Centers (FQHC)</t>
+          <t>Count of Substance Use Treatment (SUT) facility (30-min drive)</t>
         </is>
       </c>
       <c r="X158" t="inlineStr"/>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB158" t="inlineStr"/>
@@ -12209,7 +12189,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
@@ -12237,36 +12217,32 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T159" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T159" t="inlineStr"/>
       <c r="U159" t="inlineStr"/>
       <c r="V159" t="inlineStr">
         <is>
-          <t>FqhcTmDr</t>
+          <t>SutMinDis</t>
         </is>
       </c>
       <c r="W159" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC)</t>
+          <t>Distance (mi) to Substance Use Treatment (SUT) facility</t>
         </is>
       </c>
       <c r="X159" t="inlineStr"/>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB159" t="inlineStr"/>
@@ -12281,7 +12257,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
@@ -12295,7 +12271,11 @@
       <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr"/>
       <c r="M160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O160" t="inlineStr"/>
       <c r="P160" t="inlineStr"/>
       <c r="Q160" t="inlineStr"/>
@@ -12313,28 +12293,28 @@
       <c r="U160" t="inlineStr"/>
       <c r="V160" t="inlineStr">
         <is>
-          <t>FqhcTmDr2</t>
+          <t>SutTmDr</t>
         </is>
       </c>
       <c r="W160" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC), with Impedance factor</t>
+          <t>Driving time (min) to Substance Use Treatment (SUT) facility</t>
         </is>
       </c>
       <c r="X160" t="inlineStr"/>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB160" t="inlineStr"/>
@@ -12349,7 +12329,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
@@ -12363,7 +12343,11 @@
       <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr"/>
       <c r="M161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O161" t="inlineStr"/>
       <c r="P161" t="inlineStr"/>
       <c r="Q161" t="inlineStr"/>
@@ -12377,28 +12361,28 @@
       <c r="U161" t="inlineStr"/>
       <c r="V161" t="inlineStr">
         <is>
-          <t>HcvCntDr</t>
+          <t>FqhcCntDr</t>
         </is>
       </c>
       <c r="W161" t="inlineStr">
         <is>
-          <t>Count of HCV Providers</t>
+          <t>Count of Federally Qualified Health Centers (FQHCs) within 30-min drive</t>
         </is>
       </c>
       <c r="X161" t="inlineStr"/>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB161" t="inlineStr"/>
@@ -12413,7 +12397,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
@@ -12427,7 +12411,11 @@
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr"/>
       <c r="M162" t="inlineStr"/>
-      <c r="N162" t="inlineStr"/>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O162" t="inlineStr"/>
       <c r="P162" t="inlineStr"/>
       <c r="Q162" t="inlineStr"/>
@@ -12441,28 +12429,28 @@
       <c r="U162" t="inlineStr"/>
       <c r="V162" t="inlineStr">
         <is>
-          <t>HcvMinDis</t>
+          <t>FqhcMinDis</t>
         </is>
       </c>
       <c r="W162" t="inlineStr">
         <is>
-          <t>Distance to nearest HCV Provider</t>
+          <t>Distance (mi) to nearest Federally Qualified Health Centers (FQHC)</t>
         </is>
       </c>
       <c r="X162" t="inlineStr"/>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB162" t="inlineStr"/>
@@ -12477,7 +12465,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
@@ -12491,7 +12479,11 @@
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr"/>
       <c r="M163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O163" t="inlineStr"/>
       <c r="P163" t="inlineStr"/>
       <c r="Q163" t="inlineStr"/>
@@ -12501,32 +12493,36 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T163" t="inlineStr"/>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U163" t="inlineStr"/>
       <c r="V163" t="inlineStr">
         <is>
-          <t>HcvTmDr</t>
+          <t>FqhcTmDr</t>
         </is>
       </c>
       <c r="W163" t="inlineStr">
         <is>
-          <t>Driving time to nearest HCV Provider</t>
+          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC)</t>
         </is>
       </c>
       <c r="X163" t="inlineStr"/>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB163" t="inlineStr"/>
@@ -12541,7 +12537,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
@@ -12565,32 +12561,36 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T164" t="inlineStr"/>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U164" t="inlineStr"/>
       <c r="V164" t="inlineStr">
         <is>
-          <t>HcvTmDr2</t>
+          <t>FqhcTmDr2</t>
         </is>
       </c>
       <c r="W164" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest HCV Testing Facility with impedance</t>
+          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC), with Impedance factor</t>
         </is>
       </c>
       <c r="X164" t="inlineStr"/>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB164" t="inlineStr"/>
@@ -12633,12 +12633,12 @@
       <c r="U165" t="inlineStr"/>
       <c r="V165" t="inlineStr">
         <is>
-          <t>HivCntDr</t>
+          <t>HcvCntDr</t>
         </is>
       </c>
       <c r="W165" t="inlineStr">
         <is>
-          <t>Count of HIV Providers</t>
+          <t>Count of HCV Providers</t>
         </is>
       </c>
       <c r="X165" t="inlineStr"/>
@@ -12697,12 +12697,12 @@
       <c r="U166" t="inlineStr"/>
       <c r="V166" t="inlineStr">
         <is>
-          <t>HivMinDis</t>
+          <t>HcvMinDis</t>
         </is>
       </c>
       <c r="W166" t="inlineStr">
         <is>
-          <t>Distance to nearest HIV Provider</t>
+          <t>Distance to nearest HCV Provider</t>
         </is>
       </c>
       <c r="X166" t="inlineStr"/>
@@ -12761,12 +12761,12 @@
       <c r="U167" t="inlineStr"/>
       <c r="V167" t="inlineStr">
         <is>
-          <t>HivTmDr</t>
+          <t>HcvTmDr</t>
         </is>
       </c>
       <c r="W167" t="inlineStr">
         <is>
-          <t>Driving time to nearest HIV Provider</t>
+          <t>Driving time to nearest HCV Provider</t>
         </is>
       </c>
       <c r="X167" t="inlineStr"/>

--- a/docs/src/reference/data-dictionaries/T_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/T_Dict.xlsx
@@ -7605,12 +7605,12 @@
       <c r="U91" t="inlineStr"/>
       <c r="V91" t="inlineStr">
         <is>
-          <t>HcvTmDr2</t>
+          <t>HivCntDr</t>
         </is>
       </c>
       <c r="W91" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest HCV Testing Facility with impedance</t>
+          <t>Count of HIV Providers</t>
         </is>
       </c>
       <c r="X91" t="inlineStr"/>
@@ -7669,12 +7669,12 @@
       <c r="U92" t="inlineStr"/>
       <c r="V92" t="inlineStr">
         <is>
-          <t>HivCntDr</t>
+          <t>HivMinDis</t>
         </is>
       </c>
       <c r="W92" t="inlineStr">
         <is>
-          <t>Count of HIV Providers</t>
+          <t>Distance to nearest HIV Provider</t>
         </is>
       </c>
       <c r="X92" t="inlineStr"/>
@@ -7733,12 +7733,12 @@
       <c r="U93" t="inlineStr"/>
       <c r="V93" t="inlineStr">
         <is>
-          <t>HivMinDis</t>
+          <t>HivTmDr</t>
         </is>
       </c>
       <c r="W93" t="inlineStr">
         <is>
-          <t>Distance to nearest HIV Provider</t>
+          <t>Driving time to nearest HIV Provider</t>
         </is>
       </c>
       <c r="X93" t="inlineStr"/>
@@ -7797,12 +7797,12 @@
       <c r="U94" t="inlineStr"/>
       <c r="V94" t="inlineStr">
         <is>
-          <t>HivTmDr</t>
+          <t>HivTmDr2</t>
         </is>
       </c>
       <c r="W94" t="inlineStr">
         <is>
-          <t>Driving time to nearest HIV Provider</t>
+          <t>Driving time (min) to nearest HIV Testing Facility, with impedance</t>
         </is>
       </c>
       <c r="X94" t="inlineStr"/>
@@ -7833,7 +7833,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Spatial Access to HIV Testing</t>
+          <t>Spatial Access to Hospitals</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -7847,7 +7847,11 @@
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr"/>
       <c r="Q95" t="inlineStr"/>
@@ -7861,28 +7865,28 @@
       <c r="U95" t="inlineStr"/>
       <c r="V95" t="inlineStr">
         <is>
-          <t>HivTmDr2</t>
+          <t>HospCntDr</t>
         </is>
       </c>
       <c r="W95" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest HIV Testing Facility, with impedance</t>
+          <t>Count of Hospitals (30-min drive)</t>
         </is>
       </c>
       <c r="X95" t="inlineStr"/>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HIVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Hospitals.md</t>
         </is>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr"/>
@@ -7929,12 +7933,12 @@
       <c r="U96" t="inlineStr"/>
       <c r="V96" t="inlineStr">
         <is>
-          <t>HospCntDr</t>
+          <t>HospMinDis</t>
         </is>
       </c>
       <c r="W96" t="inlineStr">
         <is>
-          <t>Count of Hospitals (30-min drive)</t>
+          <t>Distance (mi) to nearest Hospital</t>
         </is>
       </c>
       <c r="X96" t="inlineStr"/>
@@ -7993,16 +7997,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T97" t="inlineStr"/>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U97" t="inlineStr"/>
       <c r="V97" t="inlineStr">
         <is>
-          <t>HospMinDis</t>
+          <t>HospTmDr</t>
         </is>
       </c>
       <c r="W97" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Hospital</t>
+          <t>Driving time (min) to nearest Hospital</t>
         </is>
       </c>
       <c r="X97" t="inlineStr"/>
@@ -8047,11 +8055,7 @@
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr"/>
       <c r="Q98" t="inlineStr"/>
@@ -8061,20 +8065,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T98" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T98" t="inlineStr"/>
       <c r="U98" t="inlineStr"/>
       <c r="V98" t="inlineStr">
         <is>
-          <t>HospTmDr</t>
+          <t>HospTmDr2</t>
         </is>
       </c>
       <c r="W98" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest Hospital</t>
+          <t>Driving time (min) to nearest Hospital with Impedance Factor</t>
         </is>
       </c>
       <c r="X98" t="inlineStr"/>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Spatial Access to Hospitals</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -8119,7 +8119,11 @@
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr"/>
       <c r="Q99" t="inlineStr"/>
@@ -8133,28 +8137,28 @@
       <c r="U99" t="inlineStr"/>
       <c r="V99" t="inlineStr">
         <is>
-          <t>HospTmDr2</t>
+          <t>BupCntBk30</t>
         </is>
       </c>
       <c r="W99" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest Hospital with Impedance Factor</t>
+          <t>Count of Buprenorphine Providers (30-min bike)</t>
         </is>
       </c>
       <c r="X99" t="inlineStr"/>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Hospitals.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr"/>
@@ -8201,12 +8205,12 @@
       <c r="U100" t="inlineStr"/>
       <c r="V100" t="inlineStr">
         <is>
-          <t>BupCntBk30</t>
+          <t>BupCntBk60</t>
         </is>
       </c>
       <c r="W100" t="inlineStr">
         <is>
-          <t>Count of Buprenorphine Providers (30-min bike)</t>
+          <t>Count of Buprenorphine Providers (60-min bike)</t>
         </is>
       </c>
       <c r="X100" t="inlineStr"/>
@@ -8269,12 +8273,12 @@
       <c r="U101" t="inlineStr"/>
       <c r="V101" t="inlineStr">
         <is>
-          <t>BupCntBk60</t>
+          <t>BupCntDr30</t>
         </is>
       </c>
       <c r="W101" t="inlineStr">
         <is>
-          <t>Count of Buprenorphine Providers (60-min bike)</t>
+          <t>Count of Buprenorphine Providers (30-min drive)</t>
         </is>
       </c>
       <c r="X101" t="inlineStr"/>
@@ -8319,11 +8323,7 @@
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr"/>
       <c r="P102" t="inlineStr"/>
       <c r="Q102" t="inlineStr"/>
@@ -8337,12 +8337,12 @@
       <c r="U102" t="inlineStr"/>
       <c r="V102" t="inlineStr">
         <is>
-          <t>BupCntDr30</t>
+          <t>BupCntDr60</t>
         </is>
       </c>
       <c r="W102" t="inlineStr">
         <is>
-          <t>Count of Buprenorphine Providers (30-min drive)</t>
+          <t>Count of buprenorphine providers (drive)</t>
         </is>
       </c>
       <c r="X102" t="inlineStr"/>
@@ -8387,7 +8387,11 @@
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr"/>
       <c r="Q103" t="inlineStr"/>
@@ -8401,12 +8405,12 @@
       <c r="U103" t="inlineStr"/>
       <c r="V103" t="inlineStr">
         <is>
-          <t>BupCntDr60</t>
+          <t>BupCntWk30</t>
         </is>
       </c>
       <c r="W103" t="inlineStr">
         <is>
-          <t>Count of buprenorphine providers (drive)</t>
+          <t>Count of Buprenorphine Providers (30-min walk)</t>
         </is>
       </c>
       <c r="X103" t="inlineStr"/>
@@ -8469,12 +8473,12 @@
       <c r="U104" t="inlineStr"/>
       <c r="V104" t="inlineStr">
         <is>
-          <t>BupCntWk30</t>
+          <t>BupCntWk60</t>
         </is>
       </c>
       <c r="W104" t="inlineStr">
         <is>
-          <t>Count of Buprenorphine Providers (30-min walk)</t>
+          <t>Count of Buprenorphine Providers (60-min walk)</t>
         </is>
       </c>
       <c r="X104" t="inlineStr"/>
@@ -8537,12 +8541,12 @@
       <c r="U105" t="inlineStr"/>
       <c r="V105" t="inlineStr">
         <is>
-          <t>BupCntWk60</t>
+          <t>BupMinDis</t>
         </is>
       </c>
       <c r="W105" t="inlineStr">
         <is>
-          <t>Count of Buprenorphine Providers (60-min walk)</t>
+          <t>Distance (mi) to nearest Buprenorphine Provider</t>
         </is>
       </c>
       <c r="X105" t="inlineStr"/>
@@ -8596,21 +8600,17 @@
       <c r="P106" t="inlineStr"/>
       <c r="Q106" t="inlineStr"/>
       <c r="R106" t="inlineStr"/>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S106" t="inlineStr"/>
       <c r="T106" t="inlineStr"/>
       <c r="U106" t="inlineStr"/>
       <c r="V106" t="inlineStr">
         <is>
-          <t>BupMinDis</t>
+          <t>BupRm30</t>
         </is>
       </c>
       <c r="W106" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Buprenorphine Provider</t>
+          <t>Buprenorphine access 30 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X106" t="inlineStr"/>
@@ -8669,12 +8669,12 @@
       <c r="U107" t="inlineStr"/>
       <c r="V107" t="inlineStr">
         <is>
-          <t>BupRm30</t>
+          <t>BupRm60</t>
         </is>
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>Buprenorphine access 30 minutes (RAAM)</t>
+          <t>Buprenorphine access 60 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X107" t="inlineStr"/>
@@ -8733,12 +8733,12 @@
       <c r="U108" t="inlineStr"/>
       <c r="V108" t="inlineStr">
         <is>
-          <t>BupRm60</t>
+          <t>BupRm90</t>
         </is>
       </c>
       <c r="W108" t="inlineStr">
         <is>
-          <t>Buprenorphine access 60 minutes (RAAM)</t>
+          <t>Buprenorphine access 90 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X108" t="inlineStr"/>
@@ -8792,17 +8792,25 @@
       <c r="P109" t="inlineStr"/>
       <c r="Q109" t="inlineStr"/>
       <c r="R109" t="inlineStr"/>
-      <c r="S109" t="inlineStr"/>
-      <c r="T109" t="inlineStr"/>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U109" t="inlineStr"/>
       <c r="V109" t="inlineStr">
         <is>
-          <t>BupRm90</t>
+          <t>BupTmBk</t>
         </is>
       </c>
       <c r="W109" t="inlineStr">
         <is>
-          <t>Buprenorphine access 90 minutes (RAAM)</t>
+          <t>Biking Time (min) to nearest Buprenorphine Provider</t>
         </is>
       </c>
       <c r="X109" t="inlineStr"/>
@@ -8869,12 +8877,12 @@
       <c r="U110" t="inlineStr"/>
       <c r="V110" t="inlineStr">
         <is>
-          <t>BupTmBk</t>
+          <t>BupTmDr</t>
         </is>
       </c>
       <c r="W110" t="inlineStr">
         <is>
-          <t>Biking Time (min) to nearest Buprenorphine Provider</t>
+          <t>Driving Time (min) to nearest Buprenorphine Provider</t>
         </is>
       </c>
       <c r="X110" t="inlineStr"/>
@@ -8941,12 +8949,12 @@
       <c r="U111" t="inlineStr"/>
       <c r="V111" t="inlineStr">
         <is>
-          <t>BupTmDr</t>
+          <t>BupTmWk</t>
         </is>
       </c>
       <c r="W111" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Buprenorphine Provider</t>
+          <t>Walking Time (min) to nearest Buprenorphine Provider</t>
         </is>
       </c>
       <c r="X111" t="inlineStr"/>
@@ -9005,20 +9013,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T112" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T112" t="inlineStr"/>
       <c r="U112" t="inlineStr"/>
       <c r="V112" t="inlineStr">
         <is>
-          <t>BupTmWk</t>
+          <t>MetCntBk30</t>
         </is>
       </c>
       <c r="W112" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Buprenorphine Provider</t>
+          <t>Count of methadone providers (30-min bike)</t>
         </is>
       </c>
       <c r="X112" t="inlineStr"/>
@@ -9081,12 +9085,12 @@
       <c r="U113" t="inlineStr"/>
       <c r="V113" t="inlineStr">
         <is>
-          <t>MetCntBk30</t>
+          <t>MetCntBk60</t>
         </is>
       </c>
       <c r="W113" t="inlineStr">
         <is>
-          <t>Count of methadone providers (30-min bike)</t>
+          <t>Count of Methadone Providers (60-min bike)</t>
         </is>
       </c>
       <c r="X113" t="inlineStr"/>
@@ -9149,12 +9153,12 @@
       <c r="U114" t="inlineStr"/>
       <c r="V114" t="inlineStr">
         <is>
-          <t>MetCntBk60</t>
+          <t>MetCntDr30</t>
         </is>
       </c>
       <c r="W114" t="inlineStr">
         <is>
-          <t>Count of Methadone Providers (60-min bike)</t>
+          <t>Count of Methadone Providers (30-min drive)</t>
         </is>
       </c>
       <c r="X114" t="inlineStr"/>
@@ -9199,11 +9203,7 @@
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr"/>
       <c r="P115" t="inlineStr"/>
       <c r="Q115" t="inlineStr"/>
@@ -9217,12 +9217,12 @@
       <c r="U115" t="inlineStr"/>
       <c r="V115" t="inlineStr">
         <is>
-          <t>MetCntDr30</t>
+          <t>MetCntDr60</t>
         </is>
       </c>
       <c r="W115" t="inlineStr">
         <is>
-          <t>Count of Methadone Providers (30-min drive)</t>
+          <t>Count of methadone providers (drive)</t>
         </is>
       </c>
       <c r="X115" t="inlineStr"/>
@@ -9267,7 +9267,11 @@
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O116" t="inlineStr"/>
       <c r="P116" t="inlineStr"/>
       <c r="Q116" t="inlineStr"/>
@@ -9281,12 +9285,12 @@
       <c r="U116" t="inlineStr"/>
       <c r="V116" t="inlineStr">
         <is>
-          <t>MetCntDr60</t>
+          <t>MetCntWk30</t>
         </is>
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>Count of methadone providers (drive)</t>
+          <t>Count of Methadone Providers (60-min walk)</t>
         </is>
       </c>
       <c r="X116" t="inlineStr"/>
@@ -9349,12 +9353,12 @@
       <c r="U117" t="inlineStr"/>
       <c r="V117" t="inlineStr">
         <is>
-          <t>MetCntWk30</t>
+          <t>MetCntWk60</t>
         </is>
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>Count of Methadone Providers (60-min walk)</t>
+          <t>Count of Methadone Providers (30-min walk)</t>
         </is>
       </c>
       <c r="X117" t="inlineStr"/>
@@ -9417,12 +9421,12 @@
       <c r="U118" t="inlineStr"/>
       <c r="V118" t="inlineStr">
         <is>
-          <t>MetCntWk60</t>
+          <t>MetMinDis</t>
         </is>
       </c>
       <c r="W118" t="inlineStr">
         <is>
-          <t>Count of Methadone Providers (30-min walk)</t>
+          <t>Distance (mi) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X118" t="inlineStr"/>
@@ -9456,10 +9460,26 @@
           <t>Spatial Access to MOUDs</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr"/>
-      <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr"/>
@@ -9476,21 +9496,17 @@
       <c r="P119" t="inlineStr"/>
       <c r="Q119" t="inlineStr"/>
       <c r="R119" t="inlineStr"/>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S119" t="inlineStr"/>
       <c r="T119" t="inlineStr"/>
       <c r="U119" t="inlineStr"/>
       <c r="V119" t="inlineStr">
         <is>
-          <t>MetMinDis</t>
+          <t>MetRm30</t>
         </is>
       </c>
       <c r="W119" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Methadone Provider</t>
+          <t>Methadone access 30 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X119" t="inlineStr"/>
@@ -9565,12 +9581,12 @@
       <c r="U120" t="inlineStr"/>
       <c r="V120" t="inlineStr">
         <is>
-          <t>MetRm30</t>
+          <t>MetRm60</t>
         </is>
       </c>
       <c r="W120" t="inlineStr">
         <is>
-          <t>Methadone access 30 minutes (RAAM)</t>
+          <t>Methadone access 60 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X120" t="inlineStr"/>
@@ -9645,12 +9661,12 @@
       <c r="U121" t="inlineStr"/>
       <c r="V121" t="inlineStr">
         <is>
-          <t>MetRm60</t>
+          <t>MetRm90</t>
         </is>
       </c>
       <c r="W121" t="inlineStr">
         <is>
-          <t>Methadone access 60 minutes (RAAM)</t>
+          <t>Methadone access 90 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X121" t="inlineStr"/>
@@ -9684,26 +9700,10 @@
           <t>Spatial Access to MOUDs</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr"/>
@@ -9720,17 +9720,25 @@
       <c r="P122" t="inlineStr"/>
       <c r="Q122" t="inlineStr"/>
       <c r="R122" t="inlineStr"/>
-      <c r="S122" t="inlineStr"/>
-      <c r="T122" t="inlineStr"/>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U122" t="inlineStr"/>
       <c r="V122" t="inlineStr">
         <is>
-          <t>MetRm90</t>
+          <t>MetTmBk</t>
         </is>
       </c>
       <c r="W122" t="inlineStr">
         <is>
-          <t>Methadone access 90 minutes (RAAM)</t>
+          <t>Biking Time (min) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X122" t="inlineStr"/>
@@ -9797,12 +9805,12 @@
       <c r="U123" t="inlineStr"/>
       <c r="V123" t="inlineStr">
         <is>
-          <t>MetTmBk</t>
+          <t>MetTmDr</t>
         </is>
       </c>
       <c r="W123" t="inlineStr">
         <is>
-          <t>Biking Time (min) to nearest Methadone Provider</t>
+          <t>Driving Time (min) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X123" t="inlineStr"/>
@@ -9869,12 +9877,12 @@
       <c r="U124" t="inlineStr"/>
       <c r="V124" t="inlineStr">
         <is>
-          <t>MetTmDr</t>
+          <t>MetTmWk</t>
         </is>
       </c>
       <c r="W124" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Methadone Provider</t>
+          <t>Walking Time (min) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X124" t="inlineStr"/>
@@ -9933,20 +9941,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T125" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T125" t="inlineStr"/>
       <c r="U125" t="inlineStr"/>
       <c r="V125" t="inlineStr">
         <is>
-          <t>MetTmWk</t>
+          <t>MoudMinDis</t>
         </is>
       </c>
       <c r="W125" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Methadone Provider</t>
+          <t>Distance (mi) to nearest MOUD (any)</t>
         </is>
       </c>
       <c r="X125" t="inlineStr"/>
@@ -10009,12 +10013,12 @@
       <c r="U126" t="inlineStr"/>
       <c r="V126" t="inlineStr">
         <is>
-          <t>MoudMinDis</t>
+          <t>NaltCntBk30</t>
         </is>
       </c>
       <c r="W126" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest MOUD (any)</t>
+          <t>Count of Naltrexone Providers (30-min bike)</t>
         </is>
       </c>
       <c r="X126" t="inlineStr"/>
@@ -10077,12 +10081,12 @@
       <c r="U127" t="inlineStr"/>
       <c r="V127" t="inlineStr">
         <is>
-          <t>NaltCntBk30</t>
+          <t>NaltCntBk60</t>
         </is>
       </c>
       <c r="W127" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (30-min bike)</t>
+          <t>Count of Naltrexone Providers (60-min bike)</t>
         </is>
       </c>
       <c r="X127" t="inlineStr"/>
@@ -10145,12 +10149,12 @@
       <c r="U128" t="inlineStr"/>
       <c r="V128" t="inlineStr">
         <is>
-          <t>NaltCntBk60</t>
+          <t>NaltCntDr30</t>
         </is>
       </c>
       <c r="W128" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (60-min bike)</t>
+          <t>Count of Naltrexone Providers (30-min drive)</t>
         </is>
       </c>
       <c r="X128" t="inlineStr"/>
@@ -10195,11 +10199,7 @@
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr"/>
-      <c r="N129" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr"/>
       <c r="P129" t="inlineStr"/>
       <c r="Q129" t="inlineStr"/>
@@ -10213,12 +10213,12 @@
       <c r="U129" t="inlineStr"/>
       <c r="V129" t="inlineStr">
         <is>
-          <t>NaltCntDr30</t>
+          <t>NaltCntDr60</t>
         </is>
       </c>
       <c r="W129" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (30-min drive)</t>
+          <t>Count of naltrexone providers (drive)</t>
         </is>
       </c>
       <c r="X129" t="inlineStr"/>
@@ -10263,7 +10263,11 @@
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr"/>
       <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O130" t="inlineStr"/>
       <c r="P130" t="inlineStr"/>
       <c r="Q130" t="inlineStr"/>
@@ -10277,12 +10281,12 @@
       <c r="U130" t="inlineStr"/>
       <c r="V130" t="inlineStr">
         <is>
-          <t>NaltCntDr60</t>
+          <t>NaltCntWk30</t>
         </is>
       </c>
       <c r="W130" t="inlineStr">
         <is>
-          <t>Count of naltrexone providers (drive)</t>
+          <t>Count of Naltrexone Providers (30-min walk)</t>
         </is>
       </c>
       <c r="X130" t="inlineStr"/>
@@ -10345,12 +10349,12 @@
       <c r="U131" t="inlineStr"/>
       <c r="V131" t="inlineStr">
         <is>
-          <t>NaltCntWk30</t>
+          <t>NaltCntWk60</t>
         </is>
       </c>
       <c r="W131" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (30-min walk)</t>
+          <t>Count of Naltrexone Providers (60-min walk)</t>
         </is>
       </c>
       <c r="X131" t="inlineStr"/>
@@ -10413,12 +10417,12 @@
       <c r="U132" t="inlineStr"/>
       <c r="V132" t="inlineStr">
         <is>
-          <t>NaltCntWk60</t>
+          <t>NaltMinDis</t>
         </is>
       </c>
       <c r="W132" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (60-min walk)</t>
+          <t>Distance (mi) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X132" t="inlineStr"/>
@@ -10472,21 +10476,17 @@
       <c r="P133" t="inlineStr"/>
       <c r="Q133" t="inlineStr"/>
       <c r="R133" t="inlineStr"/>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S133" t="inlineStr"/>
       <c r="T133" t="inlineStr"/>
       <c r="U133" t="inlineStr"/>
       <c r="V133" t="inlineStr">
         <is>
-          <t>NaltMinDis</t>
+          <t>NaltRm30</t>
         </is>
       </c>
       <c r="W133" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Naltrexone Provider</t>
+          <t>Naltrexone access 30 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X133" t="inlineStr"/>
@@ -10545,12 +10545,12 @@
       <c r="U134" t="inlineStr"/>
       <c r="V134" t="inlineStr">
         <is>
-          <t>NaltRm30</t>
+          <t>NaltRm60</t>
         </is>
       </c>
       <c r="W134" t="inlineStr">
         <is>
-          <t>Naltrexone access 30 minutes (RAAM)</t>
+          <t>Naltrexone access 60 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X134" t="inlineStr"/>
@@ -10609,12 +10609,12 @@
       <c r="U135" t="inlineStr"/>
       <c r="V135" t="inlineStr">
         <is>
-          <t>NaltRm60</t>
+          <t>NaltRm90</t>
         </is>
       </c>
       <c r="W135" t="inlineStr">
         <is>
-          <t>Naltrexone access 60 minutes (RAAM)</t>
+          <t>Naltrexone access 90 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X135" t="inlineStr"/>
@@ -10668,17 +10668,25 @@
       <c r="P136" t="inlineStr"/>
       <c r="Q136" t="inlineStr"/>
       <c r="R136" t="inlineStr"/>
-      <c r="S136" t="inlineStr"/>
-      <c r="T136" t="inlineStr"/>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U136" t="inlineStr"/>
       <c r="V136" t="inlineStr">
         <is>
-          <t>NaltRm90</t>
+          <t>NaltTmBk</t>
         </is>
       </c>
       <c r="W136" t="inlineStr">
         <is>
-          <t>Naltrexone access 90 minutes (RAAM)</t>
+          <t>Biking Time (min) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X136" t="inlineStr"/>
@@ -10745,12 +10753,12 @@
       <c r="U137" t="inlineStr"/>
       <c r="V137" t="inlineStr">
         <is>
-          <t>NaltTmBk</t>
+          <t>NaltTmDr</t>
         </is>
       </c>
       <c r="W137" t="inlineStr">
         <is>
-          <t>Biking Time (min) to nearest Naltrexone Provider</t>
+          <t>Driving Time (min) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X137" t="inlineStr"/>
@@ -10817,12 +10825,12 @@
       <c r="U138" t="inlineStr"/>
       <c r="V138" t="inlineStr">
         <is>
-          <t>NaltTmDr</t>
+          <t>NaltTmWk</t>
         </is>
       </c>
       <c r="W138" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Naltrexone Provider</t>
+          <t>Walking Time (min) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X138" t="inlineStr"/>
@@ -10867,12 +10875,12 @@
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr"/>
       <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr"/>
       <c r="Q139" t="inlineStr"/>
       <c r="R139" t="inlineStr"/>
@@ -10881,20 +10889,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T139" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T139" t="inlineStr"/>
       <c r="U139" t="inlineStr"/>
       <c r="V139" t="inlineStr">
         <is>
-          <t>NaltTmWk</t>
+          <t>OtpCntDr</t>
         </is>
       </c>
       <c r="W139" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Naltrexone Provider</t>
+          <t>Count of Opioid Treatment Programs (OTP) (30-min drive)</t>
         </is>
       </c>
       <c r="X139" t="inlineStr"/>
@@ -10957,12 +10961,12 @@
       <c r="U140" t="inlineStr"/>
       <c r="V140" t="inlineStr">
         <is>
-          <t>OtpCntDr</t>
+          <t>OtpMinDis</t>
         </is>
       </c>
       <c r="W140" t="inlineStr">
         <is>
-          <t>Count of Opioid Treatment Programs (OTP) (30-min drive)</t>
+          <t>Distance to nearest OTP</t>
         </is>
       </c>
       <c r="X140" t="inlineStr"/>
@@ -11021,16 +11025,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T141" t="inlineStr"/>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U141" t="inlineStr"/>
       <c r="V141" t="inlineStr">
         <is>
-          <t>OtpMinDis</t>
+          <t>OtpTmDr</t>
         </is>
       </c>
       <c r="W141" t="inlineStr">
         <is>
-          <t>Distance to nearest OTP</t>
+          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP)</t>
         </is>
       </c>
       <c r="X141" t="inlineStr"/>
@@ -11076,11 +11084,7 @@
       <c r="L142" t="inlineStr"/>
       <c r="M142" t="inlineStr"/>
       <c r="N142" t="inlineStr"/>
-      <c r="O142" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="O142" t="inlineStr"/>
       <c r="P142" t="inlineStr"/>
       <c r="Q142" t="inlineStr"/>
       <c r="R142" t="inlineStr"/>
@@ -11089,20 +11093,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T142" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T142" t="inlineStr"/>
       <c r="U142" t="inlineStr"/>
       <c r="V142" t="inlineStr">
         <is>
-          <t>OtpTmDr</t>
+          <t>TlBupCntBk30</t>
         </is>
       </c>
       <c r="W142" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP)</t>
+          <t>Count of telehealth buprenorphine providers within 30-minute bike ride</t>
         </is>
       </c>
       <c r="X142" t="inlineStr"/>
@@ -11161,12 +11161,12 @@
       <c r="U143" t="inlineStr"/>
       <c r="V143" t="inlineStr">
         <is>
-          <t>TlBupCntBk30</t>
+          <t>TlBupCntDr30</t>
         </is>
       </c>
       <c r="W143" t="inlineStr">
         <is>
-          <t>Count of telehealth buprenorphine providers within 30-minute bike ride</t>
+          <t>Count of telehealth buprenorphine providers within 30-minute drive</t>
         </is>
       </c>
       <c r="X143" t="inlineStr"/>
@@ -11225,12 +11225,12 @@
       <c r="U144" t="inlineStr"/>
       <c r="V144" t="inlineStr">
         <is>
-          <t>TlBupCntDr30</t>
+          <t>TlBupCntDr60</t>
         </is>
       </c>
       <c r="W144" t="inlineStr">
         <is>
-          <t>Count of telehealth buprenorphine providers within 30-minute drive</t>
+          <t>Count of telehealth buprenorphine providers within 60-minute drive</t>
         </is>
       </c>
       <c r="X144" t="inlineStr"/>
@@ -11289,12 +11289,12 @@
       <c r="U145" t="inlineStr"/>
       <c r="V145" t="inlineStr">
         <is>
-          <t>TlBupCntDr60</t>
+          <t>TlBupCntWk30</t>
         </is>
       </c>
       <c r="W145" t="inlineStr">
         <is>
-          <t>Count of telehealth buprenorphine providers within 60-minute drive</t>
+          <t>Count of telehealth buprenorphine providers within 30-minute walk</t>
         </is>
       </c>
       <c r="X145" t="inlineStr"/>
@@ -11353,12 +11353,12 @@
       <c r="U146" t="inlineStr"/>
       <c r="V146" t="inlineStr">
         <is>
-          <t>TlBupCntWk30</t>
+          <t>TlBupMinDis</t>
         </is>
       </c>
       <c r="W146" t="inlineStr">
         <is>
-          <t>Count of telehealth buprenorphine providers within 30-minute walk</t>
+          <t>Minimum distance to telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X146" t="inlineStr"/>
@@ -11417,12 +11417,12 @@
       <c r="U147" t="inlineStr"/>
       <c r="V147" t="inlineStr">
         <is>
-          <t>TlBupMinDis</t>
+          <t>TlBupTmBk</t>
         </is>
       </c>
       <c r="W147" t="inlineStr">
         <is>
-          <t>Minimum distance to telehealth buprenorphine provider</t>
+          <t>Biking time to nearest telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X147" t="inlineStr"/>
@@ -11481,12 +11481,12 @@
       <c r="U148" t="inlineStr"/>
       <c r="V148" t="inlineStr">
         <is>
-          <t>TlBupTmBk</t>
+          <t>TlBupTmDr</t>
         </is>
       </c>
       <c r="W148" t="inlineStr">
         <is>
-          <t>Biking time to nearest telehealth buprenorphine provider</t>
+          <t>Driving time to nearest telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X148" t="inlineStr"/>
@@ -11545,12 +11545,12 @@
       <c r="U149" t="inlineStr"/>
       <c r="V149" t="inlineStr">
         <is>
-          <t>TlBupTmDr</t>
+          <t>TlBupTmWk</t>
         </is>
       </c>
       <c r="W149" t="inlineStr">
         <is>
-          <t>Driving time to nearest telehealth buprenorphine provider</t>
+          <t>Walking time to nearest telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X149" t="inlineStr"/>
@@ -11581,7 +11581,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Spatial Access to MOUDs</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -11595,7 +11595,11 @@
       <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr"/>
       <c r="M150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O150" t="inlineStr"/>
       <c r="P150" t="inlineStr"/>
       <c r="Q150" t="inlineStr"/>
@@ -11609,28 +11613,28 @@
       <c r="U150" t="inlineStr"/>
       <c r="V150" t="inlineStr">
         <is>
-          <t>TlBupTmWk</t>
+          <t>MhCntDr</t>
         </is>
       </c>
       <c r="W150" t="inlineStr">
         <is>
-          <t>Walking time to nearest telehealth buprenorphine provider</t>
+          <t>Count of Mental Health Providers (30-min drive)</t>
         </is>
       </c>
       <c r="X150" t="inlineStr"/>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr"/>
@@ -11677,12 +11681,12 @@
       <c r="U151" t="inlineStr"/>
       <c r="V151" t="inlineStr">
         <is>
-          <t>MhCntDr</t>
+          <t>MhMinDis</t>
         </is>
       </c>
       <c r="W151" t="inlineStr">
         <is>
-          <t>Count of Mental Health Providers (30-min drive)</t>
+          <t>Distance (mi) to nearest Mental Health Provider</t>
         </is>
       </c>
       <c r="X151" t="inlineStr"/>
@@ -11741,16 +11745,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T152" t="inlineStr"/>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U152" t="inlineStr"/>
       <c r="V152" t="inlineStr">
         <is>
-          <t>MhMinDis</t>
+          <t>MhTmDr</t>
         </is>
       </c>
       <c r="W152" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Mental Health Provider</t>
+          <t>Driving Time (min) to nearest Mental Health Provider</t>
         </is>
       </c>
       <c r="X152" t="inlineStr"/>
@@ -11781,7 +11789,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -11794,12 +11802,12 @@
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr"/>
-      <c r="M153" t="inlineStr"/>
-      <c r="N153" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr"/>
       <c r="O153" t="inlineStr"/>
       <c r="P153" t="inlineStr"/>
       <c r="Q153" t="inlineStr"/>
@@ -11809,36 +11817,32 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T153" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T153" t="inlineStr"/>
       <c r="U153" t="inlineStr"/>
       <c r="V153" t="inlineStr">
         <is>
-          <t>MhTmDr</t>
+          <t>RxCntDr</t>
         </is>
       </c>
       <c r="W153" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Mental Health Provider</t>
+          <t>Count of Pharmacies (30-min drive)</t>
         </is>
       </c>
       <c r="X153" t="inlineStr"/>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB153" t="inlineStr"/>
@@ -11876,21 +11880,17 @@
       <c r="P154" t="inlineStr"/>
       <c r="Q154" t="inlineStr"/>
       <c r="R154" t="inlineStr"/>
-      <c r="S154" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S154" t="inlineStr"/>
       <c r="T154" t="inlineStr"/>
       <c r="U154" t="inlineStr"/>
       <c r="V154" t="inlineStr">
         <is>
-          <t>RxCntDr</t>
+          <t>RxMinDis</t>
         </is>
       </c>
       <c r="W154" t="inlineStr">
         <is>
-          <t>Count of Pharmacies (30-min drive)</t>
+          <t>Distance (mi) to nearest Pharmacy</t>
         </is>
       </c>
       <c r="X154" t="inlineStr"/>
@@ -11944,17 +11944,25 @@
       <c r="P155" t="inlineStr"/>
       <c r="Q155" t="inlineStr"/>
       <c r="R155" t="inlineStr"/>
-      <c r="S155" t="inlineStr"/>
-      <c r="T155" t="inlineStr"/>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U155" t="inlineStr"/>
       <c r="V155" t="inlineStr">
         <is>
-          <t>RxMinDis</t>
+          <t>RxTmDr</t>
         </is>
       </c>
       <c r="W155" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Pharmacy</t>
+          <t>Driving Time (min) to nearest Pharmacy</t>
         </is>
       </c>
       <c r="X155" t="inlineStr"/>
@@ -11998,11 +12006,7 @@
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M156" t="inlineStr"/>
       <c r="N156" t="inlineStr"/>
       <c r="O156" t="inlineStr"/>
       <c r="P156" t="inlineStr"/>
@@ -12013,20 +12017,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T156" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T156" t="inlineStr"/>
       <c r="U156" t="inlineStr"/>
       <c r="V156" t="inlineStr">
         <is>
-          <t>RxTmDr</t>
+          <t>RxTmDr2</t>
         </is>
       </c>
       <c r="W156" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Pharmacy</t>
+          <t>Driving Time (min) to nearest Pharmacy with Impedance Factor</t>
         </is>
       </c>
       <c r="X156" t="inlineStr"/>
@@ -12057,7 +12057,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -12071,7 +12071,11 @@
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr"/>
       <c r="M157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O157" t="inlineStr"/>
       <c r="P157" t="inlineStr"/>
       <c r="Q157" t="inlineStr"/>
@@ -12085,28 +12089,28 @@
       <c r="U157" t="inlineStr"/>
       <c r="V157" t="inlineStr">
         <is>
-          <t>RxTmDr2</t>
+          <t>SutCntDr</t>
         </is>
       </c>
       <c r="W157" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Pharmacy with Impedance Factor</t>
+          <t>Count of Substance Use Treatment (SUT) facility (30-min drive)</t>
         </is>
       </c>
       <c r="X157" t="inlineStr"/>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB157" t="inlineStr"/>
@@ -12153,12 +12157,12 @@
       <c r="U158" t="inlineStr"/>
       <c r="V158" t="inlineStr">
         <is>
-          <t>SutCntDr</t>
+          <t>SutMinDis</t>
         </is>
       </c>
       <c r="W158" t="inlineStr">
         <is>
-          <t>Count of Substance Use Treatment (SUT) facility (30-min drive)</t>
+          <t>Distance (mi) to Substance Use Treatment (SUT) facility</t>
         </is>
       </c>
       <c r="X158" t="inlineStr"/>
@@ -12217,16 +12221,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T159" t="inlineStr"/>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U159" t="inlineStr"/>
       <c r="V159" t="inlineStr">
         <is>
-          <t>SutMinDis</t>
+          <t>SutTmDr</t>
         </is>
       </c>
       <c r="W159" t="inlineStr">
         <is>
-          <t>Distance (mi) to Substance Use Treatment (SUT) facility</t>
+          <t>Driving time (min) to Substance Use Treatment (SUT) facility</t>
         </is>
       </c>
       <c r="X159" t="inlineStr"/>
@@ -12257,7 +12265,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
@@ -12285,36 +12293,32 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T160" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T160" t="inlineStr"/>
       <c r="U160" t="inlineStr"/>
       <c r="V160" t="inlineStr">
         <is>
-          <t>SutTmDr</t>
+          <t>FqhcCntDr</t>
         </is>
       </c>
       <c r="W160" t="inlineStr">
         <is>
-          <t>Driving time (min) to Substance Use Treatment (SUT) facility</t>
+          <t>Count of Federally Qualified Health Centers (FQHCs) within 30-min drive</t>
         </is>
       </c>
       <c r="X160" t="inlineStr"/>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB160" t="inlineStr"/>
@@ -12361,12 +12365,12 @@
       <c r="U161" t="inlineStr"/>
       <c r="V161" t="inlineStr">
         <is>
-          <t>FqhcCntDr</t>
+          <t>FqhcMinDis</t>
         </is>
       </c>
       <c r="W161" t="inlineStr">
         <is>
-          <t>Count of Federally Qualified Health Centers (FQHCs) within 30-min drive</t>
+          <t>Distance (mi) to nearest Federally Qualified Health Centers (FQHC)</t>
         </is>
       </c>
       <c r="X161" t="inlineStr"/>
@@ -12425,16 +12429,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T162" t="inlineStr"/>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U162" t="inlineStr"/>
       <c r="V162" t="inlineStr">
         <is>
-          <t>FqhcMinDis</t>
+          <t>FqhcTmDr</t>
         </is>
       </c>
       <c r="W162" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Federally Qualified Health Centers (FQHC)</t>
+          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC)</t>
         </is>
       </c>
       <c r="X162" t="inlineStr"/>
@@ -12479,11 +12487,7 @@
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr"/>
       <c r="M163" t="inlineStr"/>
-      <c r="N163" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N163" t="inlineStr"/>
       <c r="O163" t="inlineStr"/>
       <c r="P163" t="inlineStr"/>
       <c r="Q163" t="inlineStr"/>
@@ -12501,12 +12505,12 @@
       <c r="U163" t="inlineStr"/>
       <c r="V163" t="inlineStr">
         <is>
-          <t>FqhcTmDr</t>
+          <t>FqhcTmDr2</t>
         </is>
       </c>
       <c r="W163" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC)</t>
+          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC), with Impedance factor</t>
         </is>
       </c>
       <c r="X163" t="inlineStr"/>
@@ -12537,7 +12541,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
@@ -12561,36 +12565,32 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T164" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T164" t="inlineStr"/>
       <c r="U164" t="inlineStr"/>
       <c r="V164" t="inlineStr">
         <is>
-          <t>FqhcTmDr2</t>
+          <t>HcvCntDr</t>
         </is>
       </c>
       <c r="W164" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC), with Impedance factor</t>
+          <t>Count of HCV Providers</t>
         </is>
       </c>
       <c r="X164" t="inlineStr"/>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB164" t="inlineStr"/>
@@ -12633,12 +12633,12 @@
       <c r="U165" t="inlineStr"/>
       <c r="V165" t="inlineStr">
         <is>
-          <t>HcvCntDr</t>
+          <t>HcvMinDis</t>
         </is>
       </c>
       <c r="W165" t="inlineStr">
         <is>
-          <t>Count of HCV Providers</t>
+          <t>Distance to nearest HCV Provider</t>
         </is>
       </c>
       <c r="X165" t="inlineStr"/>
@@ -12697,12 +12697,12 @@
       <c r="U166" t="inlineStr"/>
       <c r="V166" t="inlineStr">
         <is>
-          <t>HcvMinDis</t>
+          <t>HcvTmDr</t>
         </is>
       </c>
       <c r="W166" t="inlineStr">
         <is>
-          <t>Distance to nearest HCV Provider</t>
+          <t>Driving time to nearest HCV Provider</t>
         </is>
       </c>
       <c r="X166" t="inlineStr"/>
@@ -12761,12 +12761,12 @@
       <c r="U167" t="inlineStr"/>
       <c r="V167" t="inlineStr">
         <is>
-          <t>HcvTmDr</t>
+          <t>HcvTmDr2</t>
         </is>
       </c>
       <c r="W167" t="inlineStr">
         <is>
-          <t>Driving time to nearest HCV Provider</t>
+          <t>Driving time (min) to nearest HCV Testing Facility with impedance</t>
         </is>
       </c>
       <c r="X167" t="inlineStr"/>

--- a/docs/src/reference/data-dictionaries/T_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/T_Dict.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD194"/>
+  <dimension ref="A1:AD200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -9403,11 +9403,7 @@
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="inlineStr"/>
       <c r="Q118" t="inlineStr"/>
@@ -9421,12 +9417,12 @@
       <c r="U118" t="inlineStr"/>
       <c r="V118" t="inlineStr">
         <is>
-          <t>MetMinDis</t>
+          <t>MetFca30</t>
         </is>
       </c>
       <c r="W118" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Methadone Provider</t>
+          <t>Two-step floating catchment area (2SFCA) measure of access to Methadone within a 30-minute drive</t>
         </is>
       </c>
       <c r="X118" t="inlineStr"/>
@@ -9460,26 +9456,10 @@
           <t>Spatial Access to MOUDs</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr"/>
@@ -9487,26 +9467,26 @@
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr"/>
       <c r="P119" t="inlineStr"/>
       <c r="Q119" t="inlineStr"/>
       <c r="R119" t="inlineStr"/>
-      <c r="S119" t="inlineStr"/>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T119" t="inlineStr"/>
       <c r="U119" t="inlineStr"/>
       <c r="V119" t="inlineStr">
         <is>
-          <t>MetRm30</t>
+          <t>MetFca60</t>
         </is>
       </c>
       <c r="W119" t="inlineStr">
         <is>
-          <t>Methadone access 30 minutes (RAAM)</t>
+          <t>Two-step floating catchment area (2SFCA) measure of access to Methadone within a 60-minute drive</t>
         </is>
       </c>
       <c r="X119" t="inlineStr"/>
@@ -9540,26 +9520,10 @@
           <t>Spatial Access to MOUDs</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr"/>
@@ -9576,17 +9540,21 @@
       <c r="P120" t="inlineStr"/>
       <c r="Q120" t="inlineStr"/>
       <c r="R120" t="inlineStr"/>
-      <c r="S120" t="inlineStr"/>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T120" t="inlineStr"/>
       <c r="U120" t="inlineStr"/>
       <c r="V120" t="inlineStr">
         <is>
-          <t>MetRm60</t>
+          <t>MetMinDis</t>
         </is>
       </c>
       <c r="W120" t="inlineStr">
         <is>
-          <t>Methadone access 60 minutes (RAAM)</t>
+          <t>Distance (mi) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X120" t="inlineStr"/>
@@ -9656,17 +9624,21 @@
       <c r="P121" t="inlineStr"/>
       <c r="Q121" t="inlineStr"/>
       <c r="R121" t="inlineStr"/>
-      <c r="S121" t="inlineStr"/>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T121" t="inlineStr"/>
       <c r="U121" t="inlineStr"/>
       <c r="V121" t="inlineStr">
         <is>
-          <t>MetRm90</t>
+          <t>MetRm30</t>
         </is>
       </c>
       <c r="W121" t="inlineStr">
         <is>
-          <t>Methadone access 90 minutes (RAAM)</t>
+          <t>Methadone access 30 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X121" t="inlineStr"/>
@@ -9700,10 +9672,26 @@
           <t>Spatial Access to MOUDs</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr"/>
-      <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr"/>
@@ -9725,20 +9713,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T122" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T122" t="inlineStr"/>
       <c r="U122" t="inlineStr"/>
       <c r="V122" t="inlineStr">
         <is>
-          <t>MetTmBk</t>
+          <t>MetRm60</t>
         </is>
       </c>
       <c r="W122" t="inlineStr">
         <is>
-          <t>Biking Time (min) to nearest Methadone Provider</t>
+          <t>Methadone access 60 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X122" t="inlineStr"/>
@@ -9772,10 +9756,26 @@
           <t>Spatial Access to MOUDs</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr"/>
-      <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
@@ -9792,25 +9792,17 @@
       <c r="P123" t="inlineStr"/>
       <c r="Q123" t="inlineStr"/>
       <c r="R123" t="inlineStr"/>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="T123" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S123" t="inlineStr"/>
+      <c r="T123" t="inlineStr"/>
       <c r="U123" t="inlineStr"/>
       <c r="V123" t="inlineStr">
         <is>
-          <t>MetTmDr</t>
+          <t>MetRm90</t>
         </is>
       </c>
       <c r="W123" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Methadone Provider</t>
+          <t>Methadone access 90 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X123" t="inlineStr"/>
@@ -9877,12 +9869,12 @@
       <c r="U124" t="inlineStr"/>
       <c r="V124" t="inlineStr">
         <is>
-          <t>MetTmWk</t>
+          <t>MetTmBk</t>
         </is>
       </c>
       <c r="W124" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Methadone Provider</t>
+          <t>Biking Time (min) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X124" t="inlineStr"/>
@@ -9941,16 +9933,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T125" t="inlineStr"/>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U125" t="inlineStr"/>
       <c r="V125" t="inlineStr">
         <is>
-          <t>MoudMinDis</t>
+          <t>MetTmDr</t>
         </is>
       </c>
       <c r="W125" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest MOUD (any)</t>
+          <t>Driving Time (min) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X125" t="inlineStr"/>
@@ -10009,16 +10005,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T126" t="inlineStr"/>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U126" t="inlineStr"/>
       <c r="V126" t="inlineStr">
         <is>
-          <t>NaltCntBk30</t>
+          <t>MetTmWk</t>
         </is>
       </c>
       <c r="W126" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (30-min bike)</t>
+          <t>Walking Time (min) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X126" t="inlineStr"/>
@@ -10081,12 +10081,12 @@
       <c r="U127" t="inlineStr"/>
       <c r="V127" t="inlineStr">
         <is>
-          <t>NaltCntBk60</t>
+          <t>MoudMinDis</t>
         </is>
       </c>
       <c r="W127" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (60-min bike)</t>
+          <t>Distance (mi) to nearest MOUD (any)</t>
         </is>
       </c>
       <c r="X127" t="inlineStr"/>
@@ -10149,12 +10149,12 @@
       <c r="U128" t="inlineStr"/>
       <c r="V128" t="inlineStr">
         <is>
-          <t>NaltCntDr30</t>
+          <t>NaltCntBk30</t>
         </is>
       </c>
       <c r="W128" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (30-min drive)</t>
+          <t>Count of Naltrexone Providers (30-min bike)</t>
         </is>
       </c>
       <c r="X128" t="inlineStr"/>
@@ -10199,7 +10199,11 @@
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O129" t="inlineStr"/>
       <c r="P129" t="inlineStr"/>
       <c r="Q129" t="inlineStr"/>
@@ -10213,12 +10217,12 @@
       <c r="U129" t="inlineStr"/>
       <c r="V129" t="inlineStr">
         <is>
-          <t>NaltCntDr60</t>
+          <t>NaltCntBk60</t>
         </is>
       </c>
       <c r="W129" t="inlineStr">
         <is>
-          <t>Count of naltrexone providers (drive)</t>
+          <t>Count of Naltrexone Providers (60-min bike)</t>
         </is>
       </c>
       <c r="X129" t="inlineStr"/>
@@ -10281,12 +10285,12 @@
       <c r="U130" t="inlineStr"/>
       <c r="V130" t="inlineStr">
         <is>
-          <t>NaltCntWk30</t>
+          <t>NaltCntDr30</t>
         </is>
       </c>
       <c r="W130" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (30-min walk)</t>
+          <t>Count of Naltrexone Providers (30-min drive)</t>
         </is>
       </c>
       <c r="X130" t="inlineStr"/>
@@ -10331,11 +10335,7 @@
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr"/>
-      <c r="N131" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr"/>
       <c r="P131" t="inlineStr"/>
       <c r="Q131" t="inlineStr"/>
@@ -10349,12 +10349,12 @@
       <c r="U131" t="inlineStr"/>
       <c r="V131" t="inlineStr">
         <is>
-          <t>NaltCntWk60</t>
+          <t>NaltCntDr60</t>
         </is>
       </c>
       <c r="W131" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (60-min walk)</t>
+          <t>Count of naltrexone providers (drive)</t>
         </is>
       </c>
       <c r="X131" t="inlineStr"/>
@@ -10417,12 +10417,12 @@
       <c r="U132" t="inlineStr"/>
       <c r="V132" t="inlineStr">
         <is>
-          <t>NaltMinDis</t>
+          <t>NaltCntWk30</t>
         </is>
       </c>
       <c r="W132" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Naltrexone Provider</t>
+          <t>Count of Naltrexone Providers (30-min walk)</t>
         </is>
       </c>
       <c r="X132" t="inlineStr"/>
@@ -10476,17 +10476,21 @@
       <c r="P133" t="inlineStr"/>
       <c r="Q133" t="inlineStr"/>
       <c r="R133" t="inlineStr"/>
-      <c r="S133" t="inlineStr"/>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T133" t="inlineStr"/>
       <c r="U133" t="inlineStr"/>
       <c r="V133" t="inlineStr">
         <is>
-          <t>NaltRm30</t>
+          <t>NaltCntWk60</t>
         </is>
       </c>
       <c r="W133" t="inlineStr">
         <is>
-          <t>Naltrexone access 30 minutes (RAAM)</t>
+          <t>Count of Naltrexone Providers (60-min walk)</t>
         </is>
       </c>
       <c r="X133" t="inlineStr"/>
@@ -10540,17 +10544,21 @@
       <c r="P134" t="inlineStr"/>
       <c r="Q134" t="inlineStr"/>
       <c r="R134" t="inlineStr"/>
-      <c r="S134" t="inlineStr"/>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T134" t="inlineStr"/>
       <c r="U134" t="inlineStr"/>
       <c r="V134" t="inlineStr">
         <is>
-          <t>NaltRm60</t>
+          <t>NaltMinDis</t>
         </is>
       </c>
       <c r="W134" t="inlineStr">
         <is>
-          <t>Naltrexone access 60 minutes (RAAM)</t>
+          <t>Distance (mi) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X134" t="inlineStr"/>
@@ -10609,12 +10617,12 @@
       <c r="U135" t="inlineStr"/>
       <c r="V135" t="inlineStr">
         <is>
-          <t>NaltRm90</t>
+          <t>NaltRm30</t>
         </is>
       </c>
       <c r="W135" t="inlineStr">
         <is>
-          <t>Naltrexone access 90 minutes (RAAM)</t>
+          <t>Naltrexone access 30 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X135" t="inlineStr"/>
@@ -10668,25 +10676,17 @@
       <c r="P136" t="inlineStr"/>
       <c r="Q136" t="inlineStr"/>
       <c r="R136" t="inlineStr"/>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="T136" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S136" t="inlineStr"/>
+      <c r="T136" t="inlineStr"/>
       <c r="U136" t="inlineStr"/>
       <c r="V136" t="inlineStr">
         <is>
-          <t>NaltTmBk</t>
+          <t>NaltRm60</t>
         </is>
       </c>
       <c r="W136" t="inlineStr">
         <is>
-          <t>Biking Time (min) to nearest Naltrexone Provider</t>
+          <t>Naltrexone access 60 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X136" t="inlineStr"/>
@@ -10740,25 +10740,17 @@
       <c r="P137" t="inlineStr"/>
       <c r="Q137" t="inlineStr"/>
       <c r="R137" t="inlineStr"/>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="T137" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S137" t="inlineStr"/>
+      <c r="T137" t="inlineStr"/>
       <c r="U137" t="inlineStr"/>
       <c r="V137" t="inlineStr">
         <is>
-          <t>NaltTmDr</t>
+          <t>NaltRm90</t>
         </is>
       </c>
       <c r="W137" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Naltrexone Provider</t>
+          <t>Naltrexone access 90 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X137" t="inlineStr"/>
@@ -10825,12 +10817,12 @@
       <c r="U138" t="inlineStr"/>
       <c r="V138" t="inlineStr">
         <is>
-          <t>NaltTmWk</t>
+          <t>NaltTmBk</t>
         </is>
       </c>
       <c r="W138" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Naltrexone Provider</t>
+          <t>Biking Time (min) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X138" t="inlineStr"/>
@@ -10875,12 +10867,12 @@
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr"/>
       <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
-      <c r="O139" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr"/>
       <c r="P139" t="inlineStr"/>
       <c r="Q139" t="inlineStr"/>
       <c r="R139" t="inlineStr"/>
@@ -10889,16 +10881,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T139" t="inlineStr"/>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U139" t="inlineStr"/>
       <c r="V139" t="inlineStr">
         <is>
-          <t>OtpCntDr</t>
+          <t>NaltTmDr</t>
         </is>
       </c>
       <c r="W139" t="inlineStr">
         <is>
-          <t>Count of Opioid Treatment Programs (OTP) (30-min drive)</t>
+          <t>Driving Time (min) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X139" t="inlineStr"/>
@@ -10943,12 +10939,12 @@
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr"/>
       <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
-      <c r="O140" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr"/>
       <c r="P140" t="inlineStr"/>
       <c r="Q140" t="inlineStr"/>
       <c r="R140" t="inlineStr"/>
@@ -10957,16 +10953,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T140" t="inlineStr"/>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U140" t="inlineStr"/>
       <c r="V140" t="inlineStr">
         <is>
-          <t>OtpMinDis</t>
+          <t>NaltTmWk</t>
         </is>
       </c>
       <c r="W140" t="inlineStr">
         <is>
-          <t>Distance to nearest OTP</t>
+          <t>Walking Time (min) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X140" t="inlineStr"/>
@@ -11025,20 +11025,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T141" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T141" t="inlineStr"/>
       <c r="U141" t="inlineStr"/>
       <c r="V141" t="inlineStr">
         <is>
-          <t>OtpTmDr</t>
+          <t>OtpCntDr</t>
         </is>
       </c>
       <c r="W141" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP)</t>
+          <t>Count of Opioid Treatment Programs (OTP) (30-min drive)</t>
         </is>
       </c>
       <c r="X141" t="inlineStr"/>
@@ -11097,12 +11093,12 @@
       <c r="U142" t="inlineStr"/>
       <c r="V142" t="inlineStr">
         <is>
-          <t>TlBupCntBk30</t>
+          <t>OtpFca30</t>
         </is>
       </c>
       <c r="W142" t="inlineStr">
         <is>
-          <t>Count of telehealth buprenorphine providers within 30-minute bike ride</t>
+          <t>Two-step floating catchment area (2SFCA) measure of access to opioid treatment programs within a 30-minute drive</t>
         </is>
       </c>
       <c r="X142" t="inlineStr"/>
@@ -11161,12 +11157,12 @@
       <c r="U143" t="inlineStr"/>
       <c r="V143" t="inlineStr">
         <is>
-          <t>TlBupCntDr30</t>
+          <t>OtpFca60</t>
         </is>
       </c>
       <c r="W143" t="inlineStr">
         <is>
-          <t>Count of telehealth buprenorphine providers within 30-minute drive</t>
+          <t>Two-step floating catchment area (2SFCA) measure of access to opioid treatment programs within a 60-minute drive</t>
         </is>
       </c>
       <c r="X143" t="inlineStr"/>
@@ -11212,7 +11208,11 @@
       <c r="L144" t="inlineStr"/>
       <c r="M144" t="inlineStr"/>
       <c r="N144" t="inlineStr"/>
-      <c r="O144" t="inlineStr"/>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr"/>
       <c r="Q144" t="inlineStr"/>
       <c r="R144" t="inlineStr"/>
@@ -11225,12 +11225,12 @@
       <c r="U144" t="inlineStr"/>
       <c r="V144" t="inlineStr">
         <is>
-          <t>TlBupCntDr60</t>
+          <t>OtpMinDis</t>
         </is>
       </c>
       <c r="W144" t="inlineStr">
         <is>
-          <t>Count of telehealth buprenorphine providers within 60-minute drive</t>
+          <t>Distance to nearest OTP</t>
         </is>
       </c>
       <c r="X144" t="inlineStr"/>
@@ -11289,12 +11289,12 @@
       <c r="U145" t="inlineStr"/>
       <c r="V145" t="inlineStr">
         <is>
-          <t>TlBupCntWk30</t>
+          <t>OtpRm30</t>
         </is>
       </c>
       <c r="W145" t="inlineStr">
         <is>
-          <t>Count of telehealth buprenorphine providers within 30-minute walk</t>
+          <t>Opioid Treatment Provider access 30 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X145" t="inlineStr"/>
@@ -11353,12 +11353,12 @@
       <c r="U146" t="inlineStr"/>
       <c r="V146" t="inlineStr">
         <is>
-          <t>TlBupMinDis</t>
+          <t>OtpRm60</t>
         </is>
       </c>
       <c r="W146" t="inlineStr">
         <is>
-          <t>Minimum distance to telehealth buprenorphine provider</t>
+          <t>Opioid Treatment Provider access 30 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X146" t="inlineStr"/>
@@ -11404,7 +11404,11 @@
       <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr"/>
       <c r="N147" t="inlineStr"/>
-      <c r="O147" t="inlineStr"/>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr"/>
       <c r="Q147" t="inlineStr"/>
       <c r="R147" t="inlineStr"/>
@@ -11413,16 +11417,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T147" t="inlineStr"/>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U147" t="inlineStr"/>
       <c r="V147" t="inlineStr">
         <is>
-          <t>TlBupTmBk</t>
+          <t>OtpTmDr</t>
         </is>
       </c>
       <c r="W147" t="inlineStr">
         <is>
-          <t>Biking time to nearest telehealth buprenorphine provider</t>
+          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP)</t>
         </is>
       </c>
       <c r="X147" t="inlineStr"/>
@@ -11481,12 +11489,12 @@
       <c r="U148" t="inlineStr"/>
       <c r="V148" t="inlineStr">
         <is>
-          <t>TlBupTmDr</t>
+          <t>TlBupCntBk30</t>
         </is>
       </c>
       <c r="W148" t="inlineStr">
         <is>
-          <t>Driving time to nearest telehealth buprenorphine provider</t>
+          <t>Count of telehealth buprenorphine providers within 30-minute bike ride</t>
         </is>
       </c>
       <c r="X148" t="inlineStr"/>
@@ -11545,12 +11553,12 @@
       <c r="U149" t="inlineStr"/>
       <c r="V149" t="inlineStr">
         <is>
-          <t>TlBupTmWk</t>
+          <t>TlBupCntDr30</t>
         </is>
       </c>
       <c r="W149" t="inlineStr">
         <is>
-          <t>Walking time to nearest telehealth buprenorphine provider</t>
+          <t>Count of telehealth buprenorphine providers within 30-minute drive</t>
         </is>
       </c>
       <c r="X149" t="inlineStr"/>
@@ -11581,7 +11589,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -11595,11 +11603,7 @@
       <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr"/>
       <c r="M150" t="inlineStr"/>
-      <c r="N150" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N150" t="inlineStr"/>
       <c r="O150" t="inlineStr"/>
       <c r="P150" t="inlineStr"/>
       <c r="Q150" t="inlineStr"/>
@@ -11613,28 +11617,28 @@
       <c r="U150" t="inlineStr"/>
       <c r="V150" t="inlineStr">
         <is>
-          <t>MhCntDr</t>
+          <t>TlBupCntDr60</t>
         </is>
       </c>
       <c r="W150" t="inlineStr">
         <is>
-          <t>Count of Mental Health Providers (30-min drive)</t>
+          <t>Count of telehealth buprenorphine providers within 60-minute drive</t>
         </is>
       </c>
       <c r="X150" t="inlineStr"/>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr"/>
@@ -11649,7 +11653,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -11663,11 +11667,7 @@
       <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr"/>
       <c r="M151" t="inlineStr"/>
-      <c r="N151" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N151" t="inlineStr"/>
       <c r="O151" t="inlineStr"/>
       <c r="P151" t="inlineStr"/>
       <c r="Q151" t="inlineStr"/>
@@ -11681,28 +11681,28 @@
       <c r="U151" t="inlineStr"/>
       <c r="V151" t="inlineStr">
         <is>
-          <t>MhMinDis</t>
+          <t>TlBupCntWk30</t>
         </is>
       </c>
       <c r="W151" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Mental Health Provider</t>
+          <t>Count of telehealth buprenorphine providers within 30-minute walk</t>
         </is>
       </c>
       <c r="X151" t="inlineStr"/>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB151" t="inlineStr"/>
@@ -11717,7 +11717,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
@@ -11731,11 +11731,7 @@
       <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr"/>
       <c r="M152" t="inlineStr"/>
-      <c r="N152" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N152" t="inlineStr"/>
       <c r="O152" t="inlineStr"/>
       <c r="P152" t="inlineStr"/>
       <c r="Q152" t="inlineStr"/>
@@ -11745,36 +11741,32 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T152" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T152" t="inlineStr"/>
       <c r="U152" t="inlineStr"/>
       <c r="V152" t="inlineStr">
         <is>
-          <t>MhTmDr</t>
+          <t>TlBupMinDis</t>
         </is>
       </c>
       <c r="W152" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Mental Health Provider</t>
+          <t>Minimum distance to telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X152" t="inlineStr"/>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB152" t="inlineStr"/>
@@ -11789,7 +11781,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -11802,11 +11794,7 @@
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr"/>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M153" t="inlineStr"/>
       <c r="N153" t="inlineStr"/>
       <c r="O153" t="inlineStr"/>
       <c r="P153" t="inlineStr"/>
@@ -11821,28 +11809,28 @@
       <c r="U153" t="inlineStr"/>
       <c r="V153" t="inlineStr">
         <is>
-          <t>RxCntDr</t>
+          <t>TlBupTmBk</t>
         </is>
       </c>
       <c r="W153" t="inlineStr">
         <is>
-          <t>Count of Pharmacies (30-min drive)</t>
+          <t>Biking time to nearest telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X153" t="inlineStr"/>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB153" t="inlineStr"/>
@@ -11857,7 +11845,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
@@ -11870,43 +11858,43 @@
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr"/>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M154" t="inlineStr"/>
       <c r="N154" t="inlineStr"/>
       <c r="O154" t="inlineStr"/>
       <c r="P154" t="inlineStr"/>
       <c r="Q154" t="inlineStr"/>
       <c r="R154" t="inlineStr"/>
-      <c r="S154" t="inlineStr"/>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T154" t="inlineStr"/>
       <c r="U154" t="inlineStr"/>
       <c r="V154" t="inlineStr">
         <is>
-          <t>RxMinDis</t>
+          <t>TlBupTmDr</t>
         </is>
       </c>
       <c r="W154" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Pharmacy</t>
+          <t>Driving time to nearest telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X154" t="inlineStr"/>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB154" t="inlineStr"/>
@@ -11921,7 +11909,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
@@ -11934,11 +11922,7 @@
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M155" t="inlineStr"/>
       <c r="N155" t="inlineStr"/>
       <c r="O155" t="inlineStr"/>
       <c r="P155" t="inlineStr"/>
@@ -11949,36 +11933,32 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T155" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T155" t="inlineStr"/>
       <c r="U155" t="inlineStr"/>
       <c r="V155" t="inlineStr">
         <is>
-          <t>RxTmDr</t>
+          <t>TlBupTmWk</t>
         </is>
       </c>
       <c r="W155" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Pharmacy</t>
+          <t>Walking time to nearest telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X155" t="inlineStr"/>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB155" t="inlineStr"/>
@@ -11993,7 +11973,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -12007,7 +11987,11 @@
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr"/>
       <c r="M156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O156" t="inlineStr"/>
       <c r="P156" t="inlineStr"/>
       <c r="Q156" t="inlineStr"/>
@@ -12021,28 +12005,28 @@
       <c r="U156" t="inlineStr"/>
       <c r="V156" t="inlineStr">
         <is>
-          <t>RxTmDr2</t>
+          <t>MhCntDr</t>
         </is>
       </c>
       <c r="W156" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Pharmacy with Impedance Factor</t>
+          <t>Count of Mental Health Providers (30-min drive)</t>
         </is>
       </c>
       <c r="X156" t="inlineStr"/>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB156" t="inlineStr"/>
@@ -12057,7 +12041,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -12089,18 +12073,18 @@
       <c r="U157" t="inlineStr"/>
       <c r="V157" t="inlineStr">
         <is>
-          <t>SutCntDr</t>
+          <t>MhMinDis</t>
         </is>
       </c>
       <c r="W157" t="inlineStr">
         <is>
-          <t>Count of Substance Use Treatment (SUT) facility (30-min drive)</t>
+          <t>Distance (mi) to nearest Mental Health Provider</t>
         </is>
       </c>
       <c r="X157" t="inlineStr"/>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z157" t="inlineStr">
@@ -12125,7 +12109,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -12153,22 +12137,26 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T158" t="inlineStr"/>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U158" t="inlineStr"/>
       <c r="V158" t="inlineStr">
         <is>
-          <t>SutMinDis</t>
+          <t>MhTmDr</t>
         </is>
       </c>
       <c r="W158" t="inlineStr">
         <is>
-          <t>Distance (mi) to Substance Use Treatment (SUT) facility</t>
+          <t>Driving Time (min) to nearest Mental Health Provider</t>
         </is>
       </c>
       <c r="X158" t="inlineStr"/>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z158" t="inlineStr">
@@ -12193,7 +12181,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
@@ -12206,12 +12194,12 @@
       <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr"/>
-      <c r="N159" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr"/>
       <c r="O159" t="inlineStr"/>
       <c r="P159" t="inlineStr"/>
       <c r="Q159" t="inlineStr"/>
@@ -12221,36 +12209,32 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T159" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T159" t="inlineStr"/>
       <c r="U159" t="inlineStr"/>
       <c r="V159" t="inlineStr">
         <is>
-          <t>SutTmDr</t>
+          <t>RxCntDr</t>
         </is>
       </c>
       <c r="W159" t="inlineStr">
         <is>
-          <t>Driving time (min) to Substance Use Treatment (SUT) facility</t>
+          <t>Count of Pharmacies (30-min drive)</t>
         </is>
       </c>
       <c r="X159" t="inlineStr"/>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB159" t="inlineStr"/>
@@ -12265,7 +12249,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
@@ -12278,47 +12262,43 @@
       <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr"/>
-      <c r="N160" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr"/>
       <c r="O160" t="inlineStr"/>
       <c r="P160" t="inlineStr"/>
       <c r="Q160" t="inlineStr"/>
       <c r="R160" t="inlineStr"/>
-      <c r="S160" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S160" t="inlineStr"/>
       <c r="T160" t="inlineStr"/>
       <c r="U160" t="inlineStr"/>
       <c r="V160" t="inlineStr">
         <is>
-          <t>FqhcCntDr</t>
+          <t>RxMinDis</t>
         </is>
       </c>
       <c r="W160" t="inlineStr">
         <is>
-          <t>Count of Federally Qualified Health Centers (FQHCs) within 30-min drive</t>
+          <t>Distance (mi) to nearest Pharmacy</t>
         </is>
       </c>
       <c r="X160" t="inlineStr"/>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB160" t="inlineStr"/>
@@ -12333,7 +12313,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
@@ -12346,12 +12326,12 @@
       <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr"/>
-      <c r="M161" t="inlineStr"/>
-      <c r="N161" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr"/>
       <c r="O161" t="inlineStr"/>
       <c r="P161" t="inlineStr"/>
       <c r="Q161" t="inlineStr"/>
@@ -12361,32 +12341,36 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T161" t="inlineStr"/>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U161" t="inlineStr"/>
       <c r="V161" t="inlineStr">
         <is>
-          <t>FqhcMinDis</t>
+          <t>RxTmDr</t>
         </is>
       </c>
       <c r="W161" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Federally Qualified Health Centers (FQHC)</t>
+          <t>Driving Time (min) to nearest Pharmacy</t>
         </is>
       </c>
       <c r="X161" t="inlineStr"/>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB161" t="inlineStr"/>
@@ -12401,7 +12385,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
@@ -12415,11 +12399,7 @@
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr"/>
       <c r="M162" t="inlineStr"/>
-      <c r="N162" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N162" t="inlineStr"/>
       <c r="O162" t="inlineStr"/>
       <c r="P162" t="inlineStr"/>
       <c r="Q162" t="inlineStr"/>
@@ -12429,36 +12409,32 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T162" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T162" t="inlineStr"/>
       <c r="U162" t="inlineStr"/>
       <c r="V162" t="inlineStr">
         <is>
-          <t>FqhcTmDr</t>
+          <t>RxTmDr2</t>
         </is>
       </c>
       <c r="W162" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC)</t>
+          <t>Driving Time (min) to nearest Pharmacy with Impedance Factor</t>
         </is>
       </c>
       <c r="X162" t="inlineStr"/>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB162" t="inlineStr"/>
@@ -12473,7 +12449,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
@@ -12487,7 +12463,11 @@
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr"/>
       <c r="M163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O163" t="inlineStr"/>
       <c r="P163" t="inlineStr"/>
       <c r="Q163" t="inlineStr"/>
@@ -12497,36 +12477,32 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T163" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T163" t="inlineStr"/>
       <c r="U163" t="inlineStr"/>
       <c r="V163" t="inlineStr">
         <is>
-          <t>FqhcTmDr2</t>
+          <t>SutCntDr</t>
         </is>
       </c>
       <c r="W163" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC), with Impedance factor</t>
+          <t>Count of Substance Use Treatment (SUT) facility (30-min drive)</t>
         </is>
       </c>
       <c r="X163" t="inlineStr"/>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB163" t="inlineStr"/>
@@ -12541,7 +12517,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
@@ -12555,7 +12531,11 @@
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr"/>
       <c r="M164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O164" t="inlineStr"/>
       <c r="P164" t="inlineStr"/>
       <c r="Q164" t="inlineStr"/>
@@ -12569,28 +12549,28 @@
       <c r="U164" t="inlineStr"/>
       <c r="V164" t="inlineStr">
         <is>
-          <t>HcvCntDr</t>
+          <t>SutMinDis</t>
         </is>
       </c>
       <c r="W164" t="inlineStr">
         <is>
-          <t>Count of HCV Providers</t>
+          <t>Distance (mi) to Substance Use Treatment (SUT) facility</t>
         </is>
       </c>
       <c r="X164" t="inlineStr"/>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB164" t="inlineStr"/>
@@ -12605,7 +12585,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
@@ -12619,7 +12599,11 @@
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr"/>
       <c r="M165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O165" t="inlineStr"/>
       <c r="P165" t="inlineStr"/>
       <c r="Q165" t="inlineStr"/>
@@ -12629,32 +12613,36 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T165" t="inlineStr"/>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U165" t="inlineStr"/>
       <c r="V165" t="inlineStr">
         <is>
-          <t>HcvMinDis</t>
+          <t>SutTmDr</t>
         </is>
       </c>
       <c r="W165" t="inlineStr">
         <is>
-          <t>Distance to nearest HCV Provider</t>
+          <t>Driving time (min) to Substance Use Treatment (SUT) facility</t>
         </is>
       </c>
       <c r="X165" t="inlineStr"/>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB165" t="inlineStr"/>
@@ -12669,7 +12657,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
@@ -12683,7 +12671,11 @@
       <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr"/>
       <c r="M166" t="inlineStr"/>
-      <c r="N166" t="inlineStr"/>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O166" t="inlineStr"/>
       <c r="P166" t="inlineStr"/>
       <c r="Q166" t="inlineStr"/>
@@ -12697,28 +12689,28 @@
       <c r="U166" t="inlineStr"/>
       <c r="V166" t="inlineStr">
         <is>
-          <t>HcvTmDr</t>
+          <t>FqhcCntDr</t>
         </is>
       </c>
       <c r="W166" t="inlineStr">
         <is>
-          <t>Driving time to nearest HCV Provider</t>
+          <t>Count of Federally Qualified Health Centers (FQHCs) within 30-min drive</t>
         </is>
       </c>
       <c r="X166" t="inlineStr"/>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB166" t="inlineStr"/>
@@ -12733,7 +12725,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
@@ -12747,7 +12739,11 @@
       <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr"/>
       <c r="M167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O167" t="inlineStr"/>
       <c r="P167" t="inlineStr"/>
       <c r="Q167" t="inlineStr"/>
@@ -12761,28 +12757,28 @@
       <c r="U167" t="inlineStr"/>
       <c r="V167" t="inlineStr">
         <is>
-          <t>HcvTmDr2</t>
+          <t>FqhcMinDis</t>
         </is>
       </c>
       <c r="W167" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest HCV Testing Facility with impedance</t>
+          <t>Distance (mi) to nearest Federally Qualified Health Centers (FQHC)</t>
         </is>
       </c>
       <c r="X167" t="inlineStr"/>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB167" t="inlineStr"/>
@@ -12797,17 +12793,13 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
@@ -12815,38 +12807,50 @@
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr"/>
       <c r="M168" t="inlineStr"/>
-      <c r="N168" t="inlineStr"/>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O168" t="inlineStr"/>
       <c r="P168" t="inlineStr"/>
       <c r="Q168" t="inlineStr"/>
       <c r="R168" t="inlineStr"/>
-      <c r="S168" t="inlineStr"/>
-      <c r="T168" t="inlineStr"/>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U168" t="inlineStr"/>
       <c r="V168" t="inlineStr">
         <is>
-          <t>Ruca1</t>
+          <t>FqhcTmDr</t>
         </is>
       </c>
       <c r="W168" t="inlineStr">
         <is>
-          <t>Primary RUCA Code</t>
+          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC)</t>
         </is>
       </c>
       <c r="X168" t="inlineStr"/>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB168" t="inlineStr"/>
@@ -12861,17 +12865,13 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr"/>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F169" t="inlineStr"/>
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr"/>
@@ -12884,33 +12884,41 @@
       <c r="P169" t="inlineStr"/>
       <c r="Q169" t="inlineStr"/>
       <c r="R169" t="inlineStr"/>
-      <c r="S169" t="inlineStr"/>
-      <c r="T169" t="inlineStr"/>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U169" t="inlineStr"/>
       <c r="V169" t="inlineStr">
         <is>
-          <t>Ruca2</t>
+          <t>FqhcTmDr2</t>
         </is>
       </c>
       <c r="W169" t="inlineStr">
         <is>
-          <t>Secondary RUCA Code</t>
+          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC), with Impedance factor</t>
         </is>
       </c>
       <c r="X169" t="inlineStr"/>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB169" t="inlineStr"/>
@@ -12925,17 +12933,13 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr"/>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F170" t="inlineStr"/>
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr"/>
@@ -12948,37 +12952,37 @@
       <c r="P170" t="inlineStr"/>
       <c r="Q170" t="inlineStr"/>
       <c r="R170" t="inlineStr"/>
-      <c r="S170" t="inlineStr"/>
-      <c r="T170" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T170" t="inlineStr"/>
       <c r="U170" t="inlineStr"/>
       <c r="V170" t="inlineStr">
         <is>
-          <t>Rurality</t>
+          <t>HcvCntDr</t>
         </is>
       </c>
       <c r="W170" t="inlineStr">
         <is>
-          <t>Urban-Suburban-Rural</t>
+          <t>Count of HCV Providers</t>
         </is>
       </c>
       <c r="X170" t="inlineStr"/>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB170" t="inlineStr"/>
@@ -12988,12 +12992,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
@@ -13005,44 +13009,44 @@
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr"/>
-      <c r="L171" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L171" t="inlineStr"/>
       <c r="M171" t="inlineStr"/>
       <c r="N171" t="inlineStr"/>
       <c r="O171" t="inlineStr"/>
       <c r="P171" t="inlineStr"/>
       <c r="Q171" t="inlineStr"/>
       <c r="R171" t="inlineStr"/>
-      <c r="S171" t="inlineStr"/>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T171" t="inlineStr"/>
       <c r="U171" t="inlineStr"/>
       <c r="V171" t="inlineStr">
         <is>
-          <t>EssnWrkE</t>
+          <t>HcvMinDis</t>
         </is>
       </c>
       <c r="W171" t="inlineStr">
         <is>
-          <t>Count of Essential Workers</t>
+          <t>Distance to nearest HCV Provider</t>
         </is>
       </c>
       <c r="X171" t="inlineStr"/>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB171" t="inlineStr"/>
@@ -13052,12 +13056,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
@@ -13069,52 +13073,44 @@
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr"/>
-      <c r="L172" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L172" t="inlineStr"/>
       <c r="M172" t="inlineStr"/>
-      <c r="N172" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N172" t="inlineStr"/>
       <c r="O172" t="inlineStr"/>
       <c r="P172" t="inlineStr"/>
-      <c r="Q172" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q172" t="inlineStr"/>
       <c r="R172" t="inlineStr"/>
-      <c r="S172" t="inlineStr"/>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T172" t="inlineStr"/>
       <c r="U172" t="inlineStr"/>
       <c r="V172" t="inlineStr">
         <is>
-          <t>EssnWrkP</t>
+          <t>HcvTmDr</t>
         </is>
       </c>
       <c r="W172" t="inlineStr">
         <is>
-          <t>Essential Workers %</t>
+          <t>Driving time to nearest HCV Provider</t>
         </is>
       </c>
       <c r="X172" t="inlineStr"/>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB172" t="inlineStr"/>
@@ -13124,12 +13120,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -13141,52 +13137,44 @@
       <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr"/>
-      <c r="L173" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L173" t="inlineStr"/>
       <c r="M173" t="inlineStr"/>
-      <c r="N173" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N173" t="inlineStr"/>
       <c r="O173" t="inlineStr"/>
       <c r="P173" t="inlineStr"/>
-      <c r="Q173" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q173" t="inlineStr"/>
       <c r="R173" t="inlineStr"/>
-      <c r="S173" t="inlineStr"/>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T173" t="inlineStr"/>
       <c r="U173" t="inlineStr"/>
       <c r="V173" t="inlineStr">
         <is>
-          <t>HghRskP</t>
+          <t>HcvTmDr2</t>
         </is>
       </c>
       <c r="W173" t="inlineStr">
         <is>
-          <t>Employed % - High Risk of Injury</t>
+          <t>Driving time (min) to nearest HCV Testing Facility with impedance</t>
         </is>
       </c>
       <c r="X173" t="inlineStr"/>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB173" t="inlineStr"/>
@@ -13196,69 +13184,61 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr"/>
-      <c r="F174" t="inlineStr"/>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr"/>
-      <c r="L174" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L174" t="inlineStr"/>
       <c r="M174" t="inlineStr"/>
-      <c r="N174" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N174" t="inlineStr"/>
       <c r="O174" t="inlineStr"/>
       <c r="P174" t="inlineStr"/>
-      <c r="Q174" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q174" t="inlineStr"/>
       <c r="R174" t="inlineStr"/>
       <c r="S174" t="inlineStr"/>
       <c r="T174" t="inlineStr"/>
       <c r="U174" t="inlineStr"/>
       <c r="V174" t="inlineStr">
         <is>
-          <t>HltCrP</t>
+          <t>Ruca1</t>
         </is>
       </c>
       <c r="W174" t="inlineStr">
         <is>
-          <t>Employed % - Health Care</t>
+          <t>Primary RUCA Code</t>
         </is>
       </c>
       <c r="X174" t="inlineStr"/>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB174" t="inlineStr"/>
@@ -13268,69 +13248,61 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr"/>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L175" t="inlineStr"/>
       <c r="M175" t="inlineStr"/>
-      <c r="N175" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N175" t="inlineStr"/>
       <c r="O175" t="inlineStr"/>
       <c r="P175" t="inlineStr"/>
-      <c r="Q175" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q175" t="inlineStr"/>
       <c r="R175" t="inlineStr"/>
       <c r="S175" t="inlineStr"/>
       <c r="T175" t="inlineStr"/>
       <c r="U175" t="inlineStr"/>
       <c r="V175" t="inlineStr">
         <is>
-          <t>RetailP</t>
+          <t>Ruca2</t>
         </is>
       </c>
       <c r="W175" t="inlineStr">
         <is>
-          <t>Employed % - Retail</t>
+          <t>Secondary RUCA Code</t>
         </is>
       </c>
       <c r="X175" t="inlineStr"/>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB175" t="inlineStr"/>
@@ -13340,69 +13312,65 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr"/>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr"/>
-      <c r="L176" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L176" t="inlineStr"/>
       <c r="M176" t="inlineStr"/>
-      <c r="N176" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N176" t="inlineStr"/>
       <c r="O176" t="inlineStr"/>
       <c r="P176" t="inlineStr"/>
-      <c r="Q176" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q176" t="inlineStr"/>
       <c r="R176" t="inlineStr"/>
       <c r="S176" t="inlineStr"/>
-      <c r="T176" t="inlineStr"/>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U176" t="inlineStr"/>
       <c r="V176" t="inlineStr">
         <is>
-          <t>TotWrkE</t>
+          <t>Rurality</t>
         </is>
       </c>
       <c r="W176" t="inlineStr">
         <is>
-          <t>Count of Working Population</t>
+          <t>Urban-Suburban-Rural</t>
         </is>
       </c>
       <c r="X176" t="inlineStr"/>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB176" t="inlineStr"/>
@@ -13417,7 +13385,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
@@ -13445,28 +13413,28 @@
       <c r="U177" t="inlineStr"/>
       <c r="V177" t="inlineStr">
         <is>
-          <t>ForDqP</t>
+          <t>EssnWrkE</t>
         </is>
       </c>
       <c r="W177" t="inlineStr">
         <is>
-          <t>Foreclosure &amp; Delinquency %</t>
+          <t>Count of Essential Workers</t>
         </is>
       </c>
       <c r="X177" t="inlineStr"/>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB177" t="inlineStr"/>
@@ -13481,7 +13449,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
@@ -13499,38 +13467,46 @@
         </is>
       </c>
       <c r="M178" t="inlineStr"/>
-      <c r="N178" t="inlineStr"/>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O178" t="inlineStr"/>
       <c r="P178" t="inlineStr"/>
-      <c r="Q178" t="inlineStr"/>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R178" t="inlineStr"/>
       <c r="S178" t="inlineStr"/>
       <c r="T178" t="inlineStr"/>
       <c r="U178" t="inlineStr"/>
       <c r="V178" t="inlineStr">
         <is>
-          <t>ForDqTot</t>
+          <t>EssnWrkP</t>
         </is>
       </c>
       <c r="W178" t="inlineStr">
         <is>
-          <t>Foreclosure &amp; Delinquency Count</t>
+          <t>Essential Workers %</t>
         </is>
       </c>
       <c r="X178" t="inlineStr"/>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB178" t="inlineStr"/>
@@ -13545,17 +13521,13 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F179" t="inlineStr"/>
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr"/>
@@ -13585,28 +13557,28 @@
       <c r="U179" t="inlineStr"/>
       <c r="V179" t="inlineStr">
         <is>
-          <t>GiniCoeff</t>
+          <t>HghRskP</t>
         </is>
       </c>
       <c r="W179" t="inlineStr">
         <is>
-          <t>Income Inequality (Gini Coefficient)</t>
+          <t>Employed % - High Risk of Injury</t>
         </is>
       </c>
       <c r="X179" t="inlineStr"/>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB179" t="inlineStr"/>
@@ -13621,7 +13593,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Internet Access</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
@@ -13633,44 +13605,52 @@
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr"/>
-      <c r="L180" t="inlineStr"/>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N180" t="inlineStr"/>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr"/>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O180" t="inlineStr"/>
       <c r="P180" t="inlineStr"/>
-      <c r="Q180" t="inlineStr"/>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R180" t="inlineStr"/>
       <c r="S180" t="inlineStr"/>
       <c r="T180" t="inlineStr"/>
       <c r="U180" t="inlineStr"/>
       <c r="V180" t="inlineStr">
         <is>
-          <t>NoIntP</t>
+          <t>HltCrP</t>
         </is>
       </c>
       <c r="W180" t="inlineStr">
         <is>
-          <t>Households without Internet Access %</t>
+          <t>Employed % - Health Care</t>
         </is>
       </c>
       <c r="X180" t="inlineStr"/>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Internet_Access.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>ACS 2019</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>American Community Survey 2015-2019 5-Year Estimate</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB180" t="inlineStr"/>
@@ -13685,17 +13665,13 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr"/>
@@ -13725,28 +13701,28 @@
       <c r="U181" t="inlineStr"/>
       <c r="V181" t="inlineStr">
         <is>
-          <t>MedInc</t>
+          <t>RetailP</t>
         </is>
       </c>
       <c r="W181" t="inlineStr">
         <is>
-          <t>Median Income</t>
+          <t>Employed % - Retail</t>
         </is>
       </c>
       <c r="X181" t="inlineStr"/>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB181" t="inlineStr"/>
@@ -13761,17 +13737,13 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
@@ -13801,28 +13773,28 @@
       <c r="U182" t="inlineStr"/>
       <c r="V182" t="inlineStr">
         <is>
-          <t>PciE</t>
+          <t>TotWrkE</t>
         </is>
       </c>
       <c r="W182" t="inlineStr">
         <is>
-          <t>Per Capita Income</t>
+          <t>Count of Working Population</t>
         </is>
       </c>
       <c r="X182" t="inlineStr"/>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB182" t="inlineStr"/>
@@ -13837,29 +13809,13 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>Great Recession Foreclosure Rate</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr"/>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
       <c r="G183" t="inlineStr"/>
       <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr"/>
@@ -13871,50 +13827,38 @@
         </is>
       </c>
       <c r="M183" t="inlineStr"/>
-      <c r="N183" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N183" t="inlineStr"/>
       <c r="O183" t="inlineStr"/>
       <c r="P183" t="inlineStr"/>
-      <c r="Q183" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q183" t="inlineStr"/>
       <c r="R183" t="inlineStr"/>
       <c r="S183" t="inlineStr"/>
       <c r="T183" t="inlineStr"/>
-      <c r="U183" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="U183" t="inlineStr"/>
       <c r="V183" t="inlineStr">
         <is>
-          <t>PovP</t>
+          <t>ForDqP</t>
         </is>
       </c>
       <c r="W183" t="inlineStr">
         <is>
-          <t>Poverty %</t>
+          <t>Foreclosure &amp; Delinquency %</t>
         </is>
       </c>
       <c r="X183" t="inlineStr"/>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
         </is>
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>HUD 2018; ACS 2012, 2018</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB183" t="inlineStr"/>
@@ -13929,29 +13873,13 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>Great Recession Foreclosure Rate</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr"/>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr"/>
       <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr"/>
@@ -13963,50 +13891,38 @@
         </is>
       </c>
       <c r="M184" t="inlineStr"/>
-      <c r="N184" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N184" t="inlineStr"/>
       <c r="O184" t="inlineStr"/>
       <c r="P184" t="inlineStr"/>
-      <c r="Q184" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q184" t="inlineStr"/>
       <c r="R184" t="inlineStr"/>
       <c r="S184" t="inlineStr"/>
       <c r="T184" t="inlineStr"/>
-      <c r="U184" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="U184" t="inlineStr"/>
       <c r="V184" t="inlineStr">
         <is>
-          <t>UnempP</t>
+          <t>ForDqTot</t>
         </is>
       </c>
       <c r="W184" t="inlineStr">
         <is>
-          <t>Unemployment %</t>
+          <t>Foreclosure &amp; Delinquency Count</t>
         </is>
       </c>
       <c r="X184" t="inlineStr"/>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
         </is>
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>HUD 2018; ACS 2012, 2018</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB184" t="inlineStr"/>
@@ -14016,65 +13932,73 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>SDOH Indices &amp; Typology</t>
+          <t>Great Recession Foreclosure Rate</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr"/>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G185" t="inlineStr"/>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr"/>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M185" t="inlineStr"/>
-      <c r="N185" t="inlineStr"/>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O185" t="inlineStr"/>
       <c r="P185" t="inlineStr"/>
-      <c r="Q185" t="inlineStr"/>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R185" t="inlineStr"/>
       <c r="S185" t="inlineStr"/>
-      <c r="T185" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T185" t="inlineStr"/>
       <c r="U185" t="inlineStr"/>
       <c r="V185" t="inlineStr">
         <is>
-          <t>LimMobInd</t>
+          <t>GiniCoeff</t>
         </is>
       </c>
       <c r="W185" t="inlineStr">
         <is>
-          <t>Limited Moblility Index</t>
+          <t>Income Inequality (Gini Coefficient)</t>
         </is>
       </c>
       <c r="X185" t="inlineStr"/>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
         </is>
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>HUD 2018; ACS 2012, 2018</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB185" t="inlineStr"/>
@@ -14084,12 +14008,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>SDOH Indices &amp; Typology</t>
+          <t>Internet Access</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
@@ -14097,52 +14021,48 @@
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr"/>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr"/>
-      <c r="M186" t="inlineStr"/>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N186" t="inlineStr"/>
       <c r="O186" t="inlineStr"/>
       <c r="P186" t="inlineStr"/>
       <c r="Q186" t="inlineStr"/>
       <c r="R186" t="inlineStr"/>
       <c r="S186" t="inlineStr"/>
-      <c r="T186" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T186" t="inlineStr"/>
       <c r="U186" t="inlineStr"/>
       <c r="V186" t="inlineStr">
         <is>
-          <t>MicaInd</t>
+          <t>NoIntP</t>
         </is>
       </c>
       <c r="W186" t="inlineStr">
         <is>
-          <t>Mixed Immigrant Cohesion and Accesibility (MICA) Index</t>
+          <t>Households without Internet Access %</t>
         </is>
       </c>
       <c r="X186" t="inlineStr"/>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Internet_Access.md</t>
         </is>
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>ACS 2019</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>American Community Survey 2015-2019 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB186" t="inlineStr"/>
@@ -14152,61 +14072,73 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>SDOH Indices &amp; Typology</t>
+          <t>Poverty, Income, Gini Coefficient</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr"/>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G187" t="inlineStr"/>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr"/>
-      <c r="L187" t="inlineStr"/>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M187" t="inlineStr"/>
-      <c r="N187" t="inlineStr"/>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O187" t="inlineStr"/>
       <c r="P187" t="inlineStr"/>
-      <c r="Q187" t="inlineStr"/>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R187" t="inlineStr"/>
       <c r="S187" t="inlineStr"/>
       <c r="T187" t="inlineStr"/>
       <c r="U187" t="inlineStr"/>
       <c r="V187" t="inlineStr">
         <is>
-          <t>NeighbTyp</t>
+          <t>MedInc</t>
         </is>
       </c>
       <c r="W187" t="inlineStr">
         <is>
-          <t>Neighborhood Type</t>
+          <t>Median Income</t>
         </is>
       </c>
       <c r="X187" t="inlineStr"/>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB187" t="inlineStr"/>
@@ -14216,65 +14148,73 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>SDOH Indices &amp; Typology</t>
+          <t>Poverty, Income, Gini Coefficient</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr"/>
-      <c r="F188" t="inlineStr"/>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G188" t="inlineStr"/>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr"/>
       <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr"/>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M188" t="inlineStr"/>
-      <c r="N188" t="inlineStr"/>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O188" t="inlineStr"/>
       <c r="P188" t="inlineStr"/>
-      <c r="Q188" t="inlineStr"/>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R188" t="inlineStr"/>
       <c r="S188" t="inlineStr"/>
-      <c r="T188" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T188" t="inlineStr"/>
       <c r="U188" t="inlineStr"/>
       <c r="V188" t="inlineStr">
         <is>
-          <t>SocEcAdvIn</t>
+          <t>PciE</t>
         </is>
       </c>
       <c r="W188" t="inlineStr">
         <is>
-          <t>Socioeconomic Advantage Index</t>
+          <t>Per Capita Income</t>
         </is>
       </c>
       <c r="X188" t="inlineStr"/>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB188" t="inlineStr"/>
@@ -14284,65 +14224,89 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>SDOH Indices &amp; Typology</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr"/>
-      <c r="D189" t="inlineStr"/>
-      <c r="E189" t="inlineStr"/>
-      <c r="F189" t="inlineStr"/>
+          <t>Poverty, Income, Gini Coefficient</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G189" t="inlineStr"/>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr"/>
-      <c r="L189" t="inlineStr"/>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M189" t="inlineStr"/>
-      <c r="N189" t="inlineStr"/>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O189" t="inlineStr"/>
       <c r="P189" t="inlineStr"/>
-      <c r="Q189" t="inlineStr"/>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R189" t="inlineStr"/>
       <c r="S189" t="inlineStr"/>
-      <c r="T189" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="U189" t="inlineStr"/>
+      <c r="T189" t="inlineStr"/>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="V189" t="inlineStr">
         <is>
-          <t>UrbCoreInd</t>
+          <t>PovP</t>
         </is>
       </c>
       <c r="W189" t="inlineStr">
         <is>
-          <t>Urban Core Opportunity Index</t>
+          <t>Poverty %</t>
         </is>
       </c>
       <c r="X189" t="inlineStr"/>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB189" t="inlineStr"/>
@@ -14352,18 +14316,34 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr"/>
-      <c r="D190" t="inlineStr"/>
-      <c r="E190" t="inlineStr"/>
-      <c r="F190" t="inlineStr"/>
+          <t>Poverty, Income, Gini Coefficient</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr"/>
@@ -14381,40 +14361,44 @@
         </is>
       </c>
       <c r="O190" t="inlineStr"/>
-      <c r="P190" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q190" t="inlineStr"/>
+      <c r="P190" t="inlineStr"/>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R190" t="inlineStr"/>
       <c r="S190" t="inlineStr"/>
       <c r="T190" t="inlineStr"/>
-      <c r="U190" t="inlineStr"/>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="V190" t="inlineStr">
         <is>
-          <t>SviSmryRnk</t>
+          <t>UnempP</t>
         </is>
       </c>
       <c r="W190" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) Summary Ranking</t>
+          <t>Unemployment %</t>
         </is>
       </c>
       <c r="X190" t="inlineStr"/>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB190" t="inlineStr"/>
@@ -14429,7 +14413,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>SDOH Indices &amp; Typology</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
@@ -14437,27 +14421,19 @@
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr"/>
-      <c r="H191" t="inlineStr"/>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr"/>
-      <c r="L191" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L191" t="inlineStr"/>
       <c r="M191" t="inlineStr"/>
-      <c r="N191" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N191" t="inlineStr"/>
       <c r="O191" t="inlineStr"/>
-      <c r="P191" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P191" t="inlineStr"/>
       <c r="Q191" t="inlineStr"/>
       <c r="R191" t="inlineStr"/>
       <c r="S191" t="inlineStr"/>
@@ -14469,28 +14445,28 @@
       <c r="U191" t="inlineStr"/>
       <c r="V191" t="inlineStr">
         <is>
-          <t>SviTh1</t>
+          <t>LimMobInd</t>
         </is>
       </c>
       <c r="W191" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 1</t>
+          <t>Limited Moblility Index</t>
         </is>
       </c>
       <c r="X191" t="inlineStr"/>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
         </is>
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AB191" t="inlineStr"/>
@@ -14505,7 +14481,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>SDOH Indices &amp; Typology</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
@@ -14513,56 +14489,52 @@
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr"/>
-      <c r="H192" t="inlineStr"/>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr"/>
-      <c r="L192" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L192" t="inlineStr"/>
       <c r="M192" t="inlineStr"/>
-      <c r="N192" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N192" t="inlineStr"/>
       <c r="O192" t="inlineStr"/>
-      <c r="P192" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P192" t="inlineStr"/>
       <c r="Q192" t="inlineStr"/>
       <c r="R192" t="inlineStr"/>
       <c r="S192" t="inlineStr"/>
-      <c r="T192" t="inlineStr"/>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U192" t="inlineStr"/>
       <c r="V192" t="inlineStr">
         <is>
-          <t>SviTh2</t>
+          <t>MicaInd</t>
         </is>
       </c>
       <c r="W192" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 2</t>
+          <t>Mixed Immigrant Cohesion and Accesibility (MICA) Index</t>
         </is>
       </c>
       <c r="X192" t="inlineStr"/>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
         </is>
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AB192" t="inlineStr"/>
@@ -14577,7 +14549,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>SDOH Indices &amp; Typology</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
@@ -14585,27 +14557,19 @@
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr"/>
-      <c r="H193" t="inlineStr"/>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr"/>
-      <c r="L193" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L193" t="inlineStr"/>
       <c r="M193" t="inlineStr"/>
-      <c r="N193" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N193" t="inlineStr"/>
       <c r="O193" t="inlineStr"/>
-      <c r="P193" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P193" t="inlineStr"/>
       <c r="Q193" t="inlineStr"/>
       <c r="R193" t="inlineStr"/>
       <c r="S193" t="inlineStr"/>
@@ -14613,28 +14577,28 @@
       <c r="U193" t="inlineStr"/>
       <c r="V193" t="inlineStr">
         <is>
-          <t>SviTh3</t>
+          <t>NeighbTyp</t>
         </is>
       </c>
       <c r="W193" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 3</t>
+          <t>Neighborhood Type</t>
         </is>
       </c>
       <c r="X193" t="inlineStr"/>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
         </is>
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AB193" t="inlineStr"/>
@@ -14649,7 +14613,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>SDOH Indices &amp; Typology</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
@@ -14657,27 +14621,19 @@
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr"/>
-      <c r="H194" t="inlineStr"/>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr"/>
-      <c r="L194" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L194" t="inlineStr"/>
       <c r="M194" t="inlineStr"/>
-      <c r="N194" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N194" t="inlineStr"/>
       <c r="O194" t="inlineStr"/>
-      <c r="P194" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P194" t="inlineStr"/>
       <c r="Q194" t="inlineStr"/>
       <c r="R194" t="inlineStr"/>
       <c r="S194" t="inlineStr"/>
@@ -14689,33 +14645,469 @@
       <c r="U194" t="inlineStr"/>
       <c r="V194" t="inlineStr">
         <is>
-          <t>SviTh4</t>
+          <t>SocEcAdvIn</t>
         </is>
       </c>
       <c r="W194" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 4</t>
+          <t>Socioeconomic Advantage Index</t>
         </is>
       </c>
       <c r="X194" t="inlineStr"/>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
         </is>
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AB194" t="inlineStr"/>
       <c r="AC194" t="inlineStr"/>
       <c r="AD194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>SDOH Indices &amp; Typology</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr"/>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
+      <c r="O195" t="inlineStr"/>
+      <c r="P195" t="inlineStr"/>
+      <c r="Q195" t="inlineStr"/>
+      <c r="R195" t="inlineStr"/>
+      <c r="S195" t="inlineStr"/>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr"/>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>UrbCoreInd</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>Urban Core Opportunity Index</t>
+        </is>
+      </c>
+      <c r="X195" t="inlineStr"/>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
+        </is>
+      </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>Kolak et al., 2020</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>Kolak et al., 2020</t>
+        </is>
+      </c>
+      <c r="AB195" t="inlineStr"/>
+      <c r="AC195" t="inlineStr"/>
+      <c r="AD195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr"/>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr"/>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr"/>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q196" t="inlineStr"/>
+      <c r="R196" t="inlineStr"/>
+      <c r="S196" t="inlineStr"/>
+      <c r="T196" t="inlineStr"/>
+      <c r="U196" t="inlineStr"/>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>SviSmryRnk</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) Summary Ranking</t>
+        </is>
+      </c>
+      <c r="X196" t="inlineStr"/>
+      <c r="Y196" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB196" t="inlineStr"/>
+      <c r="AC196" t="inlineStr"/>
+      <c r="AD196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr"/>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr"/>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr"/>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr"/>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr"/>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q197" t="inlineStr"/>
+      <c r="R197" t="inlineStr"/>
+      <c r="S197" t="inlineStr"/>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr"/>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>SviTh1</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 1</t>
+        </is>
+      </c>
+      <c r="X197" t="inlineStr"/>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB197" t="inlineStr"/>
+      <c r="AC197" t="inlineStr"/>
+      <c r="AD197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr"/>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr"/>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr"/>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr"/>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr"/>
+      <c r="R198" t="inlineStr"/>
+      <c r="S198" t="inlineStr"/>
+      <c r="T198" t="inlineStr"/>
+      <c r="U198" t="inlineStr"/>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>SviTh2</t>
+        </is>
+      </c>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 2</t>
+        </is>
+      </c>
+      <c r="X198" t="inlineStr"/>
+      <c r="Y198" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB198" t="inlineStr"/>
+      <c r="AC198" t="inlineStr"/>
+      <c r="AD198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr"/>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr"/>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr"/>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr"/>
+      <c r="R199" t="inlineStr"/>
+      <c r="S199" t="inlineStr"/>
+      <c r="T199" t="inlineStr"/>
+      <c r="U199" t="inlineStr"/>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>SviTh3</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 3</t>
+        </is>
+      </c>
+      <c r="X199" t="inlineStr"/>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB199" t="inlineStr"/>
+      <c r="AC199" t="inlineStr"/>
+      <c r="AD199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr"/>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr"/>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr"/>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr"/>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr"/>
+      <c r="R200" t="inlineStr"/>
+      <c r="S200" t="inlineStr"/>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr"/>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>SviTh4</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 4</t>
+        </is>
+      </c>
+      <c r="X200" t="inlineStr"/>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB200" t="inlineStr"/>
+      <c r="AC200" t="inlineStr"/>
+      <c r="AD200" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/src/reference/data-dictionaries/T_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/T_Dict.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD200"/>
+  <dimension ref="A1:AD201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -12021,12 +12021,12 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB156" t="inlineStr"/>
@@ -12089,12 +12089,12 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB157" t="inlineStr"/>
@@ -12161,12 +12161,12 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB158" t="inlineStr"/>
@@ -12181,7 +12181,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
@@ -12194,11 +12194,7 @@
       <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M159" t="inlineStr"/>
       <c r="N159" t="inlineStr"/>
       <c r="O159" t="inlineStr"/>
       <c r="P159" t="inlineStr"/>
@@ -12213,28 +12209,28 @@
       <c r="U159" t="inlineStr"/>
       <c r="V159" t="inlineStr">
         <is>
-          <t>RxCntDr</t>
+          <t>MhTmDr2</t>
         </is>
       </c>
       <c r="W159" t="inlineStr">
         <is>
-          <t>Count of Pharmacies (30-min drive)</t>
+          <t>Driving time (min) to nearest Mental Health Provider with impedance</t>
         </is>
       </c>
       <c r="X159" t="inlineStr"/>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB159" t="inlineStr"/>
@@ -12272,17 +12268,21 @@
       <c r="P160" t="inlineStr"/>
       <c r="Q160" t="inlineStr"/>
       <c r="R160" t="inlineStr"/>
-      <c r="S160" t="inlineStr"/>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T160" t="inlineStr"/>
       <c r="U160" t="inlineStr"/>
       <c r="V160" t="inlineStr">
         <is>
-          <t>RxMinDis</t>
+          <t>RxCntDr</t>
         </is>
       </c>
       <c r="W160" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Pharmacy</t>
+          <t>Count of Pharmacies (30-min drive)</t>
         </is>
       </c>
       <c r="X160" t="inlineStr"/>
@@ -12336,25 +12336,17 @@
       <c r="P161" t="inlineStr"/>
       <c r="Q161" t="inlineStr"/>
       <c r="R161" t="inlineStr"/>
-      <c r="S161" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="T161" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S161" t="inlineStr"/>
+      <c r="T161" t="inlineStr"/>
       <c r="U161" t="inlineStr"/>
       <c r="V161" t="inlineStr">
         <is>
-          <t>RxTmDr</t>
+          <t>RxMinDis</t>
         </is>
       </c>
       <c r="W161" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Pharmacy</t>
+          <t>Distance (mi) to nearest Pharmacy</t>
         </is>
       </c>
       <c r="X161" t="inlineStr"/>
@@ -12398,7 +12390,11 @@
       <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr"/>
-      <c r="M162" t="inlineStr"/>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N162" t="inlineStr"/>
       <c r="O162" t="inlineStr"/>
       <c r="P162" t="inlineStr"/>
@@ -12409,16 +12405,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T162" t="inlineStr"/>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U162" t="inlineStr"/>
       <c r="V162" t="inlineStr">
         <is>
-          <t>RxTmDr2</t>
+          <t>RxTmDr</t>
         </is>
       </c>
       <c r="W162" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Pharmacy with Impedance Factor</t>
+          <t>Driving Time (min) to nearest Pharmacy</t>
         </is>
       </c>
       <c r="X162" t="inlineStr"/>
@@ -12449,7 +12449,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
@@ -12463,11 +12463,7 @@
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr"/>
       <c r="M163" t="inlineStr"/>
-      <c r="N163" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N163" t="inlineStr"/>
       <c r="O163" t="inlineStr"/>
       <c r="P163" t="inlineStr"/>
       <c r="Q163" t="inlineStr"/>
@@ -12481,28 +12477,28 @@
       <c r="U163" t="inlineStr"/>
       <c r="V163" t="inlineStr">
         <is>
-          <t>SutCntDr</t>
+          <t>RxTmDr2</t>
         </is>
       </c>
       <c r="W163" t="inlineStr">
         <is>
-          <t>Count of Substance Use Treatment (SUT) facility (30-min drive)</t>
+          <t>Driving Time (min) to nearest Pharmacy with Impedance Factor</t>
         </is>
       </c>
       <c r="X163" t="inlineStr"/>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB163" t="inlineStr"/>
@@ -12549,12 +12545,12 @@
       <c r="U164" t="inlineStr"/>
       <c r="V164" t="inlineStr">
         <is>
-          <t>SutMinDis</t>
+          <t>SutCntDr</t>
         </is>
       </c>
       <c r="W164" t="inlineStr">
         <is>
-          <t>Distance (mi) to Substance Use Treatment (SUT) facility</t>
+          <t>Count of Substance Use Treatment (SUT) facility (30-min drive)</t>
         </is>
       </c>
       <c r="X164" t="inlineStr"/>
@@ -12613,20 +12609,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T165" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T165" t="inlineStr"/>
       <c r="U165" t="inlineStr"/>
       <c r="V165" t="inlineStr">
         <is>
-          <t>SutTmDr</t>
+          <t>SutMinDis</t>
         </is>
       </c>
       <c r="W165" t="inlineStr">
         <is>
-          <t>Driving time (min) to Substance Use Treatment (SUT) facility</t>
+          <t>Distance (mi) to Substance Use Treatment (SUT) facility</t>
         </is>
       </c>
       <c r="X165" t="inlineStr"/>
@@ -12657,7 +12649,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
@@ -12685,32 +12677,36 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T166" t="inlineStr"/>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U166" t="inlineStr"/>
       <c r="V166" t="inlineStr">
         <is>
-          <t>FqhcCntDr</t>
+          <t>SutTmDr</t>
         </is>
       </c>
       <c r="W166" t="inlineStr">
         <is>
-          <t>Count of Federally Qualified Health Centers (FQHCs) within 30-min drive</t>
+          <t>Driving time (min) to Substance Use Treatment (SUT) facility</t>
         </is>
       </c>
       <c r="X166" t="inlineStr"/>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB166" t="inlineStr"/>
@@ -12757,12 +12753,12 @@
       <c r="U167" t="inlineStr"/>
       <c r="V167" t="inlineStr">
         <is>
-          <t>FqhcMinDis</t>
+          <t>FqhcCntDr</t>
         </is>
       </c>
       <c r="W167" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Federally Qualified Health Centers (FQHC)</t>
+          <t>Count of Federally Qualified Health Centers (FQHCs) within 30-min drive</t>
         </is>
       </c>
       <c r="X167" t="inlineStr"/>
@@ -12821,20 +12817,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T168" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T168" t="inlineStr"/>
       <c r="U168" t="inlineStr"/>
       <c r="V168" t="inlineStr">
         <is>
-          <t>FqhcTmDr</t>
+          <t>FqhcMinDis</t>
         </is>
       </c>
       <c r="W168" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC)</t>
+          <t>Distance (mi) to nearest Federally Qualified Health Centers (FQHC)</t>
         </is>
       </c>
       <c r="X168" t="inlineStr"/>
@@ -12879,7 +12871,11 @@
       <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr"/>
       <c r="M169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O169" t="inlineStr"/>
       <c r="P169" t="inlineStr"/>
       <c r="Q169" t="inlineStr"/>
@@ -12897,12 +12893,12 @@
       <c r="U169" t="inlineStr"/>
       <c r="V169" t="inlineStr">
         <is>
-          <t>FqhcTmDr2</t>
+          <t>FqhcTmDr</t>
         </is>
       </c>
       <c r="W169" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC), with Impedance factor</t>
+          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC)</t>
         </is>
       </c>
       <c r="X169" t="inlineStr"/>
@@ -12933,7 +12929,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
@@ -12957,32 +12953,36 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T170" t="inlineStr"/>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U170" t="inlineStr"/>
       <c r="V170" t="inlineStr">
         <is>
-          <t>HcvCntDr</t>
+          <t>FqhcTmDr2</t>
         </is>
       </c>
       <c r="W170" t="inlineStr">
         <is>
-          <t>Count of HCV Providers</t>
+          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC), with Impedance factor</t>
         </is>
       </c>
       <c r="X170" t="inlineStr"/>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB170" t="inlineStr"/>
@@ -13025,12 +13025,12 @@
       <c r="U171" t="inlineStr"/>
       <c r="V171" t="inlineStr">
         <is>
-          <t>HcvMinDis</t>
+          <t>HcvCntDr</t>
         </is>
       </c>
       <c r="W171" t="inlineStr">
         <is>
-          <t>Distance to nearest HCV Provider</t>
+          <t>Count of HCV Providers</t>
         </is>
       </c>
       <c r="X171" t="inlineStr"/>
@@ -13089,12 +13089,12 @@
       <c r="U172" t="inlineStr"/>
       <c r="V172" t="inlineStr">
         <is>
-          <t>HcvTmDr</t>
+          <t>HcvMinDis</t>
         </is>
       </c>
       <c r="W172" t="inlineStr">
         <is>
-          <t>Driving time to nearest HCV Provider</t>
+          <t>Distance to nearest HCV Provider</t>
         </is>
       </c>
       <c r="X172" t="inlineStr"/>
@@ -13153,12 +13153,12 @@
       <c r="U173" t="inlineStr"/>
       <c r="V173" t="inlineStr">
         <is>
-          <t>HcvTmDr2</t>
+          <t>HcvTmDr</t>
         </is>
       </c>
       <c r="W173" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest HCV Testing Facility with impedance</t>
+          <t>Driving time to nearest HCV Provider</t>
         </is>
       </c>
       <c r="X173" t="inlineStr"/>
@@ -13189,17 +13189,13 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr"/>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F174" t="inlineStr"/>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
@@ -13212,33 +13208,37 @@
       <c r="P174" t="inlineStr"/>
       <c r="Q174" t="inlineStr"/>
       <c r="R174" t="inlineStr"/>
-      <c r="S174" t="inlineStr"/>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T174" t="inlineStr"/>
       <c r="U174" t="inlineStr"/>
       <c r="V174" t="inlineStr">
         <is>
-          <t>Ruca1</t>
+          <t>HcvTmDr2</t>
         </is>
       </c>
       <c r="W174" t="inlineStr">
         <is>
-          <t>Primary RUCA Code</t>
+          <t>Driving time (min) to nearest HCV Testing Facility with impedance</t>
         </is>
       </c>
       <c r="X174" t="inlineStr"/>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB174" t="inlineStr"/>
@@ -13281,12 +13281,12 @@
       <c r="U175" t="inlineStr"/>
       <c r="V175" t="inlineStr">
         <is>
-          <t>Ruca2</t>
+          <t>Ruca1</t>
         </is>
       </c>
       <c r="W175" t="inlineStr">
         <is>
-          <t>Secondary RUCA Code</t>
+          <t>Primary RUCA Code</t>
         </is>
       </c>
       <c r="X175" t="inlineStr"/>
@@ -13341,20 +13341,16 @@
       <c r="Q176" t="inlineStr"/>
       <c r="R176" t="inlineStr"/>
       <c r="S176" t="inlineStr"/>
-      <c r="T176" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T176" t="inlineStr"/>
       <c r="U176" t="inlineStr"/>
       <c r="V176" t="inlineStr">
         <is>
-          <t>Rurality</t>
+          <t>Ruca2</t>
         </is>
       </c>
       <c r="W176" t="inlineStr">
         <is>
-          <t>Urban-Suburban-Rural</t>
+          <t>Secondary RUCA Code</t>
         </is>
       </c>
       <c r="X176" t="inlineStr"/>
@@ -13380,28 +13376,28 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr"/>
-      <c r="F177" t="inlineStr"/>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr"/>
-      <c r="L177" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L177" t="inlineStr"/>
       <c r="M177" t="inlineStr"/>
       <c r="N177" t="inlineStr"/>
       <c r="O177" t="inlineStr"/>
@@ -13409,32 +13405,36 @@
       <c r="Q177" t="inlineStr"/>
       <c r="R177" t="inlineStr"/>
       <c r="S177" t="inlineStr"/>
-      <c r="T177" t="inlineStr"/>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U177" t="inlineStr"/>
       <c r="V177" t="inlineStr">
         <is>
-          <t>EssnWrkE</t>
+          <t>Rurality</t>
         </is>
       </c>
       <c r="W177" t="inlineStr">
         <is>
-          <t>Count of Essential Workers</t>
+          <t>Urban-Suburban-Rural</t>
         </is>
       </c>
       <c r="X177" t="inlineStr"/>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB177" t="inlineStr"/>
@@ -13467,30 +13467,22 @@
         </is>
       </c>
       <c r="M178" t="inlineStr"/>
-      <c r="N178" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N178" t="inlineStr"/>
       <c r="O178" t="inlineStr"/>
       <c r="P178" t="inlineStr"/>
-      <c r="Q178" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q178" t="inlineStr"/>
       <c r="R178" t="inlineStr"/>
       <c r="S178" t="inlineStr"/>
       <c r="T178" t="inlineStr"/>
       <c r="U178" t="inlineStr"/>
       <c r="V178" t="inlineStr">
         <is>
-          <t>EssnWrkP</t>
+          <t>EssnWrkE</t>
         </is>
       </c>
       <c r="W178" t="inlineStr">
         <is>
-          <t>Essential Workers %</t>
+          <t>Count of Essential Workers</t>
         </is>
       </c>
       <c r="X178" t="inlineStr"/>
@@ -13557,12 +13549,12 @@
       <c r="U179" t="inlineStr"/>
       <c r="V179" t="inlineStr">
         <is>
-          <t>HghRskP</t>
+          <t>EssnWrkP</t>
         </is>
       </c>
       <c r="W179" t="inlineStr">
         <is>
-          <t>Employed % - High Risk of Injury</t>
+          <t>Essential Workers %</t>
         </is>
       </c>
       <c r="X179" t="inlineStr"/>
@@ -13629,12 +13621,12 @@
       <c r="U180" t="inlineStr"/>
       <c r="V180" t="inlineStr">
         <is>
-          <t>HltCrP</t>
+          <t>HghRskP</t>
         </is>
       </c>
       <c r="W180" t="inlineStr">
         <is>
-          <t>Employed % - Health Care</t>
+          <t>Employed % - High Risk of Injury</t>
         </is>
       </c>
       <c r="X180" t="inlineStr"/>
@@ -13701,12 +13693,12 @@
       <c r="U181" t="inlineStr"/>
       <c r="V181" t="inlineStr">
         <is>
-          <t>RetailP</t>
+          <t>HltCrP</t>
         </is>
       </c>
       <c r="W181" t="inlineStr">
         <is>
-          <t>Employed % - Retail</t>
+          <t>Employed % - Health Care</t>
         </is>
       </c>
       <c r="X181" t="inlineStr"/>
@@ -13773,12 +13765,12 @@
       <c r="U182" t="inlineStr"/>
       <c r="V182" t="inlineStr">
         <is>
-          <t>TotWrkE</t>
+          <t>RetailP</t>
         </is>
       </c>
       <c r="W182" t="inlineStr">
         <is>
-          <t>Count of Working Population</t>
+          <t>Employed % - Retail</t>
         </is>
       </c>
       <c r="X182" t="inlineStr"/>
@@ -13809,7 +13801,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
@@ -13827,38 +13819,46 @@
         </is>
       </c>
       <c r="M183" t="inlineStr"/>
-      <c r="N183" t="inlineStr"/>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O183" t="inlineStr"/>
       <c r="P183" t="inlineStr"/>
-      <c r="Q183" t="inlineStr"/>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R183" t="inlineStr"/>
       <c r="S183" t="inlineStr"/>
       <c r="T183" t="inlineStr"/>
       <c r="U183" t="inlineStr"/>
       <c r="V183" t="inlineStr">
         <is>
-          <t>ForDqP</t>
+          <t>TotWrkE</t>
         </is>
       </c>
       <c r="W183" t="inlineStr">
         <is>
-          <t>Foreclosure &amp; Delinquency %</t>
+          <t>Count of Working Population</t>
         </is>
       </c>
       <c r="X183" t="inlineStr"/>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB183" t="inlineStr"/>
@@ -13901,12 +13901,12 @@
       <c r="U184" t="inlineStr"/>
       <c r="V184" t="inlineStr">
         <is>
-          <t>ForDqTot</t>
+          <t>ForDqP</t>
         </is>
       </c>
       <c r="W184" t="inlineStr">
         <is>
-          <t>Foreclosure &amp; Delinquency Count</t>
+          <t>Foreclosure &amp; Delinquency %</t>
         </is>
       </c>
       <c r="X184" t="inlineStr"/>
@@ -13943,11 +13943,7 @@
       <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F185" t="inlineStr"/>
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr"/>
@@ -13959,30 +13955,22 @@
         </is>
       </c>
       <c r="M185" t="inlineStr"/>
-      <c r="N185" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N185" t="inlineStr"/>
       <c r="O185" t="inlineStr"/>
       <c r="P185" t="inlineStr"/>
-      <c r="Q185" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q185" t="inlineStr"/>
       <c r="R185" t="inlineStr"/>
       <c r="S185" t="inlineStr"/>
       <c r="T185" t="inlineStr"/>
       <c r="U185" t="inlineStr"/>
       <c r="V185" t="inlineStr">
         <is>
-          <t>GiniCoeff</t>
+          <t>ForDqTot</t>
         </is>
       </c>
       <c r="W185" t="inlineStr">
         <is>
-          <t>Income Inequality (Gini Coefficient)</t>
+          <t>Foreclosure &amp; Delinquency Count</t>
         </is>
       </c>
       <c r="X185" t="inlineStr"/>
@@ -14013,56 +14001,68 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Internet Access</t>
+          <t>Great Recession Foreclosure Rate</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr"/>
-      <c r="F186" t="inlineStr"/>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr"/>
-      <c r="L186" t="inlineStr"/>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N186" t="inlineStr"/>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr"/>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O186" t="inlineStr"/>
       <c r="P186" t="inlineStr"/>
-      <c r="Q186" t="inlineStr"/>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R186" t="inlineStr"/>
       <c r="S186" t="inlineStr"/>
       <c r="T186" t="inlineStr"/>
       <c r="U186" t="inlineStr"/>
       <c r="V186" t="inlineStr">
         <is>
-          <t>NoIntP</t>
+          <t>GiniCoeff</t>
         </is>
       </c>
       <c r="W186" t="inlineStr">
         <is>
-          <t>Households without Internet Access %</t>
+          <t>Income Inequality (Gini Coefficient)</t>
         </is>
       </c>
       <c r="X186" t="inlineStr"/>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Internet_Access.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
         </is>
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>ACS 2019</t>
+          <t>HUD 2018; ACS 2012, 2018</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>American Community Survey 2015-2019 5-Year Estimate</t>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB186" t="inlineStr"/>
@@ -14077,68 +14077,56 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
+          <t>Internet Access</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F187" t="inlineStr"/>
       <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr"/>
-      <c r="L187" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M187" t="inlineStr"/>
-      <c r="N187" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr"/>
       <c r="O187" t="inlineStr"/>
       <c r="P187" t="inlineStr"/>
-      <c r="Q187" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q187" t="inlineStr"/>
       <c r="R187" t="inlineStr"/>
       <c r="S187" t="inlineStr"/>
       <c r="T187" t="inlineStr"/>
       <c r="U187" t="inlineStr"/>
       <c r="V187" t="inlineStr">
         <is>
-          <t>MedInc</t>
+          <t>NoIntP</t>
         </is>
       </c>
       <c r="W187" t="inlineStr">
         <is>
-          <t>Median Income</t>
+          <t>Households without Internet Access %</t>
         </is>
       </c>
       <c r="X187" t="inlineStr"/>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Internet_Access.md</t>
         </is>
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>ACS 2019</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>American Community Survey 2015-2019 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB187" t="inlineStr"/>
@@ -14193,12 +14181,12 @@
       <c r="U188" t="inlineStr"/>
       <c r="V188" t="inlineStr">
         <is>
-          <t>PciE</t>
+          <t>MedInc</t>
         </is>
       </c>
       <c r="W188" t="inlineStr">
         <is>
-          <t>Per Capita Income</t>
+          <t>Median Income</t>
         </is>
       </c>
       <c r="X188" t="inlineStr"/>
@@ -14232,21 +14220,9 @@
           <t>Poverty, Income, Gini Coefficient</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="C189" t="inlineStr"/>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
           <t>x</t>
@@ -14278,19 +14254,15 @@
       <c r="R189" t="inlineStr"/>
       <c r="S189" t="inlineStr"/>
       <c r="T189" t="inlineStr"/>
-      <c r="U189" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="U189" t="inlineStr"/>
       <c r="V189" t="inlineStr">
         <is>
-          <t>PovP</t>
+          <t>PciE</t>
         </is>
       </c>
       <c r="W189" t="inlineStr">
         <is>
-          <t>Poverty %</t>
+          <t>Per Capita Income</t>
         </is>
       </c>
       <c r="X189" t="inlineStr"/>
@@ -14377,12 +14349,12 @@
       </c>
       <c r="V190" t="inlineStr">
         <is>
-          <t>UnempP</t>
+          <t>PovP</t>
         </is>
       </c>
       <c r="W190" t="inlineStr">
         <is>
-          <t>Unemployment %</t>
+          <t>Poverty %</t>
         </is>
       </c>
       <c r="X190" t="inlineStr"/>
@@ -14408,65 +14380,89 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>SDOH Indices &amp; Typology</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr"/>
-      <c r="D191" t="inlineStr"/>
-      <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr"/>
+          <t>Poverty, Income, Gini Coefficient</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G191" t="inlineStr"/>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr"/>
-      <c r="L191" t="inlineStr"/>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M191" t="inlineStr"/>
-      <c r="N191" t="inlineStr"/>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O191" t="inlineStr"/>
       <c r="P191" t="inlineStr"/>
-      <c r="Q191" t="inlineStr"/>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R191" t="inlineStr"/>
       <c r="S191" t="inlineStr"/>
-      <c r="T191" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="U191" t="inlineStr"/>
+      <c r="T191" t="inlineStr"/>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="V191" t="inlineStr">
         <is>
-          <t>LimMobInd</t>
+          <t>UnempP</t>
         </is>
       </c>
       <c r="W191" t="inlineStr">
         <is>
-          <t>Limited Moblility Index</t>
+          <t>Unemployment %</t>
         </is>
       </c>
       <c r="X191" t="inlineStr"/>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB191" t="inlineStr"/>
@@ -14513,12 +14509,12 @@
       <c r="U192" t="inlineStr"/>
       <c r="V192" t="inlineStr">
         <is>
-          <t>MicaInd</t>
+          <t>LimMobInd</t>
         </is>
       </c>
       <c r="W192" t="inlineStr">
         <is>
-          <t>Mixed Immigrant Cohesion and Accesibility (MICA) Index</t>
+          <t>Limited Moblility Index</t>
         </is>
       </c>
       <c r="X192" t="inlineStr"/>
@@ -14573,16 +14569,20 @@
       <c r="Q193" t="inlineStr"/>
       <c r="R193" t="inlineStr"/>
       <c r="S193" t="inlineStr"/>
-      <c r="T193" t="inlineStr"/>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U193" t="inlineStr"/>
       <c r="V193" t="inlineStr">
         <is>
-          <t>NeighbTyp</t>
+          <t>MicaInd</t>
         </is>
       </c>
       <c r="W193" t="inlineStr">
         <is>
-          <t>Neighborhood Type</t>
+          <t>Mixed Immigrant Cohesion and Accesibility (MICA) Index</t>
         </is>
       </c>
       <c r="X193" t="inlineStr"/>
@@ -14637,20 +14637,16 @@
       <c r="Q194" t="inlineStr"/>
       <c r="R194" t="inlineStr"/>
       <c r="S194" t="inlineStr"/>
-      <c r="T194" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T194" t="inlineStr"/>
       <c r="U194" t="inlineStr"/>
       <c r="V194" t="inlineStr">
         <is>
-          <t>SocEcAdvIn</t>
+          <t>NeighbTyp</t>
         </is>
       </c>
       <c r="W194" t="inlineStr">
         <is>
-          <t>Socioeconomic Advantage Index</t>
+          <t>Neighborhood Type</t>
         </is>
       </c>
       <c r="X194" t="inlineStr"/>
@@ -14713,12 +14709,12 @@
       <c r="U195" t="inlineStr"/>
       <c r="V195" t="inlineStr">
         <is>
-          <t>UrbCoreInd</t>
+          <t>SocEcAdvIn</t>
         </is>
       </c>
       <c r="W195" t="inlineStr">
         <is>
-          <t>Urban Core Opportunity Index</t>
+          <t>Socioeconomic Advantage Index</t>
         </is>
       </c>
       <c r="X195" t="inlineStr"/>
@@ -14749,7 +14745,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>SDOH Indices &amp; Typology</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
@@ -14757,56 +14753,52 @@
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr"/>
-      <c r="H196" t="inlineStr"/>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr"/>
-      <c r="L196" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L196" t="inlineStr"/>
       <c r="M196" t="inlineStr"/>
-      <c r="N196" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N196" t="inlineStr"/>
       <c r="O196" t="inlineStr"/>
-      <c r="P196" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P196" t="inlineStr"/>
       <c r="Q196" t="inlineStr"/>
       <c r="R196" t="inlineStr"/>
       <c r="S196" t="inlineStr"/>
-      <c r="T196" t="inlineStr"/>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U196" t="inlineStr"/>
       <c r="V196" t="inlineStr">
         <is>
-          <t>SviSmryRnk</t>
+          <t>UrbCoreInd</t>
         </is>
       </c>
       <c r="W196" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) Summary Ranking</t>
+          <t>Urban Core Opportunity Index</t>
         </is>
       </c>
       <c r="X196" t="inlineStr"/>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
         </is>
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AB196" t="inlineStr"/>
@@ -14853,20 +14845,16 @@
       <c r="Q197" t="inlineStr"/>
       <c r="R197" t="inlineStr"/>
       <c r="S197" t="inlineStr"/>
-      <c r="T197" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T197" t="inlineStr"/>
       <c r="U197" t="inlineStr"/>
       <c r="V197" t="inlineStr">
         <is>
-          <t>SviTh1</t>
+          <t>SviSmryRnk</t>
         </is>
       </c>
       <c r="W197" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 1</t>
+          <t>Social Vulnerability Index (SVI) Summary Ranking</t>
         </is>
       </c>
       <c r="X197" t="inlineStr"/>
@@ -14929,16 +14917,20 @@
       <c r="Q198" t="inlineStr"/>
       <c r="R198" t="inlineStr"/>
       <c r="S198" t="inlineStr"/>
-      <c r="T198" t="inlineStr"/>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U198" t="inlineStr"/>
       <c r="V198" t="inlineStr">
         <is>
-          <t>SviTh2</t>
+          <t>SviTh1</t>
         </is>
       </c>
       <c r="W198" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 2</t>
+          <t>Social Vulnerability Index (SVI) 1</t>
         </is>
       </c>
       <c r="X198" t="inlineStr"/>
@@ -15005,12 +14997,12 @@
       <c r="U199" t="inlineStr"/>
       <c r="V199" t="inlineStr">
         <is>
-          <t>SviTh3</t>
+          <t>SviTh2</t>
         </is>
       </c>
       <c r="W199" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 3</t>
+          <t>Social Vulnerability Index (SVI) 2</t>
         </is>
       </c>
       <c r="X199" t="inlineStr"/>
@@ -15073,20 +15065,16 @@
       <c r="Q200" t="inlineStr"/>
       <c r="R200" t="inlineStr"/>
       <c r="S200" t="inlineStr"/>
-      <c r="T200" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T200" t="inlineStr"/>
       <c r="U200" t="inlineStr"/>
       <c r="V200" t="inlineStr">
         <is>
-          <t>SviTh4</t>
+          <t>SviTh3</t>
         </is>
       </c>
       <c r="W200" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 4</t>
+          <t>Social Vulnerability Index (SVI) 3</t>
         </is>
       </c>
       <c r="X200" t="inlineStr"/>
@@ -15108,6 +15096,82 @@
       <c r="AB200" t="inlineStr"/>
       <c r="AC200" t="inlineStr"/>
       <c r="AD200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr"/>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr"/>
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr"/>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr"/>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr"/>
+      <c r="R201" t="inlineStr"/>
+      <c r="S201" t="inlineStr"/>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr"/>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>SviTh4</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 4</t>
+        </is>
+      </c>
+      <c r="X201" t="inlineStr"/>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB201" t="inlineStr"/>
+      <c r="AC201" t="inlineStr"/>
+      <c r="AD201" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/src/reference/data-dictionaries/T_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/T_Dict.xlsx
@@ -11358,7 +11358,7 @@
       </c>
       <c r="W146" t="inlineStr">
         <is>
-          <t>Opioid Treatment Provider access 30 minutes (RAAM)</t>
+          <t>Opioid Treatment Provider access 60 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X146" t="inlineStr"/>

--- a/docs/src/reference/data-dictionaries/T_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/T_Dict.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD201"/>
+  <dimension ref="A1:AD205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -8523,11 +8523,7 @@
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr"/>
       <c r="Q105" t="inlineStr"/>
@@ -8541,12 +8537,12 @@
       <c r="U105" t="inlineStr"/>
       <c r="V105" t="inlineStr">
         <is>
-          <t>BupMinDis</t>
+          <t>BupFca30</t>
         </is>
       </c>
       <c r="W105" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Buprenorphine Provider</t>
+          <t>Two-step floating catchment area (2SFCA) measure of access to Buprenorphine within a 30-minute drive</t>
         </is>
       </c>
       <c r="X105" t="inlineStr"/>
@@ -8591,26 +8587,26 @@
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr"/>
       <c r="P106" t="inlineStr"/>
       <c r="Q106" t="inlineStr"/>
       <c r="R106" t="inlineStr"/>
-      <c r="S106" t="inlineStr"/>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T106" t="inlineStr"/>
       <c r="U106" t="inlineStr"/>
       <c r="V106" t="inlineStr">
         <is>
-          <t>BupRm30</t>
+          <t>BupFca60</t>
         </is>
       </c>
       <c r="W106" t="inlineStr">
         <is>
-          <t>Buprenorphine access 30 minutes (RAAM)</t>
+          <t>Two-step floating catchment area (2SFCA) measure of access to Buprenorphine within a 60-minute drive</t>
         </is>
       </c>
       <c r="X106" t="inlineStr"/>
@@ -8664,17 +8660,21 @@
       <c r="P107" t="inlineStr"/>
       <c r="Q107" t="inlineStr"/>
       <c r="R107" t="inlineStr"/>
-      <c r="S107" t="inlineStr"/>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T107" t="inlineStr"/>
       <c r="U107" t="inlineStr"/>
       <c r="V107" t="inlineStr">
         <is>
-          <t>BupRm60</t>
+          <t>BupMinDis</t>
         </is>
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>Buprenorphine access 60 minutes (RAAM)</t>
+          <t>Distance (mi) to nearest Buprenorphine Provider</t>
         </is>
       </c>
       <c r="X107" t="inlineStr"/>
@@ -8728,17 +8728,21 @@
       <c r="P108" t="inlineStr"/>
       <c r="Q108" t="inlineStr"/>
       <c r="R108" t="inlineStr"/>
-      <c r="S108" t="inlineStr"/>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T108" t="inlineStr"/>
       <c r="U108" t="inlineStr"/>
       <c r="V108" t="inlineStr">
         <is>
-          <t>BupRm90</t>
+          <t>BupRm30</t>
         </is>
       </c>
       <c r="W108" t="inlineStr">
         <is>
-          <t>Buprenorphine access 90 minutes (RAAM)</t>
+          <t>Buprenorphine access 30 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X108" t="inlineStr"/>
@@ -8797,20 +8801,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T109" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T109" t="inlineStr"/>
       <c r="U109" t="inlineStr"/>
       <c r="V109" t="inlineStr">
         <is>
-          <t>BupTmBk</t>
+          <t>BupRm60</t>
         </is>
       </c>
       <c r="W109" t="inlineStr">
         <is>
-          <t>Biking Time (min) to nearest Buprenorphine Provider</t>
+          <t>Buprenorphine access 60 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X109" t="inlineStr"/>
@@ -8864,25 +8864,17 @@
       <c r="P110" t="inlineStr"/>
       <c r="Q110" t="inlineStr"/>
       <c r="R110" t="inlineStr"/>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="T110" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S110" t="inlineStr"/>
+      <c r="T110" t="inlineStr"/>
       <c r="U110" t="inlineStr"/>
       <c r="V110" t="inlineStr">
         <is>
-          <t>BupTmDr</t>
+          <t>BupRm90</t>
         </is>
       </c>
       <c r="W110" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Buprenorphine Provider</t>
+          <t>Buprenorphine access 90 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X110" t="inlineStr"/>
@@ -8949,12 +8941,12 @@
       <c r="U111" t="inlineStr"/>
       <c r="V111" t="inlineStr">
         <is>
-          <t>BupTmWk</t>
+          <t>BupTmBk</t>
         </is>
       </c>
       <c r="W111" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Buprenorphine Provider</t>
+          <t>Biking Time (min) to nearest Buprenorphine Provider</t>
         </is>
       </c>
       <c r="X111" t="inlineStr"/>
@@ -9013,16 +9005,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T112" t="inlineStr"/>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U112" t="inlineStr"/>
       <c r="V112" t="inlineStr">
         <is>
-          <t>MetCntBk30</t>
+          <t>BupTmDr</t>
         </is>
       </c>
       <c r="W112" t="inlineStr">
         <is>
-          <t>Count of methadone providers (30-min bike)</t>
+          <t>Driving Time (min) to nearest Buprenorphine Provider</t>
         </is>
       </c>
       <c r="X112" t="inlineStr"/>
@@ -9081,16 +9077,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T113" t="inlineStr"/>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U113" t="inlineStr"/>
       <c r="V113" t="inlineStr">
         <is>
-          <t>MetCntBk60</t>
+          <t>BupTmWk</t>
         </is>
       </c>
       <c r="W113" t="inlineStr">
         <is>
-          <t>Count of Methadone Providers (60-min bike)</t>
+          <t>Walking Time (min) to nearest Buprenorphine Provider</t>
         </is>
       </c>
       <c r="X113" t="inlineStr"/>
@@ -9153,12 +9153,12 @@
       <c r="U114" t="inlineStr"/>
       <c r="V114" t="inlineStr">
         <is>
-          <t>MetCntDr30</t>
+          <t>MetCntBk30</t>
         </is>
       </c>
       <c r="W114" t="inlineStr">
         <is>
-          <t>Count of Methadone Providers (30-min drive)</t>
+          <t>Count of methadone providers (30-min bike)</t>
         </is>
       </c>
       <c r="X114" t="inlineStr"/>
@@ -9203,7 +9203,11 @@
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O115" t="inlineStr"/>
       <c r="P115" t="inlineStr"/>
       <c r="Q115" t="inlineStr"/>
@@ -9217,12 +9221,12 @@
       <c r="U115" t="inlineStr"/>
       <c r="V115" t="inlineStr">
         <is>
-          <t>MetCntDr60</t>
+          <t>MetCntBk60</t>
         </is>
       </c>
       <c r="W115" t="inlineStr">
         <is>
-          <t>Count of methadone providers (drive)</t>
+          <t>Count of Methadone Providers (60-min bike)</t>
         </is>
       </c>
       <c r="X115" t="inlineStr"/>
@@ -9285,12 +9289,12 @@
       <c r="U116" t="inlineStr"/>
       <c r="V116" t="inlineStr">
         <is>
-          <t>MetCntWk30</t>
+          <t>MetCntDr30</t>
         </is>
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>Count of Methadone Providers (60-min walk)</t>
+          <t>Count of Methadone Providers (30-min drive)</t>
         </is>
       </c>
       <c r="X116" t="inlineStr"/>
@@ -9335,11 +9339,7 @@
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr"/>
       <c r="P117" t="inlineStr"/>
       <c r="Q117" t="inlineStr"/>
@@ -9353,12 +9353,12 @@
       <c r="U117" t="inlineStr"/>
       <c r="V117" t="inlineStr">
         <is>
-          <t>MetCntWk60</t>
+          <t>MetCntDr60</t>
         </is>
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>Count of Methadone Providers (30-min walk)</t>
+          <t>Count of methadone providers (drive)</t>
         </is>
       </c>
       <c r="X117" t="inlineStr"/>
@@ -9403,7 +9403,11 @@
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="inlineStr"/>
       <c r="Q118" t="inlineStr"/>
@@ -9417,12 +9421,12 @@
       <c r="U118" t="inlineStr"/>
       <c r="V118" t="inlineStr">
         <is>
-          <t>MetFca30</t>
+          <t>MetCntWk30</t>
         </is>
       </c>
       <c r="W118" t="inlineStr">
         <is>
-          <t>Two-step floating catchment area (2SFCA) measure of access to Methadone within a 30-minute drive</t>
+          <t>Count of Methadone Providers (60-min walk)</t>
         </is>
       </c>
       <c r="X118" t="inlineStr"/>
@@ -9467,7 +9471,11 @@
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O119" t="inlineStr"/>
       <c r="P119" t="inlineStr"/>
       <c r="Q119" t="inlineStr"/>
@@ -9481,12 +9489,12 @@
       <c r="U119" t="inlineStr"/>
       <c r="V119" t="inlineStr">
         <is>
-          <t>MetFca60</t>
+          <t>MetCntWk60</t>
         </is>
       </c>
       <c r="W119" t="inlineStr">
         <is>
-          <t>Two-step floating catchment area (2SFCA) measure of access to Methadone within a 60-minute drive</t>
+          <t>Count of Methadone Providers (30-min walk)</t>
         </is>
       </c>
       <c r="X119" t="inlineStr"/>
@@ -9531,11 +9539,7 @@
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr"/>
       <c r="P120" t="inlineStr"/>
       <c r="Q120" t="inlineStr"/>
@@ -9549,12 +9553,12 @@
       <c r="U120" t="inlineStr"/>
       <c r="V120" t="inlineStr">
         <is>
-          <t>MetMinDis</t>
+          <t>MetFca30</t>
         </is>
       </c>
       <c r="W120" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Methadone Provider</t>
+          <t>Two-step floating catchment area (2SFCA) measure of access to Methadone within a 30-minute drive</t>
         </is>
       </c>
       <c r="X120" t="inlineStr"/>
@@ -9588,26 +9592,10 @@
           <t>Spatial Access to MOUDs</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr"/>
@@ -9615,11 +9603,7 @@
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr"/>
       <c r="P121" t="inlineStr"/>
       <c r="Q121" t="inlineStr"/>
@@ -9633,12 +9617,12 @@
       <c r="U121" t="inlineStr"/>
       <c r="V121" t="inlineStr">
         <is>
-          <t>MetRm30</t>
+          <t>MetFca60</t>
         </is>
       </c>
       <c r="W121" t="inlineStr">
         <is>
-          <t>Methadone access 30 minutes (RAAM)</t>
+          <t>Two-step floating catchment area (2SFCA) measure of access to Methadone within a 60-minute drive</t>
         </is>
       </c>
       <c r="X121" t="inlineStr"/>
@@ -9672,26 +9656,10 @@
           <t>Spatial Access to MOUDs</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr"/>
@@ -9717,12 +9685,12 @@
       <c r="U122" t="inlineStr"/>
       <c r="V122" t="inlineStr">
         <is>
-          <t>MetRm60</t>
+          <t>MetMinDis</t>
         </is>
       </c>
       <c r="W122" t="inlineStr">
         <is>
-          <t>Methadone access 60 minutes (RAAM)</t>
+          <t>Distance (mi) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X122" t="inlineStr"/>
@@ -9792,17 +9760,21 @@
       <c r="P123" t="inlineStr"/>
       <c r="Q123" t="inlineStr"/>
       <c r="R123" t="inlineStr"/>
-      <c r="S123" t="inlineStr"/>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T123" t="inlineStr"/>
       <c r="U123" t="inlineStr"/>
       <c r="V123" t="inlineStr">
         <is>
-          <t>MetRm90</t>
+          <t>MetRm30</t>
         </is>
       </c>
       <c r="W123" t="inlineStr">
         <is>
-          <t>Methadone access 90 minutes (RAAM)</t>
+          <t>Methadone access 30 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X123" t="inlineStr"/>
@@ -9836,10 +9808,26 @@
           <t>Spatial Access to MOUDs</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr"/>
-      <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr"/>
@@ -9861,20 +9849,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T124" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T124" t="inlineStr"/>
       <c r="U124" t="inlineStr"/>
       <c r="V124" t="inlineStr">
         <is>
-          <t>MetTmBk</t>
+          <t>MetRm60</t>
         </is>
       </c>
       <c r="W124" t="inlineStr">
         <is>
-          <t>Biking Time (min) to nearest Methadone Provider</t>
+          <t>Methadone access 60 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X124" t="inlineStr"/>
@@ -9908,10 +9892,26 @@
           <t>Spatial Access to MOUDs</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr"/>
-      <c r="D125" t="inlineStr"/>
-      <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr"/>
@@ -9928,25 +9928,17 @@
       <c r="P125" t="inlineStr"/>
       <c r="Q125" t="inlineStr"/>
       <c r="R125" t="inlineStr"/>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="T125" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S125" t="inlineStr"/>
+      <c r="T125" t="inlineStr"/>
       <c r="U125" t="inlineStr"/>
       <c r="V125" t="inlineStr">
         <is>
-          <t>MetTmDr</t>
+          <t>MetRm90</t>
         </is>
       </c>
       <c r="W125" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Methadone Provider</t>
+          <t>Methadone access 90 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X125" t="inlineStr"/>
@@ -10013,12 +10005,12 @@
       <c r="U126" t="inlineStr"/>
       <c r="V126" t="inlineStr">
         <is>
-          <t>MetTmWk</t>
+          <t>MetTmBk</t>
         </is>
       </c>
       <c r="W126" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Methadone Provider</t>
+          <t>Biking Time (min) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X126" t="inlineStr"/>
@@ -10077,16 +10069,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T127" t="inlineStr"/>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U127" t="inlineStr"/>
       <c r="V127" t="inlineStr">
         <is>
-          <t>MoudMinDis</t>
+          <t>MetTmDr</t>
         </is>
       </c>
       <c r="W127" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest MOUD (any)</t>
+          <t>Driving Time (min) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X127" t="inlineStr"/>
@@ -10145,16 +10141,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T128" t="inlineStr"/>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U128" t="inlineStr"/>
       <c r="V128" t="inlineStr">
         <is>
-          <t>NaltCntBk30</t>
+          <t>MetTmWk</t>
         </is>
       </c>
       <c r="W128" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (30-min bike)</t>
+          <t>Walking Time (min) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X128" t="inlineStr"/>
@@ -10217,12 +10217,12 @@
       <c r="U129" t="inlineStr"/>
       <c r="V129" t="inlineStr">
         <is>
-          <t>NaltCntBk60</t>
+          <t>MoudMinDis</t>
         </is>
       </c>
       <c r="W129" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (60-min bike)</t>
+          <t>Distance (mi) to nearest MOUD (any)</t>
         </is>
       </c>
       <c r="X129" t="inlineStr"/>
@@ -10285,12 +10285,12 @@
       <c r="U130" t="inlineStr"/>
       <c r="V130" t="inlineStr">
         <is>
-          <t>NaltCntDr30</t>
+          <t>NaltCntBk30</t>
         </is>
       </c>
       <c r="W130" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (30-min drive)</t>
+          <t>Count of Naltrexone Providers (30-min bike)</t>
         </is>
       </c>
       <c r="X130" t="inlineStr"/>
@@ -10335,7 +10335,11 @@
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O131" t="inlineStr"/>
       <c r="P131" t="inlineStr"/>
       <c r="Q131" t="inlineStr"/>
@@ -10349,12 +10353,12 @@
       <c r="U131" t="inlineStr"/>
       <c r="V131" t="inlineStr">
         <is>
-          <t>NaltCntDr60</t>
+          <t>NaltCntBk60</t>
         </is>
       </c>
       <c r="W131" t="inlineStr">
         <is>
-          <t>Count of naltrexone providers (drive)</t>
+          <t>Count of Naltrexone Providers (60-min bike)</t>
         </is>
       </c>
       <c r="X131" t="inlineStr"/>
@@ -10417,12 +10421,12 @@
       <c r="U132" t="inlineStr"/>
       <c r="V132" t="inlineStr">
         <is>
-          <t>NaltCntWk30</t>
+          <t>NaltCntDr30</t>
         </is>
       </c>
       <c r="W132" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (30-min walk)</t>
+          <t>Count of Naltrexone Providers (30-min drive)</t>
         </is>
       </c>
       <c r="X132" t="inlineStr"/>
@@ -10467,11 +10471,7 @@
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N133" t="inlineStr"/>
       <c r="O133" t="inlineStr"/>
       <c r="P133" t="inlineStr"/>
       <c r="Q133" t="inlineStr"/>
@@ -10485,12 +10485,12 @@
       <c r="U133" t="inlineStr"/>
       <c r="V133" t="inlineStr">
         <is>
-          <t>NaltCntWk60</t>
+          <t>NaltCntDr60</t>
         </is>
       </c>
       <c r="W133" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (60-min walk)</t>
+          <t>Count of naltrexone providers (drive)</t>
         </is>
       </c>
       <c r="X133" t="inlineStr"/>
@@ -10553,12 +10553,12 @@
       <c r="U134" t="inlineStr"/>
       <c r="V134" t="inlineStr">
         <is>
-          <t>NaltMinDis</t>
+          <t>NaltCntWk30</t>
         </is>
       </c>
       <c r="W134" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Naltrexone Provider</t>
+          <t>Count of Naltrexone Providers (30-min walk)</t>
         </is>
       </c>
       <c r="X134" t="inlineStr"/>
@@ -10612,17 +10612,21 @@
       <c r="P135" t="inlineStr"/>
       <c r="Q135" t="inlineStr"/>
       <c r="R135" t="inlineStr"/>
-      <c r="S135" t="inlineStr"/>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T135" t="inlineStr"/>
       <c r="U135" t="inlineStr"/>
       <c r="V135" t="inlineStr">
         <is>
-          <t>NaltRm30</t>
+          <t>NaltCntWk60</t>
         </is>
       </c>
       <c r="W135" t="inlineStr">
         <is>
-          <t>Naltrexone access 30 minutes (RAAM)</t>
+          <t>Count of Naltrexone Providers (60-min walk)</t>
         </is>
       </c>
       <c r="X135" t="inlineStr"/>
@@ -10667,26 +10671,26 @@
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr"/>
       <c r="P136" t="inlineStr"/>
       <c r="Q136" t="inlineStr"/>
       <c r="R136" t="inlineStr"/>
-      <c r="S136" t="inlineStr"/>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T136" t="inlineStr"/>
       <c r="U136" t="inlineStr"/>
       <c r="V136" t="inlineStr">
         <is>
-          <t>NaltRm60</t>
+          <t>NaltFca30</t>
         </is>
       </c>
       <c r="W136" t="inlineStr">
         <is>
-          <t>Naltrexone access 60 minutes (RAAM)</t>
+          <t>Two-step floating catchment area (2SFCA) measure of access to Naltrexone within a 30-minute drive</t>
         </is>
       </c>
       <c r="X136" t="inlineStr"/>
@@ -10731,26 +10735,26 @@
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr"/>
       <c r="P137" t="inlineStr"/>
       <c r="Q137" t="inlineStr"/>
       <c r="R137" t="inlineStr"/>
-      <c r="S137" t="inlineStr"/>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T137" t="inlineStr"/>
       <c r="U137" t="inlineStr"/>
       <c r="V137" t="inlineStr">
         <is>
-          <t>NaltRm90</t>
+          <t>NaltFca60</t>
         </is>
       </c>
       <c r="W137" t="inlineStr">
         <is>
-          <t>Naltrexone access 90 minutes (RAAM)</t>
+          <t>Two-step floating catchment area (2SFCA) measure of access to Naltrexone within a 60-minute drive</t>
         </is>
       </c>
       <c r="X137" t="inlineStr"/>
@@ -10809,20 +10813,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T138" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T138" t="inlineStr"/>
       <c r="U138" t="inlineStr"/>
       <c r="V138" t="inlineStr">
         <is>
-          <t>NaltTmBk</t>
+          <t>NaltMinDis</t>
         </is>
       </c>
       <c r="W138" t="inlineStr">
         <is>
-          <t>Biking Time (min) to nearest Naltrexone Provider</t>
+          <t>Distance (mi) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X138" t="inlineStr"/>
@@ -10881,20 +10881,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T139" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T139" t="inlineStr"/>
       <c r="U139" t="inlineStr"/>
       <c r="V139" t="inlineStr">
         <is>
-          <t>NaltTmDr</t>
+          <t>NaltRm30</t>
         </is>
       </c>
       <c r="W139" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Naltrexone Provider</t>
+          <t>Naltrexone access 30 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X139" t="inlineStr"/>
@@ -10953,20 +10949,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T140" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T140" t="inlineStr"/>
       <c r="U140" t="inlineStr"/>
       <c r="V140" t="inlineStr">
         <is>
-          <t>NaltTmWk</t>
+          <t>NaltRm60</t>
         </is>
       </c>
       <c r="W140" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Naltrexone Provider</t>
+          <t>Naltrexone access 60 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X140" t="inlineStr"/>
@@ -11011,30 +11003,26 @@
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
-      <c r="O141" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr"/>
       <c r="P141" t="inlineStr"/>
       <c r="Q141" t="inlineStr"/>
       <c r="R141" t="inlineStr"/>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S141" t="inlineStr"/>
       <c r="T141" t="inlineStr"/>
       <c r="U141" t="inlineStr"/>
       <c r="V141" t="inlineStr">
         <is>
-          <t>OtpCntDr</t>
+          <t>NaltRm90</t>
         </is>
       </c>
       <c r="W141" t="inlineStr">
         <is>
-          <t>Count of Opioid Treatment Programs (OTP) (30-min drive)</t>
+          <t>Naltrexone access 90 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X141" t="inlineStr"/>
@@ -11079,7 +11067,11 @@
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr"/>
       <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O142" t="inlineStr"/>
       <c r="P142" t="inlineStr"/>
       <c r="Q142" t="inlineStr"/>
@@ -11089,16 +11081,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T142" t="inlineStr"/>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U142" t="inlineStr"/>
       <c r="V142" t="inlineStr">
         <is>
-          <t>OtpFca30</t>
+          <t>NaltTmBk</t>
         </is>
       </c>
       <c r="W142" t="inlineStr">
         <is>
-          <t>Two-step floating catchment area (2SFCA) measure of access to opioid treatment programs within a 30-minute drive</t>
+          <t>Biking Time (min) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X142" t="inlineStr"/>
@@ -11143,7 +11139,11 @@
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O143" t="inlineStr"/>
       <c r="P143" t="inlineStr"/>
       <c r="Q143" t="inlineStr"/>
@@ -11153,16 +11153,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T143" t="inlineStr"/>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U143" t="inlineStr"/>
       <c r="V143" t="inlineStr">
         <is>
-          <t>OtpFca60</t>
+          <t>NaltTmDr</t>
         </is>
       </c>
       <c r="W143" t="inlineStr">
         <is>
-          <t>Two-step floating catchment area (2SFCA) measure of access to opioid treatment programs within a 60-minute drive</t>
+          <t>Driving Time (min) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X143" t="inlineStr"/>
@@ -11207,12 +11211,12 @@
       <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr"/>
       <c r="M144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
-      <c r="O144" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr"/>
       <c r="P144" t="inlineStr"/>
       <c r="Q144" t="inlineStr"/>
       <c r="R144" t="inlineStr"/>
@@ -11221,16 +11225,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T144" t="inlineStr"/>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U144" t="inlineStr"/>
       <c r="V144" t="inlineStr">
         <is>
-          <t>OtpMinDis</t>
+          <t>NaltTmWk</t>
         </is>
       </c>
       <c r="W144" t="inlineStr">
         <is>
-          <t>Distance to nearest OTP</t>
+          <t>Walking Time (min) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X144" t="inlineStr"/>
@@ -11276,7 +11284,11 @@
       <c r="L145" t="inlineStr"/>
       <c r="M145" t="inlineStr"/>
       <c r="N145" t="inlineStr"/>
-      <c r="O145" t="inlineStr"/>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr"/>
       <c r="Q145" t="inlineStr"/>
       <c r="R145" t="inlineStr"/>
@@ -11289,12 +11301,12 @@
       <c r="U145" t="inlineStr"/>
       <c r="V145" t="inlineStr">
         <is>
-          <t>OtpRm30</t>
+          <t>OtpCntDr</t>
         </is>
       </c>
       <c r="W145" t="inlineStr">
         <is>
-          <t>Opioid Treatment Provider access 30 minutes (RAAM)</t>
+          <t>Count of Opioid Treatment Programs (OTP) (30-min drive)</t>
         </is>
       </c>
       <c r="X145" t="inlineStr"/>
@@ -11353,12 +11365,12 @@
       <c r="U146" t="inlineStr"/>
       <c r="V146" t="inlineStr">
         <is>
-          <t>OtpRm60</t>
+          <t>OtpFca30</t>
         </is>
       </c>
       <c r="W146" t="inlineStr">
         <is>
-          <t>Opioid Treatment Provider access 60 minutes (RAAM)</t>
+          <t>Two-step floating catchment area (2SFCA) measure of access to opioid treatment programs within a 30-minute drive</t>
         </is>
       </c>
       <c r="X146" t="inlineStr"/>
@@ -11404,11 +11416,7 @@
       <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr"/>
       <c r="N147" t="inlineStr"/>
-      <c r="O147" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="O147" t="inlineStr"/>
       <c r="P147" t="inlineStr"/>
       <c r="Q147" t="inlineStr"/>
       <c r="R147" t="inlineStr"/>
@@ -11417,20 +11425,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T147" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T147" t="inlineStr"/>
       <c r="U147" t="inlineStr"/>
       <c r="V147" t="inlineStr">
         <is>
-          <t>OtpTmDr</t>
+          <t>OtpFca60</t>
         </is>
       </c>
       <c r="W147" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP)</t>
+          <t>Two-step floating catchment area (2SFCA) measure of access to opioid treatment programs within a 60-minute drive</t>
         </is>
       </c>
       <c r="X147" t="inlineStr"/>
@@ -11476,7 +11480,11 @@
       <c r="L148" t="inlineStr"/>
       <c r="M148" t="inlineStr"/>
       <c r="N148" t="inlineStr"/>
-      <c r="O148" t="inlineStr"/>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr"/>
       <c r="Q148" t="inlineStr"/>
       <c r="R148" t="inlineStr"/>
@@ -11489,12 +11497,12 @@
       <c r="U148" t="inlineStr"/>
       <c r="V148" t="inlineStr">
         <is>
-          <t>TlBupCntBk30</t>
+          <t>OtpMinDis</t>
         </is>
       </c>
       <c r="W148" t="inlineStr">
         <is>
-          <t>Count of telehealth buprenorphine providers within 30-minute bike ride</t>
+          <t>Distance to nearest OTP</t>
         </is>
       </c>
       <c r="X148" t="inlineStr"/>
@@ -11553,12 +11561,12 @@
       <c r="U149" t="inlineStr"/>
       <c r="V149" t="inlineStr">
         <is>
-          <t>TlBupCntDr30</t>
+          <t>OtpRm30</t>
         </is>
       </c>
       <c r="W149" t="inlineStr">
         <is>
-          <t>Count of telehealth buprenorphine providers within 30-minute drive</t>
+          <t>Opioid Treatment Provider access 30 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X149" t="inlineStr"/>
@@ -11617,12 +11625,12 @@
       <c r="U150" t="inlineStr"/>
       <c r="V150" t="inlineStr">
         <is>
-          <t>TlBupCntDr60</t>
+          <t>OtpRm60</t>
         </is>
       </c>
       <c r="W150" t="inlineStr">
         <is>
-          <t>Count of telehealth buprenorphine providers within 60-minute drive</t>
+          <t>Opioid Treatment Provider access 60 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X150" t="inlineStr"/>
@@ -11668,7 +11676,11 @@
       <c r="L151" t="inlineStr"/>
       <c r="M151" t="inlineStr"/>
       <c r="N151" t="inlineStr"/>
-      <c r="O151" t="inlineStr"/>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P151" t="inlineStr"/>
       <c r="Q151" t="inlineStr"/>
       <c r="R151" t="inlineStr"/>
@@ -11677,16 +11689,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T151" t="inlineStr"/>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U151" t="inlineStr"/>
       <c r="V151" t="inlineStr">
         <is>
-          <t>TlBupCntWk30</t>
+          <t>OtpTmDr</t>
         </is>
       </c>
       <c r="W151" t="inlineStr">
         <is>
-          <t>Count of telehealth buprenorphine providers within 30-minute walk</t>
+          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP)</t>
         </is>
       </c>
       <c r="X151" t="inlineStr"/>
@@ -11745,12 +11761,12 @@
       <c r="U152" t="inlineStr"/>
       <c r="V152" t="inlineStr">
         <is>
-          <t>TlBupMinDis</t>
+          <t>TlBupCntBk30</t>
         </is>
       </c>
       <c r="W152" t="inlineStr">
         <is>
-          <t>Minimum distance to telehealth buprenorphine provider</t>
+          <t>Count of telehealth buprenorphine providers within 30-minute bike ride</t>
         </is>
       </c>
       <c r="X152" t="inlineStr"/>
@@ -11809,12 +11825,12 @@
       <c r="U153" t="inlineStr"/>
       <c r="V153" t="inlineStr">
         <is>
-          <t>TlBupTmBk</t>
+          <t>TlBupCntDr30</t>
         </is>
       </c>
       <c r="W153" t="inlineStr">
         <is>
-          <t>Biking time to nearest telehealth buprenorphine provider</t>
+          <t>Count of telehealth buprenorphine providers within 30-minute drive</t>
         </is>
       </c>
       <c r="X153" t="inlineStr"/>
@@ -11873,12 +11889,12 @@
       <c r="U154" t="inlineStr"/>
       <c r="V154" t="inlineStr">
         <is>
-          <t>TlBupTmDr</t>
+          <t>TlBupCntDr60</t>
         </is>
       </c>
       <c r="W154" t="inlineStr">
         <is>
-          <t>Driving time to nearest telehealth buprenorphine provider</t>
+          <t>Count of telehealth buprenorphine providers within 60-minute drive</t>
         </is>
       </c>
       <c r="X154" t="inlineStr"/>
@@ -11937,12 +11953,12 @@
       <c r="U155" t="inlineStr"/>
       <c r="V155" t="inlineStr">
         <is>
-          <t>TlBupTmWk</t>
+          <t>TlBupCntWk30</t>
         </is>
       </c>
       <c r="W155" t="inlineStr">
         <is>
-          <t>Walking time to nearest telehealth buprenorphine provider</t>
+          <t>Count of telehealth buprenorphine providers within 30-minute walk</t>
         </is>
       </c>
       <c r="X155" t="inlineStr"/>
@@ -11973,7 +11989,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -11987,11 +12003,7 @@
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr"/>
       <c r="M156" t="inlineStr"/>
-      <c r="N156" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N156" t="inlineStr"/>
       <c r="O156" t="inlineStr"/>
       <c r="P156" t="inlineStr"/>
       <c r="Q156" t="inlineStr"/>
@@ -12005,28 +12017,28 @@
       <c r="U156" t="inlineStr"/>
       <c r="V156" t="inlineStr">
         <is>
-          <t>MhCntDr</t>
+          <t>TlBupMinDis</t>
         </is>
       </c>
       <c r="W156" t="inlineStr">
         <is>
-          <t>Count of Mental Health Providers (30-min drive)</t>
+          <t>Minimum distance to telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X156" t="inlineStr"/>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB156" t="inlineStr"/>
@@ -12041,7 +12053,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -12055,11 +12067,7 @@
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr"/>
       <c r="M157" t="inlineStr"/>
-      <c r="N157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N157" t="inlineStr"/>
       <c r="O157" t="inlineStr"/>
       <c r="P157" t="inlineStr"/>
       <c r="Q157" t="inlineStr"/>
@@ -12073,28 +12081,28 @@
       <c r="U157" t="inlineStr"/>
       <c r="V157" t="inlineStr">
         <is>
-          <t>MhMinDis</t>
+          <t>TlBupTmBk</t>
         </is>
       </c>
       <c r="W157" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Mental Health Provider</t>
+          <t>Biking time to nearest telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X157" t="inlineStr"/>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB157" t="inlineStr"/>
@@ -12109,7 +12117,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -12123,11 +12131,7 @@
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr"/>
       <c r="M158" t="inlineStr"/>
-      <c r="N158" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N158" t="inlineStr"/>
       <c r="O158" t="inlineStr"/>
       <c r="P158" t="inlineStr"/>
       <c r="Q158" t="inlineStr"/>
@@ -12137,36 +12141,32 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T158" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T158" t="inlineStr"/>
       <c r="U158" t="inlineStr"/>
       <c r="V158" t="inlineStr">
         <is>
-          <t>MhTmDr</t>
+          <t>TlBupTmDr</t>
         </is>
       </c>
       <c r="W158" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Mental Health Provider</t>
+          <t>Driving time to nearest telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X158" t="inlineStr"/>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB158" t="inlineStr"/>
@@ -12181,7 +12181,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
@@ -12209,28 +12209,28 @@
       <c r="U159" t="inlineStr"/>
       <c r="V159" t="inlineStr">
         <is>
-          <t>MhTmDr2</t>
+          <t>TlBupTmWk</t>
         </is>
       </c>
       <c r="W159" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest Mental Health Provider with impedance</t>
+          <t>Walking time to nearest telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X159" t="inlineStr"/>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB159" t="inlineStr"/>
@@ -12245,7 +12245,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
@@ -12258,12 +12258,12 @@
       <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N160" t="inlineStr"/>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O160" t="inlineStr"/>
       <c r="P160" t="inlineStr"/>
       <c r="Q160" t="inlineStr"/>
@@ -12277,28 +12277,28 @@
       <c r="U160" t="inlineStr"/>
       <c r="V160" t="inlineStr">
         <is>
-          <t>RxCntDr</t>
+          <t>MhCntDr</t>
         </is>
       </c>
       <c r="W160" t="inlineStr">
         <is>
-          <t>Count of Pharmacies (30-min drive)</t>
+          <t>Count of Mental Health Providers (30-min drive)</t>
         </is>
       </c>
       <c r="X160" t="inlineStr"/>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB160" t="inlineStr"/>
@@ -12313,7 +12313,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
@@ -12326,43 +12326,47 @@
       <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr"/>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N161" t="inlineStr"/>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O161" t="inlineStr"/>
       <c r="P161" t="inlineStr"/>
       <c r="Q161" t="inlineStr"/>
       <c r="R161" t="inlineStr"/>
-      <c r="S161" t="inlineStr"/>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T161" t="inlineStr"/>
       <c r="U161" t="inlineStr"/>
       <c r="V161" t="inlineStr">
         <is>
-          <t>RxMinDis</t>
+          <t>MhMinDis</t>
         </is>
       </c>
       <c r="W161" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Pharmacy</t>
+          <t>Distance (mi) to nearest Mental Health Provider</t>
         </is>
       </c>
       <c r="X161" t="inlineStr"/>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB161" t="inlineStr"/>
@@ -12377,7 +12381,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
@@ -12390,12 +12394,12 @@
       <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr"/>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N162" t="inlineStr"/>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O162" t="inlineStr"/>
       <c r="P162" t="inlineStr"/>
       <c r="Q162" t="inlineStr"/>
@@ -12413,28 +12417,28 @@
       <c r="U162" t="inlineStr"/>
       <c r="V162" t="inlineStr">
         <is>
-          <t>RxTmDr</t>
+          <t>MhTmDr</t>
         </is>
       </c>
       <c r="W162" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Pharmacy</t>
+          <t>Driving Time (min) to nearest Mental Health Provider</t>
         </is>
       </c>
       <c r="X162" t="inlineStr"/>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB162" t="inlineStr"/>
@@ -12449,7 +12453,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
@@ -12477,28 +12481,28 @@
       <c r="U163" t="inlineStr"/>
       <c r="V163" t="inlineStr">
         <is>
-          <t>RxTmDr2</t>
+          <t>MhTmDr2</t>
         </is>
       </c>
       <c r="W163" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Pharmacy with Impedance Factor</t>
+          <t>Driving time (min) to nearest Mental Health Provider with impedance</t>
         </is>
       </c>
       <c r="X163" t="inlineStr"/>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB163" t="inlineStr"/>
@@ -12513,7 +12517,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
@@ -12526,12 +12530,12 @@
       <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr"/>
-      <c r="M164" t="inlineStr"/>
-      <c r="N164" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr"/>
       <c r="O164" t="inlineStr"/>
       <c r="P164" t="inlineStr"/>
       <c r="Q164" t="inlineStr"/>
@@ -12545,28 +12549,28 @@
       <c r="U164" t="inlineStr"/>
       <c r="V164" t="inlineStr">
         <is>
-          <t>SutCntDr</t>
+          <t>RxCntDr</t>
         </is>
       </c>
       <c r="W164" t="inlineStr">
         <is>
-          <t>Count of Substance Use Treatment (SUT) facility (30-min drive)</t>
+          <t>Count of Pharmacies (30-min drive)</t>
         </is>
       </c>
       <c r="X164" t="inlineStr"/>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB164" t="inlineStr"/>
@@ -12581,7 +12585,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
@@ -12594,47 +12598,43 @@
       <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr"/>
-      <c r="N165" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr"/>
       <c r="O165" t="inlineStr"/>
       <c r="P165" t="inlineStr"/>
       <c r="Q165" t="inlineStr"/>
       <c r="R165" t="inlineStr"/>
-      <c r="S165" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S165" t="inlineStr"/>
       <c r="T165" t="inlineStr"/>
       <c r="U165" t="inlineStr"/>
       <c r="V165" t="inlineStr">
         <is>
-          <t>SutMinDis</t>
+          <t>RxMinDis</t>
         </is>
       </c>
       <c r="W165" t="inlineStr">
         <is>
-          <t>Distance (mi) to Substance Use Treatment (SUT) facility</t>
+          <t>Distance (mi) to nearest Pharmacy</t>
         </is>
       </c>
       <c r="X165" t="inlineStr"/>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB165" t="inlineStr"/>
@@ -12649,7 +12649,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
@@ -12662,12 +12662,12 @@
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr"/>
-      <c r="N166" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr"/>
       <c r="O166" t="inlineStr"/>
       <c r="P166" t="inlineStr"/>
       <c r="Q166" t="inlineStr"/>
@@ -12685,28 +12685,28 @@
       <c r="U166" t="inlineStr"/>
       <c r="V166" t="inlineStr">
         <is>
-          <t>SutTmDr</t>
+          <t>RxTmDr</t>
         </is>
       </c>
       <c r="W166" t="inlineStr">
         <is>
-          <t>Driving time (min) to Substance Use Treatment (SUT) facility</t>
+          <t>Driving Time (min) to nearest Pharmacy</t>
         </is>
       </c>
       <c r="X166" t="inlineStr"/>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB166" t="inlineStr"/>
@@ -12721,7 +12721,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
@@ -12735,11 +12735,7 @@
       <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr"/>
       <c r="M167" t="inlineStr"/>
-      <c r="N167" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N167" t="inlineStr"/>
       <c r="O167" t="inlineStr"/>
       <c r="P167" t="inlineStr"/>
       <c r="Q167" t="inlineStr"/>
@@ -12753,28 +12749,28 @@
       <c r="U167" t="inlineStr"/>
       <c r="V167" t="inlineStr">
         <is>
-          <t>FqhcCntDr</t>
+          <t>RxTmDr2</t>
         </is>
       </c>
       <c r="W167" t="inlineStr">
         <is>
-          <t>Count of Federally Qualified Health Centers (FQHCs) within 30-min drive</t>
+          <t>Driving Time (min) to nearest Pharmacy with Impedance Factor</t>
         </is>
       </c>
       <c r="X167" t="inlineStr"/>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB167" t="inlineStr"/>
@@ -12789,7 +12785,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
@@ -12821,28 +12817,28 @@
       <c r="U168" t="inlineStr"/>
       <c r="V168" t="inlineStr">
         <is>
-          <t>FqhcMinDis</t>
+          <t>SutCntDr</t>
         </is>
       </c>
       <c r="W168" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Federally Qualified Health Centers (FQHC)</t>
+          <t>Count of Substance Use Treatment (SUT) facility (30-min drive)</t>
         </is>
       </c>
       <c r="X168" t="inlineStr"/>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB168" t="inlineStr"/>
@@ -12857,7 +12853,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
@@ -12885,36 +12881,32 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T169" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T169" t="inlineStr"/>
       <c r="U169" t="inlineStr"/>
       <c r="V169" t="inlineStr">
         <is>
-          <t>FqhcTmDr</t>
+          <t>SutMinDis</t>
         </is>
       </c>
       <c r="W169" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC)</t>
+          <t>Distance (mi) to Substance Use Treatment (SUT) facility</t>
         </is>
       </c>
       <c r="X169" t="inlineStr"/>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB169" t="inlineStr"/>
@@ -12929,7 +12921,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
@@ -12943,7 +12935,11 @@
       <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr"/>
       <c r="M170" t="inlineStr"/>
-      <c r="N170" t="inlineStr"/>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O170" t="inlineStr"/>
       <c r="P170" t="inlineStr"/>
       <c r="Q170" t="inlineStr"/>
@@ -12961,28 +12957,28 @@
       <c r="U170" t="inlineStr"/>
       <c r="V170" t="inlineStr">
         <is>
-          <t>FqhcTmDr2</t>
+          <t>SutTmDr</t>
         </is>
       </c>
       <c r="W170" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC), with Impedance factor</t>
+          <t>Driving time (min) to Substance Use Treatment (SUT) facility</t>
         </is>
       </c>
       <c r="X170" t="inlineStr"/>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB170" t="inlineStr"/>
@@ -12997,7 +12993,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
@@ -13011,7 +13007,11 @@
       <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr"/>
       <c r="M171" t="inlineStr"/>
-      <c r="N171" t="inlineStr"/>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O171" t="inlineStr"/>
       <c r="P171" t="inlineStr"/>
       <c r="Q171" t="inlineStr"/>
@@ -13025,28 +13025,28 @@
       <c r="U171" t="inlineStr"/>
       <c r="V171" t="inlineStr">
         <is>
-          <t>HcvCntDr</t>
+          <t>FqhcCntDr</t>
         </is>
       </c>
       <c r="W171" t="inlineStr">
         <is>
-          <t>Count of HCV Providers</t>
+          <t>Count of Federally Qualified Health Centers (FQHCs) within 30-min drive</t>
         </is>
       </c>
       <c r="X171" t="inlineStr"/>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB171" t="inlineStr"/>
@@ -13061,7 +13061,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
@@ -13075,7 +13075,11 @@
       <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr"/>
       <c r="M172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O172" t="inlineStr"/>
       <c r="P172" t="inlineStr"/>
       <c r="Q172" t="inlineStr"/>
@@ -13089,28 +13093,28 @@
       <c r="U172" t="inlineStr"/>
       <c r="V172" t="inlineStr">
         <is>
-          <t>HcvMinDis</t>
+          <t>FqhcMinDis</t>
         </is>
       </c>
       <c r="W172" t="inlineStr">
         <is>
-          <t>Distance to nearest HCV Provider</t>
+          <t>Distance (mi) to nearest Federally Qualified Health Centers (FQHC)</t>
         </is>
       </c>
       <c r="X172" t="inlineStr"/>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB172" t="inlineStr"/>
@@ -13125,7 +13129,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -13139,7 +13143,11 @@
       <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr"/>
       <c r="M173" t="inlineStr"/>
-      <c r="N173" t="inlineStr"/>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O173" t="inlineStr"/>
       <c r="P173" t="inlineStr"/>
       <c r="Q173" t="inlineStr"/>
@@ -13149,32 +13157,36 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T173" t="inlineStr"/>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U173" t="inlineStr"/>
       <c r="V173" t="inlineStr">
         <is>
-          <t>HcvTmDr</t>
+          <t>FqhcTmDr</t>
         </is>
       </c>
       <c r="W173" t="inlineStr">
         <is>
-          <t>Driving time to nearest HCV Provider</t>
+          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC)</t>
         </is>
       </c>
       <c r="X173" t="inlineStr"/>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB173" t="inlineStr"/>
@@ -13189,7 +13201,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
@@ -13213,32 +13225,36 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T174" t="inlineStr"/>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U174" t="inlineStr"/>
       <c r="V174" t="inlineStr">
         <is>
-          <t>HcvTmDr2</t>
+          <t>FqhcTmDr2</t>
         </is>
       </c>
       <c r="W174" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest HCV Testing Facility with impedance</t>
+          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC), with Impedance factor</t>
         </is>
       </c>
       <c r="X174" t="inlineStr"/>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB174" t="inlineStr"/>
@@ -13253,17 +13269,13 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F175" t="inlineStr"/>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr"/>
@@ -13276,33 +13288,37 @@
       <c r="P175" t="inlineStr"/>
       <c r="Q175" t="inlineStr"/>
       <c r="R175" t="inlineStr"/>
-      <c r="S175" t="inlineStr"/>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T175" t="inlineStr"/>
       <c r="U175" t="inlineStr"/>
       <c r="V175" t="inlineStr">
         <is>
-          <t>Ruca1</t>
+          <t>HcvCntDr</t>
         </is>
       </c>
       <c r="W175" t="inlineStr">
         <is>
-          <t>Primary RUCA Code</t>
+          <t>Count of HCV Providers</t>
         </is>
       </c>
       <c r="X175" t="inlineStr"/>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB175" t="inlineStr"/>
@@ -13317,17 +13333,13 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F176" t="inlineStr"/>
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr"/>
@@ -13340,33 +13352,37 @@
       <c r="P176" t="inlineStr"/>
       <c r="Q176" t="inlineStr"/>
       <c r="R176" t="inlineStr"/>
-      <c r="S176" t="inlineStr"/>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T176" t="inlineStr"/>
       <c r="U176" t="inlineStr"/>
       <c r="V176" t="inlineStr">
         <is>
-          <t>Ruca2</t>
+          <t>HcvMinDis</t>
         </is>
       </c>
       <c r="W176" t="inlineStr">
         <is>
-          <t>Secondary RUCA Code</t>
+          <t>Distance to nearest HCV Provider</t>
         </is>
       </c>
       <c r="X176" t="inlineStr"/>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB176" t="inlineStr"/>
@@ -13381,17 +13397,13 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr"/>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F177" t="inlineStr"/>
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr"/>
@@ -13404,37 +13416,37 @@
       <c r="P177" t="inlineStr"/>
       <c r="Q177" t="inlineStr"/>
       <c r="R177" t="inlineStr"/>
-      <c r="S177" t="inlineStr"/>
-      <c r="T177" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T177" t="inlineStr"/>
       <c r="U177" t="inlineStr"/>
       <c r="V177" t="inlineStr">
         <is>
-          <t>Rurality</t>
+          <t>HcvTmDr</t>
         </is>
       </c>
       <c r="W177" t="inlineStr">
         <is>
-          <t>Urban-Suburban-Rural</t>
+          <t>Driving time to nearest HCV Provider</t>
         </is>
       </c>
       <c r="X177" t="inlineStr"/>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB177" t="inlineStr"/>
@@ -13444,12 +13456,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
@@ -13461,44 +13473,44 @@
       <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr"/>
-      <c r="L178" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L178" t="inlineStr"/>
       <c r="M178" t="inlineStr"/>
       <c r="N178" t="inlineStr"/>
       <c r="O178" t="inlineStr"/>
       <c r="P178" t="inlineStr"/>
       <c r="Q178" t="inlineStr"/>
       <c r="R178" t="inlineStr"/>
-      <c r="S178" t="inlineStr"/>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T178" t="inlineStr"/>
       <c r="U178" t="inlineStr"/>
       <c r="V178" t="inlineStr">
         <is>
-          <t>EssnWrkE</t>
+          <t>HcvTmDr2</t>
         </is>
       </c>
       <c r="W178" t="inlineStr">
         <is>
-          <t>Count of Essential Workers</t>
+          <t>Driving time (min) to nearest HCV Testing Facility with impedance</t>
         </is>
       </c>
       <c r="X178" t="inlineStr"/>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB178" t="inlineStr"/>
@@ -13508,69 +13520,61 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr"/>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr"/>
-      <c r="L179" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L179" t="inlineStr"/>
       <c r="M179" t="inlineStr"/>
-      <c r="N179" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N179" t="inlineStr"/>
       <c r="O179" t="inlineStr"/>
       <c r="P179" t="inlineStr"/>
-      <c r="Q179" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q179" t="inlineStr"/>
       <c r="R179" t="inlineStr"/>
       <c r="S179" t="inlineStr"/>
       <c r="T179" t="inlineStr"/>
       <c r="U179" t="inlineStr"/>
       <c r="V179" t="inlineStr">
         <is>
-          <t>EssnWrkP</t>
+          <t>Ruca1</t>
         </is>
       </c>
       <c r="W179" t="inlineStr">
         <is>
-          <t>Essential Workers %</t>
+          <t>Primary RUCA Code</t>
         </is>
       </c>
       <c r="X179" t="inlineStr"/>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB179" t="inlineStr"/>
@@ -13580,69 +13584,61 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr"/>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr"/>
-      <c r="L180" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L180" t="inlineStr"/>
       <c r="M180" t="inlineStr"/>
-      <c r="N180" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N180" t="inlineStr"/>
       <c r="O180" t="inlineStr"/>
       <c r="P180" t="inlineStr"/>
-      <c r="Q180" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q180" t="inlineStr"/>
       <c r="R180" t="inlineStr"/>
       <c r="S180" t="inlineStr"/>
       <c r="T180" t="inlineStr"/>
       <c r="U180" t="inlineStr"/>
       <c r="V180" t="inlineStr">
         <is>
-          <t>HghRskP</t>
+          <t>Ruca2</t>
         </is>
       </c>
       <c r="W180" t="inlineStr">
         <is>
-          <t>Employed % - High Risk of Injury</t>
+          <t>Secondary RUCA Code</t>
         </is>
       </c>
       <c r="X180" t="inlineStr"/>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB180" t="inlineStr"/>
@@ -13652,69 +13648,65 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr"/>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr"/>
-      <c r="L181" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L181" t="inlineStr"/>
       <c r="M181" t="inlineStr"/>
-      <c r="N181" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N181" t="inlineStr"/>
       <c r="O181" t="inlineStr"/>
       <c r="P181" t="inlineStr"/>
-      <c r="Q181" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q181" t="inlineStr"/>
       <c r="R181" t="inlineStr"/>
       <c r="S181" t="inlineStr"/>
-      <c r="T181" t="inlineStr"/>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U181" t="inlineStr"/>
       <c r="V181" t="inlineStr">
         <is>
-          <t>HltCrP</t>
+          <t>Rurality</t>
         </is>
       </c>
       <c r="W181" t="inlineStr">
         <is>
-          <t>Employed % - Health Care</t>
+          <t>Urban-Suburban-Rural</t>
         </is>
       </c>
       <c r="X181" t="inlineStr"/>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB181" t="inlineStr"/>
@@ -13747,30 +13739,22 @@
         </is>
       </c>
       <c r="M182" t="inlineStr"/>
-      <c r="N182" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N182" t="inlineStr"/>
       <c r="O182" t="inlineStr"/>
       <c r="P182" t="inlineStr"/>
-      <c r="Q182" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q182" t="inlineStr"/>
       <c r="R182" t="inlineStr"/>
       <c r="S182" t="inlineStr"/>
       <c r="T182" t="inlineStr"/>
       <c r="U182" t="inlineStr"/>
       <c r="V182" t="inlineStr">
         <is>
-          <t>RetailP</t>
+          <t>EssnWrkE</t>
         </is>
       </c>
       <c r="W182" t="inlineStr">
         <is>
-          <t>Employed % - Retail</t>
+          <t>Count of Essential Workers</t>
         </is>
       </c>
       <c r="X182" t="inlineStr"/>
@@ -13837,12 +13821,12 @@
       <c r="U183" t="inlineStr"/>
       <c r="V183" t="inlineStr">
         <is>
-          <t>TotWrkE</t>
+          <t>EssnWrkP</t>
         </is>
       </c>
       <c r="W183" t="inlineStr">
         <is>
-          <t>Count of Working Population</t>
+          <t>Essential Workers %</t>
         </is>
       </c>
       <c r="X183" t="inlineStr"/>
@@ -13873,7 +13857,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
@@ -13891,38 +13875,46 @@
         </is>
       </c>
       <c r="M184" t="inlineStr"/>
-      <c r="N184" t="inlineStr"/>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O184" t="inlineStr"/>
       <c r="P184" t="inlineStr"/>
-      <c r="Q184" t="inlineStr"/>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R184" t="inlineStr"/>
       <c r="S184" t="inlineStr"/>
       <c r="T184" t="inlineStr"/>
       <c r="U184" t="inlineStr"/>
       <c r="V184" t="inlineStr">
         <is>
-          <t>ForDqP</t>
+          <t>HghRskP</t>
         </is>
       </c>
       <c r="W184" t="inlineStr">
         <is>
-          <t>Foreclosure &amp; Delinquency %</t>
+          <t>Employed % - High Risk of Injury</t>
         </is>
       </c>
       <c r="X184" t="inlineStr"/>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB184" t="inlineStr"/>
@@ -13937,7 +13929,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
@@ -13955,38 +13947,46 @@
         </is>
       </c>
       <c r="M185" t="inlineStr"/>
-      <c r="N185" t="inlineStr"/>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O185" t="inlineStr"/>
       <c r="P185" t="inlineStr"/>
-      <c r="Q185" t="inlineStr"/>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R185" t="inlineStr"/>
       <c r="S185" t="inlineStr"/>
       <c r="T185" t="inlineStr"/>
       <c r="U185" t="inlineStr"/>
       <c r="V185" t="inlineStr">
         <is>
-          <t>ForDqTot</t>
+          <t>HltCrP</t>
         </is>
       </c>
       <c r="W185" t="inlineStr">
         <is>
-          <t>Foreclosure &amp; Delinquency Count</t>
+          <t>Employed % - Health Care</t>
         </is>
       </c>
       <c r="X185" t="inlineStr"/>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB185" t="inlineStr"/>
@@ -14001,17 +14001,13 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr"/>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr"/>
@@ -14041,28 +14037,28 @@
       <c r="U186" t="inlineStr"/>
       <c r="V186" t="inlineStr">
         <is>
-          <t>GiniCoeff</t>
+          <t>RetailP</t>
         </is>
       </c>
       <c r="W186" t="inlineStr">
         <is>
-          <t>Income Inequality (Gini Coefficient)</t>
+          <t>Employed % - Retail</t>
         </is>
       </c>
       <c r="X186" t="inlineStr"/>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB186" t="inlineStr"/>
@@ -14077,7 +14073,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Internet Access</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
@@ -14089,44 +14085,52 @@
       <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr"/>
-      <c r="L187" t="inlineStr"/>
-      <c r="M187" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N187" t="inlineStr"/>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr"/>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O187" t="inlineStr"/>
       <c r="P187" t="inlineStr"/>
-      <c r="Q187" t="inlineStr"/>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R187" t="inlineStr"/>
       <c r="S187" t="inlineStr"/>
       <c r="T187" t="inlineStr"/>
       <c r="U187" t="inlineStr"/>
       <c r="V187" t="inlineStr">
         <is>
-          <t>NoIntP</t>
+          <t>TotWrkE</t>
         </is>
       </c>
       <c r="W187" t="inlineStr">
         <is>
-          <t>Households without Internet Access %</t>
+          <t>Count of Working Population</t>
         </is>
       </c>
       <c r="X187" t="inlineStr"/>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Internet_Access.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>ACS 2019</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>American Community Survey 2015-2019 5-Year Estimate</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB187" t="inlineStr"/>
@@ -14141,17 +14145,13 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
+          <t>Great Recession Foreclosure Rate</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr"/>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F188" t="inlineStr"/>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr"/>
@@ -14163,46 +14163,38 @@
         </is>
       </c>
       <c r="M188" t="inlineStr"/>
-      <c r="N188" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N188" t="inlineStr"/>
       <c r="O188" t="inlineStr"/>
       <c r="P188" t="inlineStr"/>
-      <c r="Q188" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q188" t="inlineStr"/>
       <c r="R188" t="inlineStr"/>
       <c r="S188" t="inlineStr"/>
       <c r="T188" t="inlineStr"/>
       <c r="U188" t="inlineStr"/>
       <c r="V188" t="inlineStr">
         <is>
-          <t>MedInc</t>
+          <t>ForDqP</t>
         </is>
       </c>
       <c r="W188" t="inlineStr">
         <is>
-          <t>Median Income</t>
+          <t>Foreclosure &amp; Delinquency %</t>
         </is>
       </c>
       <c r="X188" t="inlineStr"/>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
         </is>
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>HUD 2018; ACS 2012, 2018</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB188" t="inlineStr"/>
@@ -14217,17 +14209,13 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
+          <t>Great Recession Foreclosure Rate</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr"/>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F189" t="inlineStr"/>
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr"/>
@@ -14239,46 +14227,38 @@
         </is>
       </c>
       <c r="M189" t="inlineStr"/>
-      <c r="N189" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N189" t="inlineStr"/>
       <c r="O189" t="inlineStr"/>
       <c r="P189" t="inlineStr"/>
-      <c r="Q189" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q189" t="inlineStr"/>
       <c r="R189" t="inlineStr"/>
       <c r="S189" t="inlineStr"/>
       <c r="T189" t="inlineStr"/>
       <c r="U189" t="inlineStr"/>
       <c r="V189" t="inlineStr">
         <is>
-          <t>PciE</t>
+          <t>ForDqTot</t>
         </is>
       </c>
       <c r="W189" t="inlineStr">
         <is>
-          <t>Per Capita Income</t>
+          <t>Foreclosure &amp; Delinquency Count</t>
         </is>
       </c>
       <c r="X189" t="inlineStr"/>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
         </is>
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>HUD 2018; ACS 2012, 2018</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB189" t="inlineStr"/>
@@ -14293,24 +14273,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>Great Recession Foreclosure Rate</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr"/>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
         <is>
           <t>x</t>
@@ -14342,35 +14310,31 @@
       <c r="R190" t="inlineStr"/>
       <c r="S190" t="inlineStr"/>
       <c r="T190" t="inlineStr"/>
-      <c r="U190" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="U190" t="inlineStr"/>
       <c r="V190" t="inlineStr">
         <is>
-          <t>PovP</t>
+          <t>GiniCoeff</t>
         </is>
       </c>
       <c r="W190" t="inlineStr">
         <is>
-          <t>Poverty %</t>
+          <t>Income Inequality (Gini Coefficient)</t>
         </is>
       </c>
       <c r="X190" t="inlineStr"/>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
         </is>
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>HUD 2018; ACS 2012, 2018</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB190" t="inlineStr"/>
@@ -14385,84 +14349,56 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>Internet Access</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr"/>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr"/>
-      <c r="L191" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M191" t="inlineStr"/>
-      <c r="N191" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr"/>
       <c r="O191" t="inlineStr"/>
       <c r="P191" t="inlineStr"/>
-      <c r="Q191" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q191" t="inlineStr"/>
       <c r="R191" t="inlineStr"/>
       <c r="S191" t="inlineStr"/>
       <c r="T191" t="inlineStr"/>
-      <c r="U191" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="U191" t="inlineStr"/>
       <c r="V191" t="inlineStr">
         <is>
-          <t>UnempP</t>
+          <t>NoIntP</t>
         </is>
       </c>
       <c r="W191" t="inlineStr">
         <is>
-          <t>Unemployment %</t>
+          <t>Households without Internet Access %</t>
         </is>
       </c>
       <c r="X191" t="inlineStr"/>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Internet_Access.md</t>
         </is>
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>ACS 2019</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>American Community Survey 2015-2019 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB191" t="inlineStr"/>
@@ -14472,65 +14408,73 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>SDOH Indices &amp; Typology</t>
+          <t>Poverty, Income, Gini Coefficient</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G192" t="inlineStr"/>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr"/>
-      <c r="L192" t="inlineStr"/>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O192" t="inlineStr"/>
       <c r="P192" t="inlineStr"/>
-      <c r="Q192" t="inlineStr"/>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R192" t="inlineStr"/>
       <c r="S192" t="inlineStr"/>
-      <c r="T192" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T192" t="inlineStr"/>
       <c r="U192" t="inlineStr"/>
       <c r="V192" t="inlineStr">
         <is>
-          <t>LimMobInd</t>
+          <t>MedInc</t>
         </is>
       </c>
       <c r="W192" t="inlineStr">
         <is>
-          <t>Limited Moblility Index</t>
+          <t>Median Income</t>
         </is>
       </c>
       <c r="X192" t="inlineStr"/>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB192" t="inlineStr"/>
@@ -14540,65 +14484,73 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>SDOH Indices &amp; Typology</t>
+          <t>Poverty, Income, Gini Coefficient</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr"/>
-      <c r="F193" t="inlineStr"/>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G193" t="inlineStr"/>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr"/>
-      <c r="L193" t="inlineStr"/>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M193" t="inlineStr"/>
-      <c r="N193" t="inlineStr"/>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O193" t="inlineStr"/>
       <c r="P193" t="inlineStr"/>
-      <c r="Q193" t="inlineStr"/>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R193" t="inlineStr"/>
       <c r="S193" t="inlineStr"/>
-      <c r="T193" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T193" t="inlineStr"/>
       <c r="U193" t="inlineStr"/>
       <c r="V193" t="inlineStr">
         <is>
-          <t>MicaInd</t>
+          <t>PciE</t>
         </is>
       </c>
       <c r="W193" t="inlineStr">
         <is>
-          <t>Mixed Immigrant Cohesion and Accesibility (MICA) Index</t>
+          <t>Per Capita Income</t>
         </is>
       </c>
       <c r="X193" t="inlineStr"/>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB193" t="inlineStr"/>
@@ -14608,61 +14560,89 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>SDOH Indices &amp; Typology</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr"/>
-      <c r="D194" t="inlineStr"/>
-      <c r="E194" t="inlineStr"/>
-      <c r="F194" t="inlineStr"/>
+          <t>Poverty, Income, Gini Coefficient</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G194" t="inlineStr"/>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr"/>
-      <c r="L194" t="inlineStr"/>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M194" t="inlineStr"/>
-      <c r="N194" t="inlineStr"/>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O194" t="inlineStr"/>
       <c r="P194" t="inlineStr"/>
-      <c r="Q194" t="inlineStr"/>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R194" t="inlineStr"/>
       <c r="S194" t="inlineStr"/>
       <c r="T194" t="inlineStr"/>
-      <c r="U194" t="inlineStr"/>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="V194" t="inlineStr">
         <is>
-          <t>NeighbTyp</t>
+          <t>PovP</t>
         </is>
       </c>
       <c r="W194" t="inlineStr">
         <is>
-          <t>Neighborhood Type</t>
+          <t>Poverty %</t>
         </is>
       </c>
       <c r="X194" t="inlineStr"/>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB194" t="inlineStr"/>
@@ -14672,65 +14652,89 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>SDOH Indices &amp; Typology</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr"/>
-      <c r="D195" t="inlineStr"/>
-      <c r="E195" t="inlineStr"/>
-      <c r="F195" t="inlineStr"/>
+          <t>Poverty, Income, Gini Coefficient</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G195" t="inlineStr"/>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr"/>
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr"/>
-      <c r="L195" t="inlineStr"/>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M195" t="inlineStr"/>
-      <c r="N195" t="inlineStr"/>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O195" t="inlineStr"/>
       <c r="P195" t="inlineStr"/>
-      <c r="Q195" t="inlineStr"/>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R195" t="inlineStr"/>
       <c r="S195" t="inlineStr"/>
-      <c r="T195" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="U195" t="inlineStr"/>
+      <c r="T195" t="inlineStr"/>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="V195" t="inlineStr">
         <is>
-          <t>SocEcAdvIn</t>
+          <t>UnempP</t>
         </is>
       </c>
       <c r="W195" t="inlineStr">
         <is>
-          <t>Socioeconomic Advantage Index</t>
+          <t>Unemployment %</t>
         </is>
       </c>
       <c r="X195" t="inlineStr"/>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB195" t="inlineStr"/>
@@ -14777,12 +14781,12 @@
       <c r="U196" t="inlineStr"/>
       <c r="V196" t="inlineStr">
         <is>
-          <t>UrbCoreInd</t>
+          <t>LimMobInd</t>
         </is>
       </c>
       <c r="W196" t="inlineStr">
         <is>
-          <t>Urban Core Opportunity Index</t>
+          <t>Limited Moblility Index</t>
         </is>
       </c>
       <c r="X196" t="inlineStr"/>
@@ -14813,7 +14817,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>SDOH Indices &amp; Typology</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
@@ -14821,56 +14825,52 @@
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr"/>
-      <c r="H197" t="inlineStr"/>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr"/>
-      <c r="L197" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L197" t="inlineStr"/>
       <c r="M197" t="inlineStr"/>
-      <c r="N197" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N197" t="inlineStr"/>
       <c r="O197" t="inlineStr"/>
-      <c r="P197" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P197" t="inlineStr"/>
       <c r="Q197" t="inlineStr"/>
       <c r="R197" t="inlineStr"/>
       <c r="S197" t="inlineStr"/>
-      <c r="T197" t="inlineStr"/>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U197" t="inlineStr"/>
       <c r="V197" t="inlineStr">
         <is>
-          <t>SviSmryRnk</t>
+          <t>MicaInd</t>
         </is>
       </c>
       <c r="W197" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) Summary Ranking</t>
+          <t>Mixed Immigrant Cohesion and Accesibility (MICA) Index</t>
         </is>
       </c>
       <c r="X197" t="inlineStr"/>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
         </is>
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AB197" t="inlineStr"/>
@@ -14885,7 +14885,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>SDOH Indices &amp; Typology</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
@@ -14893,60 +14893,48 @@
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr"/>
-      <c r="H198" t="inlineStr"/>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr"/>
-      <c r="L198" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L198" t="inlineStr"/>
       <c r="M198" t="inlineStr"/>
-      <c r="N198" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N198" t="inlineStr"/>
       <c r="O198" t="inlineStr"/>
-      <c r="P198" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P198" t="inlineStr"/>
       <c r="Q198" t="inlineStr"/>
       <c r="R198" t="inlineStr"/>
       <c r="S198" t="inlineStr"/>
-      <c r="T198" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T198" t="inlineStr"/>
       <c r="U198" t="inlineStr"/>
       <c r="V198" t="inlineStr">
         <is>
-          <t>SviTh1</t>
+          <t>NeighbTyp</t>
         </is>
       </c>
       <c r="W198" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 1</t>
+          <t>Neighborhood Type</t>
         </is>
       </c>
       <c r="X198" t="inlineStr"/>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
         </is>
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AB198" t="inlineStr"/>
@@ -14961,7 +14949,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>SDOH Indices &amp; Typology</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
@@ -14969,56 +14957,52 @@
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr"/>
-      <c r="H199" t="inlineStr"/>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr"/>
-      <c r="L199" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L199" t="inlineStr"/>
       <c r="M199" t="inlineStr"/>
-      <c r="N199" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N199" t="inlineStr"/>
       <c r="O199" t="inlineStr"/>
-      <c r="P199" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P199" t="inlineStr"/>
       <c r="Q199" t="inlineStr"/>
       <c r="R199" t="inlineStr"/>
       <c r="S199" t="inlineStr"/>
-      <c r="T199" t="inlineStr"/>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U199" t="inlineStr"/>
       <c r="V199" t="inlineStr">
         <is>
-          <t>SviTh2</t>
+          <t>SocEcAdvIn</t>
         </is>
       </c>
       <c r="W199" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 2</t>
+          <t>Socioeconomic Advantage Index</t>
         </is>
       </c>
       <c r="X199" t="inlineStr"/>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
         </is>
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AB199" t="inlineStr"/>
@@ -15033,7 +15017,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>SDOH Indices &amp; Typology</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
@@ -15041,56 +15025,52 @@
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr"/>
       <c r="G200" t="inlineStr"/>
-      <c r="H200" t="inlineStr"/>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr"/>
-      <c r="L200" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L200" t="inlineStr"/>
       <c r="M200" t="inlineStr"/>
-      <c r="N200" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N200" t="inlineStr"/>
       <c r="O200" t="inlineStr"/>
-      <c r="P200" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P200" t="inlineStr"/>
       <c r="Q200" t="inlineStr"/>
       <c r="R200" t="inlineStr"/>
       <c r="S200" t="inlineStr"/>
-      <c r="T200" t="inlineStr"/>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U200" t="inlineStr"/>
       <c r="V200" t="inlineStr">
         <is>
-          <t>SviTh3</t>
+          <t>UrbCoreInd</t>
         </is>
       </c>
       <c r="W200" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 3</t>
+          <t>Urban Core Opportunity Index</t>
         </is>
       </c>
       <c r="X200" t="inlineStr"/>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
         </is>
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AB200" t="inlineStr"/>
@@ -15137,20 +15117,16 @@
       <c r="Q201" t="inlineStr"/>
       <c r="R201" t="inlineStr"/>
       <c r="S201" t="inlineStr"/>
-      <c r="T201" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T201" t="inlineStr"/>
       <c r="U201" t="inlineStr"/>
       <c r="V201" t="inlineStr">
         <is>
-          <t>SviTh4</t>
+          <t>SviSmryRnk</t>
         </is>
       </c>
       <c r="W201" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 4</t>
+          <t>Social Vulnerability Index (SVI) Summary Ranking</t>
         </is>
       </c>
       <c r="X201" t="inlineStr"/>
@@ -15172,6 +15148,302 @@
       <c r="AB201" t="inlineStr"/>
       <c r="AC201" t="inlineStr"/>
       <c r="AD201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr"/>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr"/>
+      <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr"/>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr"/>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr"/>
+      <c r="R202" t="inlineStr"/>
+      <c r="S202" t="inlineStr"/>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr"/>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>SviTh1</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 1</t>
+        </is>
+      </c>
+      <c r="X202" t="inlineStr"/>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB202" t="inlineStr"/>
+      <c r="AC202" t="inlineStr"/>
+      <c r="AD202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr"/>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr"/>
+      <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr"/>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr"/>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr"/>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr"/>
+      <c r="R203" t="inlineStr"/>
+      <c r="S203" t="inlineStr"/>
+      <c r="T203" t="inlineStr"/>
+      <c r="U203" t="inlineStr"/>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>SviTh2</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 2</t>
+        </is>
+      </c>
+      <c r="X203" t="inlineStr"/>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB203" t="inlineStr"/>
+      <c r="AC203" t="inlineStr"/>
+      <c r="AD203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr"/>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr"/>
+      <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
+      <c r="J204" t="inlineStr"/>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr"/>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr"/>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr"/>
+      <c r="R204" t="inlineStr"/>
+      <c r="S204" t="inlineStr"/>
+      <c r="T204" t="inlineStr"/>
+      <c r="U204" t="inlineStr"/>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>SviTh3</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 3</t>
+        </is>
+      </c>
+      <c r="X204" t="inlineStr"/>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB204" t="inlineStr"/>
+      <c r="AC204" t="inlineStr"/>
+      <c r="AD204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr"/>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr"/>
+      <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr"/>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr"/>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr"/>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr"/>
+      <c r="R205" t="inlineStr"/>
+      <c r="S205" t="inlineStr"/>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr"/>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>SviTh4</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 4</t>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr"/>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB205" t="inlineStr"/>
+      <c r="AC205" t="inlineStr"/>
+      <c r="AD205" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/src/reference/data-dictionaries/T_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/T_Dict.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD205"/>
+  <dimension ref="A1:AD207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -13525,17 +13525,13 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial access to Syringe Services Programs</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F179" t="inlineStr"/>
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr"/>
@@ -13548,33 +13544,37 @@
       <c r="P179" t="inlineStr"/>
       <c r="Q179" t="inlineStr"/>
       <c r="R179" t="inlineStr"/>
-      <c r="S179" t="inlineStr"/>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T179" t="inlineStr"/>
       <c r="U179" t="inlineStr"/>
       <c r="V179" t="inlineStr">
         <is>
-          <t>Ruca1</t>
+          <t>SspTmDr</t>
         </is>
       </c>
       <c r="W179" t="inlineStr">
         <is>
-          <t>Primary RUCA Code</t>
+          <t>Driving time to nearest SSP</t>
         </is>
       </c>
       <c r="X179" t="inlineStr"/>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/nasen_ssp/metadata/Access_SSP.md</t>
         </is>
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>NASEN</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>North American Syringe Exchange Network</t>
         </is>
       </c>
       <c r="AB179" t="inlineStr"/>
@@ -13589,17 +13589,13 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial access to Syringe Services Programs</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F180" t="inlineStr"/>
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr"/>
@@ -13612,33 +13608,37 @@
       <c r="P180" t="inlineStr"/>
       <c r="Q180" t="inlineStr"/>
       <c r="R180" t="inlineStr"/>
-      <c r="S180" t="inlineStr"/>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T180" t="inlineStr"/>
       <c r="U180" t="inlineStr"/>
       <c r="V180" t="inlineStr">
         <is>
-          <t>Ruca2</t>
+          <t>SspTmDr2</t>
         </is>
       </c>
       <c r="W180" t="inlineStr">
         <is>
-          <t>Secondary RUCA Code</t>
+          <t>Round trip driving time to nearest SSP</t>
         </is>
       </c>
       <c r="X180" t="inlineStr"/>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/nasen_ssp/metadata/Access_SSP.md</t>
         </is>
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>NASEN</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>North American Syringe Exchange Network</t>
         </is>
       </c>
       <c r="AB180" t="inlineStr"/>
@@ -13677,20 +13677,16 @@
       <c r="Q181" t="inlineStr"/>
       <c r="R181" t="inlineStr"/>
       <c r="S181" t="inlineStr"/>
-      <c r="T181" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T181" t="inlineStr"/>
       <c r="U181" t="inlineStr"/>
       <c r="V181" t="inlineStr">
         <is>
-          <t>Rurality</t>
+          <t>Ruca1</t>
         </is>
       </c>
       <c r="W181" t="inlineStr">
         <is>
-          <t>Urban-Suburban-Rural</t>
+          <t>Primary RUCA Code</t>
         </is>
       </c>
       <c r="X181" t="inlineStr"/>
@@ -13716,28 +13712,28 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr"/>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr"/>
-      <c r="L182" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L182" t="inlineStr"/>
       <c r="M182" t="inlineStr"/>
       <c r="N182" t="inlineStr"/>
       <c r="O182" t="inlineStr"/>
@@ -13749,28 +13745,28 @@
       <c r="U182" t="inlineStr"/>
       <c r="V182" t="inlineStr">
         <is>
-          <t>EssnWrkE</t>
+          <t>Ruca2</t>
         </is>
       </c>
       <c r="W182" t="inlineStr">
         <is>
-          <t>Count of Essential Workers</t>
+          <t>Secondary RUCA Code</t>
         </is>
       </c>
       <c r="X182" t="inlineStr"/>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB182" t="inlineStr"/>
@@ -13780,69 +13776,65 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr"/>
-      <c r="F183" t="inlineStr"/>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G183" t="inlineStr"/>
       <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr"/>
-      <c r="L183" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L183" t="inlineStr"/>
       <c r="M183" t="inlineStr"/>
-      <c r="N183" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N183" t="inlineStr"/>
       <c r="O183" t="inlineStr"/>
       <c r="P183" t="inlineStr"/>
-      <c r="Q183" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q183" t="inlineStr"/>
       <c r="R183" t="inlineStr"/>
       <c r="S183" t="inlineStr"/>
-      <c r="T183" t="inlineStr"/>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U183" t="inlineStr"/>
       <c r="V183" t="inlineStr">
         <is>
-          <t>EssnWrkP</t>
+          <t>Rurality</t>
         </is>
       </c>
       <c r="W183" t="inlineStr">
         <is>
-          <t>Essential Workers %</t>
+          <t>Urban-Suburban-Rural</t>
         </is>
       </c>
       <c r="X183" t="inlineStr"/>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB183" t="inlineStr"/>
@@ -13875,30 +13867,22 @@
         </is>
       </c>
       <c r="M184" t="inlineStr"/>
-      <c r="N184" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N184" t="inlineStr"/>
       <c r="O184" t="inlineStr"/>
       <c r="P184" t="inlineStr"/>
-      <c r="Q184" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q184" t="inlineStr"/>
       <c r="R184" t="inlineStr"/>
       <c r="S184" t="inlineStr"/>
       <c r="T184" t="inlineStr"/>
       <c r="U184" t="inlineStr"/>
       <c r="V184" t="inlineStr">
         <is>
-          <t>HghRskP</t>
+          <t>EssnWrkE</t>
         </is>
       </c>
       <c r="W184" t="inlineStr">
         <is>
-          <t>Employed % - High Risk of Injury</t>
+          <t>Count of Essential Workers</t>
         </is>
       </c>
       <c r="X184" t="inlineStr"/>
@@ -13965,12 +13949,12 @@
       <c r="U185" t="inlineStr"/>
       <c r="V185" t="inlineStr">
         <is>
-          <t>HltCrP</t>
+          <t>EssnWrkP</t>
         </is>
       </c>
       <c r="W185" t="inlineStr">
         <is>
-          <t>Employed % - Health Care</t>
+          <t>Essential Workers %</t>
         </is>
       </c>
       <c r="X185" t="inlineStr"/>
@@ -14037,12 +14021,12 @@
       <c r="U186" t="inlineStr"/>
       <c r="V186" t="inlineStr">
         <is>
-          <t>RetailP</t>
+          <t>HghRskP</t>
         </is>
       </c>
       <c r="W186" t="inlineStr">
         <is>
-          <t>Employed % - Retail</t>
+          <t>Employed % - High Risk of Injury</t>
         </is>
       </c>
       <c r="X186" t="inlineStr"/>
@@ -14109,12 +14093,12 @@
       <c r="U187" t="inlineStr"/>
       <c r="V187" t="inlineStr">
         <is>
-          <t>TotWrkE</t>
+          <t>HltCrP</t>
         </is>
       </c>
       <c r="W187" t="inlineStr">
         <is>
-          <t>Count of Working Population</t>
+          <t>Employed % - Health Care</t>
         </is>
       </c>
       <c r="X187" t="inlineStr"/>
@@ -14145,7 +14129,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
@@ -14163,38 +14147,46 @@
         </is>
       </c>
       <c r="M188" t="inlineStr"/>
-      <c r="N188" t="inlineStr"/>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O188" t="inlineStr"/>
       <c r="P188" t="inlineStr"/>
-      <c r="Q188" t="inlineStr"/>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R188" t="inlineStr"/>
       <c r="S188" t="inlineStr"/>
       <c r="T188" t="inlineStr"/>
       <c r="U188" t="inlineStr"/>
       <c r="V188" t="inlineStr">
         <is>
-          <t>ForDqP</t>
+          <t>RetailP</t>
         </is>
       </c>
       <c r="W188" t="inlineStr">
         <is>
-          <t>Foreclosure &amp; Delinquency %</t>
+          <t>Employed % - Retail</t>
         </is>
       </c>
       <c r="X188" t="inlineStr"/>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB188" t="inlineStr"/>
@@ -14209,7 +14201,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
@@ -14227,38 +14219,46 @@
         </is>
       </c>
       <c r="M189" t="inlineStr"/>
-      <c r="N189" t="inlineStr"/>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O189" t="inlineStr"/>
       <c r="P189" t="inlineStr"/>
-      <c r="Q189" t="inlineStr"/>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R189" t="inlineStr"/>
       <c r="S189" t="inlineStr"/>
       <c r="T189" t="inlineStr"/>
       <c r="U189" t="inlineStr"/>
       <c r="V189" t="inlineStr">
         <is>
-          <t>ForDqTot</t>
+          <t>TotWrkE</t>
         </is>
       </c>
       <c r="W189" t="inlineStr">
         <is>
-          <t>Foreclosure &amp; Delinquency Count</t>
+          <t>Count of Working Population</t>
         </is>
       </c>
       <c r="X189" t="inlineStr"/>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB189" t="inlineStr"/>
@@ -14279,11 +14279,7 @@
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr"/>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F190" t="inlineStr"/>
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr"/>
@@ -14295,30 +14291,22 @@
         </is>
       </c>
       <c r="M190" t="inlineStr"/>
-      <c r="N190" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N190" t="inlineStr"/>
       <c r="O190" t="inlineStr"/>
       <c r="P190" t="inlineStr"/>
-      <c r="Q190" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q190" t="inlineStr"/>
       <c r="R190" t="inlineStr"/>
       <c r="S190" t="inlineStr"/>
       <c r="T190" t="inlineStr"/>
       <c r="U190" t="inlineStr"/>
       <c r="V190" t="inlineStr">
         <is>
-          <t>GiniCoeff</t>
+          <t>ForDqP</t>
         </is>
       </c>
       <c r="W190" t="inlineStr">
         <is>
-          <t>Income Inequality (Gini Coefficient)</t>
+          <t>Foreclosure &amp; Delinquency %</t>
         </is>
       </c>
       <c r="X190" t="inlineStr"/>
@@ -14349,7 +14337,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Internet Access</t>
+          <t>Great Recession Foreclosure Rate</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
@@ -14361,12 +14349,12 @@
       <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr"/>
-      <c r="L191" t="inlineStr"/>
-      <c r="M191" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr"/>
       <c r="N191" t="inlineStr"/>
       <c r="O191" t="inlineStr"/>
       <c r="P191" t="inlineStr"/>
@@ -14377,28 +14365,28 @@
       <c r="U191" t="inlineStr"/>
       <c r="V191" t="inlineStr">
         <is>
-          <t>NoIntP</t>
+          <t>ForDqTot</t>
         </is>
       </c>
       <c r="W191" t="inlineStr">
         <is>
-          <t>Households without Internet Access %</t>
+          <t>Foreclosure &amp; Delinquency Count</t>
         </is>
       </c>
       <c r="X191" t="inlineStr"/>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Internet_Access.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
         </is>
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>ACS 2019</t>
+          <t>HUD 2018; ACS 2012, 2018</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>American Community Survey 2015-2019 5-Year Estimate</t>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB191" t="inlineStr"/>
@@ -14413,7 +14401,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
+          <t>Great Recession Foreclosure Rate</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
@@ -14453,28 +14441,28 @@
       <c r="U192" t="inlineStr"/>
       <c r="V192" t="inlineStr">
         <is>
-          <t>MedInc</t>
+          <t>GiniCoeff</t>
         </is>
       </c>
       <c r="W192" t="inlineStr">
         <is>
-          <t>Median Income</t>
+          <t>Income Inequality (Gini Coefficient)</t>
         </is>
       </c>
       <c r="X192" t="inlineStr"/>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
         </is>
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>HUD 2018; ACS 2012, 2018</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB192" t="inlineStr"/>
@@ -14489,68 +14477,56 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
+          <t>Internet Access</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr"/>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr"/>
-      <c r="L193" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M193" t="inlineStr"/>
-      <c r="N193" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr"/>
       <c r="O193" t="inlineStr"/>
       <c r="P193" t="inlineStr"/>
-      <c r="Q193" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q193" t="inlineStr"/>
       <c r="R193" t="inlineStr"/>
       <c r="S193" t="inlineStr"/>
       <c r="T193" t="inlineStr"/>
       <c r="U193" t="inlineStr"/>
       <c r="V193" t="inlineStr">
         <is>
-          <t>PciE</t>
+          <t>NoIntP</t>
         </is>
       </c>
       <c r="W193" t="inlineStr">
         <is>
-          <t>Per Capita Income</t>
+          <t>Households without Internet Access %</t>
         </is>
       </c>
       <c r="X193" t="inlineStr"/>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Internet_Access.md</t>
         </is>
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>ACS 2019</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>American Community Survey 2015-2019 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB193" t="inlineStr"/>
@@ -14568,21 +14544,9 @@
           <t>Poverty, Income, Gini Coefficient</t>
         </is>
       </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="C194" t="inlineStr"/>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
         <is>
           <t>x</t>
@@ -14614,19 +14578,15 @@
       <c r="R194" t="inlineStr"/>
       <c r="S194" t="inlineStr"/>
       <c r="T194" t="inlineStr"/>
-      <c r="U194" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="U194" t="inlineStr"/>
       <c r="V194" t="inlineStr">
         <is>
-          <t>PovP</t>
+          <t>MedInc</t>
         </is>
       </c>
       <c r="W194" t="inlineStr">
         <is>
-          <t>Poverty %</t>
+          <t>Median Income</t>
         </is>
       </c>
       <c r="X194" t="inlineStr"/>
@@ -14660,21 +14620,9 @@
           <t>Poverty, Income, Gini Coefficient</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="C195" t="inlineStr"/>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr">
         <is>
           <t>x</t>
@@ -14706,19 +14654,15 @@
       <c r="R195" t="inlineStr"/>
       <c r="S195" t="inlineStr"/>
       <c r="T195" t="inlineStr"/>
-      <c r="U195" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="U195" t="inlineStr"/>
       <c r="V195" t="inlineStr">
         <is>
-          <t>UnempP</t>
+          <t>PciE</t>
         </is>
       </c>
       <c r="W195" t="inlineStr">
         <is>
-          <t>Unemployment %</t>
+          <t>Per Capita Income</t>
         </is>
       </c>
       <c r="X195" t="inlineStr"/>
@@ -14744,65 +14688,89 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>SDOH Indices &amp; Typology</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr"/>
-      <c r="D196" t="inlineStr"/>
-      <c r="E196" t="inlineStr"/>
-      <c r="F196" t="inlineStr"/>
+          <t>Poverty, Income, Gini Coefficient</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G196" t="inlineStr"/>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr"/>
-      <c r="L196" t="inlineStr"/>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M196" t="inlineStr"/>
-      <c r="N196" t="inlineStr"/>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O196" t="inlineStr"/>
       <c r="P196" t="inlineStr"/>
-      <c r="Q196" t="inlineStr"/>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R196" t="inlineStr"/>
       <c r="S196" t="inlineStr"/>
-      <c r="T196" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="U196" t="inlineStr"/>
+      <c r="T196" t="inlineStr"/>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="V196" t="inlineStr">
         <is>
-          <t>LimMobInd</t>
+          <t>PovP</t>
         </is>
       </c>
       <c r="W196" t="inlineStr">
         <is>
-          <t>Limited Moblility Index</t>
+          <t>Poverty %</t>
         </is>
       </c>
       <c r="X196" t="inlineStr"/>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB196" t="inlineStr"/>
@@ -14812,65 +14780,89 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>SDOH Indices &amp; Typology</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr"/>
-      <c r="D197" t="inlineStr"/>
-      <c r="E197" t="inlineStr"/>
-      <c r="F197" t="inlineStr"/>
+          <t>Poverty, Income, Gini Coefficient</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G197" t="inlineStr"/>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr"/>
-      <c r="L197" t="inlineStr"/>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M197" t="inlineStr"/>
-      <c r="N197" t="inlineStr"/>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O197" t="inlineStr"/>
       <c r="P197" t="inlineStr"/>
-      <c r="Q197" t="inlineStr"/>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R197" t="inlineStr"/>
       <c r="S197" t="inlineStr"/>
-      <c r="T197" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="U197" t="inlineStr"/>
+      <c r="T197" t="inlineStr"/>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="V197" t="inlineStr">
         <is>
-          <t>MicaInd</t>
+          <t>UnempP</t>
         </is>
       </c>
       <c r="W197" t="inlineStr">
         <is>
-          <t>Mixed Immigrant Cohesion and Accesibility (MICA) Index</t>
+          <t>Unemployment %</t>
         </is>
       </c>
       <c r="X197" t="inlineStr"/>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB197" t="inlineStr"/>
@@ -14909,16 +14901,20 @@
       <c r="Q198" t="inlineStr"/>
       <c r="R198" t="inlineStr"/>
       <c r="S198" t="inlineStr"/>
-      <c r="T198" t="inlineStr"/>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U198" t="inlineStr"/>
       <c r="V198" t="inlineStr">
         <is>
-          <t>NeighbTyp</t>
+          <t>LimMobInd</t>
         </is>
       </c>
       <c r="W198" t="inlineStr">
         <is>
-          <t>Neighborhood Type</t>
+          <t>Limited Moblility Index</t>
         </is>
       </c>
       <c r="X198" t="inlineStr"/>
@@ -14981,12 +14977,12 @@
       <c r="U199" t="inlineStr"/>
       <c r="V199" t="inlineStr">
         <is>
-          <t>SocEcAdvIn</t>
+          <t>MicaInd</t>
         </is>
       </c>
       <c r="W199" t="inlineStr">
         <is>
-          <t>Socioeconomic Advantage Index</t>
+          <t>Mixed Immigrant Cohesion and Accesibility (MICA) Index</t>
         </is>
       </c>
       <c r="X199" t="inlineStr"/>
@@ -15041,20 +15037,16 @@
       <c r="Q200" t="inlineStr"/>
       <c r="R200" t="inlineStr"/>
       <c r="S200" t="inlineStr"/>
-      <c r="T200" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T200" t="inlineStr"/>
       <c r="U200" t="inlineStr"/>
       <c r="V200" t="inlineStr">
         <is>
-          <t>UrbCoreInd</t>
+          <t>NeighbTyp</t>
         </is>
       </c>
       <c r="W200" t="inlineStr">
         <is>
-          <t>Urban Core Opportunity Index</t>
+          <t>Neighborhood Type</t>
         </is>
       </c>
       <c r="X200" t="inlineStr"/>
@@ -15085,7 +15077,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>SDOH Indices &amp; Typology</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
@@ -15093,56 +15085,52 @@
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr"/>
       <c r="G201" t="inlineStr"/>
-      <c r="H201" t="inlineStr"/>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr"/>
-      <c r="L201" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L201" t="inlineStr"/>
       <c r="M201" t="inlineStr"/>
-      <c r="N201" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N201" t="inlineStr"/>
       <c r="O201" t="inlineStr"/>
-      <c r="P201" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P201" t="inlineStr"/>
       <c r="Q201" t="inlineStr"/>
       <c r="R201" t="inlineStr"/>
       <c r="S201" t="inlineStr"/>
-      <c r="T201" t="inlineStr"/>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U201" t="inlineStr"/>
       <c r="V201" t="inlineStr">
         <is>
-          <t>SviSmryRnk</t>
+          <t>SocEcAdvIn</t>
         </is>
       </c>
       <c r="W201" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) Summary Ranking</t>
+          <t>Socioeconomic Advantage Index</t>
         </is>
       </c>
       <c r="X201" t="inlineStr"/>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
         </is>
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AB201" t="inlineStr"/>
@@ -15157,7 +15145,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>SDOH Indices &amp; Typology</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
@@ -15165,27 +15153,19 @@
       <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr"/>
       <c r="G202" t="inlineStr"/>
-      <c r="H202" t="inlineStr"/>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr"/>
-      <c r="L202" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L202" t="inlineStr"/>
       <c r="M202" t="inlineStr"/>
-      <c r="N202" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N202" t="inlineStr"/>
       <c r="O202" t="inlineStr"/>
-      <c r="P202" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P202" t="inlineStr"/>
       <c r="Q202" t="inlineStr"/>
       <c r="R202" t="inlineStr"/>
       <c r="S202" t="inlineStr"/>
@@ -15197,28 +15177,28 @@
       <c r="U202" t="inlineStr"/>
       <c r="V202" t="inlineStr">
         <is>
-          <t>SviTh1</t>
+          <t>UrbCoreInd</t>
         </is>
       </c>
       <c r="W202" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 1</t>
+          <t>Urban Core Opportunity Index</t>
         </is>
       </c>
       <c r="X202" t="inlineStr"/>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
         </is>
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AB202" t="inlineStr"/>
@@ -15269,12 +15249,12 @@
       <c r="U203" t="inlineStr"/>
       <c r="V203" t="inlineStr">
         <is>
-          <t>SviTh2</t>
+          <t>SviSmryRnk</t>
         </is>
       </c>
       <c r="W203" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 2</t>
+          <t>Social Vulnerability Index (SVI) Summary Ranking</t>
         </is>
       </c>
       <c r="X203" t="inlineStr"/>
@@ -15337,16 +15317,20 @@
       <c r="Q204" t="inlineStr"/>
       <c r="R204" t="inlineStr"/>
       <c r="S204" t="inlineStr"/>
-      <c r="T204" t="inlineStr"/>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U204" t="inlineStr"/>
       <c r="V204" t="inlineStr">
         <is>
-          <t>SviTh3</t>
+          <t>SviTh1</t>
         </is>
       </c>
       <c r="W204" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 3</t>
+          <t>Social Vulnerability Index (SVI) 1</t>
         </is>
       </c>
       <c r="X204" t="inlineStr"/>
@@ -15409,20 +15393,16 @@
       <c r="Q205" t="inlineStr"/>
       <c r="R205" t="inlineStr"/>
       <c r="S205" t="inlineStr"/>
-      <c r="T205" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T205" t="inlineStr"/>
       <c r="U205" t="inlineStr"/>
       <c r="V205" t="inlineStr">
         <is>
-          <t>SviTh4</t>
+          <t>SviTh2</t>
         </is>
       </c>
       <c r="W205" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 4</t>
+          <t>Social Vulnerability Index (SVI) 2</t>
         </is>
       </c>
       <c r="X205" t="inlineStr"/>
@@ -15444,6 +15424,154 @@
       <c r="AB205" t="inlineStr"/>
       <c r="AC205" t="inlineStr"/>
       <c r="AD205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr"/>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr"/>
+      <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr"/>
+      <c r="J206" t="inlineStr"/>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr"/>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr"/>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr"/>
+      <c r="R206" t="inlineStr"/>
+      <c r="S206" t="inlineStr"/>
+      <c r="T206" t="inlineStr"/>
+      <c r="U206" t="inlineStr"/>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>SviTh3</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 3</t>
+        </is>
+      </c>
+      <c r="X206" t="inlineStr"/>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB206" t="inlineStr"/>
+      <c r="AC206" t="inlineStr"/>
+      <c r="AD206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr"/>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr"/>
+      <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr"/>
+      <c r="J207" t="inlineStr"/>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr"/>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr"/>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr"/>
+      <c r="R207" t="inlineStr"/>
+      <c r="S207" t="inlineStr"/>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr"/>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>SviTh4</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 4</t>
+        </is>
+      </c>
+      <c r="X207" t="inlineStr"/>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB207" t="inlineStr"/>
+      <c r="AC207" t="inlineStr"/>
+      <c r="AD207" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/src/reference/data-dictionaries/T_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/T_Dict.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD207"/>
+  <dimension ref="A1:AD208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -12833,12 +12833,12 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB168" t="inlineStr"/>
@@ -12901,12 +12901,12 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB169" t="inlineStr"/>
@@ -12973,12 +12973,12 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB170" t="inlineStr"/>
@@ -12993,7 +12993,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
@@ -13007,11 +13007,7 @@
       <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr"/>
       <c r="M171" t="inlineStr"/>
-      <c r="N171" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N171" t="inlineStr"/>
       <c r="O171" t="inlineStr"/>
       <c r="P171" t="inlineStr"/>
       <c r="Q171" t="inlineStr"/>
@@ -13025,28 +13021,28 @@
       <c r="U171" t="inlineStr"/>
       <c r="V171" t="inlineStr">
         <is>
-          <t>FqhcCntDr</t>
+          <t>SutTmDr2</t>
         </is>
       </c>
       <c r="W171" t="inlineStr">
         <is>
-          <t>Count of Federally Qualified Health Centers (FQHCs) within 30-min drive</t>
+          <t>Driving time to nearest Substance Use Treatment Provider (with impedance)</t>
         </is>
       </c>
       <c r="X171" t="inlineStr"/>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB171" t="inlineStr"/>
@@ -13093,12 +13089,12 @@
       <c r="U172" t="inlineStr"/>
       <c r="V172" t="inlineStr">
         <is>
-          <t>FqhcMinDis</t>
+          <t>FqhcCntDr</t>
         </is>
       </c>
       <c r="W172" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Federally Qualified Health Centers (FQHC)</t>
+          <t>Count of Federally Qualified Health Centers (FQHCs) within 30-min drive</t>
         </is>
       </c>
       <c r="X172" t="inlineStr"/>
@@ -13157,20 +13153,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T173" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T173" t="inlineStr"/>
       <c r="U173" t="inlineStr"/>
       <c r="V173" t="inlineStr">
         <is>
-          <t>FqhcTmDr</t>
+          <t>FqhcMinDis</t>
         </is>
       </c>
       <c r="W173" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC)</t>
+          <t>Distance (mi) to nearest Federally Qualified Health Centers (FQHC)</t>
         </is>
       </c>
       <c r="X173" t="inlineStr"/>
@@ -13215,7 +13207,11 @@
       <c r="K174" t="inlineStr"/>
       <c r="L174" t="inlineStr"/>
       <c r="M174" t="inlineStr"/>
-      <c r="N174" t="inlineStr"/>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O174" t="inlineStr"/>
       <c r="P174" t="inlineStr"/>
       <c r="Q174" t="inlineStr"/>
@@ -13233,12 +13229,12 @@
       <c r="U174" t="inlineStr"/>
       <c r="V174" t="inlineStr">
         <is>
-          <t>FqhcTmDr2</t>
+          <t>FqhcTmDr</t>
         </is>
       </c>
       <c r="W174" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC), with Impedance factor</t>
+          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC)</t>
         </is>
       </c>
       <c r="X174" t="inlineStr"/>
@@ -13269,7 +13265,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
@@ -13293,32 +13289,36 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T175" t="inlineStr"/>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U175" t="inlineStr"/>
       <c r="V175" t="inlineStr">
         <is>
-          <t>HcvCntDr</t>
+          <t>FqhcTmDr2</t>
         </is>
       </c>
       <c r="W175" t="inlineStr">
         <is>
-          <t>Count of HCV Providers</t>
+          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC), with Impedance factor</t>
         </is>
       </c>
       <c r="X175" t="inlineStr"/>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB175" t="inlineStr"/>
@@ -13361,12 +13361,12 @@
       <c r="U176" t="inlineStr"/>
       <c r="V176" t="inlineStr">
         <is>
-          <t>HcvMinDis</t>
+          <t>HcvCntDr</t>
         </is>
       </c>
       <c r="W176" t="inlineStr">
         <is>
-          <t>Distance to nearest HCV Provider</t>
+          <t>Count of HCV Providers</t>
         </is>
       </c>
       <c r="X176" t="inlineStr"/>
@@ -13425,12 +13425,12 @@
       <c r="U177" t="inlineStr"/>
       <c r="V177" t="inlineStr">
         <is>
-          <t>HcvTmDr</t>
+          <t>HcvMinDis</t>
         </is>
       </c>
       <c r="W177" t="inlineStr">
         <is>
-          <t>Driving time to nearest HCV Provider</t>
+          <t>Distance to nearest HCV Provider</t>
         </is>
       </c>
       <c r="X177" t="inlineStr"/>
@@ -13489,12 +13489,12 @@
       <c r="U178" t="inlineStr"/>
       <c r="V178" t="inlineStr">
         <is>
-          <t>HcvTmDr2</t>
+          <t>HcvTmDr</t>
         </is>
       </c>
       <c r="W178" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest HCV Testing Facility with impedance</t>
+          <t>Driving time to nearest HCV Provider</t>
         </is>
       </c>
       <c r="X178" t="inlineStr"/>
@@ -13525,7 +13525,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Spatial access to Syringe Services Programs</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
@@ -13553,28 +13553,28 @@
       <c r="U179" t="inlineStr"/>
       <c r="V179" t="inlineStr">
         <is>
-          <t>SspTmDr</t>
+          <t>HcvTmDr2</t>
         </is>
       </c>
       <c r="W179" t="inlineStr">
         <is>
-          <t>Driving time to nearest SSP</t>
+          <t>Driving time (min) to nearest HCV Testing Facility with impedance</t>
         </is>
       </c>
       <c r="X179" t="inlineStr"/>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/nasen_ssp/metadata/Access_SSP.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>NASEN</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>North American Syringe Exchange Network</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB179" t="inlineStr"/>
@@ -13617,12 +13617,12 @@
       <c r="U180" t="inlineStr"/>
       <c r="V180" t="inlineStr">
         <is>
-          <t>SspTmDr2</t>
+          <t>SspTmDr</t>
         </is>
       </c>
       <c r="W180" t="inlineStr">
         <is>
-          <t>Round trip driving time to nearest SSP</t>
+          <t>Driving time to nearest SSP</t>
         </is>
       </c>
       <c r="X180" t="inlineStr"/>
@@ -13653,17 +13653,13 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial access to Syringe Services Programs</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr"/>
@@ -13676,33 +13672,37 @@
       <c r="P181" t="inlineStr"/>
       <c r="Q181" t="inlineStr"/>
       <c r="R181" t="inlineStr"/>
-      <c r="S181" t="inlineStr"/>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T181" t="inlineStr"/>
       <c r="U181" t="inlineStr"/>
       <c r="V181" t="inlineStr">
         <is>
-          <t>Ruca1</t>
+          <t>SspTmDr2</t>
         </is>
       </c>
       <c r="W181" t="inlineStr">
         <is>
-          <t>Primary RUCA Code</t>
+          <t>Round trip driving time to nearest SSP</t>
         </is>
       </c>
       <c r="X181" t="inlineStr"/>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/nasen_ssp/metadata/Access_SSP.md</t>
         </is>
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>NASEN</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>North American Syringe Exchange Network</t>
         </is>
       </c>
       <c r="AB181" t="inlineStr"/>
@@ -13745,12 +13745,12 @@
       <c r="U182" t="inlineStr"/>
       <c r="V182" t="inlineStr">
         <is>
-          <t>Ruca2</t>
+          <t>Ruca1</t>
         </is>
       </c>
       <c r="W182" t="inlineStr">
         <is>
-          <t>Secondary RUCA Code</t>
+          <t>Primary RUCA Code</t>
         </is>
       </c>
       <c r="X182" t="inlineStr"/>
@@ -13805,20 +13805,16 @@
       <c r="Q183" t="inlineStr"/>
       <c r="R183" t="inlineStr"/>
       <c r="S183" t="inlineStr"/>
-      <c r="T183" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T183" t="inlineStr"/>
       <c r="U183" t="inlineStr"/>
       <c r="V183" t="inlineStr">
         <is>
-          <t>Rurality</t>
+          <t>Ruca2</t>
         </is>
       </c>
       <c r="W183" t="inlineStr">
         <is>
-          <t>Urban-Suburban-Rural</t>
+          <t>Secondary RUCA Code</t>
         </is>
       </c>
       <c r="X183" t="inlineStr"/>
@@ -13844,28 +13840,28 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr"/>
-      <c r="F184" t="inlineStr"/>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr"/>
-      <c r="L184" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L184" t="inlineStr"/>
       <c r="M184" t="inlineStr"/>
       <c r="N184" t="inlineStr"/>
       <c r="O184" t="inlineStr"/>
@@ -13873,32 +13869,36 @@
       <c r="Q184" t="inlineStr"/>
       <c r="R184" t="inlineStr"/>
       <c r="S184" t="inlineStr"/>
-      <c r="T184" t="inlineStr"/>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U184" t="inlineStr"/>
       <c r="V184" t="inlineStr">
         <is>
-          <t>EssnWrkE</t>
+          <t>Rurality</t>
         </is>
       </c>
       <c r="W184" t="inlineStr">
         <is>
-          <t>Count of Essential Workers</t>
+          <t>Urban-Suburban-Rural</t>
         </is>
       </c>
       <c r="X184" t="inlineStr"/>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB184" t="inlineStr"/>
@@ -13931,30 +13931,22 @@
         </is>
       </c>
       <c r="M185" t="inlineStr"/>
-      <c r="N185" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N185" t="inlineStr"/>
       <c r="O185" t="inlineStr"/>
       <c r="P185" t="inlineStr"/>
-      <c r="Q185" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q185" t="inlineStr"/>
       <c r="R185" t="inlineStr"/>
       <c r="S185" t="inlineStr"/>
       <c r="T185" t="inlineStr"/>
       <c r="U185" t="inlineStr"/>
       <c r="V185" t="inlineStr">
         <is>
-          <t>EssnWrkP</t>
+          <t>EssnWrkE</t>
         </is>
       </c>
       <c r="W185" t="inlineStr">
         <is>
-          <t>Essential Workers %</t>
+          <t>Count of Essential Workers</t>
         </is>
       </c>
       <c r="X185" t="inlineStr"/>
@@ -14021,12 +14013,12 @@
       <c r="U186" t="inlineStr"/>
       <c r="V186" t="inlineStr">
         <is>
-          <t>HghRskP</t>
+          <t>EssnWrkP</t>
         </is>
       </c>
       <c r="W186" t="inlineStr">
         <is>
-          <t>Employed % - High Risk of Injury</t>
+          <t>Essential Workers %</t>
         </is>
       </c>
       <c r="X186" t="inlineStr"/>
@@ -14093,12 +14085,12 @@
       <c r="U187" t="inlineStr"/>
       <c r="V187" t="inlineStr">
         <is>
-          <t>HltCrP</t>
+          <t>HghRskP</t>
         </is>
       </c>
       <c r="W187" t="inlineStr">
         <is>
-          <t>Employed % - Health Care</t>
+          <t>Employed % - High Risk of Injury</t>
         </is>
       </c>
       <c r="X187" t="inlineStr"/>
@@ -14165,12 +14157,12 @@
       <c r="U188" t="inlineStr"/>
       <c r="V188" t="inlineStr">
         <is>
-          <t>RetailP</t>
+          <t>HltCrP</t>
         </is>
       </c>
       <c r="W188" t="inlineStr">
         <is>
-          <t>Employed % - Retail</t>
+          <t>Employed % - Health Care</t>
         </is>
       </c>
       <c r="X188" t="inlineStr"/>
@@ -14237,12 +14229,12 @@
       <c r="U189" t="inlineStr"/>
       <c r="V189" t="inlineStr">
         <is>
-          <t>TotWrkE</t>
+          <t>RetailP</t>
         </is>
       </c>
       <c r="W189" t="inlineStr">
         <is>
-          <t>Count of Working Population</t>
+          <t>Employed % - Retail</t>
         </is>
       </c>
       <c r="X189" t="inlineStr"/>
@@ -14273,7 +14265,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
@@ -14291,38 +14283,46 @@
         </is>
       </c>
       <c r="M190" t="inlineStr"/>
-      <c r="N190" t="inlineStr"/>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O190" t="inlineStr"/>
       <c r="P190" t="inlineStr"/>
-      <c r="Q190" t="inlineStr"/>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R190" t="inlineStr"/>
       <c r="S190" t="inlineStr"/>
       <c r="T190" t="inlineStr"/>
       <c r="U190" t="inlineStr"/>
       <c r="V190" t="inlineStr">
         <is>
-          <t>ForDqP</t>
+          <t>TotWrkE</t>
         </is>
       </c>
       <c r="W190" t="inlineStr">
         <is>
-          <t>Foreclosure &amp; Delinquency %</t>
+          <t>Count of Working Population</t>
         </is>
       </c>
       <c r="X190" t="inlineStr"/>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB190" t="inlineStr"/>
@@ -14365,12 +14365,12 @@
       <c r="U191" t="inlineStr"/>
       <c r="V191" t="inlineStr">
         <is>
-          <t>ForDqTot</t>
+          <t>ForDqP</t>
         </is>
       </c>
       <c r="W191" t="inlineStr">
         <is>
-          <t>Foreclosure &amp; Delinquency Count</t>
+          <t>Foreclosure &amp; Delinquency %</t>
         </is>
       </c>
       <c r="X191" t="inlineStr"/>
@@ -14407,11 +14407,7 @@
       <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr"/>
@@ -14423,30 +14419,22 @@
         </is>
       </c>
       <c r="M192" t="inlineStr"/>
-      <c r="N192" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N192" t="inlineStr"/>
       <c r="O192" t="inlineStr"/>
       <c r="P192" t="inlineStr"/>
-      <c r="Q192" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q192" t="inlineStr"/>
       <c r="R192" t="inlineStr"/>
       <c r="S192" t="inlineStr"/>
       <c r="T192" t="inlineStr"/>
       <c r="U192" t="inlineStr"/>
       <c r="V192" t="inlineStr">
         <is>
-          <t>GiniCoeff</t>
+          <t>ForDqTot</t>
         </is>
       </c>
       <c r="W192" t="inlineStr">
         <is>
-          <t>Income Inequality (Gini Coefficient)</t>
+          <t>Foreclosure &amp; Delinquency Count</t>
         </is>
       </c>
       <c r="X192" t="inlineStr"/>
@@ -14477,56 +14465,68 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Internet Access</t>
+          <t>Great Recession Foreclosure Rate</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr"/>
-      <c r="F193" t="inlineStr"/>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr"/>
-      <c r="L193" t="inlineStr"/>
-      <c r="M193" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N193" t="inlineStr"/>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr"/>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O193" t="inlineStr"/>
       <c r="P193" t="inlineStr"/>
-      <c r="Q193" t="inlineStr"/>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R193" t="inlineStr"/>
       <c r="S193" t="inlineStr"/>
       <c r="T193" t="inlineStr"/>
       <c r="U193" t="inlineStr"/>
       <c r="V193" t="inlineStr">
         <is>
-          <t>NoIntP</t>
+          <t>GiniCoeff</t>
         </is>
       </c>
       <c r="W193" t="inlineStr">
         <is>
-          <t>Households without Internet Access %</t>
+          <t>Income Inequality (Gini Coefficient)</t>
         </is>
       </c>
       <c r="X193" t="inlineStr"/>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Internet_Access.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
         </is>
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>ACS 2019</t>
+          <t>HUD 2018; ACS 2012, 2018</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>American Community Survey 2015-2019 5-Year Estimate</t>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB193" t="inlineStr"/>
@@ -14541,68 +14541,56 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
+          <t>Internet Access</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr"/>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr"/>
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr"/>
-      <c r="L194" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M194" t="inlineStr"/>
-      <c r="N194" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr"/>
       <c r="O194" t="inlineStr"/>
       <c r="P194" t="inlineStr"/>
-      <c r="Q194" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q194" t="inlineStr"/>
       <c r="R194" t="inlineStr"/>
       <c r="S194" t="inlineStr"/>
       <c r="T194" t="inlineStr"/>
       <c r="U194" t="inlineStr"/>
       <c r="V194" t="inlineStr">
         <is>
-          <t>MedInc</t>
+          <t>NoIntP</t>
         </is>
       </c>
       <c r="W194" t="inlineStr">
         <is>
-          <t>Median Income</t>
+          <t>Households without Internet Access %</t>
         </is>
       </c>
       <c r="X194" t="inlineStr"/>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Internet_Access.md</t>
         </is>
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>ACS 2019</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>American Community Survey 2015-2019 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB194" t="inlineStr"/>
@@ -14657,12 +14645,12 @@
       <c r="U195" t="inlineStr"/>
       <c r="V195" t="inlineStr">
         <is>
-          <t>PciE</t>
+          <t>MedInc</t>
         </is>
       </c>
       <c r="W195" t="inlineStr">
         <is>
-          <t>Per Capita Income</t>
+          <t>Median Income</t>
         </is>
       </c>
       <c r="X195" t="inlineStr"/>
@@ -14696,21 +14684,9 @@
           <t>Poverty, Income, Gini Coefficient</t>
         </is>
       </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="C196" t="inlineStr"/>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
         <is>
           <t>x</t>
@@ -14742,19 +14718,15 @@
       <c r="R196" t="inlineStr"/>
       <c r="S196" t="inlineStr"/>
       <c r="T196" t="inlineStr"/>
-      <c r="U196" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="U196" t="inlineStr"/>
       <c r="V196" t="inlineStr">
         <is>
-          <t>PovP</t>
+          <t>PciE</t>
         </is>
       </c>
       <c r="W196" t="inlineStr">
         <is>
-          <t>Poverty %</t>
+          <t>Per Capita Income</t>
         </is>
       </c>
       <c r="X196" t="inlineStr"/>
@@ -14841,12 +14813,12 @@
       </c>
       <c r="V197" t="inlineStr">
         <is>
-          <t>UnempP</t>
+          <t>PovP</t>
         </is>
       </c>
       <c r="W197" t="inlineStr">
         <is>
-          <t>Unemployment %</t>
+          <t>Poverty %</t>
         </is>
       </c>
       <c r="X197" t="inlineStr"/>
@@ -14872,65 +14844,89 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>SDOH Indices &amp; Typology</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr"/>
-      <c r="D198" t="inlineStr"/>
-      <c r="E198" t="inlineStr"/>
-      <c r="F198" t="inlineStr"/>
+          <t>Poverty, Income, Gini Coefficient</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G198" t="inlineStr"/>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr"/>
-      <c r="L198" t="inlineStr"/>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M198" t="inlineStr"/>
-      <c r="N198" t="inlineStr"/>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O198" t="inlineStr"/>
       <c r="P198" t="inlineStr"/>
-      <c r="Q198" t="inlineStr"/>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R198" t="inlineStr"/>
       <c r="S198" t="inlineStr"/>
-      <c r="T198" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="U198" t="inlineStr"/>
+      <c r="T198" t="inlineStr"/>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="V198" t="inlineStr">
         <is>
-          <t>LimMobInd</t>
+          <t>UnempP</t>
         </is>
       </c>
       <c r="W198" t="inlineStr">
         <is>
-          <t>Limited Moblility Index</t>
+          <t>Unemployment %</t>
         </is>
       </c>
       <c r="X198" t="inlineStr"/>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB198" t="inlineStr"/>
@@ -14977,12 +14973,12 @@
       <c r="U199" t="inlineStr"/>
       <c r="V199" t="inlineStr">
         <is>
-          <t>MicaInd</t>
+          <t>LimMobInd</t>
         </is>
       </c>
       <c r="W199" t="inlineStr">
         <is>
-          <t>Mixed Immigrant Cohesion and Accesibility (MICA) Index</t>
+          <t>Limited Moblility Index</t>
         </is>
       </c>
       <c r="X199" t="inlineStr"/>
@@ -15037,16 +15033,20 @@
       <c r="Q200" t="inlineStr"/>
       <c r="R200" t="inlineStr"/>
       <c r="S200" t="inlineStr"/>
-      <c r="T200" t="inlineStr"/>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U200" t="inlineStr"/>
       <c r="V200" t="inlineStr">
         <is>
-          <t>NeighbTyp</t>
+          <t>MicaInd</t>
         </is>
       </c>
       <c r="W200" t="inlineStr">
         <is>
-          <t>Neighborhood Type</t>
+          <t>Mixed Immigrant Cohesion and Accesibility (MICA) Index</t>
         </is>
       </c>
       <c r="X200" t="inlineStr"/>
@@ -15101,20 +15101,16 @@
       <c r="Q201" t="inlineStr"/>
       <c r="R201" t="inlineStr"/>
       <c r="S201" t="inlineStr"/>
-      <c r="T201" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T201" t="inlineStr"/>
       <c r="U201" t="inlineStr"/>
       <c r="V201" t="inlineStr">
         <is>
-          <t>SocEcAdvIn</t>
+          <t>NeighbTyp</t>
         </is>
       </c>
       <c r="W201" t="inlineStr">
         <is>
-          <t>Socioeconomic Advantage Index</t>
+          <t>Neighborhood Type</t>
         </is>
       </c>
       <c r="X201" t="inlineStr"/>
@@ -15177,12 +15173,12 @@
       <c r="U202" t="inlineStr"/>
       <c r="V202" t="inlineStr">
         <is>
-          <t>UrbCoreInd</t>
+          <t>SocEcAdvIn</t>
         </is>
       </c>
       <c r="W202" t="inlineStr">
         <is>
-          <t>Urban Core Opportunity Index</t>
+          <t>Socioeconomic Advantage Index</t>
         </is>
       </c>
       <c r="X202" t="inlineStr"/>
@@ -15213,7 +15209,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>SDOH Indices &amp; Typology</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
@@ -15221,56 +15217,52 @@
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr"/>
       <c r="G203" t="inlineStr"/>
-      <c r="H203" t="inlineStr"/>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="I203" t="inlineStr"/>
       <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr"/>
-      <c r="L203" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L203" t="inlineStr"/>
       <c r="M203" t="inlineStr"/>
-      <c r="N203" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N203" t="inlineStr"/>
       <c r="O203" t="inlineStr"/>
-      <c r="P203" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P203" t="inlineStr"/>
       <c r="Q203" t="inlineStr"/>
       <c r="R203" t="inlineStr"/>
       <c r="S203" t="inlineStr"/>
-      <c r="T203" t="inlineStr"/>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U203" t="inlineStr"/>
       <c r="V203" t="inlineStr">
         <is>
-          <t>SviSmryRnk</t>
+          <t>UrbCoreInd</t>
         </is>
       </c>
       <c r="W203" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) Summary Ranking</t>
+          <t>Urban Core Opportunity Index</t>
         </is>
       </c>
       <c r="X203" t="inlineStr"/>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
         </is>
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AB203" t="inlineStr"/>
@@ -15317,20 +15309,16 @@
       <c r="Q204" t="inlineStr"/>
       <c r="R204" t="inlineStr"/>
       <c r="S204" t="inlineStr"/>
-      <c r="T204" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T204" t="inlineStr"/>
       <c r="U204" t="inlineStr"/>
       <c r="V204" t="inlineStr">
         <is>
-          <t>SviTh1</t>
+          <t>SviSmryRnk</t>
         </is>
       </c>
       <c r="W204" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 1</t>
+          <t>Social Vulnerability Index (SVI) Summary Ranking</t>
         </is>
       </c>
       <c r="X204" t="inlineStr"/>
@@ -15393,16 +15381,20 @@
       <c r="Q205" t="inlineStr"/>
       <c r="R205" t="inlineStr"/>
       <c r="S205" t="inlineStr"/>
-      <c r="T205" t="inlineStr"/>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U205" t="inlineStr"/>
       <c r="V205" t="inlineStr">
         <is>
-          <t>SviTh2</t>
+          <t>SviTh1</t>
         </is>
       </c>
       <c r="W205" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 2</t>
+          <t>Social Vulnerability Index (SVI) 1</t>
         </is>
       </c>
       <c r="X205" t="inlineStr"/>
@@ -15469,12 +15461,12 @@
       <c r="U206" t="inlineStr"/>
       <c r="V206" t="inlineStr">
         <is>
-          <t>SviTh3</t>
+          <t>SviTh2</t>
         </is>
       </c>
       <c r="W206" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 3</t>
+          <t>Social Vulnerability Index (SVI) 2</t>
         </is>
       </c>
       <c r="X206" t="inlineStr"/>
@@ -15537,20 +15529,16 @@
       <c r="Q207" t="inlineStr"/>
       <c r="R207" t="inlineStr"/>
       <c r="S207" t="inlineStr"/>
-      <c r="T207" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T207" t="inlineStr"/>
       <c r="U207" t="inlineStr"/>
       <c r="V207" t="inlineStr">
         <is>
-          <t>SviTh4</t>
+          <t>SviTh3</t>
         </is>
       </c>
       <c r="W207" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 4</t>
+          <t>Social Vulnerability Index (SVI) 3</t>
         </is>
       </c>
       <c r="X207" t="inlineStr"/>
@@ -15572,6 +15560,82 @@
       <c r="AB207" t="inlineStr"/>
       <c r="AC207" t="inlineStr"/>
       <c r="AD207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr"/>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr"/>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr"/>
+      <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr"/>
+      <c r="J208" t="inlineStr"/>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr"/>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr"/>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr"/>
+      <c r="R208" t="inlineStr"/>
+      <c r="S208" t="inlineStr"/>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr"/>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>SviTh4</t>
+        </is>
+      </c>
+      <c r="W208" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 4</t>
+        </is>
+      </c>
+      <c r="X208" t="inlineStr"/>
+      <c r="Y208" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB208" t="inlineStr"/>
+      <c r="AC208" t="inlineStr"/>
+      <c r="AD208" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/src/reference/data-dictionaries/T_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/T_Dict.xlsx
@@ -12608,7 +12608,11 @@
       <c r="P165" t="inlineStr"/>
       <c r="Q165" t="inlineStr"/>
       <c r="R165" t="inlineStr"/>
-      <c r="S165" t="inlineStr"/>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T165" t="inlineStr"/>
       <c r="U165" t="inlineStr"/>
       <c r="V165" t="inlineStr">

--- a/docs/src/reference/data-dictionaries/T_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/T_Dict.xlsx
@@ -930,7 +930,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>% Persons aged 25 years and over with a bachelor’s degree as their highest level of education</t>
+          <t>% Bachelor's degree</t>
         </is>
       </c>
       <c r="X4" t="inlineStr"/>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>% Population aged 25 years and over whose highest educational attainment is a high school diploma (or equivalent)</t>
+          <t>% High School Graduate</t>
         </is>
       </c>
       <c r="X5" t="inlineStr"/>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>% Population aged 25 years and over with less than a high school diploma</t>
+          <t>% No High School Diploma</t>
         </is>
       </c>
       <c r="X6" t="inlineStr"/>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Proportion of the population aged 5+ who speak a language other than English at home but are proficient in English</t>
+          <t xml:space="preserve">% English Proficiency </t>
         </is>
       </c>
       <c r="X7" t="inlineStr"/>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>% Population aged 25 years and over with a graduate or professional degree</t>
+          <t>% Graduate or Professional Degree</t>
         </is>
       </c>
       <c r="X8" t="inlineStr"/>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>% Population 25 years and over with some college, but no degree</t>
+          <t>% Some College, but No Degree</t>
         </is>
       </c>
       <c r="X9" t="inlineStr"/>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Proportion of occupied housing units that are considered crowded (more than 1 person per room)</t>
+          <t>Crowded Housing</t>
         </is>
       </c>
       <c r="X10" t="inlineStr"/>

--- a/docs/src/reference/data-dictionaries/T_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/T_Dict.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD208"/>
+  <dimension ref="A1:AD212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -9063,11 +9063,7 @@
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr"/>
       <c r="P113" t="inlineStr"/>
       <c r="Q113" t="inlineStr"/>
@@ -9085,12 +9081,12 @@
       <c r="U113" t="inlineStr"/>
       <c r="V113" t="inlineStr">
         <is>
-          <t>BupTmWk</t>
+          <t>BupTmDr2</t>
         </is>
       </c>
       <c r="W113" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Buprenorphine Provider</t>
+          <t>Driving time to nearest buprenorphine provider (with impedance)</t>
         </is>
       </c>
       <c r="X113" t="inlineStr"/>
@@ -9149,16 +9145,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T114" t="inlineStr"/>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U114" t="inlineStr"/>
       <c r="V114" t="inlineStr">
         <is>
-          <t>MetCntBk30</t>
+          <t>BupTmWk</t>
         </is>
       </c>
       <c r="W114" t="inlineStr">
         <is>
-          <t>Count of methadone providers (30-min bike)</t>
+          <t>Walking Time (min) to nearest Buprenorphine Provider</t>
         </is>
       </c>
       <c r="X114" t="inlineStr"/>
@@ -9221,12 +9221,12 @@
       <c r="U115" t="inlineStr"/>
       <c r="V115" t="inlineStr">
         <is>
-          <t>MetCntBk60</t>
+          <t>MetCntBk30</t>
         </is>
       </c>
       <c r="W115" t="inlineStr">
         <is>
-          <t>Count of Methadone Providers (60-min bike)</t>
+          <t>Count of methadone providers (30-min bike)</t>
         </is>
       </c>
       <c r="X115" t="inlineStr"/>
@@ -9289,12 +9289,12 @@
       <c r="U116" t="inlineStr"/>
       <c r="V116" t="inlineStr">
         <is>
-          <t>MetCntDr30</t>
+          <t>MetCntBk60</t>
         </is>
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>Count of Methadone Providers (30-min drive)</t>
+          <t>Count of Methadone Providers (60-min bike)</t>
         </is>
       </c>
       <c r="X116" t="inlineStr"/>
@@ -9339,7 +9339,11 @@
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O117" t="inlineStr"/>
       <c r="P117" t="inlineStr"/>
       <c r="Q117" t="inlineStr"/>
@@ -9353,12 +9357,12 @@
       <c r="U117" t="inlineStr"/>
       <c r="V117" t="inlineStr">
         <is>
-          <t>MetCntDr60</t>
+          <t>MetCntDr30</t>
         </is>
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>Count of methadone providers (drive)</t>
+          <t>Count of Methadone Providers (30-min drive)</t>
         </is>
       </c>
       <c r="X117" t="inlineStr"/>
@@ -9403,11 +9407,7 @@
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="inlineStr"/>
       <c r="Q118" t="inlineStr"/>
@@ -9421,12 +9421,12 @@
       <c r="U118" t="inlineStr"/>
       <c r="V118" t="inlineStr">
         <is>
-          <t>MetCntWk30</t>
+          <t>MetCntDr60</t>
         </is>
       </c>
       <c r="W118" t="inlineStr">
         <is>
-          <t>Count of Methadone Providers (60-min walk)</t>
+          <t>Count of methadone providers (drive)</t>
         </is>
       </c>
       <c r="X118" t="inlineStr"/>
@@ -9489,12 +9489,12 @@
       <c r="U119" t="inlineStr"/>
       <c r="V119" t="inlineStr">
         <is>
-          <t>MetCntWk60</t>
+          <t>MetCntWk30</t>
         </is>
       </c>
       <c r="W119" t="inlineStr">
         <is>
-          <t>Count of Methadone Providers (30-min walk)</t>
+          <t>Count of Methadone Providers (60-min walk)</t>
         </is>
       </c>
       <c r="X119" t="inlineStr"/>
@@ -9539,7 +9539,11 @@
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O120" t="inlineStr"/>
       <c r="P120" t="inlineStr"/>
       <c r="Q120" t="inlineStr"/>
@@ -9553,12 +9557,12 @@
       <c r="U120" t="inlineStr"/>
       <c r="V120" t="inlineStr">
         <is>
-          <t>MetFca30</t>
+          <t>MetCntWk60</t>
         </is>
       </c>
       <c r="W120" t="inlineStr">
         <is>
-          <t>Two-step floating catchment area (2SFCA) measure of access to Methadone within a 30-minute drive</t>
+          <t>Count of Methadone Providers (30-min walk)</t>
         </is>
       </c>
       <c r="X120" t="inlineStr"/>
@@ -9617,12 +9621,12 @@
       <c r="U121" t="inlineStr"/>
       <c r="V121" t="inlineStr">
         <is>
-          <t>MetFca60</t>
+          <t>MetFca30</t>
         </is>
       </c>
       <c r="W121" t="inlineStr">
         <is>
-          <t>Two-step floating catchment area (2SFCA) measure of access to Methadone within a 60-minute drive</t>
+          <t>Two-step floating catchment area (2SFCA) measure of access to Methadone within a 30-minute drive</t>
         </is>
       </c>
       <c r="X121" t="inlineStr"/>
@@ -9667,11 +9671,7 @@
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr"/>
       <c r="P122" t="inlineStr"/>
       <c r="Q122" t="inlineStr"/>
@@ -9685,12 +9685,12 @@
       <c r="U122" t="inlineStr"/>
       <c r="V122" t="inlineStr">
         <is>
-          <t>MetMinDis</t>
+          <t>MetFca60</t>
         </is>
       </c>
       <c r="W122" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Methadone Provider</t>
+          <t>Two-step floating catchment area (2SFCA) measure of access to Methadone within a 60-minute drive</t>
         </is>
       </c>
       <c r="X122" t="inlineStr"/>
@@ -9724,26 +9724,10 @@
           <t>Spatial Access to MOUDs</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
@@ -9769,12 +9753,12 @@
       <c r="U123" t="inlineStr"/>
       <c r="V123" t="inlineStr">
         <is>
-          <t>MetRm30</t>
+          <t>MetMinDis</t>
         </is>
       </c>
       <c r="W123" t="inlineStr">
         <is>
-          <t>Methadone access 30 minutes (RAAM)</t>
+          <t>Distance (mi) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X123" t="inlineStr"/>
@@ -9853,12 +9837,12 @@
       <c r="U124" t="inlineStr"/>
       <c r="V124" t="inlineStr">
         <is>
-          <t>MetRm60</t>
+          <t>MetRm30</t>
         </is>
       </c>
       <c r="W124" t="inlineStr">
         <is>
-          <t>Methadone access 60 minutes (RAAM)</t>
+          <t>Methadone access 30 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X124" t="inlineStr"/>
@@ -9928,17 +9912,21 @@
       <c r="P125" t="inlineStr"/>
       <c r="Q125" t="inlineStr"/>
       <c r="R125" t="inlineStr"/>
-      <c r="S125" t="inlineStr"/>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T125" t="inlineStr"/>
       <c r="U125" t="inlineStr"/>
       <c r="V125" t="inlineStr">
         <is>
-          <t>MetRm90</t>
+          <t>MetRm60</t>
         </is>
       </c>
       <c r="W125" t="inlineStr">
         <is>
-          <t>Methadone access 90 minutes (RAAM)</t>
+          <t>Methadone access 60 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X125" t="inlineStr"/>
@@ -9972,10 +9960,26 @@
           <t>Spatial Access to MOUDs</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr"/>
-      <c r="D126" t="inlineStr"/>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr"/>
@@ -9992,25 +9996,17 @@
       <c r="P126" t="inlineStr"/>
       <c r="Q126" t="inlineStr"/>
       <c r="R126" t="inlineStr"/>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="T126" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S126" t="inlineStr"/>
+      <c r="T126" t="inlineStr"/>
       <c r="U126" t="inlineStr"/>
       <c r="V126" t="inlineStr">
         <is>
-          <t>MetTmBk</t>
+          <t>MetRm90</t>
         </is>
       </c>
       <c r="W126" t="inlineStr">
         <is>
-          <t>Biking Time (min) to nearest Methadone Provider</t>
+          <t>Methadone access 90 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X126" t="inlineStr"/>
@@ -10077,12 +10073,12 @@
       <c r="U127" t="inlineStr"/>
       <c r="V127" t="inlineStr">
         <is>
-          <t>MetTmDr</t>
+          <t>MetTmBk</t>
         </is>
       </c>
       <c r="W127" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Methadone Provider</t>
+          <t>Biking Time (min) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X127" t="inlineStr"/>
@@ -10149,12 +10145,12 @@
       <c r="U128" t="inlineStr"/>
       <c r="V128" t="inlineStr">
         <is>
-          <t>MetTmWk</t>
+          <t>MetTmDr</t>
         </is>
       </c>
       <c r="W128" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Methadone Provider</t>
+          <t>Driving Time (min) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X128" t="inlineStr"/>
@@ -10199,11 +10195,7 @@
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr"/>
-      <c r="N129" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr"/>
       <c r="P129" t="inlineStr"/>
       <c r="Q129" t="inlineStr"/>
@@ -10213,16 +10205,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T129" t="inlineStr"/>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U129" t="inlineStr"/>
       <c r="V129" t="inlineStr">
         <is>
-          <t>MoudMinDis</t>
+          <t>MetTmDr2</t>
         </is>
       </c>
       <c r="W129" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest MOUD (any)</t>
+          <t>Driving time to nearest methadone provider (with impedance)</t>
         </is>
       </c>
       <c r="X129" t="inlineStr"/>
@@ -10281,16 +10277,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T130" t="inlineStr"/>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U130" t="inlineStr"/>
       <c r="V130" t="inlineStr">
         <is>
-          <t>NaltCntBk30</t>
+          <t>MetTmWk</t>
         </is>
       </c>
       <c r="W130" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (30-min bike)</t>
+          <t>Walking Time (min) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X130" t="inlineStr"/>
@@ -10353,12 +10353,12 @@
       <c r="U131" t="inlineStr"/>
       <c r="V131" t="inlineStr">
         <is>
-          <t>NaltCntBk60</t>
+          <t>MoudMinDis</t>
         </is>
       </c>
       <c r="W131" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (60-min bike)</t>
+          <t>Distance (mi) to nearest MOUD (any)</t>
         </is>
       </c>
       <c r="X131" t="inlineStr"/>
@@ -10421,12 +10421,12 @@
       <c r="U132" t="inlineStr"/>
       <c r="V132" t="inlineStr">
         <is>
-          <t>NaltCntDr30</t>
+          <t>NaltCntBk30</t>
         </is>
       </c>
       <c r="W132" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (30-min drive)</t>
+          <t>Count of Naltrexone Providers (30-min bike)</t>
         </is>
       </c>
       <c r="X132" t="inlineStr"/>
@@ -10471,7 +10471,11 @@
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O133" t="inlineStr"/>
       <c r="P133" t="inlineStr"/>
       <c r="Q133" t="inlineStr"/>
@@ -10485,12 +10489,12 @@
       <c r="U133" t="inlineStr"/>
       <c r="V133" t="inlineStr">
         <is>
-          <t>NaltCntDr60</t>
+          <t>NaltCntBk60</t>
         </is>
       </c>
       <c r="W133" t="inlineStr">
         <is>
-          <t>Count of naltrexone providers (drive)</t>
+          <t>Count of Naltrexone Providers (60-min bike)</t>
         </is>
       </c>
       <c r="X133" t="inlineStr"/>
@@ -10553,12 +10557,12 @@
       <c r="U134" t="inlineStr"/>
       <c r="V134" t="inlineStr">
         <is>
-          <t>NaltCntWk30</t>
+          <t>NaltCntDr30</t>
         </is>
       </c>
       <c r="W134" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (30-min walk)</t>
+          <t>Count of Naltrexone Providers (30-min drive)</t>
         </is>
       </c>
       <c r="X134" t="inlineStr"/>
@@ -10603,11 +10607,7 @@
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr"/>
       <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr"/>
       <c r="P135" t="inlineStr"/>
       <c r="Q135" t="inlineStr"/>
@@ -10621,12 +10621,12 @@
       <c r="U135" t="inlineStr"/>
       <c r="V135" t="inlineStr">
         <is>
-          <t>NaltCntWk60</t>
+          <t>NaltCntDr60</t>
         </is>
       </c>
       <c r="W135" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (60-min walk)</t>
+          <t>Count of naltrexone providers (drive)</t>
         </is>
       </c>
       <c r="X135" t="inlineStr"/>
@@ -10671,7 +10671,11 @@
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O136" t="inlineStr"/>
       <c r="P136" t="inlineStr"/>
       <c r="Q136" t="inlineStr"/>
@@ -10685,12 +10689,12 @@
       <c r="U136" t="inlineStr"/>
       <c r="V136" t="inlineStr">
         <is>
-          <t>NaltFca30</t>
+          <t>NaltCntWk30</t>
         </is>
       </c>
       <c r="W136" t="inlineStr">
         <is>
-          <t>Two-step floating catchment area (2SFCA) measure of access to Naltrexone within a 30-minute drive</t>
+          <t>Count of Naltrexone Providers (30-min walk)</t>
         </is>
       </c>
       <c r="X136" t="inlineStr"/>
@@ -10735,7 +10739,11 @@
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O137" t="inlineStr"/>
       <c r="P137" t="inlineStr"/>
       <c r="Q137" t="inlineStr"/>
@@ -10749,12 +10757,12 @@
       <c r="U137" t="inlineStr"/>
       <c r="V137" t="inlineStr">
         <is>
-          <t>NaltFca60</t>
+          <t>NaltCntWk60</t>
         </is>
       </c>
       <c r="W137" t="inlineStr">
         <is>
-          <t>Two-step floating catchment area (2SFCA) measure of access to Naltrexone within a 60-minute drive</t>
+          <t>Count of Naltrexone Providers (60-min walk)</t>
         </is>
       </c>
       <c r="X137" t="inlineStr"/>
@@ -10799,11 +10807,7 @@
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr"/>
       <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr"/>
       <c r="P138" t="inlineStr"/>
       <c r="Q138" t="inlineStr"/>
@@ -10817,12 +10821,12 @@
       <c r="U138" t="inlineStr"/>
       <c r="V138" t="inlineStr">
         <is>
-          <t>NaltMinDis</t>
+          <t>NaltFca30</t>
         </is>
       </c>
       <c r="W138" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Naltrexone Provider</t>
+          <t>Two-step floating catchment area (2SFCA) measure of access to Naltrexone within a 30-minute drive</t>
         </is>
       </c>
       <c r="X138" t="inlineStr"/>
@@ -10867,11 +10871,7 @@
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr"/>
       <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr"/>
       <c r="P139" t="inlineStr"/>
       <c r="Q139" t="inlineStr"/>
@@ -10885,12 +10885,12 @@
       <c r="U139" t="inlineStr"/>
       <c r="V139" t="inlineStr">
         <is>
-          <t>NaltRm30</t>
+          <t>NaltFca60</t>
         </is>
       </c>
       <c r="W139" t="inlineStr">
         <is>
-          <t>Naltrexone access 30 minutes (RAAM)</t>
+          <t>Two-step floating catchment area (2SFCA) measure of access to Naltrexone within a 60-minute drive</t>
         </is>
       </c>
       <c r="X139" t="inlineStr"/>
@@ -10953,12 +10953,12 @@
       <c r="U140" t="inlineStr"/>
       <c r="V140" t="inlineStr">
         <is>
-          <t>NaltRm60</t>
+          <t>NaltMinDis</t>
         </is>
       </c>
       <c r="W140" t="inlineStr">
         <is>
-          <t>Naltrexone access 60 minutes (RAAM)</t>
+          <t>Distance (mi) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X140" t="inlineStr"/>
@@ -11012,17 +11012,21 @@
       <c r="P141" t="inlineStr"/>
       <c r="Q141" t="inlineStr"/>
       <c r="R141" t="inlineStr"/>
-      <c r="S141" t="inlineStr"/>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T141" t="inlineStr"/>
       <c r="U141" t="inlineStr"/>
       <c r="V141" t="inlineStr">
         <is>
-          <t>NaltRm90</t>
+          <t>NaltRm30</t>
         </is>
       </c>
       <c r="W141" t="inlineStr">
         <is>
-          <t>Naltrexone access 90 minutes (RAAM)</t>
+          <t>Naltrexone access 30 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X141" t="inlineStr"/>
@@ -11081,20 +11085,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T142" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T142" t="inlineStr"/>
       <c r="U142" t="inlineStr"/>
       <c r="V142" t="inlineStr">
         <is>
-          <t>NaltTmBk</t>
+          <t>NaltRm60</t>
         </is>
       </c>
       <c r="W142" t="inlineStr">
         <is>
-          <t>Biking Time (min) to nearest Naltrexone Provider</t>
+          <t>Naltrexone access 60 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X142" t="inlineStr"/>
@@ -11148,25 +11148,17 @@
       <c r="P143" t="inlineStr"/>
       <c r="Q143" t="inlineStr"/>
       <c r="R143" t="inlineStr"/>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="T143" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S143" t="inlineStr"/>
+      <c r="T143" t="inlineStr"/>
       <c r="U143" t="inlineStr"/>
       <c r="V143" t="inlineStr">
         <is>
-          <t>NaltTmDr</t>
+          <t>NaltRm90</t>
         </is>
       </c>
       <c r="W143" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Naltrexone Provider</t>
+          <t>Naltrexone access 90 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X143" t="inlineStr"/>
@@ -11233,12 +11225,12 @@
       <c r="U144" t="inlineStr"/>
       <c r="V144" t="inlineStr">
         <is>
-          <t>NaltTmWk</t>
+          <t>NaltTmBk</t>
         </is>
       </c>
       <c r="W144" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Naltrexone Provider</t>
+          <t>Biking Time (min) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X144" t="inlineStr"/>
@@ -11283,12 +11275,12 @@
       <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr"/>
       <c r="M145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
-      <c r="O145" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr"/>
       <c r="P145" t="inlineStr"/>
       <c r="Q145" t="inlineStr"/>
       <c r="R145" t="inlineStr"/>
@@ -11297,16 +11289,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T145" t="inlineStr"/>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U145" t="inlineStr"/>
       <c r="V145" t="inlineStr">
         <is>
-          <t>OtpCntDr</t>
+          <t>NaltTmDr</t>
         </is>
       </c>
       <c r="W145" t="inlineStr">
         <is>
-          <t>Count of Opioid Treatment Programs (OTP) (30-min drive)</t>
+          <t>Driving Time (min) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X145" t="inlineStr"/>
@@ -11365,12 +11361,12 @@
       <c r="U146" t="inlineStr"/>
       <c r="V146" t="inlineStr">
         <is>
-          <t>OtpFca30</t>
+          <t>NaltTmDr2</t>
         </is>
       </c>
       <c r="W146" t="inlineStr">
         <is>
-          <t>Two-step floating catchment area (2SFCA) measure of access to opioid treatment programs within a 30-minute drive</t>
+          <t>Driving time to nearest naltrexone provider (with impedance)</t>
         </is>
       </c>
       <c r="X146" t="inlineStr"/>
@@ -11415,7 +11411,11 @@
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O147" t="inlineStr"/>
       <c r="P147" t="inlineStr"/>
       <c r="Q147" t="inlineStr"/>
@@ -11425,16 +11425,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T147" t="inlineStr"/>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U147" t="inlineStr"/>
       <c r="V147" t="inlineStr">
         <is>
-          <t>OtpFca60</t>
+          <t>NaltTmWk</t>
         </is>
       </c>
       <c r="W147" t="inlineStr">
         <is>
-          <t>Two-step floating catchment area (2SFCA) measure of access to opioid treatment programs within a 60-minute drive</t>
+          <t>Walking Time (min) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X147" t="inlineStr"/>
@@ -11497,12 +11501,12 @@
       <c r="U148" t="inlineStr"/>
       <c r="V148" t="inlineStr">
         <is>
-          <t>OtpMinDis</t>
+          <t>OtpCntDr</t>
         </is>
       </c>
       <c r="W148" t="inlineStr">
         <is>
-          <t>Distance to nearest OTP</t>
+          <t>Count of Opioid Treatment Programs (OTP) (30-min drive)</t>
         </is>
       </c>
       <c r="X148" t="inlineStr"/>
@@ -11561,12 +11565,12 @@
       <c r="U149" t="inlineStr"/>
       <c r="V149" t="inlineStr">
         <is>
-          <t>OtpRm30</t>
+          <t>OtpFca30</t>
         </is>
       </c>
       <c r="W149" t="inlineStr">
         <is>
-          <t>Opioid Treatment Provider access 30 minutes (RAAM)</t>
+          <t>Two-step floating catchment area (2SFCA) measure of access to opioid treatment programs within a 30-minute drive</t>
         </is>
       </c>
       <c r="X149" t="inlineStr"/>
@@ -11625,12 +11629,12 @@
       <c r="U150" t="inlineStr"/>
       <c r="V150" t="inlineStr">
         <is>
-          <t>OtpRm60</t>
+          <t>OtpFca60</t>
         </is>
       </c>
       <c r="W150" t="inlineStr">
         <is>
-          <t>Opioid Treatment Provider access 60 minutes (RAAM)</t>
+          <t>Two-step floating catchment area (2SFCA) measure of access to opioid treatment programs within a 60-minute drive</t>
         </is>
       </c>
       <c r="X150" t="inlineStr"/>
@@ -11689,20 +11693,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T151" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T151" t="inlineStr"/>
       <c r="U151" t="inlineStr"/>
       <c r="V151" t="inlineStr">
         <is>
-          <t>OtpTmDr</t>
+          <t>OtpMinDis</t>
         </is>
       </c>
       <c r="W151" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP)</t>
+          <t>Distance to nearest OTP</t>
         </is>
       </c>
       <c r="X151" t="inlineStr"/>
@@ -11761,12 +11761,12 @@
       <c r="U152" t="inlineStr"/>
       <c r="V152" t="inlineStr">
         <is>
-          <t>TlBupCntBk30</t>
+          <t>OtpRm30</t>
         </is>
       </c>
       <c r="W152" t="inlineStr">
         <is>
-          <t>Count of telehealth buprenorphine providers within 30-minute bike ride</t>
+          <t>Opioid Treatment Provider access 30 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X152" t="inlineStr"/>
@@ -11825,12 +11825,12 @@
       <c r="U153" t="inlineStr"/>
       <c r="V153" t="inlineStr">
         <is>
-          <t>TlBupCntDr30</t>
+          <t>OtpRm60</t>
         </is>
       </c>
       <c r="W153" t="inlineStr">
         <is>
-          <t>Count of telehealth buprenorphine providers within 30-minute drive</t>
+          <t>Opioid Treatment Provider access 60 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X153" t="inlineStr"/>
@@ -11876,7 +11876,11 @@
       <c r="L154" t="inlineStr"/>
       <c r="M154" t="inlineStr"/>
       <c r="N154" t="inlineStr"/>
-      <c r="O154" t="inlineStr"/>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P154" t="inlineStr"/>
       <c r="Q154" t="inlineStr"/>
       <c r="R154" t="inlineStr"/>
@@ -11885,16 +11889,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T154" t="inlineStr"/>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U154" t="inlineStr"/>
       <c r="V154" t="inlineStr">
         <is>
-          <t>TlBupCntDr60</t>
+          <t>OtpTmDr</t>
         </is>
       </c>
       <c r="W154" t="inlineStr">
         <is>
-          <t>Count of telehealth buprenorphine providers within 60-minute drive</t>
+          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP)</t>
         </is>
       </c>
       <c r="X154" t="inlineStr"/>
@@ -11953,12 +11961,12 @@
       <c r="U155" t="inlineStr"/>
       <c r="V155" t="inlineStr">
         <is>
-          <t>TlBupCntWk30</t>
+          <t>OtpTmDr2</t>
         </is>
       </c>
       <c r="W155" t="inlineStr">
         <is>
-          <t>Count of telehealth buprenorphine providers within 30-minute walk</t>
+          <t>Driving time to nearest OTP (impedance-adjusted)</t>
         </is>
       </c>
       <c r="X155" t="inlineStr"/>
@@ -12017,12 +12025,12 @@
       <c r="U156" t="inlineStr"/>
       <c r="V156" t="inlineStr">
         <is>
-          <t>TlBupMinDis</t>
+          <t>TlBupCntBk30</t>
         </is>
       </c>
       <c r="W156" t="inlineStr">
         <is>
-          <t>Minimum distance to telehealth buprenorphine provider</t>
+          <t>Count of telehealth buprenorphine providers within 30-minute bike ride</t>
         </is>
       </c>
       <c r="X156" t="inlineStr"/>
@@ -12081,12 +12089,12 @@
       <c r="U157" t="inlineStr"/>
       <c r="V157" t="inlineStr">
         <is>
-          <t>TlBupTmBk</t>
+          <t>TlBupCntDr30</t>
         </is>
       </c>
       <c r="W157" t="inlineStr">
         <is>
-          <t>Biking time to nearest telehealth buprenorphine provider</t>
+          <t>Count of telehealth buprenorphine providers within 30-minute drive</t>
         </is>
       </c>
       <c r="X157" t="inlineStr"/>
@@ -12145,12 +12153,12 @@
       <c r="U158" t="inlineStr"/>
       <c r="V158" t="inlineStr">
         <is>
-          <t>TlBupTmDr</t>
+          <t>TlBupCntDr60</t>
         </is>
       </c>
       <c r="W158" t="inlineStr">
         <is>
-          <t>Driving time to nearest telehealth buprenorphine provider</t>
+          <t>Count of telehealth buprenorphine providers within 60-minute drive</t>
         </is>
       </c>
       <c r="X158" t="inlineStr"/>
@@ -12209,12 +12217,12 @@
       <c r="U159" t="inlineStr"/>
       <c r="V159" t="inlineStr">
         <is>
-          <t>TlBupTmWk</t>
+          <t>TlBupCntWk30</t>
         </is>
       </c>
       <c r="W159" t="inlineStr">
         <is>
-          <t>Walking time to nearest telehealth buprenorphine provider</t>
+          <t>Count of telehealth buprenorphine providers within 30-minute walk</t>
         </is>
       </c>
       <c r="X159" t="inlineStr"/>
@@ -12245,7 +12253,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
@@ -12259,11 +12267,7 @@
       <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr"/>
       <c r="M160" t="inlineStr"/>
-      <c r="N160" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N160" t="inlineStr"/>
       <c r="O160" t="inlineStr"/>
       <c r="P160" t="inlineStr"/>
       <c r="Q160" t="inlineStr"/>
@@ -12277,28 +12281,28 @@
       <c r="U160" t="inlineStr"/>
       <c r="V160" t="inlineStr">
         <is>
-          <t>MhCntDr</t>
+          <t>TlBupMinDis</t>
         </is>
       </c>
       <c r="W160" t="inlineStr">
         <is>
-          <t>Count of Mental Health Providers (30-min drive)</t>
+          <t>Minimum distance to telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X160" t="inlineStr"/>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB160" t="inlineStr"/>
@@ -12313,7 +12317,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
@@ -12327,11 +12331,7 @@
       <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr"/>
       <c r="M161" t="inlineStr"/>
-      <c r="N161" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N161" t="inlineStr"/>
       <c r="O161" t="inlineStr"/>
       <c r="P161" t="inlineStr"/>
       <c r="Q161" t="inlineStr"/>
@@ -12345,28 +12345,28 @@
       <c r="U161" t="inlineStr"/>
       <c r="V161" t="inlineStr">
         <is>
-          <t>MhMinDis</t>
+          <t>TlBupTmBk</t>
         </is>
       </c>
       <c r="W161" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Mental Health Provider</t>
+          <t>Biking time to nearest telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X161" t="inlineStr"/>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB161" t="inlineStr"/>
@@ -12381,7 +12381,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
@@ -12395,11 +12395,7 @@
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr"/>
       <c r="M162" t="inlineStr"/>
-      <c r="N162" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N162" t="inlineStr"/>
       <c r="O162" t="inlineStr"/>
       <c r="P162" t="inlineStr"/>
       <c r="Q162" t="inlineStr"/>
@@ -12409,36 +12405,32 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T162" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T162" t="inlineStr"/>
       <c r="U162" t="inlineStr"/>
       <c r="V162" t="inlineStr">
         <is>
-          <t>MhTmDr</t>
+          <t>TlBupTmDr</t>
         </is>
       </c>
       <c r="W162" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Mental Health Provider</t>
+          <t>Driving time to nearest telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X162" t="inlineStr"/>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB162" t="inlineStr"/>
@@ -12453,7 +12445,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
@@ -12481,28 +12473,28 @@
       <c r="U163" t="inlineStr"/>
       <c r="V163" t="inlineStr">
         <is>
-          <t>MhTmDr2</t>
+          <t>TlBupTmWk</t>
         </is>
       </c>
       <c r="W163" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest Mental Health Provider with impedance</t>
+          <t>Walking time to nearest telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X163" t="inlineStr"/>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB163" t="inlineStr"/>
@@ -12517,7 +12509,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
@@ -12530,12 +12522,12 @@
       <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr"/>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N164" t="inlineStr"/>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O164" t="inlineStr"/>
       <c r="P164" t="inlineStr"/>
       <c r="Q164" t="inlineStr"/>
@@ -12549,28 +12541,28 @@
       <c r="U164" t="inlineStr"/>
       <c r="V164" t="inlineStr">
         <is>
-          <t>RxCntDr</t>
+          <t>MhCntDr</t>
         </is>
       </c>
       <c r="W164" t="inlineStr">
         <is>
-          <t>Count of Pharmacies (30-min drive)</t>
+          <t>Count of Mental Health Providers (30-min drive)</t>
         </is>
       </c>
       <c r="X164" t="inlineStr"/>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB164" t="inlineStr"/>
@@ -12585,7 +12577,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
@@ -12598,12 +12590,12 @@
       <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N165" t="inlineStr"/>
+      <c r="M165" t="inlineStr"/>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O165" t="inlineStr"/>
       <c r="P165" t="inlineStr"/>
       <c r="Q165" t="inlineStr"/>
@@ -12617,28 +12609,28 @@
       <c r="U165" t="inlineStr"/>
       <c r="V165" t="inlineStr">
         <is>
-          <t>RxMinDis</t>
+          <t>MhMinDis</t>
         </is>
       </c>
       <c r="W165" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Pharmacy</t>
+          <t>Distance (mi) to nearest Mental Health Provider</t>
         </is>
       </c>
       <c r="X165" t="inlineStr"/>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB165" t="inlineStr"/>
@@ -12653,7 +12645,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
@@ -12666,12 +12658,12 @@
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N166" t="inlineStr"/>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O166" t="inlineStr"/>
       <c r="P166" t="inlineStr"/>
       <c r="Q166" t="inlineStr"/>
@@ -12689,28 +12681,28 @@
       <c r="U166" t="inlineStr"/>
       <c r="V166" t="inlineStr">
         <is>
-          <t>RxTmDr</t>
+          <t>MhTmDr</t>
         </is>
       </c>
       <c r="W166" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Pharmacy</t>
+          <t>Driving Time (min) to nearest Mental Health Provider</t>
         </is>
       </c>
       <c r="X166" t="inlineStr"/>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB166" t="inlineStr"/>
@@ -12725,7 +12717,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
@@ -12753,28 +12745,28 @@
       <c r="U167" t="inlineStr"/>
       <c r="V167" t="inlineStr">
         <is>
-          <t>RxTmDr2</t>
+          <t>MhTmDr2</t>
         </is>
       </c>
       <c r="W167" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Pharmacy with Impedance Factor</t>
+          <t>Driving time (min) to nearest Mental Health Provider with impedance</t>
         </is>
       </c>
       <c r="X167" t="inlineStr"/>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB167" t="inlineStr"/>
@@ -12789,7 +12781,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
@@ -12802,12 +12794,12 @@
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr"/>
-      <c r="N168" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr"/>
       <c r="O168" t="inlineStr"/>
       <c r="P168" t="inlineStr"/>
       <c r="Q168" t="inlineStr"/>
@@ -12821,28 +12813,28 @@
       <c r="U168" t="inlineStr"/>
       <c r="V168" t="inlineStr">
         <is>
-          <t>SutCntDr</t>
+          <t>RxCntDr</t>
         </is>
       </c>
       <c r="W168" t="inlineStr">
         <is>
-          <t>Count of Substance Use Treatment (SUT) facility (30-min drive)</t>
+          <t>Count of Pharmacies (30-min drive)</t>
         </is>
       </c>
       <c r="X168" t="inlineStr"/>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB168" t="inlineStr"/>
@@ -12857,7 +12849,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
@@ -12870,12 +12862,12 @@
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr"/>
-      <c r="M169" t="inlineStr"/>
-      <c r="N169" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr"/>
       <c r="O169" t="inlineStr"/>
       <c r="P169" t="inlineStr"/>
       <c r="Q169" t="inlineStr"/>
@@ -12889,28 +12881,28 @@
       <c r="U169" t="inlineStr"/>
       <c r="V169" t="inlineStr">
         <is>
-          <t>SutMinDis</t>
+          <t>RxMinDis</t>
         </is>
       </c>
       <c r="W169" t="inlineStr">
         <is>
-          <t>Distance (mi) to Substance Use Treatment (SUT) facility</t>
+          <t>Distance (mi) to nearest Pharmacy</t>
         </is>
       </c>
       <c r="X169" t="inlineStr"/>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB169" t="inlineStr"/>
@@ -12925,7 +12917,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
@@ -12938,12 +12930,12 @@
       <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr"/>
-      <c r="M170" t="inlineStr"/>
-      <c r="N170" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr"/>
       <c r="O170" t="inlineStr"/>
       <c r="P170" t="inlineStr"/>
       <c r="Q170" t="inlineStr"/>
@@ -12961,28 +12953,28 @@
       <c r="U170" t="inlineStr"/>
       <c r="V170" t="inlineStr">
         <is>
-          <t>SutTmDr</t>
+          <t>RxTmDr</t>
         </is>
       </c>
       <c r="W170" t="inlineStr">
         <is>
-          <t>Driving time (min) to Substance Use Treatment (SUT) facility</t>
+          <t>Driving Time (min) to nearest Pharmacy</t>
         </is>
       </c>
       <c r="X170" t="inlineStr"/>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB170" t="inlineStr"/>
@@ -12997,7 +12989,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
@@ -13025,28 +13017,28 @@
       <c r="U171" t="inlineStr"/>
       <c r="V171" t="inlineStr">
         <is>
-          <t>SutTmDr2</t>
+          <t>RxTmDr2</t>
         </is>
       </c>
       <c r="W171" t="inlineStr">
         <is>
-          <t>Driving time to nearest Substance Use Treatment Provider (with impedance)</t>
+          <t>Driving Time (min) to nearest Pharmacy with Impedance Factor</t>
         </is>
       </c>
       <c r="X171" t="inlineStr"/>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB171" t="inlineStr"/>
@@ -13061,7 +13053,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
@@ -13093,28 +13085,28 @@
       <c r="U172" t="inlineStr"/>
       <c r="V172" t="inlineStr">
         <is>
-          <t>FqhcCntDr</t>
+          <t>SutCntDr</t>
         </is>
       </c>
       <c r="W172" t="inlineStr">
         <is>
-          <t>Count of Federally Qualified Health Centers (FQHCs) within 30-min drive</t>
+          <t>Count of Substance Use Treatment (SUT) facility (30-min drive)</t>
         </is>
       </c>
       <c r="X172" t="inlineStr"/>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB172" t="inlineStr"/>
@@ -13129,7 +13121,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -13161,28 +13153,28 @@
       <c r="U173" t="inlineStr"/>
       <c r="V173" t="inlineStr">
         <is>
-          <t>FqhcMinDis</t>
+          <t>SutMinDis</t>
         </is>
       </c>
       <c r="W173" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Federally Qualified Health Centers (FQHC)</t>
+          <t>Distance (mi) to Substance Use Treatment (SUT) facility</t>
         </is>
       </c>
       <c r="X173" t="inlineStr"/>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB173" t="inlineStr"/>
@@ -13197,7 +13189,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
@@ -13233,28 +13225,28 @@
       <c r="U174" t="inlineStr"/>
       <c r="V174" t="inlineStr">
         <is>
-          <t>FqhcTmDr</t>
+          <t>SutTmDr</t>
         </is>
       </c>
       <c r="W174" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC)</t>
+          <t>Driving time (min) to Substance Use Treatment (SUT) facility</t>
         </is>
       </c>
       <c r="X174" t="inlineStr"/>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB174" t="inlineStr"/>
@@ -13269,7 +13261,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
@@ -13293,36 +13285,32 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T175" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T175" t="inlineStr"/>
       <c r="U175" t="inlineStr"/>
       <c r="V175" t="inlineStr">
         <is>
-          <t>FqhcTmDr2</t>
+          <t>SutTmDr2</t>
         </is>
       </c>
       <c r="W175" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC), with Impedance factor</t>
+          <t>Driving time to nearest Substance Use Treatment Provider (with impedance)</t>
         </is>
       </c>
       <c r="X175" t="inlineStr"/>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB175" t="inlineStr"/>
@@ -13337,7 +13325,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
@@ -13351,7 +13339,11 @@
       <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr"/>
       <c r="M176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O176" t="inlineStr"/>
       <c r="P176" t="inlineStr"/>
       <c r="Q176" t="inlineStr"/>
@@ -13365,28 +13357,28 @@
       <c r="U176" t="inlineStr"/>
       <c r="V176" t="inlineStr">
         <is>
-          <t>HcvCntDr</t>
+          <t>FqhcCntDr</t>
         </is>
       </c>
       <c r="W176" t="inlineStr">
         <is>
-          <t>Count of HCV Providers</t>
+          <t>Count of Federally Qualified Health Centers (FQHCs) within 30-min drive</t>
         </is>
       </c>
       <c r="X176" t="inlineStr"/>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB176" t="inlineStr"/>
@@ -13401,7 +13393,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
@@ -13415,7 +13407,11 @@
       <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr"/>
       <c r="M177" t="inlineStr"/>
-      <c r="N177" t="inlineStr"/>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O177" t="inlineStr"/>
       <c r="P177" t="inlineStr"/>
       <c r="Q177" t="inlineStr"/>
@@ -13429,28 +13425,28 @@
       <c r="U177" t="inlineStr"/>
       <c r="V177" t="inlineStr">
         <is>
-          <t>HcvMinDis</t>
+          <t>FqhcMinDis</t>
         </is>
       </c>
       <c r="W177" t="inlineStr">
         <is>
-          <t>Distance to nearest HCV Provider</t>
+          <t>Distance (mi) to nearest Federally Qualified Health Centers (FQHC)</t>
         </is>
       </c>
       <c r="X177" t="inlineStr"/>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB177" t="inlineStr"/>
@@ -13465,7 +13461,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
@@ -13479,7 +13475,11 @@
       <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr"/>
       <c r="M178" t="inlineStr"/>
-      <c r="N178" t="inlineStr"/>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O178" t="inlineStr"/>
       <c r="P178" t="inlineStr"/>
       <c r="Q178" t="inlineStr"/>
@@ -13489,32 +13489,36 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T178" t="inlineStr"/>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U178" t="inlineStr"/>
       <c r="V178" t="inlineStr">
         <is>
-          <t>HcvTmDr</t>
+          <t>FqhcTmDr</t>
         </is>
       </c>
       <c r="W178" t="inlineStr">
         <is>
-          <t>Driving time to nearest HCV Provider</t>
+          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC)</t>
         </is>
       </c>
       <c r="X178" t="inlineStr"/>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB178" t="inlineStr"/>
@@ -13529,7 +13533,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
@@ -13553,32 +13557,36 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T179" t="inlineStr"/>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U179" t="inlineStr"/>
       <c r="V179" t="inlineStr">
         <is>
-          <t>HcvTmDr2</t>
+          <t>FqhcTmDr2</t>
         </is>
       </c>
       <c r="W179" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest HCV Testing Facility with impedance</t>
+          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC), with Impedance factor</t>
         </is>
       </c>
       <c r="X179" t="inlineStr"/>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB179" t="inlineStr"/>
@@ -13593,7 +13601,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Spatial access to Syringe Services Programs</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
@@ -13621,28 +13629,28 @@
       <c r="U180" t="inlineStr"/>
       <c r="V180" t="inlineStr">
         <is>
-          <t>SspTmDr</t>
+          <t>HcvCntDr</t>
         </is>
       </c>
       <c r="W180" t="inlineStr">
         <is>
-          <t>Driving time to nearest SSP</t>
+          <t>Count of HCV Providers</t>
         </is>
       </c>
       <c r="X180" t="inlineStr"/>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/nasen_ssp/metadata/Access_SSP.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>NASEN</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>North American Syringe Exchange Network</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB180" t="inlineStr"/>
@@ -13657,7 +13665,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Spatial access to Syringe Services Programs</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
@@ -13685,28 +13693,28 @@
       <c r="U181" t="inlineStr"/>
       <c r="V181" t="inlineStr">
         <is>
-          <t>SspTmDr2</t>
+          <t>HcvMinDis</t>
         </is>
       </c>
       <c r="W181" t="inlineStr">
         <is>
-          <t>Round trip driving time to nearest SSP</t>
+          <t>Distance to nearest HCV Provider</t>
         </is>
       </c>
       <c r="X181" t="inlineStr"/>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/nasen_ssp/metadata/Access_SSP.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>NASEN</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>North American Syringe Exchange Network</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB181" t="inlineStr"/>
@@ -13721,17 +13729,13 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
@@ -13744,33 +13748,37 @@
       <c r="P182" t="inlineStr"/>
       <c r="Q182" t="inlineStr"/>
       <c r="R182" t="inlineStr"/>
-      <c r="S182" t="inlineStr"/>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T182" t="inlineStr"/>
       <c r="U182" t="inlineStr"/>
       <c r="V182" t="inlineStr">
         <is>
-          <t>Ruca1</t>
+          <t>HcvTmDr</t>
         </is>
       </c>
       <c r="W182" t="inlineStr">
         <is>
-          <t>Primary RUCA Code</t>
+          <t>Driving time to nearest HCV Provider</t>
         </is>
       </c>
       <c r="X182" t="inlineStr"/>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB182" t="inlineStr"/>
@@ -13785,17 +13793,13 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr"/>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F183" t="inlineStr"/>
       <c r="G183" t="inlineStr"/>
       <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr"/>
@@ -13808,33 +13812,37 @@
       <c r="P183" t="inlineStr"/>
       <c r="Q183" t="inlineStr"/>
       <c r="R183" t="inlineStr"/>
-      <c r="S183" t="inlineStr"/>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T183" t="inlineStr"/>
       <c r="U183" t="inlineStr"/>
       <c r="V183" t="inlineStr">
         <is>
-          <t>Ruca2</t>
+          <t>HcvTmDr2</t>
         </is>
       </c>
       <c r="W183" t="inlineStr">
         <is>
-          <t>Secondary RUCA Code</t>
+          <t>Driving time (min) to nearest HCV Testing Facility with impedance</t>
         </is>
       </c>
       <c r="X183" t="inlineStr"/>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB183" t="inlineStr"/>
@@ -13849,17 +13857,13 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial access to Syringe Services Programs</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr"/>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F184" t="inlineStr"/>
       <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr"/>
@@ -13872,37 +13876,37 @@
       <c r="P184" t="inlineStr"/>
       <c r="Q184" t="inlineStr"/>
       <c r="R184" t="inlineStr"/>
-      <c r="S184" t="inlineStr"/>
-      <c r="T184" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T184" t="inlineStr"/>
       <c r="U184" t="inlineStr"/>
       <c r="V184" t="inlineStr">
         <is>
-          <t>Rurality</t>
+          <t>SspTmDr</t>
         </is>
       </c>
       <c r="W184" t="inlineStr">
         <is>
-          <t>Urban-Suburban-Rural</t>
+          <t>Driving time to nearest SSP</t>
         </is>
       </c>
       <c r="X184" t="inlineStr"/>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/nasen_ssp/metadata/Access_SSP.md</t>
         </is>
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>NASEN</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>North American Syringe Exchange Network</t>
         </is>
       </c>
       <c r="AB184" t="inlineStr"/>
@@ -13912,12 +13916,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Spatial access to Syringe Services Programs</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
@@ -13929,44 +13933,44 @@
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L185" t="inlineStr"/>
       <c r="M185" t="inlineStr"/>
       <c r="N185" t="inlineStr"/>
       <c r="O185" t="inlineStr"/>
       <c r="P185" t="inlineStr"/>
       <c r="Q185" t="inlineStr"/>
       <c r="R185" t="inlineStr"/>
-      <c r="S185" t="inlineStr"/>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T185" t="inlineStr"/>
       <c r="U185" t="inlineStr"/>
       <c r="V185" t="inlineStr">
         <is>
-          <t>EssnWrkE</t>
+          <t>SspTmDr2</t>
         </is>
       </c>
       <c r="W185" t="inlineStr">
         <is>
-          <t>Count of Essential Workers</t>
+          <t>Round trip driving time to nearest SSP</t>
         </is>
       </c>
       <c r="X185" t="inlineStr"/>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/nasen_ssp/metadata/Access_SSP.md</t>
         </is>
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>NASEN</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>North American Syringe Exchange Network</t>
         </is>
       </c>
       <c r="AB185" t="inlineStr"/>
@@ -13976,69 +13980,61 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr"/>
-      <c r="F186" t="inlineStr"/>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr"/>
-      <c r="L186" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L186" t="inlineStr"/>
       <c r="M186" t="inlineStr"/>
-      <c r="N186" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N186" t="inlineStr"/>
       <c r="O186" t="inlineStr"/>
       <c r="P186" t="inlineStr"/>
-      <c r="Q186" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q186" t="inlineStr"/>
       <c r="R186" t="inlineStr"/>
       <c r="S186" t="inlineStr"/>
       <c r="T186" t="inlineStr"/>
       <c r="U186" t="inlineStr"/>
       <c r="V186" t="inlineStr">
         <is>
-          <t>EssnWrkP</t>
+          <t>Ruca1</t>
         </is>
       </c>
       <c r="W186" t="inlineStr">
         <is>
-          <t>Essential Workers %</t>
+          <t>Primary RUCA Code</t>
         </is>
       </c>
       <c r="X186" t="inlineStr"/>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB186" t="inlineStr"/>
@@ -14048,69 +14044,61 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr"/>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr"/>
-      <c r="L187" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L187" t="inlineStr"/>
       <c r="M187" t="inlineStr"/>
-      <c r="N187" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N187" t="inlineStr"/>
       <c r="O187" t="inlineStr"/>
       <c r="P187" t="inlineStr"/>
-      <c r="Q187" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q187" t="inlineStr"/>
       <c r="R187" t="inlineStr"/>
       <c r="S187" t="inlineStr"/>
       <c r="T187" t="inlineStr"/>
       <c r="U187" t="inlineStr"/>
       <c r="V187" t="inlineStr">
         <is>
-          <t>HghRskP</t>
+          <t>Ruca2</t>
         </is>
       </c>
       <c r="W187" t="inlineStr">
         <is>
-          <t>Employed % - High Risk of Injury</t>
+          <t>Secondary RUCA Code</t>
         </is>
       </c>
       <c r="X187" t="inlineStr"/>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB187" t="inlineStr"/>
@@ -14120,69 +14108,65 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr"/>
-      <c r="F188" t="inlineStr"/>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr"/>
       <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L188" t="inlineStr"/>
       <c r="M188" t="inlineStr"/>
-      <c r="N188" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N188" t="inlineStr"/>
       <c r="O188" t="inlineStr"/>
       <c r="P188" t="inlineStr"/>
-      <c r="Q188" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q188" t="inlineStr"/>
       <c r="R188" t="inlineStr"/>
       <c r="S188" t="inlineStr"/>
-      <c r="T188" t="inlineStr"/>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U188" t="inlineStr"/>
       <c r="V188" t="inlineStr">
         <is>
-          <t>HltCrP</t>
+          <t>Rurality</t>
         </is>
       </c>
       <c r="W188" t="inlineStr">
         <is>
-          <t>Employed % - Health Care</t>
+          <t>Urban-Suburban-Rural</t>
         </is>
       </c>
       <c r="X188" t="inlineStr"/>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB188" t="inlineStr"/>
@@ -14215,30 +14199,22 @@
         </is>
       </c>
       <c r="M189" t="inlineStr"/>
-      <c r="N189" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N189" t="inlineStr"/>
       <c r="O189" t="inlineStr"/>
       <c r="P189" t="inlineStr"/>
-      <c r="Q189" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q189" t="inlineStr"/>
       <c r="R189" t="inlineStr"/>
       <c r="S189" t="inlineStr"/>
       <c r="T189" t="inlineStr"/>
       <c r="U189" t="inlineStr"/>
       <c r="V189" t="inlineStr">
         <is>
-          <t>RetailP</t>
+          <t>EssnWrkE</t>
         </is>
       </c>
       <c r="W189" t="inlineStr">
         <is>
-          <t>Employed % - Retail</t>
+          <t>Count of Essential Workers</t>
         </is>
       </c>
       <c r="X189" t="inlineStr"/>
@@ -14305,12 +14281,12 @@
       <c r="U190" t="inlineStr"/>
       <c r="V190" t="inlineStr">
         <is>
-          <t>TotWrkE</t>
+          <t>EssnWrkP</t>
         </is>
       </c>
       <c r="W190" t="inlineStr">
         <is>
-          <t>Count of Working Population</t>
+          <t>Essential Workers %</t>
         </is>
       </c>
       <c r="X190" t="inlineStr"/>
@@ -14341,7 +14317,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
@@ -14359,38 +14335,46 @@
         </is>
       </c>
       <c r="M191" t="inlineStr"/>
-      <c r="N191" t="inlineStr"/>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O191" t="inlineStr"/>
       <c r="P191" t="inlineStr"/>
-      <c r="Q191" t="inlineStr"/>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R191" t="inlineStr"/>
       <c r="S191" t="inlineStr"/>
       <c r="T191" t="inlineStr"/>
       <c r="U191" t="inlineStr"/>
       <c r="V191" t="inlineStr">
         <is>
-          <t>ForDqP</t>
+          <t>HghRskP</t>
         </is>
       </c>
       <c r="W191" t="inlineStr">
         <is>
-          <t>Foreclosure &amp; Delinquency %</t>
+          <t>Employed % - High Risk of Injury</t>
         </is>
       </c>
       <c r="X191" t="inlineStr"/>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB191" t="inlineStr"/>
@@ -14405,7 +14389,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
@@ -14423,38 +14407,46 @@
         </is>
       </c>
       <c r="M192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O192" t="inlineStr"/>
       <c r="P192" t="inlineStr"/>
-      <c r="Q192" t="inlineStr"/>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R192" t="inlineStr"/>
       <c r="S192" t="inlineStr"/>
       <c r="T192" t="inlineStr"/>
       <c r="U192" t="inlineStr"/>
       <c r="V192" t="inlineStr">
         <is>
-          <t>ForDqTot</t>
+          <t>HltCrP</t>
         </is>
       </c>
       <c r="W192" t="inlineStr">
         <is>
-          <t>Foreclosure &amp; Delinquency Count</t>
+          <t>Employed % - Health Care</t>
         </is>
       </c>
       <c r="X192" t="inlineStr"/>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB192" t="inlineStr"/>
@@ -14469,17 +14461,13 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr"/>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr"/>
@@ -14509,28 +14497,28 @@
       <c r="U193" t="inlineStr"/>
       <c r="V193" t="inlineStr">
         <is>
-          <t>GiniCoeff</t>
+          <t>RetailP</t>
         </is>
       </c>
       <c r="W193" t="inlineStr">
         <is>
-          <t>Income Inequality (Gini Coefficient)</t>
+          <t>Employed % - Retail</t>
         </is>
       </c>
       <c r="X193" t="inlineStr"/>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB193" t="inlineStr"/>
@@ -14545,7 +14533,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Internet Access</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
@@ -14557,44 +14545,52 @@
       <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr"/>
-      <c r="L194" t="inlineStr"/>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N194" t="inlineStr"/>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr"/>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O194" t="inlineStr"/>
       <c r="P194" t="inlineStr"/>
-      <c r="Q194" t="inlineStr"/>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R194" t="inlineStr"/>
       <c r="S194" t="inlineStr"/>
       <c r="T194" t="inlineStr"/>
       <c r="U194" t="inlineStr"/>
       <c r="V194" t="inlineStr">
         <is>
-          <t>NoIntP</t>
+          <t>TotWrkE</t>
         </is>
       </c>
       <c r="W194" t="inlineStr">
         <is>
-          <t>Households without Internet Access %</t>
+          <t>Count of Working Population</t>
         </is>
       </c>
       <c r="X194" t="inlineStr"/>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Internet_Access.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>ACS 2019</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>American Community Survey 2015-2019 5-Year Estimate</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB194" t="inlineStr"/>
@@ -14609,17 +14605,13 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
+          <t>Great Recession Foreclosure Rate</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr"/>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr"/>
       <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr"/>
@@ -14631,46 +14623,38 @@
         </is>
       </c>
       <c r="M195" t="inlineStr"/>
-      <c r="N195" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N195" t="inlineStr"/>
       <c r="O195" t="inlineStr"/>
       <c r="P195" t="inlineStr"/>
-      <c r="Q195" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q195" t="inlineStr"/>
       <c r="R195" t="inlineStr"/>
       <c r="S195" t="inlineStr"/>
       <c r="T195" t="inlineStr"/>
       <c r="U195" t="inlineStr"/>
       <c r="V195" t="inlineStr">
         <is>
-          <t>MedInc</t>
+          <t>ForDqP</t>
         </is>
       </c>
       <c r="W195" t="inlineStr">
         <is>
-          <t>Median Income</t>
+          <t>Foreclosure &amp; Delinquency %</t>
         </is>
       </c>
       <c r="X195" t="inlineStr"/>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
         </is>
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>HUD 2018; ACS 2012, 2018</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB195" t="inlineStr"/>
@@ -14685,17 +14669,13 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
+          <t>Great Recession Foreclosure Rate</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr"/>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr"/>
       <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr"/>
@@ -14707,46 +14687,38 @@
         </is>
       </c>
       <c r="M196" t="inlineStr"/>
-      <c r="N196" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N196" t="inlineStr"/>
       <c r="O196" t="inlineStr"/>
       <c r="P196" t="inlineStr"/>
-      <c r="Q196" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q196" t="inlineStr"/>
       <c r="R196" t="inlineStr"/>
       <c r="S196" t="inlineStr"/>
       <c r="T196" t="inlineStr"/>
       <c r="U196" t="inlineStr"/>
       <c r="V196" t="inlineStr">
         <is>
-          <t>PciE</t>
+          <t>ForDqTot</t>
         </is>
       </c>
       <c r="W196" t="inlineStr">
         <is>
-          <t>Per Capita Income</t>
+          <t>Foreclosure &amp; Delinquency Count</t>
         </is>
       </c>
       <c r="X196" t="inlineStr"/>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
         </is>
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>HUD 2018; ACS 2012, 2018</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB196" t="inlineStr"/>
@@ -14761,24 +14733,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>Great Recession Foreclosure Rate</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr"/>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
         <is>
           <t>x</t>
@@ -14810,35 +14770,31 @@
       <c r="R197" t="inlineStr"/>
       <c r="S197" t="inlineStr"/>
       <c r="T197" t="inlineStr"/>
-      <c r="U197" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="U197" t="inlineStr"/>
       <c r="V197" t="inlineStr">
         <is>
-          <t>PovP</t>
+          <t>GiniCoeff</t>
         </is>
       </c>
       <c r="W197" t="inlineStr">
         <is>
-          <t>Poverty %</t>
+          <t>Income Inequality (Gini Coefficient)</t>
         </is>
       </c>
       <c r="X197" t="inlineStr"/>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
         </is>
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>HUD 2018; ACS 2012, 2018</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB197" t="inlineStr"/>
@@ -14853,84 +14809,56 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>Internet Access</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr"/>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr"/>
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr"/>
-      <c r="L198" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M198" t="inlineStr"/>
-      <c r="N198" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr"/>
       <c r="O198" t="inlineStr"/>
       <c r="P198" t="inlineStr"/>
-      <c r="Q198" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q198" t="inlineStr"/>
       <c r="R198" t="inlineStr"/>
       <c r="S198" t="inlineStr"/>
       <c r="T198" t="inlineStr"/>
-      <c r="U198" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="U198" t="inlineStr"/>
       <c r="V198" t="inlineStr">
         <is>
-          <t>UnempP</t>
+          <t>NoIntP</t>
         </is>
       </c>
       <c r="W198" t="inlineStr">
         <is>
-          <t>Unemployment %</t>
+          <t>Households without Internet Access %</t>
         </is>
       </c>
       <c r="X198" t="inlineStr"/>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Internet_Access.md</t>
         </is>
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>ACS 2019</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>American Community Survey 2015-2019 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB198" t="inlineStr"/>
@@ -14940,65 +14868,73 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>SDOH Indices &amp; Typology</t>
+          <t>Poverty, Income, Gini Coefficient</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr"/>
-      <c r="F199" t="inlineStr"/>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G199" t="inlineStr"/>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr"/>
-      <c r="L199" t="inlineStr"/>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M199" t="inlineStr"/>
-      <c r="N199" t="inlineStr"/>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O199" t="inlineStr"/>
       <c r="P199" t="inlineStr"/>
-      <c r="Q199" t="inlineStr"/>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R199" t="inlineStr"/>
       <c r="S199" t="inlineStr"/>
-      <c r="T199" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T199" t="inlineStr"/>
       <c r="U199" t="inlineStr"/>
       <c r="V199" t="inlineStr">
         <is>
-          <t>LimMobInd</t>
+          <t>MedInc</t>
         </is>
       </c>
       <c r="W199" t="inlineStr">
         <is>
-          <t>Limited Moblility Index</t>
+          <t>Median Income</t>
         </is>
       </c>
       <c r="X199" t="inlineStr"/>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB199" t="inlineStr"/>
@@ -15008,65 +14944,73 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>SDOH Indices &amp; Typology</t>
+          <t>Poverty, Income, Gini Coefficient</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr"/>
-      <c r="F200" t="inlineStr"/>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G200" t="inlineStr"/>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr"/>
-      <c r="L200" t="inlineStr"/>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M200" t="inlineStr"/>
-      <c r="N200" t="inlineStr"/>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O200" t="inlineStr"/>
       <c r="P200" t="inlineStr"/>
-      <c r="Q200" t="inlineStr"/>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R200" t="inlineStr"/>
       <c r="S200" t="inlineStr"/>
-      <c r="T200" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T200" t="inlineStr"/>
       <c r="U200" t="inlineStr"/>
       <c r="V200" t="inlineStr">
         <is>
-          <t>MicaInd</t>
+          <t>PciE</t>
         </is>
       </c>
       <c r="W200" t="inlineStr">
         <is>
-          <t>Mixed Immigrant Cohesion and Accesibility (MICA) Index</t>
+          <t>Per Capita Income</t>
         </is>
       </c>
       <c r="X200" t="inlineStr"/>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB200" t="inlineStr"/>
@@ -15076,61 +15020,89 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>SDOH Indices &amp; Typology</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr"/>
-      <c r="D201" t="inlineStr"/>
-      <c r="E201" t="inlineStr"/>
-      <c r="F201" t="inlineStr"/>
+          <t>Poverty, Income, Gini Coefficient</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G201" t="inlineStr"/>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="H201" t="inlineStr"/>
       <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr"/>
-      <c r="L201" t="inlineStr"/>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M201" t="inlineStr"/>
-      <c r="N201" t="inlineStr"/>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O201" t="inlineStr"/>
       <c r="P201" t="inlineStr"/>
-      <c r="Q201" t="inlineStr"/>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R201" t="inlineStr"/>
       <c r="S201" t="inlineStr"/>
       <c r="T201" t="inlineStr"/>
-      <c r="U201" t="inlineStr"/>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="V201" t="inlineStr">
         <is>
-          <t>NeighbTyp</t>
+          <t>PovP</t>
         </is>
       </c>
       <c r="W201" t="inlineStr">
         <is>
-          <t>Neighborhood Type</t>
+          <t>Poverty %</t>
         </is>
       </c>
       <c r="X201" t="inlineStr"/>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB201" t="inlineStr"/>
@@ -15140,65 +15112,89 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>SDOH Indices &amp; Typology</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr"/>
-      <c r="D202" t="inlineStr"/>
-      <c r="E202" t="inlineStr"/>
-      <c r="F202" t="inlineStr"/>
+          <t>Poverty, Income, Gini Coefficient</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G202" t="inlineStr"/>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="H202" t="inlineStr"/>
       <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr"/>
-      <c r="L202" t="inlineStr"/>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M202" t="inlineStr"/>
-      <c r="N202" t="inlineStr"/>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O202" t="inlineStr"/>
       <c r="P202" t="inlineStr"/>
-      <c r="Q202" t="inlineStr"/>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R202" t="inlineStr"/>
       <c r="S202" t="inlineStr"/>
-      <c r="T202" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="U202" t="inlineStr"/>
+      <c r="T202" t="inlineStr"/>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="V202" t="inlineStr">
         <is>
-          <t>SocEcAdvIn</t>
+          <t>UnempP</t>
         </is>
       </c>
       <c r="W202" t="inlineStr">
         <is>
-          <t>Socioeconomic Advantage Index</t>
+          <t>Unemployment %</t>
         </is>
       </c>
       <c r="X202" t="inlineStr"/>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB202" t="inlineStr"/>
@@ -15245,12 +15241,12 @@
       <c r="U203" t="inlineStr"/>
       <c r="V203" t="inlineStr">
         <is>
-          <t>UrbCoreInd</t>
+          <t>LimMobInd</t>
         </is>
       </c>
       <c r="W203" t="inlineStr">
         <is>
-          <t>Urban Core Opportunity Index</t>
+          <t>Limited Moblility Index</t>
         </is>
       </c>
       <c r="X203" t="inlineStr"/>
@@ -15281,7 +15277,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>SDOH Indices &amp; Typology</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
@@ -15289,56 +15285,52 @@
       <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr"/>
       <c r="G204" t="inlineStr"/>
-      <c r="H204" t="inlineStr"/>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr"/>
-      <c r="L204" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L204" t="inlineStr"/>
       <c r="M204" t="inlineStr"/>
-      <c r="N204" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N204" t="inlineStr"/>
       <c r="O204" t="inlineStr"/>
-      <c r="P204" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P204" t="inlineStr"/>
       <c r="Q204" t="inlineStr"/>
       <c r="R204" t="inlineStr"/>
       <c r="S204" t="inlineStr"/>
-      <c r="T204" t="inlineStr"/>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U204" t="inlineStr"/>
       <c r="V204" t="inlineStr">
         <is>
-          <t>SviSmryRnk</t>
+          <t>MicaInd</t>
         </is>
       </c>
       <c r="W204" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) Summary Ranking</t>
+          <t>Mixed Immigrant Cohesion and Accesibility (MICA) Index</t>
         </is>
       </c>
       <c r="X204" t="inlineStr"/>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
         </is>
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AB204" t="inlineStr"/>
@@ -15353,7 +15345,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>SDOH Indices &amp; Typology</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
@@ -15361,60 +15353,48 @@
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr"/>
       <c r="G205" t="inlineStr"/>
-      <c r="H205" t="inlineStr"/>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="I205" t="inlineStr"/>
       <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr"/>
-      <c r="L205" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L205" t="inlineStr"/>
       <c r="M205" t="inlineStr"/>
-      <c r="N205" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N205" t="inlineStr"/>
       <c r="O205" t="inlineStr"/>
-      <c r="P205" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P205" t="inlineStr"/>
       <c r="Q205" t="inlineStr"/>
       <c r="R205" t="inlineStr"/>
       <c r="S205" t="inlineStr"/>
-      <c r="T205" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T205" t="inlineStr"/>
       <c r="U205" t="inlineStr"/>
       <c r="V205" t="inlineStr">
         <is>
-          <t>SviTh1</t>
+          <t>NeighbTyp</t>
         </is>
       </c>
       <c r="W205" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 1</t>
+          <t>Neighborhood Type</t>
         </is>
       </c>
       <c r="X205" t="inlineStr"/>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
         </is>
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AB205" t="inlineStr"/>
@@ -15429,7 +15409,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>SDOH Indices &amp; Typology</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
@@ -15437,56 +15417,52 @@
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr"/>
       <c r="G206" t="inlineStr"/>
-      <c r="H206" t="inlineStr"/>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="I206" t="inlineStr"/>
       <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr"/>
-      <c r="L206" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L206" t="inlineStr"/>
       <c r="M206" t="inlineStr"/>
-      <c r="N206" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N206" t="inlineStr"/>
       <c r="O206" t="inlineStr"/>
-      <c r="P206" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P206" t="inlineStr"/>
       <c r="Q206" t="inlineStr"/>
       <c r="R206" t="inlineStr"/>
       <c r="S206" t="inlineStr"/>
-      <c r="T206" t="inlineStr"/>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U206" t="inlineStr"/>
       <c r="V206" t="inlineStr">
         <is>
-          <t>SviTh2</t>
+          <t>SocEcAdvIn</t>
         </is>
       </c>
       <c r="W206" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 2</t>
+          <t>Socioeconomic Advantage Index</t>
         </is>
       </c>
       <c r="X206" t="inlineStr"/>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
         </is>
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AB206" t="inlineStr"/>
@@ -15501,7 +15477,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>SDOH Indices &amp; Typology</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
@@ -15509,56 +15485,52 @@
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr"/>
       <c r="G207" t="inlineStr"/>
-      <c r="H207" t="inlineStr"/>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="I207" t="inlineStr"/>
       <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr"/>
-      <c r="L207" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L207" t="inlineStr"/>
       <c r="M207" t="inlineStr"/>
-      <c r="N207" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N207" t="inlineStr"/>
       <c r="O207" t="inlineStr"/>
-      <c r="P207" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P207" t="inlineStr"/>
       <c r="Q207" t="inlineStr"/>
       <c r="R207" t="inlineStr"/>
       <c r="S207" t="inlineStr"/>
-      <c r="T207" t="inlineStr"/>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U207" t="inlineStr"/>
       <c r="V207" t="inlineStr">
         <is>
-          <t>SviTh3</t>
+          <t>UrbCoreInd</t>
         </is>
       </c>
       <c r="W207" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 3</t>
+          <t>Urban Core Opportunity Index</t>
         </is>
       </c>
       <c r="X207" t="inlineStr"/>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
         </is>
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AB207" t="inlineStr"/>
@@ -15605,20 +15577,16 @@
       <c r="Q208" t="inlineStr"/>
       <c r="R208" t="inlineStr"/>
       <c r="S208" t="inlineStr"/>
-      <c r="T208" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T208" t="inlineStr"/>
       <c r="U208" t="inlineStr"/>
       <c r="V208" t="inlineStr">
         <is>
-          <t>SviTh4</t>
+          <t>SviSmryRnk</t>
         </is>
       </c>
       <c r="W208" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 4</t>
+          <t>Social Vulnerability Index (SVI) Summary Ranking</t>
         </is>
       </c>
       <c r="X208" t="inlineStr"/>
@@ -15640,6 +15608,302 @@
       <c r="AB208" t="inlineStr"/>
       <c r="AC208" t="inlineStr"/>
       <c r="AD208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr"/>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="inlineStr"/>
+      <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr"/>
+      <c r="J209" t="inlineStr"/>
+      <c r="K209" t="inlineStr"/>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr"/>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr"/>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr"/>
+      <c r="R209" t="inlineStr"/>
+      <c r="S209" t="inlineStr"/>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr"/>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>SviTh1</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 1</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr"/>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB209" t="inlineStr"/>
+      <c r="AC209" t="inlineStr"/>
+      <c r="AD209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr"/>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="inlineStr"/>
+      <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr"/>
+      <c r="J210" t="inlineStr"/>
+      <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr"/>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr"/>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr"/>
+      <c r="R210" t="inlineStr"/>
+      <c r="S210" t="inlineStr"/>
+      <c r="T210" t="inlineStr"/>
+      <c r="U210" t="inlineStr"/>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>SviTh2</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 2</t>
+        </is>
+      </c>
+      <c r="X210" t="inlineStr"/>
+      <c r="Y210" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB210" t="inlineStr"/>
+      <c r="AC210" t="inlineStr"/>
+      <c r="AD210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr"/>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr"/>
+      <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr"/>
+      <c r="K211" t="inlineStr"/>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr"/>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr"/>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr"/>
+      <c r="R211" t="inlineStr"/>
+      <c r="S211" t="inlineStr"/>
+      <c r="T211" t="inlineStr"/>
+      <c r="U211" t="inlineStr"/>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>SviTh3</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 3</t>
+        </is>
+      </c>
+      <c r="X211" t="inlineStr"/>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB211" t="inlineStr"/>
+      <c r="AC211" t="inlineStr"/>
+      <c r="AD211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr"/>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="inlineStr"/>
+      <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr"/>
+      <c r="J212" t="inlineStr"/>
+      <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr"/>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr"/>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr"/>
+      <c r="R212" t="inlineStr"/>
+      <c r="S212" t="inlineStr"/>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr"/>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>SviTh4</t>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 4</t>
+        </is>
+      </c>
+      <c r="X212" t="inlineStr"/>
+      <c r="Y212" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB212" t="inlineStr"/>
+      <c r="AC212" t="inlineStr"/>
+      <c r="AD212" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/src/reference/data-dictionaries/T_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/T_Dict.xlsx
@@ -5050,7 +5050,7 @@
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>Count Black/African American Populationw</t>
+          <t>Count Black/African American Population</t>
         </is>
       </c>
       <c r="X57" t="inlineStr"/>
@@ -5142,7 +5142,7 @@
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>% Black/African American Populationw</t>
+          <t>% Black/African American Population</t>
         </is>
       </c>
       <c r="X58" t="inlineStr"/>

--- a/docs/src/reference/data-dictionaries/T_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/T_Dict.xlsx
@@ -3022,7 +3022,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>% Population: Age 15-44</t>
+          <t>Population: Age 15-44 (count)</t>
         </is>
       </c>
       <c r="X33" t="inlineStr"/>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>% Population: Age 15-44</t>
+          <t>% Population: Age 15-44 (percent)</t>
         </is>
       </c>
       <c r="X34" t="inlineStr"/>
@@ -4090,7 +4090,7 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>% Population: Age 65+</t>
+          <t>Population: Age 65+ (count)</t>
         </is>
       </c>
       <c r="X46" t="inlineStr"/>
@@ -4182,7 +4182,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>% Population: Age 65+</t>
+          <t>% Population: Age 65+ (percent)</t>
         </is>
       </c>
       <c r="X47" t="inlineStr"/>
@@ -8946,7 +8946,7 @@
       </c>
       <c r="W111" t="inlineStr">
         <is>
-          <t>Biking Time (min) to nearest Buprenorphine Provider</t>
+          <t>Biking Time (min) to nearest Buprenorphine Provider (tract/ZIP)</t>
         </is>
       </c>
       <c r="X111" t="inlineStr"/>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="W112" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Buprenorphine Provider</t>
+          <t>Driving Time (min) to nearest Buprenorphine Provider (tract/ZIP)</t>
         </is>
       </c>
       <c r="X112" t="inlineStr"/>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="W114" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Buprenorphine Provider</t>
+          <t>Walking Time (min) to nearest Buprenorphine Provider (tract/ZIP)</t>
         </is>
       </c>
       <c r="X114" t="inlineStr"/>
@@ -10078,7 +10078,7 @@
       </c>
       <c r="W127" t="inlineStr">
         <is>
-          <t>Biking Time (min) to nearest Methadone Provider</t>
+          <t>Biking Time (min) to nearest Methadone Provider (tract/ZIP)</t>
         </is>
       </c>
       <c r="X127" t="inlineStr"/>
@@ -10150,7 +10150,7 @@
       </c>
       <c r="W128" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Methadone Provider</t>
+          <t>Driving Time (min) to nearest Methadone Provider (tract/ZIP)</t>
         </is>
       </c>
       <c r="X128" t="inlineStr"/>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="W130" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Methadone Provider</t>
+          <t>Walking Time (min) to nearest Methadone Provider (tract/ZIP)</t>
         </is>
       </c>
       <c r="X130" t="inlineStr"/>
@@ -11230,7 +11230,7 @@
       </c>
       <c r="W144" t="inlineStr">
         <is>
-          <t>Biking Time (min) to nearest Naltrexone Provider</t>
+          <t>Biking Time (min) to nearest Naltrexone Provider (tract/ZIP)</t>
         </is>
       </c>
       <c r="X144" t="inlineStr"/>
@@ -11302,7 +11302,7 @@
       </c>
       <c r="W145" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Naltrexone Provider</t>
+          <t>Driving Time (min) to nearest Naltrexone Provider (tract/ZIP)</t>
         </is>
       </c>
       <c r="X145" t="inlineStr"/>
@@ -11438,7 +11438,7 @@
       </c>
       <c r="W147" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Naltrexone Provider</t>
+          <t>Walking Time (min) to nearest Naltrexone Provider (tract/ZIP)</t>
         </is>
       </c>
       <c r="X147" t="inlineStr"/>
@@ -11902,7 +11902,7 @@
       </c>
       <c r="W154" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP)</t>
+          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP) (tract/ZIP)</t>
         </is>
       </c>
       <c r="X154" t="inlineStr"/>
@@ -12686,7 +12686,7 @@
       </c>
       <c r="W166" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Mental Health Provider</t>
+          <t>Driving Time (min) to nearest Mental Health Provider (tract/ZIP)</t>
         </is>
       </c>
       <c r="X166" t="inlineStr"/>

--- a/docs/src/reference/data-dictionaries/T_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/T_Dict.xlsx
@@ -9086,7 +9086,7 @@
       </c>
       <c r="W113" t="inlineStr">
         <is>
-          <t>Driving time to nearest buprenorphine provider (with impedance)</t>
+          <t>Driving Time (min) to Nearest Buprenorphine Provider (with impedance)</t>
         </is>
       </c>
       <c r="X113" t="inlineStr"/>
@@ -10218,7 +10218,7 @@
       </c>
       <c r="W129" t="inlineStr">
         <is>
-          <t>Driving time to nearest methadone provider (with impedance)</t>
+          <t>Driving Time (min) to Nearest Methadone Provider (with impedance)</t>
         </is>
       </c>
       <c r="X129" t="inlineStr"/>
@@ -11366,7 +11366,7 @@
       </c>
       <c r="W146" t="inlineStr">
         <is>
-          <t>Driving time to nearest naltrexone provider (with impedance)</t>
+          <t>Driving Time (min) to Nearest Naltrexone Provider (with impedance)</t>
         </is>
       </c>
       <c r="X146" t="inlineStr"/>
@@ -11966,7 +11966,7 @@
       </c>
       <c r="W155" t="inlineStr">
         <is>
-          <t>Driving time to nearest OTP (impedance-adjusted)</t>
+          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP), with impedance</t>
         </is>
       </c>
       <c r="X155" t="inlineStr"/>

--- a/docs/src/reference/data-dictionaries/T_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/T_Dict.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD212"/>
+  <dimension ref="A1:AD213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -10403,11 +10403,7 @@
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr"/>
       <c r="P132" t="inlineStr"/>
       <c r="Q132" t="inlineStr"/>
@@ -10417,16 +10413,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T132" t="inlineStr"/>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U132" t="inlineStr"/>
       <c r="V132" t="inlineStr">
         <is>
-          <t>NaltCntBk30</t>
+          <t>MoudTyp</t>
         </is>
       </c>
       <c r="W132" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (30-min bike)</t>
+          <t>MOUD Types Within 30-Min Drive (impedance, adjusted)</t>
         </is>
       </c>
       <c r="X132" t="inlineStr"/>
@@ -10489,12 +10489,12 @@
       <c r="U133" t="inlineStr"/>
       <c r="V133" t="inlineStr">
         <is>
-          <t>NaltCntBk60</t>
+          <t>NaltCntBk30</t>
         </is>
       </c>
       <c r="W133" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (60-min bike)</t>
+          <t>Count of Naltrexone Providers (30-min bike)</t>
         </is>
       </c>
       <c r="X133" t="inlineStr"/>
@@ -10557,12 +10557,12 @@
       <c r="U134" t="inlineStr"/>
       <c r="V134" t="inlineStr">
         <is>
-          <t>NaltCntDr30</t>
+          <t>NaltCntBk60</t>
         </is>
       </c>
       <c r="W134" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (30-min drive)</t>
+          <t>Count of Naltrexone Providers (60-min bike)</t>
         </is>
       </c>
       <c r="X134" t="inlineStr"/>
@@ -10607,7 +10607,11 @@
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr"/>
       <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O135" t="inlineStr"/>
       <c r="P135" t="inlineStr"/>
       <c r="Q135" t="inlineStr"/>
@@ -10621,12 +10625,12 @@
       <c r="U135" t="inlineStr"/>
       <c r="V135" t="inlineStr">
         <is>
-          <t>NaltCntDr60</t>
+          <t>NaltCntDr30</t>
         </is>
       </c>
       <c r="W135" t="inlineStr">
         <is>
-          <t>Count of naltrexone providers (drive)</t>
+          <t>Count of Naltrexone Providers (30-min drive)</t>
         </is>
       </c>
       <c r="X135" t="inlineStr"/>
@@ -10671,11 +10675,7 @@
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr"/>
       <c r="P136" t="inlineStr"/>
       <c r="Q136" t="inlineStr"/>
@@ -10689,12 +10689,12 @@
       <c r="U136" t="inlineStr"/>
       <c r="V136" t="inlineStr">
         <is>
-          <t>NaltCntWk30</t>
+          <t>NaltCntDr60</t>
         </is>
       </c>
       <c r="W136" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (30-min walk)</t>
+          <t>Count of naltrexone providers (drive)</t>
         </is>
       </c>
       <c r="X136" t="inlineStr"/>
@@ -10757,12 +10757,12 @@
       <c r="U137" t="inlineStr"/>
       <c r="V137" t="inlineStr">
         <is>
-          <t>NaltCntWk60</t>
+          <t>NaltCntWk30</t>
         </is>
       </c>
       <c r="W137" t="inlineStr">
         <is>
-          <t>Count of Naltrexone Providers (60-min walk)</t>
+          <t>Count of Naltrexone Providers (30-min walk)</t>
         </is>
       </c>
       <c r="X137" t="inlineStr"/>
@@ -10807,7 +10807,11 @@
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr"/>
       <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O138" t="inlineStr"/>
       <c r="P138" t="inlineStr"/>
       <c r="Q138" t="inlineStr"/>
@@ -10821,12 +10825,12 @@
       <c r="U138" t="inlineStr"/>
       <c r="V138" t="inlineStr">
         <is>
-          <t>NaltFca30</t>
+          <t>NaltCntWk60</t>
         </is>
       </c>
       <c r="W138" t="inlineStr">
         <is>
-          <t>Two-step floating catchment area (2SFCA) measure of access to Naltrexone within a 30-minute drive</t>
+          <t>Count of Naltrexone Providers (60-min walk)</t>
         </is>
       </c>
       <c r="X138" t="inlineStr"/>
@@ -10885,12 +10889,12 @@
       <c r="U139" t="inlineStr"/>
       <c r="V139" t="inlineStr">
         <is>
-          <t>NaltFca60</t>
+          <t>NaltFca30</t>
         </is>
       </c>
       <c r="W139" t="inlineStr">
         <is>
-          <t>Two-step floating catchment area (2SFCA) measure of access to Naltrexone within a 60-minute drive</t>
+          <t>Two-step floating catchment area (2SFCA) measure of access to Naltrexone within a 30-minute drive</t>
         </is>
       </c>
       <c r="X139" t="inlineStr"/>
@@ -10935,11 +10939,7 @@
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr"/>
       <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr"/>
       <c r="P140" t="inlineStr"/>
       <c r="Q140" t="inlineStr"/>
@@ -10953,12 +10953,12 @@
       <c r="U140" t="inlineStr"/>
       <c r="V140" t="inlineStr">
         <is>
-          <t>NaltMinDis</t>
+          <t>NaltFca60</t>
         </is>
       </c>
       <c r="W140" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Naltrexone Provider</t>
+          <t>Two-step floating catchment area (2SFCA) measure of access to Naltrexone within a 60-minute drive</t>
         </is>
       </c>
       <c r="X140" t="inlineStr"/>
@@ -11021,12 +11021,12 @@
       <c r="U141" t="inlineStr"/>
       <c r="V141" t="inlineStr">
         <is>
-          <t>NaltRm30</t>
+          <t>NaltMinDis</t>
         </is>
       </c>
       <c r="W141" t="inlineStr">
         <is>
-          <t>Naltrexone access 30 minutes (RAAM)</t>
+          <t>Distance (mi) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X141" t="inlineStr"/>
@@ -11089,12 +11089,12 @@
       <c r="U142" t="inlineStr"/>
       <c r="V142" t="inlineStr">
         <is>
-          <t>NaltRm60</t>
+          <t>NaltRm30</t>
         </is>
       </c>
       <c r="W142" t="inlineStr">
         <is>
-          <t>Naltrexone access 60 minutes (RAAM)</t>
+          <t>Naltrexone access 30 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X142" t="inlineStr"/>
@@ -11148,17 +11148,21 @@
       <c r="P143" t="inlineStr"/>
       <c r="Q143" t="inlineStr"/>
       <c r="R143" t="inlineStr"/>
-      <c r="S143" t="inlineStr"/>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T143" t="inlineStr"/>
       <c r="U143" t="inlineStr"/>
       <c r="V143" t="inlineStr">
         <is>
-          <t>NaltRm90</t>
+          <t>NaltRm60</t>
         </is>
       </c>
       <c r="W143" t="inlineStr">
         <is>
-          <t>Naltrexone access 90 minutes (RAAM)</t>
+          <t>Naltrexone access 60 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X143" t="inlineStr"/>
@@ -11212,25 +11216,17 @@
       <c r="P144" t="inlineStr"/>
       <c r="Q144" t="inlineStr"/>
       <c r="R144" t="inlineStr"/>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="T144" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S144" t="inlineStr"/>
+      <c r="T144" t="inlineStr"/>
       <c r="U144" t="inlineStr"/>
       <c r="V144" t="inlineStr">
         <is>
-          <t>NaltTmBk</t>
+          <t>NaltRm90</t>
         </is>
       </c>
       <c r="W144" t="inlineStr">
         <is>
-          <t>Biking Time (min) to nearest Naltrexone Provider (tract/ZIP)</t>
+          <t>Naltrexone access 90 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X144" t="inlineStr"/>
@@ -11297,12 +11293,12 @@
       <c r="U145" t="inlineStr"/>
       <c r="V145" t="inlineStr">
         <is>
-          <t>NaltTmDr</t>
+          <t>NaltTmBk</t>
         </is>
       </c>
       <c r="W145" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Naltrexone Provider (tract/ZIP)</t>
+          <t>Biking Time (min) to nearest Naltrexone Provider (tract/ZIP)</t>
         </is>
       </c>
       <c r="X145" t="inlineStr"/>
@@ -11347,7 +11343,11 @@
       <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr"/>
       <c r="M146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O146" t="inlineStr"/>
       <c r="P146" t="inlineStr"/>
       <c r="Q146" t="inlineStr"/>
@@ -11357,16 +11357,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T146" t="inlineStr"/>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U146" t="inlineStr"/>
       <c r="V146" t="inlineStr">
         <is>
-          <t>NaltTmDr2</t>
+          <t>NaltTmDr</t>
         </is>
       </c>
       <c r="W146" t="inlineStr">
         <is>
-          <t>Driving Time (min) to Nearest Naltrexone Provider (with impedance)</t>
+          <t>Driving Time (min) to nearest Naltrexone Provider (tract/ZIP)</t>
         </is>
       </c>
       <c r="X146" t="inlineStr"/>
@@ -11411,11 +11415,7 @@
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr"/>
-      <c r="N147" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N147" t="inlineStr"/>
       <c r="O147" t="inlineStr"/>
       <c r="P147" t="inlineStr"/>
       <c r="Q147" t="inlineStr"/>
@@ -11425,20 +11425,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T147" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T147" t="inlineStr"/>
       <c r="U147" t="inlineStr"/>
       <c r="V147" t="inlineStr">
         <is>
-          <t>NaltTmWk</t>
+          <t>NaltTmDr2</t>
         </is>
       </c>
       <c r="W147" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Naltrexone Provider (tract/ZIP)</t>
+          <t>Driving Time (min) to Nearest Naltrexone Provider (with impedance)</t>
         </is>
       </c>
       <c r="X147" t="inlineStr"/>
@@ -11483,12 +11479,12 @@
       <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr"/>
       <c r="M148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
-      <c r="O148" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr"/>
       <c r="P148" t="inlineStr"/>
       <c r="Q148" t="inlineStr"/>
       <c r="R148" t="inlineStr"/>
@@ -11497,16 +11493,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T148" t="inlineStr"/>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U148" t="inlineStr"/>
       <c r="V148" t="inlineStr">
         <is>
-          <t>OtpCntDr</t>
+          <t>NaltTmWk</t>
         </is>
       </c>
       <c r="W148" t="inlineStr">
         <is>
-          <t>Count of Opioid Treatment Programs (OTP) (30-min drive)</t>
+          <t>Walking Time (min) to nearest Naltrexone Provider (tract/ZIP)</t>
         </is>
       </c>
       <c r="X148" t="inlineStr"/>
@@ -11552,7 +11552,11 @@
       <c r="L149" t="inlineStr"/>
       <c r="M149" t="inlineStr"/>
       <c r="N149" t="inlineStr"/>
-      <c r="O149" t="inlineStr"/>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr"/>
       <c r="Q149" t="inlineStr"/>
       <c r="R149" t="inlineStr"/>
@@ -11565,12 +11569,12 @@
       <c r="U149" t="inlineStr"/>
       <c r="V149" t="inlineStr">
         <is>
-          <t>OtpFca30</t>
+          <t>OtpCntDr</t>
         </is>
       </c>
       <c r="W149" t="inlineStr">
         <is>
-          <t>Two-step floating catchment area (2SFCA) measure of access to opioid treatment programs within a 30-minute drive</t>
+          <t>Count of Opioid Treatment Programs (OTP) (30-min drive)</t>
         </is>
       </c>
       <c r="X149" t="inlineStr"/>
@@ -11629,12 +11633,12 @@
       <c r="U150" t="inlineStr"/>
       <c r="V150" t="inlineStr">
         <is>
-          <t>OtpFca60</t>
+          <t>OtpFca30</t>
         </is>
       </c>
       <c r="W150" t="inlineStr">
         <is>
-          <t>Two-step floating catchment area (2SFCA) measure of access to opioid treatment programs within a 60-minute drive</t>
+          <t>Two-step floating catchment area (2SFCA) measure of access to opioid treatment programs within a 30-minute drive</t>
         </is>
       </c>
       <c r="X150" t="inlineStr"/>
@@ -11680,11 +11684,7 @@
       <c r="L151" t="inlineStr"/>
       <c r="M151" t="inlineStr"/>
       <c r="N151" t="inlineStr"/>
-      <c r="O151" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="O151" t="inlineStr"/>
       <c r="P151" t="inlineStr"/>
       <c r="Q151" t="inlineStr"/>
       <c r="R151" t="inlineStr"/>
@@ -11697,12 +11697,12 @@
       <c r="U151" t="inlineStr"/>
       <c r="V151" t="inlineStr">
         <is>
-          <t>OtpMinDis</t>
+          <t>OtpFca60</t>
         </is>
       </c>
       <c r="W151" t="inlineStr">
         <is>
-          <t>Distance to nearest OTP</t>
+          <t>Two-step floating catchment area (2SFCA) measure of access to opioid treatment programs within a 60-minute drive</t>
         </is>
       </c>
       <c r="X151" t="inlineStr"/>
@@ -11748,7 +11748,11 @@
       <c r="L152" t="inlineStr"/>
       <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr"/>
-      <c r="O152" t="inlineStr"/>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P152" t="inlineStr"/>
       <c r="Q152" t="inlineStr"/>
       <c r="R152" t="inlineStr"/>
@@ -11761,12 +11765,12 @@
       <c r="U152" t="inlineStr"/>
       <c r="V152" t="inlineStr">
         <is>
-          <t>OtpRm30</t>
+          <t>OtpMinDis</t>
         </is>
       </c>
       <c r="W152" t="inlineStr">
         <is>
-          <t>Opioid Treatment Provider access 30 minutes (RAAM)</t>
+          <t>Distance to nearest OTP</t>
         </is>
       </c>
       <c r="X152" t="inlineStr"/>
@@ -11825,12 +11829,12 @@
       <c r="U153" t="inlineStr"/>
       <c r="V153" t="inlineStr">
         <is>
-          <t>OtpRm60</t>
+          <t>OtpRm30</t>
         </is>
       </c>
       <c r="W153" t="inlineStr">
         <is>
-          <t>Opioid Treatment Provider access 60 minutes (RAAM)</t>
+          <t>Opioid Treatment Provider access 30 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X153" t="inlineStr"/>
@@ -11876,11 +11880,7 @@
       <c r="L154" t="inlineStr"/>
       <c r="M154" t="inlineStr"/>
       <c r="N154" t="inlineStr"/>
-      <c r="O154" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="O154" t="inlineStr"/>
       <c r="P154" t="inlineStr"/>
       <c r="Q154" t="inlineStr"/>
       <c r="R154" t="inlineStr"/>
@@ -11889,20 +11889,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T154" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T154" t="inlineStr"/>
       <c r="U154" t="inlineStr"/>
       <c r="V154" t="inlineStr">
         <is>
-          <t>OtpTmDr</t>
+          <t>OtpRm60</t>
         </is>
       </c>
       <c r="W154" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP) (tract/ZIP)</t>
+          <t>Opioid Treatment Provider access 60 minutes (RAAM)</t>
         </is>
       </c>
       <c r="X154" t="inlineStr"/>
@@ -11948,7 +11944,11 @@
       <c r="L155" t="inlineStr"/>
       <c r="M155" t="inlineStr"/>
       <c r="N155" t="inlineStr"/>
-      <c r="O155" t="inlineStr"/>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P155" t="inlineStr"/>
       <c r="Q155" t="inlineStr"/>
       <c r="R155" t="inlineStr"/>
@@ -11957,16 +11957,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T155" t="inlineStr"/>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U155" t="inlineStr"/>
       <c r="V155" t="inlineStr">
         <is>
-          <t>OtpTmDr2</t>
+          <t>OtpTmDr</t>
         </is>
       </c>
       <c r="W155" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP), with impedance</t>
+          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP) (tract/ZIP)</t>
         </is>
       </c>
       <c r="X155" t="inlineStr"/>
@@ -12025,12 +12029,12 @@
       <c r="U156" t="inlineStr"/>
       <c r="V156" t="inlineStr">
         <is>
-          <t>TlBupCntBk30</t>
+          <t>OtpTmDr2</t>
         </is>
       </c>
       <c r="W156" t="inlineStr">
         <is>
-          <t>Count of telehealth buprenorphine providers within 30-minute bike ride</t>
+          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP), with impedance</t>
         </is>
       </c>
       <c r="X156" t="inlineStr"/>
@@ -12089,12 +12093,12 @@
       <c r="U157" t="inlineStr"/>
       <c r="V157" t="inlineStr">
         <is>
-          <t>TlBupCntDr30</t>
+          <t>TlBupCntBk30</t>
         </is>
       </c>
       <c r="W157" t="inlineStr">
         <is>
-          <t>Count of telehealth buprenorphine providers within 30-minute drive</t>
+          <t>Count of telehealth buprenorphine providers within 30-minute bike ride</t>
         </is>
       </c>
       <c r="X157" t="inlineStr"/>
@@ -12153,12 +12157,12 @@
       <c r="U158" t="inlineStr"/>
       <c r="V158" t="inlineStr">
         <is>
-          <t>TlBupCntDr60</t>
+          <t>TlBupCntDr30</t>
         </is>
       </c>
       <c r="W158" t="inlineStr">
         <is>
-          <t>Count of telehealth buprenorphine providers within 60-minute drive</t>
+          <t>Count of telehealth buprenorphine providers within 30-minute drive</t>
         </is>
       </c>
       <c r="X158" t="inlineStr"/>
@@ -12217,12 +12221,12 @@
       <c r="U159" t="inlineStr"/>
       <c r="V159" t="inlineStr">
         <is>
-          <t>TlBupCntWk30</t>
+          <t>TlBupCntDr60</t>
         </is>
       </c>
       <c r="W159" t="inlineStr">
         <is>
-          <t>Count of telehealth buprenorphine providers within 30-minute walk</t>
+          <t>Count of telehealth buprenorphine providers within 60-minute drive</t>
         </is>
       </c>
       <c r="X159" t="inlineStr"/>
@@ -12281,12 +12285,12 @@
       <c r="U160" t="inlineStr"/>
       <c r="V160" t="inlineStr">
         <is>
-          <t>TlBupMinDis</t>
+          <t>TlBupCntWk30</t>
         </is>
       </c>
       <c r="W160" t="inlineStr">
         <is>
-          <t>Minimum distance to telehealth buprenorphine provider</t>
+          <t>Count of telehealth buprenorphine providers within 30-minute walk</t>
         </is>
       </c>
       <c r="X160" t="inlineStr"/>
@@ -12345,12 +12349,12 @@
       <c r="U161" t="inlineStr"/>
       <c r="V161" t="inlineStr">
         <is>
-          <t>TlBupTmBk</t>
+          <t>TlBupMinDis</t>
         </is>
       </c>
       <c r="W161" t="inlineStr">
         <is>
-          <t>Biking time to nearest telehealth buprenorphine provider</t>
+          <t>Minimum distance to telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X161" t="inlineStr"/>
@@ -12409,12 +12413,12 @@
       <c r="U162" t="inlineStr"/>
       <c r="V162" t="inlineStr">
         <is>
-          <t>TlBupTmDr</t>
+          <t>TlBupTmBk</t>
         </is>
       </c>
       <c r="W162" t="inlineStr">
         <is>
-          <t>Driving time to nearest telehealth buprenorphine provider</t>
+          <t>Biking time to nearest telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X162" t="inlineStr"/>
@@ -12473,12 +12477,12 @@
       <c r="U163" t="inlineStr"/>
       <c r="V163" t="inlineStr">
         <is>
-          <t>TlBupTmWk</t>
+          <t>TlBupTmDr</t>
         </is>
       </c>
       <c r="W163" t="inlineStr">
         <is>
-          <t>Walking time to nearest telehealth buprenorphine provider</t>
+          <t>Driving time to nearest telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X163" t="inlineStr"/>
@@ -12509,7 +12513,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
@@ -12523,11 +12527,7 @@
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr"/>
       <c r="M164" t="inlineStr"/>
-      <c r="N164" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N164" t="inlineStr"/>
       <c r="O164" t="inlineStr"/>
       <c r="P164" t="inlineStr"/>
       <c r="Q164" t="inlineStr"/>
@@ -12541,28 +12541,28 @@
       <c r="U164" t="inlineStr"/>
       <c r="V164" t="inlineStr">
         <is>
-          <t>MhCntDr</t>
+          <t>TlBupTmWk</t>
         </is>
       </c>
       <c r="W164" t="inlineStr">
         <is>
-          <t>Count of Mental Health Providers (30-min drive)</t>
+          <t>Walking time to nearest telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X164" t="inlineStr"/>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB164" t="inlineStr"/>
@@ -12609,12 +12609,12 @@
       <c r="U165" t="inlineStr"/>
       <c r="V165" t="inlineStr">
         <is>
-          <t>MhMinDis</t>
+          <t>MhCntDr</t>
         </is>
       </c>
       <c r="W165" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Mental Health Provider</t>
+          <t>Count of Mental Health Providers (30-min drive)</t>
         </is>
       </c>
       <c r="X165" t="inlineStr"/>
@@ -12673,20 +12673,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T166" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T166" t="inlineStr"/>
       <c r="U166" t="inlineStr"/>
       <c r="V166" t="inlineStr">
         <is>
-          <t>MhTmDr</t>
+          <t>MhMinDis</t>
         </is>
       </c>
       <c r="W166" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Mental Health Provider (tract/ZIP)</t>
+          <t>Distance (mi) to nearest Mental Health Provider</t>
         </is>
       </c>
       <c r="X166" t="inlineStr"/>
@@ -12731,7 +12727,11 @@
       <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr"/>
       <c r="M167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O167" t="inlineStr"/>
       <c r="P167" t="inlineStr"/>
       <c r="Q167" t="inlineStr"/>
@@ -12741,16 +12741,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T167" t="inlineStr"/>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U167" t="inlineStr"/>
       <c r="V167" t="inlineStr">
         <is>
-          <t>MhTmDr2</t>
+          <t>MhTmDr</t>
         </is>
       </c>
       <c r="W167" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest Mental Health Provider with impedance</t>
+          <t>Driving Time (min) to nearest Mental Health Provider (tract/ZIP)</t>
         </is>
       </c>
       <c r="X167" t="inlineStr"/>
@@ -12781,7 +12785,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
@@ -12794,11 +12798,7 @@
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M168" t="inlineStr"/>
       <c r="N168" t="inlineStr"/>
       <c r="O168" t="inlineStr"/>
       <c r="P168" t="inlineStr"/>
@@ -12813,28 +12813,28 @@
       <c r="U168" t="inlineStr"/>
       <c r="V168" t="inlineStr">
         <is>
-          <t>RxCntDr</t>
+          <t>MhTmDr2</t>
         </is>
       </c>
       <c r="W168" t="inlineStr">
         <is>
-          <t>Count of Pharmacies (30-min drive)</t>
+          <t>Driving time (min) to nearest Mental Health Provider with impedance</t>
         </is>
       </c>
       <c r="X168" t="inlineStr"/>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB168" t="inlineStr"/>
@@ -12881,12 +12881,12 @@
       <c r="U169" t="inlineStr"/>
       <c r="V169" t="inlineStr">
         <is>
-          <t>RxMinDis</t>
+          <t>RxCntDr</t>
         </is>
       </c>
       <c r="W169" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Pharmacy</t>
+          <t>Count of Pharmacies (30-min drive)</t>
         </is>
       </c>
       <c r="X169" t="inlineStr"/>
@@ -12945,20 +12945,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T170" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T170" t="inlineStr"/>
       <c r="U170" t="inlineStr"/>
       <c r="V170" t="inlineStr">
         <is>
-          <t>RxTmDr</t>
+          <t>RxMinDis</t>
         </is>
       </c>
       <c r="W170" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Pharmacy</t>
+          <t>Distance (mi) to nearest Pharmacy</t>
         </is>
       </c>
       <c r="X170" t="inlineStr"/>
@@ -13002,7 +12998,11 @@
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr"/>
-      <c r="M171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N171" t="inlineStr"/>
       <c r="O171" t="inlineStr"/>
       <c r="P171" t="inlineStr"/>
@@ -13013,16 +13013,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T171" t="inlineStr"/>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U171" t="inlineStr"/>
       <c r="V171" t="inlineStr">
         <is>
-          <t>RxTmDr2</t>
+          <t>RxTmDr</t>
         </is>
       </c>
       <c r="W171" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Pharmacy with Impedance Factor</t>
+          <t>Driving Time (min) to nearest Pharmacy</t>
         </is>
       </c>
       <c r="X171" t="inlineStr"/>
@@ -13053,7 +13057,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
@@ -13067,11 +13071,7 @@
       <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr"/>
       <c r="M172" t="inlineStr"/>
-      <c r="N172" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N172" t="inlineStr"/>
       <c r="O172" t="inlineStr"/>
       <c r="P172" t="inlineStr"/>
       <c r="Q172" t="inlineStr"/>
@@ -13085,28 +13085,28 @@
       <c r="U172" t="inlineStr"/>
       <c r="V172" t="inlineStr">
         <is>
-          <t>SutCntDr</t>
+          <t>RxTmDr2</t>
         </is>
       </c>
       <c r="W172" t="inlineStr">
         <is>
-          <t>Count of Substance Use Treatment (SUT) facility (30-min drive)</t>
+          <t>Driving Time (min) to nearest Pharmacy with Impedance Factor</t>
         </is>
       </c>
       <c r="X172" t="inlineStr"/>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB172" t="inlineStr"/>
@@ -13153,12 +13153,12 @@
       <c r="U173" t="inlineStr"/>
       <c r="V173" t="inlineStr">
         <is>
-          <t>SutMinDis</t>
+          <t>SutCntDr</t>
         </is>
       </c>
       <c r="W173" t="inlineStr">
         <is>
-          <t>Distance (mi) to Substance Use Treatment (SUT) facility</t>
+          <t>Count of Substance Use Treatment (SUT) facility (30-min drive)</t>
         </is>
       </c>
       <c r="X173" t="inlineStr"/>
@@ -13217,20 +13217,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T174" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T174" t="inlineStr"/>
       <c r="U174" t="inlineStr"/>
       <c r="V174" t="inlineStr">
         <is>
-          <t>SutTmDr</t>
+          <t>SutMinDis</t>
         </is>
       </c>
       <c r="W174" t="inlineStr">
         <is>
-          <t>Driving time (min) to Substance Use Treatment (SUT) facility</t>
+          <t>Distance (mi) to Substance Use Treatment (SUT) facility</t>
         </is>
       </c>
       <c r="X174" t="inlineStr"/>
@@ -13275,7 +13271,11 @@
       <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr"/>
       <c r="M175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O175" t="inlineStr"/>
       <c r="P175" t="inlineStr"/>
       <c r="Q175" t="inlineStr"/>
@@ -13285,16 +13285,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T175" t="inlineStr"/>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U175" t="inlineStr"/>
       <c r="V175" t="inlineStr">
         <is>
-          <t>SutTmDr2</t>
+          <t>SutTmDr</t>
         </is>
       </c>
       <c r="W175" t="inlineStr">
         <is>
-          <t>Driving time to nearest Substance Use Treatment Provider (with impedance)</t>
+          <t>Driving time (min) to Substance Use Treatment (SUT) facility</t>
         </is>
       </c>
       <c r="X175" t="inlineStr"/>
@@ -13325,7 +13329,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
@@ -13339,11 +13343,7 @@
       <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr"/>
       <c r="M176" t="inlineStr"/>
-      <c r="N176" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N176" t="inlineStr"/>
       <c r="O176" t="inlineStr"/>
       <c r="P176" t="inlineStr"/>
       <c r="Q176" t="inlineStr"/>
@@ -13357,28 +13357,28 @@
       <c r="U176" t="inlineStr"/>
       <c r="V176" t="inlineStr">
         <is>
-          <t>FqhcCntDr</t>
+          <t>SutTmDr2</t>
         </is>
       </c>
       <c r="W176" t="inlineStr">
         <is>
-          <t>Count of Federally Qualified Health Centers (FQHCs) within 30-min drive</t>
+          <t>Driving time to nearest Substance Use Treatment Provider (with impedance)</t>
         </is>
       </c>
       <c r="X176" t="inlineStr"/>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB176" t="inlineStr"/>
@@ -13425,12 +13425,12 @@
       <c r="U177" t="inlineStr"/>
       <c r="V177" t="inlineStr">
         <is>
-          <t>FqhcMinDis</t>
+          <t>FqhcCntDr</t>
         </is>
       </c>
       <c r="W177" t="inlineStr">
         <is>
-          <t>Distance (mi) to nearest Federally Qualified Health Centers (FQHC)</t>
+          <t>Count of Federally Qualified Health Centers (FQHCs) within 30-min drive</t>
         </is>
       </c>
       <c r="X177" t="inlineStr"/>
@@ -13489,20 +13489,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T178" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T178" t="inlineStr"/>
       <c r="U178" t="inlineStr"/>
       <c r="V178" t="inlineStr">
         <is>
-          <t>FqhcTmDr</t>
+          <t>FqhcMinDis</t>
         </is>
       </c>
       <c r="W178" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC)</t>
+          <t>Distance (mi) to nearest Federally Qualified Health Centers (FQHC)</t>
         </is>
       </c>
       <c r="X178" t="inlineStr"/>
@@ -13547,7 +13543,11 @@
       <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr"/>
       <c r="M179" t="inlineStr"/>
-      <c r="N179" t="inlineStr"/>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O179" t="inlineStr"/>
       <c r="P179" t="inlineStr"/>
       <c r="Q179" t="inlineStr"/>
@@ -13565,12 +13565,12 @@
       <c r="U179" t="inlineStr"/>
       <c r="V179" t="inlineStr">
         <is>
-          <t>FqhcTmDr2</t>
+          <t>FqhcTmDr</t>
         </is>
       </c>
       <c r="W179" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC), with Impedance factor</t>
+          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC)</t>
         </is>
       </c>
       <c r="X179" t="inlineStr"/>
@@ -13601,7 +13601,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
@@ -13625,32 +13625,36 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T180" t="inlineStr"/>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U180" t="inlineStr"/>
       <c r="V180" t="inlineStr">
         <is>
-          <t>HcvCntDr</t>
+          <t>FqhcTmDr2</t>
         </is>
       </c>
       <c r="W180" t="inlineStr">
         <is>
-          <t>Count of HCV Providers</t>
+          <t>Driving time (min) to nearest Federally Qualified Health Centers (FQHC), with Impedance factor</t>
         </is>
       </c>
       <c r="X180" t="inlineStr"/>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB180" t="inlineStr"/>
@@ -13693,12 +13697,12 @@
       <c r="U181" t="inlineStr"/>
       <c r="V181" t="inlineStr">
         <is>
-          <t>HcvMinDis</t>
+          <t>HcvCntDr</t>
         </is>
       </c>
       <c r="W181" t="inlineStr">
         <is>
-          <t>Distance to nearest HCV Provider</t>
+          <t>Count of HCV Providers</t>
         </is>
       </c>
       <c r="X181" t="inlineStr"/>
@@ -13757,12 +13761,12 @@
       <c r="U182" t="inlineStr"/>
       <c r="V182" t="inlineStr">
         <is>
-          <t>HcvTmDr</t>
+          <t>HcvMinDis</t>
         </is>
       </c>
       <c r="W182" t="inlineStr">
         <is>
-          <t>Driving time to nearest HCV Provider</t>
+          <t>Distance to nearest HCV Provider</t>
         </is>
       </c>
       <c r="X182" t="inlineStr"/>
@@ -13821,12 +13825,12 @@
       <c r="U183" t="inlineStr"/>
       <c r="V183" t="inlineStr">
         <is>
-          <t>HcvTmDr2</t>
+          <t>HcvTmDr</t>
         </is>
       </c>
       <c r="W183" t="inlineStr">
         <is>
-          <t>Driving time (min) to nearest HCV Testing Facility with impedance</t>
+          <t>Driving time to nearest HCV Provider</t>
         </is>
       </c>
       <c r="X183" t="inlineStr"/>
@@ -13857,7 +13861,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Spatial access to Syringe Services Programs</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
@@ -13885,28 +13889,28 @@
       <c r="U184" t="inlineStr"/>
       <c r="V184" t="inlineStr">
         <is>
-          <t>SspTmDr</t>
+          <t>HcvTmDr2</t>
         </is>
       </c>
       <c r="W184" t="inlineStr">
         <is>
-          <t>Driving time to nearest SSP</t>
+          <t>Driving time (min) to nearest HCV Testing Facility with impedance</t>
         </is>
       </c>
       <c r="X184" t="inlineStr"/>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/nasen_ssp/metadata/Access_SSP.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>NASEN</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>North American Syringe Exchange Network</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB184" t="inlineStr"/>
@@ -13949,12 +13953,12 @@
       <c r="U185" t="inlineStr"/>
       <c r="V185" t="inlineStr">
         <is>
-          <t>SspTmDr2</t>
+          <t>SspTmDr</t>
         </is>
       </c>
       <c r="W185" t="inlineStr">
         <is>
-          <t>Round trip driving time to nearest SSP</t>
+          <t>Driving time to nearest SSP</t>
         </is>
       </c>
       <c r="X185" t="inlineStr"/>
@@ -13985,17 +13989,13 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial access to Syringe Services Programs</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr"/>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr"/>
@@ -14008,33 +14008,37 @@
       <c r="P186" t="inlineStr"/>
       <c r="Q186" t="inlineStr"/>
       <c r="R186" t="inlineStr"/>
-      <c r="S186" t="inlineStr"/>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T186" t="inlineStr"/>
       <c r="U186" t="inlineStr"/>
       <c r="V186" t="inlineStr">
         <is>
-          <t>Ruca1</t>
+          <t>SspTmDr2</t>
         </is>
       </c>
       <c r="W186" t="inlineStr">
         <is>
-          <t>Primary RUCA Code</t>
+          <t>Round trip driving time to nearest SSP</t>
         </is>
       </c>
       <c r="X186" t="inlineStr"/>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/nasen_ssp/metadata/Access_SSP.md</t>
         </is>
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>NASEN</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>North American Syringe Exchange Network</t>
         </is>
       </c>
       <c r="AB186" t="inlineStr"/>
@@ -14077,12 +14081,12 @@
       <c r="U187" t="inlineStr"/>
       <c r="V187" t="inlineStr">
         <is>
-          <t>Ruca2</t>
+          <t>Ruca1</t>
         </is>
       </c>
       <c r="W187" t="inlineStr">
         <is>
-          <t>Secondary RUCA Code</t>
+          <t>Primary RUCA Code</t>
         </is>
       </c>
       <c r="X187" t="inlineStr"/>
@@ -14137,20 +14141,16 @@
       <c r="Q188" t="inlineStr"/>
       <c r="R188" t="inlineStr"/>
       <c r="S188" t="inlineStr"/>
-      <c r="T188" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T188" t="inlineStr"/>
       <c r="U188" t="inlineStr"/>
       <c r="V188" t="inlineStr">
         <is>
-          <t>Rurality</t>
+          <t>Ruca2</t>
         </is>
       </c>
       <c r="W188" t="inlineStr">
         <is>
-          <t>Urban-Suburban-Rural</t>
+          <t>Secondary RUCA Code</t>
         </is>
       </c>
       <c r="X188" t="inlineStr"/>
@@ -14176,28 +14176,28 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr"/>
-      <c r="F189" t="inlineStr"/>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr"/>
-      <c r="L189" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L189" t="inlineStr"/>
       <c r="M189" t="inlineStr"/>
       <c r="N189" t="inlineStr"/>
       <c r="O189" t="inlineStr"/>
@@ -14205,32 +14205,36 @@
       <c r="Q189" t="inlineStr"/>
       <c r="R189" t="inlineStr"/>
       <c r="S189" t="inlineStr"/>
-      <c r="T189" t="inlineStr"/>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U189" t="inlineStr"/>
       <c r="V189" t="inlineStr">
         <is>
-          <t>EssnWrkE</t>
+          <t>Rurality</t>
         </is>
       </c>
       <c r="W189" t="inlineStr">
         <is>
-          <t>Count of Essential Workers</t>
+          <t>Urban-Suburban-Rural</t>
         </is>
       </c>
       <c r="X189" t="inlineStr"/>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB189" t="inlineStr"/>
@@ -14263,30 +14267,22 @@
         </is>
       </c>
       <c r="M190" t="inlineStr"/>
-      <c r="N190" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N190" t="inlineStr"/>
       <c r="O190" t="inlineStr"/>
       <c r="P190" t="inlineStr"/>
-      <c r="Q190" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q190" t="inlineStr"/>
       <c r="R190" t="inlineStr"/>
       <c r="S190" t="inlineStr"/>
       <c r="T190" t="inlineStr"/>
       <c r="U190" t="inlineStr"/>
       <c r="V190" t="inlineStr">
         <is>
-          <t>EssnWrkP</t>
+          <t>EssnWrkE</t>
         </is>
       </c>
       <c r="W190" t="inlineStr">
         <is>
-          <t>Essential Workers %</t>
+          <t>Count of Essential Workers</t>
         </is>
       </c>
       <c r="X190" t="inlineStr"/>
@@ -14353,12 +14349,12 @@
       <c r="U191" t="inlineStr"/>
       <c r="V191" t="inlineStr">
         <is>
-          <t>HghRskP</t>
+          <t>EssnWrkP</t>
         </is>
       </c>
       <c r="W191" t="inlineStr">
         <is>
-          <t>Employed % - High Risk of Injury</t>
+          <t>Essential Workers %</t>
         </is>
       </c>
       <c r="X191" t="inlineStr"/>
@@ -14425,12 +14421,12 @@
       <c r="U192" t="inlineStr"/>
       <c r="V192" t="inlineStr">
         <is>
-          <t>HltCrP</t>
+          <t>HghRskP</t>
         </is>
       </c>
       <c r="W192" t="inlineStr">
         <is>
-          <t>Employed % - Health Care</t>
+          <t>Employed % - High Risk of Injury</t>
         </is>
       </c>
       <c r="X192" t="inlineStr"/>
@@ -14497,12 +14493,12 @@
       <c r="U193" t="inlineStr"/>
       <c r="V193" t="inlineStr">
         <is>
-          <t>RetailP</t>
+          <t>HltCrP</t>
         </is>
       </c>
       <c r="W193" t="inlineStr">
         <is>
-          <t>Employed % - Retail</t>
+          <t>Employed % - Health Care</t>
         </is>
       </c>
       <c r="X193" t="inlineStr"/>
@@ -14569,12 +14565,12 @@
       <c r="U194" t="inlineStr"/>
       <c r="V194" t="inlineStr">
         <is>
-          <t>TotWrkE</t>
+          <t>RetailP</t>
         </is>
       </c>
       <c r="W194" t="inlineStr">
         <is>
-          <t>Count of Working Population</t>
+          <t>Employed % - Retail</t>
         </is>
       </c>
       <c r="X194" t="inlineStr"/>
@@ -14605,7 +14601,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
@@ -14623,38 +14619,46 @@
         </is>
       </c>
       <c r="M195" t="inlineStr"/>
-      <c r="N195" t="inlineStr"/>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O195" t="inlineStr"/>
       <c r="P195" t="inlineStr"/>
-      <c r="Q195" t="inlineStr"/>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R195" t="inlineStr"/>
       <c r="S195" t="inlineStr"/>
       <c r="T195" t="inlineStr"/>
       <c r="U195" t="inlineStr"/>
       <c r="V195" t="inlineStr">
         <is>
-          <t>ForDqP</t>
+          <t>TotWrkE</t>
         </is>
       </c>
       <c r="W195" t="inlineStr">
         <is>
-          <t>Foreclosure &amp; Delinquency %</t>
+          <t>Count of Working Population</t>
         </is>
       </c>
       <c r="X195" t="inlineStr"/>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB195" t="inlineStr"/>
@@ -14697,12 +14701,12 @@
       <c r="U196" t="inlineStr"/>
       <c r="V196" t="inlineStr">
         <is>
-          <t>ForDqTot</t>
+          <t>ForDqP</t>
         </is>
       </c>
       <c r="W196" t="inlineStr">
         <is>
-          <t>Foreclosure &amp; Delinquency Count</t>
+          <t>Foreclosure &amp; Delinquency %</t>
         </is>
       </c>
       <c r="X196" t="inlineStr"/>
@@ -14739,11 +14743,7 @@
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr"/>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr"/>
       <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr"/>
@@ -14755,30 +14755,22 @@
         </is>
       </c>
       <c r="M197" t="inlineStr"/>
-      <c r="N197" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N197" t="inlineStr"/>
       <c r="O197" t="inlineStr"/>
       <c r="P197" t="inlineStr"/>
-      <c r="Q197" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q197" t="inlineStr"/>
       <c r="R197" t="inlineStr"/>
       <c r="S197" t="inlineStr"/>
       <c r="T197" t="inlineStr"/>
       <c r="U197" t="inlineStr"/>
       <c r="V197" t="inlineStr">
         <is>
-          <t>GiniCoeff</t>
+          <t>ForDqTot</t>
         </is>
       </c>
       <c r="W197" t="inlineStr">
         <is>
-          <t>Income Inequality (Gini Coefficient)</t>
+          <t>Foreclosure &amp; Delinquency Count</t>
         </is>
       </c>
       <c r="X197" t="inlineStr"/>
@@ -14809,56 +14801,68 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Internet Access</t>
+          <t>Great Recession Foreclosure Rate</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr"/>
-      <c r="F198" t="inlineStr"/>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G198" t="inlineStr"/>
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr"/>
-      <c r="L198" t="inlineStr"/>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N198" t="inlineStr"/>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr"/>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O198" t="inlineStr"/>
       <c r="P198" t="inlineStr"/>
-      <c r="Q198" t="inlineStr"/>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R198" t="inlineStr"/>
       <c r="S198" t="inlineStr"/>
       <c r="T198" t="inlineStr"/>
       <c r="U198" t="inlineStr"/>
       <c r="V198" t="inlineStr">
         <is>
-          <t>NoIntP</t>
+          <t>GiniCoeff</t>
         </is>
       </c>
       <c r="W198" t="inlineStr">
         <is>
-          <t>Households without Internet Access %</t>
+          <t>Income Inequality (Gini Coefficient)</t>
         </is>
       </c>
       <c r="X198" t="inlineStr"/>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Internet_Access.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
         </is>
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>ACS 2019</t>
+          <t>HUD 2018; ACS 2012, 2018</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>American Community Survey 2015-2019 5-Year Estimate</t>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB198" t="inlineStr"/>
@@ -14873,68 +14877,56 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
+          <t>Internet Access</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr"/>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr"/>
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr"/>
-      <c r="L199" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M199" t="inlineStr"/>
-      <c r="N199" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr"/>
       <c r="O199" t="inlineStr"/>
       <c r="P199" t="inlineStr"/>
-      <c r="Q199" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q199" t="inlineStr"/>
       <c r="R199" t="inlineStr"/>
       <c r="S199" t="inlineStr"/>
       <c r="T199" t="inlineStr"/>
       <c r="U199" t="inlineStr"/>
       <c r="V199" t="inlineStr">
         <is>
-          <t>MedInc</t>
+          <t>NoIntP</t>
         </is>
       </c>
       <c r="W199" t="inlineStr">
         <is>
-          <t>Median Income</t>
+          <t>Households without Internet Access %</t>
         </is>
       </c>
       <c r="X199" t="inlineStr"/>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Internet_Access.md</t>
         </is>
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>ACS 2019</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>American Community Survey 2015-2019 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB199" t="inlineStr"/>
@@ -14989,12 +14981,12 @@
       <c r="U200" t="inlineStr"/>
       <c r="V200" t="inlineStr">
         <is>
-          <t>PciE</t>
+          <t>MedInc</t>
         </is>
       </c>
       <c r="W200" t="inlineStr">
         <is>
-          <t>Per Capita Income</t>
+          <t>Median Income</t>
         </is>
       </c>
       <c r="X200" t="inlineStr"/>
@@ -15028,21 +15020,9 @@
           <t>Poverty, Income, Gini Coefficient</t>
         </is>
       </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="C201" t="inlineStr"/>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
         <is>
           <t>x</t>
@@ -15074,19 +15054,15 @@
       <c r="R201" t="inlineStr"/>
       <c r="S201" t="inlineStr"/>
       <c r="T201" t="inlineStr"/>
-      <c r="U201" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="U201" t="inlineStr"/>
       <c r="V201" t="inlineStr">
         <is>
-          <t>PovP</t>
+          <t>PciE</t>
         </is>
       </c>
       <c r="W201" t="inlineStr">
         <is>
-          <t>Poverty %</t>
+          <t>Per Capita Income</t>
         </is>
       </c>
       <c r="X201" t="inlineStr"/>
@@ -15173,12 +15149,12 @@
       </c>
       <c r="V202" t="inlineStr">
         <is>
-          <t>UnempP</t>
+          <t>PovP</t>
         </is>
       </c>
       <c r="W202" t="inlineStr">
         <is>
-          <t>Unemployment %</t>
+          <t>Poverty %</t>
         </is>
       </c>
       <c r="X202" t="inlineStr"/>
@@ -15204,65 +15180,89 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>SDOH Indices &amp; Typology</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr"/>
-      <c r="D203" t="inlineStr"/>
-      <c r="E203" t="inlineStr"/>
-      <c r="F203" t="inlineStr"/>
+          <t>Poverty, Income, Gini Coefficient</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G203" t="inlineStr"/>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="H203" t="inlineStr"/>
       <c r="I203" t="inlineStr"/>
       <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr"/>
-      <c r="L203" t="inlineStr"/>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M203" t="inlineStr"/>
-      <c r="N203" t="inlineStr"/>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O203" t="inlineStr"/>
       <c r="P203" t="inlineStr"/>
-      <c r="Q203" t="inlineStr"/>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R203" t="inlineStr"/>
       <c r="S203" t="inlineStr"/>
-      <c r="T203" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="U203" t="inlineStr"/>
+      <c r="T203" t="inlineStr"/>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="V203" t="inlineStr">
         <is>
-          <t>LimMobInd</t>
+          <t>UnempP</t>
         </is>
       </c>
       <c r="W203" t="inlineStr">
         <is>
-          <t>Limited Moblility Index</t>
+          <t>Unemployment %</t>
         </is>
       </c>
       <c r="X203" t="inlineStr"/>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>Kolak et al., 2020</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB203" t="inlineStr"/>
@@ -15309,12 +15309,12 @@
       <c r="U204" t="inlineStr"/>
       <c r="V204" t="inlineStr">
         <is>
-          <t>MicaInd</t>
+          <t>LimMobInd</t>
         </is>
       </c>
       <c r="W204" t="inlineStr">
         <is>
-          <t>Mixed Immigrant Cohesion and Accesibility (MICA) Index</t>
+          <t>Limited Moblility Index</t>
         </is>
       </c>
       <c r="X204" t="inlineStr"/>
@@ -15369,16 +15369,20 @@
       <c r="Q205" t="inlineStr"/>
       <c r="R205" t="inlineStr"/>
       <c r="S205" t="inlineStr"/>
-      <c r="T205" t="inlineStr"/>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U205" t="inlineStr"/>
       <c r="V205" t="inlineStr">
         <is>
-          <t>NeighbTyp</t>
+          <t>MicaInd</t>
         </is>
       </c>
       <c r="W205" t="inlineStr">
         <is>
-          <t>Neighborhood Type</t>
+          <t>Mixed Immigrant Cohesion and Accesibility (MICA) Index</t>
         </is>
       </c>
       <c r="X205" t="inlineStr"/>
@@ -15433,20 +15437,16 @@
       <c r="Q206" t="inlineStr"/>
       <c r="R206" t="inlineStr"/>
       <c r="S206" t="inlineStr"/>
-      <c r="T206" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T206" t="inlineStr"/>
       <c r="U206" t="inlineStr"/>
       <c r="V206" t="inlineStr">
         <is>
-          <t>SocEcAdvIn</t>
+          <t>NeighbTyp</t>
         </is>
       </c>
       <c r="W206" t="inlineStr">
         <is>
-          <t>Socioeconomic Advantage Index</t>
+          <t>Neighborhood Type</t>
         </is>
       </c>
       <c r="X206" t="inlineStr"/>
@@ -15509,12 +15509,12 @@
       <c r="U207" t="inlineStr"/>
       <c r="V207" t="inlineStr">
         <is>
-          <t>UrbCoreInd</t>
+          <t>SocEcAdvIn</t>
         </is>
       </c>
       <c r="W207" t="inlineStr">
         <is>
-          <t>Urban Core Opportunity Index</t>
+          <t>Socioeconomic Advantage Index</t>
         </is>
       </c>
       <c r="X207" t="inlineStr"/>
@@ -15545,7 +15545,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>SDOH Indices &amp; Typology</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
@@ -15553,56 +15553,52 @@
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr"/>
       <c r="G208" t="inlineStr"/>
-      <c r="H208" t="inlineStr"/>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="I208" t="inlineStr"/>
       <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr"/>
-      <c r="L208" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L208" t="inlineStr"/>
       <c r="M208" t="inlineStr"/>
-      <c r="N208" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N208" t="inlineStr"/>
       <c r="O208" t="inlineStr"/>
-      <c r="P208" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P208" t="inlineStr"/>
       <c r="Q208" t="inlineStr"/>
       <c r="R208" t="inlineStr"/>
       <c r="S208" t="inlineStr"/>
-      <c r="T208" t="inlineStr"/>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U208" t="inlineStr"/>
       <c r="V208" t="inlineStr">
         <is>
-          <t>SviSmryRnk</t>
+          <t>UrbCoreInd</t>
         </is>
       </c>
       <c r="W208" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) Summary Ranking</t>
+          <t>Urban Core Opportunity Index</t>
         </is>
       </c>
       <c r="X208" t="inlineStr"/>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/SDOHIndices.md</t>
         </is>
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>Kolak et al., 2020</t>
         </is>
       </c>
       <c r="AB208" t="inlineStr"/>
@@ -15649,20 +15645,16 @@
       <c r="Q209" t="inlineStr"/>
       <c r="R209" t="inlineStr"/>
       <c r="S209" t="inlineStr"/>
-      <c r="T209" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T209" t="inlineStr"/>
       <c r="U209" t="inlineStr"/>
       <c r="V209" t="inlineStr">
         <is>
-          <t>SviTh1</t>
+          <t>SviSmryRnk</t>
         </is>
       </c>
       <c r="W209" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 1</t>
+          <t>Social Vulnerability Index (SVI) Summary Ranking</t>
         </is>
       </c>
       <c r="X209" t="inlineStr"/>
@@ -15725,16 +15717,20 @@
       <c r="Q210" t="inlineStr"/>
       <c r="R210" t="inlineStr"/>
       <c r="S210" t="inlineStr"/>
-      <c r="T210" t="inlineStr"/>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U210" t="inlineStr"/>
       <c r="V210" t="inlineStr">
         <is>
-          <t>SviTh2</t>
+          <t>SviTh1</t>
         </is>
       </c>
       <c r="W210" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 2</t>
+          <t>Social Vulnerability Index (SVI) 1</t>
         </is>
       </c>
       <c r="X210" t="inlineStr"/>
@@ -15801,12 +15797,12 @@
       <c r="U211" t="inlineStr"/>
       <c r="V211" t="inlineStr">
         <is>
-          <t>SviTh3</t>
+          <t>SviTh2</t>
         </is>
       </c>
       <c r="W211" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 3</t>
+          <t>Social Vulnerability Index (SVI) 2</t>
         </is>
       </c>
       <c r="X211" t="inlineStr"/>
@@ -15869,20 +15865,16 @@
       <c r="Q212" t="inlineStr"/>
       <c r="R212" t="inlineStr"/>
       <c r="S212" t="inlineStr"/>
-      <c r="T212" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T212" t="inlineStr"/>
       <c r="U212" t="inlineStr"/>
       <c r="V212" t="inlineStr">
         <is>
-          <t>SviTh4</t>
+          <t>SviTh3</t>
         </is>
       </c>
       <c r="W212" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 4</t>
+          <t>Social Vulnerability Index (SVI) 3</t>
         </is>
       </c>
       <c r="X212" t="inlineStr"/>
@@ -15904,6 +15896,82 @@
       <c r="AB212" t="inlineStr"/>
       <c r="AC212" t="inlineStr"/>
       <c r="AD212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr"/>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="inlineStr"/>
+      <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr"/>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr"/>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr"/>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr"/>
+      <c r="R213" t="inlineStr"/>
+      <c r="S213" t="inlineStr"/>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr"/>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>SviTh4</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 4</t>
+        </is>
+      </c>
+      <c r="X213" t="inlineStr"/>
+      <c r="Y213" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z213" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB213" t="inlineStr"/>
+      <c r="AC213" t="inlineStr"/>
+      <c r="AD213" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/src/reference/data-dictionaries/T_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/T_Dict.xlsx
@@ -14071,7 +14071,11 @@
       <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr"/>
       <c r="M187" t="inlineStr"/>
-      <c r="N187" t="inlineStr"/>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O187" t="inlineStr"/>
       <c r="P187" t="inlineStr"/>
       <c r="Q187" t="inlineStr"/>
@@ -14097,12 +14101,12 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>USDA-ERS 2010; ACS 2018, USDA-ERS 2020</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate; United States Department of Agriculture Economic Research Service, 2020</t>
         </is>
       </c>
       <c r="AB187" t="inlineStr"/>
@@ -14135,7 +14139,11 @@
       <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr"/>
       <c r="M188" t="inlineStr"/>
-      <c r="N188" t="inlineStr"/>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O188" t="inlineStr"/>
       <c r="P188" t="inlineStr"/>
       <c r="Q188" t="inlineStr"/>
@@ -14161,12 +14169,12 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>USDA-ERS 2010; ACS 2018, USDA-ERS 2020</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate; United States Department of Agriculture Economic Research Service, 2020</t>
         </is>
       </c>
       <c r="AB188" t="inlineStr"/>
@@ -14199,7 +14207,11 @@
       <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr"/>
       <c r="M189" t="inlineStr"/>
-      <c r="N189" t="inlineStr"/>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O189" t="inlineStr"/>
       <c r="P189" t="inlineStr"/>
       <c r="Q189" t="inlineStr"/>
@@ -14229,12 +14241,12 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>USDA-ERS 2010; ACS 2018, USDA-ERS 2020</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate; United States Department of Agriculture Economic Research Service, 2020</t>
         </is>
       </c>
       <c r="AB189" t="inlineStr"/>
